--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/06 Junio/Liquidacióncvs -ACTUALIZADO/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD251EF9-1BEF-42DB-B616-ECD0CCFA4ED9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="209">
   <si>
     <t>Producto</t>
   </si>
@@ -617,6 +617,36 @@
   </si>
   <si>
     <t>79%</t>
+  </si>
+  <si>
+    <t>7%</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
+    <t>Vacaciones del 3 al 22 de julio</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Vacaciones del 26 de jun al 13 de julio</t>
   </si>
 </sst>
 </file>
@@ -980,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L216"/>
+  <dimension ref="A1:L236"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -8696,6 +8726,712 @@
         <v>74.3</v>
       </c>
     </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>12</v>
+      </c>
+      <c r="B217">
+        <v>28</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+      <c r="D217" t="s">
+        <v>199</v>
+      </c>
+      <c r="E217" t="s">
+        <v>32</v>
+      </c>
+      <c r="F217" t="s">
+        <v>15</v>
+      </c>
+      <c r="G217" t="s">
+        <v>33</v>
+      </c>
+      <c r="H217" t="s">
+        <v>200</v>
+      </c>
+      <c r="I217" t="s">
+        <v>18</v>
+      </c>
+      <c r="K217">
+        <v>100</v>
+      </c>
+      <c r="L217">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>20</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+      <c r="C218">
+        <v>0</v>
+      </c>
+      <c r="D218" t="s">
+        <v>21</v>
+      </c>
+      <c r="E218" t="s">
+        <v>32</v>
+      </c>
+      <c r="F218" t="s">
+        <v>15</v>
+      </c>
+      <c r="G218" t="s">
+        <v>33</v>
+      </c>
+      <c r="H218" t="s">
+        <v>200</v>
+      </c>
+      <c r="I218" t="s">
+        <v>18</v>
+      </c>
+      <c r="K218">
+        <v>100</v>
+      </c>
+      <c r="L218">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>22</v>
+      </c>
+      <c r="B219">
+        <v>34</v>
+      </c>
+      <c r="C219">
+        <v>4</v>
+      </c>
+      <c r="D219" t="s">
+        <v>169</v>
+      </c>
+      <c r="E219" t="s">
+        <v>32</v>
+      </c>
+      <c r="F219" t="s">
+        <v>15</v>
+      </c>
+      <c r="G219" t="s">
+        <v>33</v>
+      </c>
+      <c r="H219" t="s">
+        <v>200</v>
+      </c>
+      <c r="I219" t="s">
+        <v>18</v>
+      </c>
+      <c r="K219">
+        <v>100</v>
+      </c>
+      <c r="L219">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220">
+        <v>61</v>
+      </c>
+      <c r="C220">
+        <v>14</v>
+      </c>
+      <c r="D220" t="s">
+        <v>201</v>
+      </c>
+      <c r="E220" t="s">
+        <v>32</v>
+      </c>
+      <c r="F220" t="s">
+        <v>15</v>
+      </c>
+      <c r="G220" t="s">
+        <v>33</v>
+      </c>
+      <c r="H220" t="s">
+        <v>200</v>
+      </c>
+      <c r="I220" t="s">
+        <v>18</v>
+      </c>
+      <c r="K220">
+        <v>100</v>
+      </c>
+      <c r="L220">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>26</v>
+      </c>
+      <c r="B221">
+        <v>912</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221" t="s">
+        <v>21</v>
+      </c>
+      <c r="E221" t="s">
+        <v>32</v>
+      </c>
+      <c r="F221" t="s">
+        <v>15</v>
+      </c>
+      <c r="G221" t="s">
+        <v>33</v>
+      </c>
+      <c r="H221" t="s">
+        <v>200</v>
+      </c>
+      <c r="I221" t="s">
+        <v>18</v>
+      </c>
+      <c r="K221">
+        <v>100</v>
+      </c>
+      <c r="L221">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>12</v>
+      </c>
+      <c r="B222">
+        <v>9</v>
+      </c>
+      <c r="C222">
+        <v>0</v>
+      </c>
+      <c r="D222" t="s">
+        <v>21</v>
+      </c>
+      <c r="E222" t="s">
+        <v>38</v>
+      </c>
+      <c r="F222" t="s">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>33</v>
+      </c>
+      <c r="H222" t="s">
+        <v>200</v>
+      </c>
+      <c r="I222" t="s">
+        <v>18</v>
+      </c>
+      <c r="J222" t="s">
+        <v>202</v>
+      </c>
+      <c r="K222">
+        <v>100</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>20</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+      <c r="C223">
+        <v>0</v>
+      </c>
+      <c r="D223" t="s">
+        <v>21</v>
+      </c>
+      <c r="E223" t="s">
+        <v>38</v>
+      </c>
+      <c r="F223" t="s">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>33</v>
+      </c>
+      <c r="H223" t="s">
+        <v>200</v>
+      </c>
+      <c r="I223" t="s">
+        <v>18</v>
+      </c>
+      <c r="K223">
+        <v>100</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>22</v>
+      </c>
+      <c r="B224">
+        <v>11</v>
+      </c>
+      <c r="C224">
+        <v>0</v>
+      </c>
+      <c r="D224" t="s">
+        <v>21</v>
+      </c>
+      <c r="E224" t="s">
+        <v>38</v>
+      </c>
+      <c r="F224" t="s">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>33</v>
+      </c>
+      <c r="H224" t="s">
+        <v>200</v>
+      </c>
+      <c r="I224" t="s">
+        <v>18</v>
+      </c>
+      <c r="K224">
+        <v>100</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>24</v>
+      </c>
+      <c r="B225">
+        <v>19</v>
+      </c>
+      <c r="C225">
+        <v>0</v>
+      </c>
+      <c r="D225" t="s">
+        <v>201</v>
+      </c>
+      <c r="E225" t="s">
+        <v>38</v>
+      </c>
+      <c r="F225" t="s">
+        <v>28</v>
+      </c>
+      <c r="G225" t="s">
+        <v>33</v>
+      </c>
+      <c r="H225" t="s">
+        <v>200</v>
+      </c>
+      <c r="I225" t="s">
+        <v>18</v>
+      </c>
+      <c r="K225">
+        <v>100</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>26</v>
+      </c>
+      <c r="B226">
+        <v>288</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226" t="s">
+        <v>21</v>
+      </c>
+      <c r="E226" t="s">
+        <v>38</v>
+      </c>
+      <c r="F226" t="s">
+        <v>28</v>
+      </c>
+      <c r="G226" t="s">
+        <v>33</v>
+      </c>
+      <c r="H226" t="s">
+        <v>200</v>
+      </c>
+      <c r="I226" t="s">
+        <v>18</v>
+      </c>
+      <c r="K226">
+        <v>100</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>12</v>
+      </c>
+      <c r="B227">
+        <v>19</v>
+      </c>
+      <c r="C227">
+        <v>9</v>
+      </c>
+      <c r="D227" t="s">
+        <v>203</v>
+      </c>
+      <c r="E227" t="s">
+        <v>204</v>
+      </c>
+      <c r="F227" t="s">
+        <v>15</v>
+      </c>
+      <c r="G227" t="s">
+        <v>205</v>
+      </c>
+      <c r="H227" t="s">
+        <v>200</v>
+      </c>
+      <c r="I227" t="s">
+        <v>18</v>
+      </c>
+      <c r="K227">
+        <v>100</v>
+      </c>
+      <c r="L227">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>20</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228" t="s">
+        <v>21</v>
+      </c>
+      <c r="E228" t="s">
+        <v>204</v>
+      </c>
+      <c r="F228" t="s">
+        <v>15</v>
+      </c>
+      <c r="G228" t="s">
+        <v>205</v>
+      </c>
+      <c r="H228" t="s">
+        <v>200</v>
+      </c>
+      <c r="I228" t="s">
+        <v>18</v>
+      </c>
+      <c r="K228">
+        <v>100</v>
+      </c>
+      <c r="L228">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>22</v>
+      </c>
+      <c r="B229">
+        <v>35</v>
+      </c>
+      <c r="C229">
+        <v>11</v>
+      </c>
+      <c r="D229" t="s">
+        <v>206</v>
+      </c>
+      <c r="E229" t="s">
+        <v>204</v>
+      </c>
+      <c r="F229" t="s">
+        <v>15</v>
+      </c>
+      <c r="G229" t="s">
+        <v>205</v>
+      </c>
+      <c r="H229" t="s">
+        <v>200</v>
+      </c>
+      <c r="I229" t="s">
+        <v>18</v>
+      </c>
+      <c r="K229">
+        <v>100</v>
+      </c>
+      <c r="L229">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>24</v>
+      </c>
+      <c r="B230">
+        <v>102</v>
+      </c>
+      <c r="C230">
+        <v>39</v>
+      </c>
+      <c r="D230" t="s">
+        <v>201</v>
+      </c>
+      <c r="E230" t="s">
+        <v>204</v>
+      </c>
+      <c r="F230" t="s">
+        <v>15</v>
+      </c>
+      <c r="G230" t="s">
+        <v>205</v>
+      </c>
+      <c r="H230" t="s">
+        <v>200</v>
+      </c>
+      <c r="I230" t="s">
+        <v>18</v>
+      </c>
+      <c r="K230">
+        <v>100</v>
+      </c>
+      <c r="L230">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>26</v>
+      </c>
+      <c r="B231">
+        <v>768</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231" t="s">
+        <v>21</v>
+      </c>
+      <c r="E231" t="s">
+        <v>204</v>
+      </c>
+      <c r="F231" t="s">
+        <v>15</v>
+      </c>
+      <c r="G231" t="s">
+        <v>205</v>
+      </c>
+      <c r="H231" t="s">
+        <v>200</v>
+      </c>
+      <c r="I231" t="s">
+        <v>18</v>
+      </c>
+      <c r="K231">
+        <v>100</v>
+      </c>
+      <c r="L231">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>12</v>
+      </c>
+      <c r="B232">
+        <v>11</v>
+      </c>
+      <c r="C232">
+        <v>0</v>
+      </c>
+      <c r="D232" t="s">
+        <v>21</v>
+      </c>
+      <c r="E232" t="s">
+        <v>207</v>
+      </c>
+      <c r="F232" t="s">
+        <v>28</v>
+      </c>
+      <c r="G232" t="s">
+        <v>205</v>
+      </c>
+      <c r="H232" t="s">
+        <v>200</v>
+      </c>
+      <c r="I232" t="s">
+        <v>18</v>
+      </c>
+      <c r="J232" t="s">
+        <v>208</v>
+      </c>
+      <c r="K232">
+        <v>100</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>20</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233" t="s">
+        <v>21</v>
+      </c>
+      <c r="E233" t="s">
+        <v>207</v>
+      </c>
+      <c r="F233" t="s">
+        <v>28</v>
+      </c>
+      <c r="G233" t="s">
+        <v>205</v>
+      </c>
+      <c r="H233" t="s">
+        <v>200</v>
+      </c>
+      <c r="I233" t="s">
+        <v>18</v>
+      </c>
+      <c r="K233">
+        <v>100</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>22</v>
+      </c>
+      <c r="B234">
+        <v>20</v>
+      </c>
+      <c r="C234">
+        <v>0</v>
+      </c>
+      <c r="D234" t="s">
+        <v>21</v>
+      </c>
+      <c r="E234" t="s">
+        <v>207</v>
+      </c>
+      <c r="F234" t="s">
+        <v>28</v>
+      </c>
+      <c r="G234" t="s">
+        <v>205</v>
+      </c>
+      <c r="H234" t="s">
+        <v>200</v>
+      </c>
+      <c r="I234" t="s">
+        <v>18</v>
+      </c>
+      <c r="K234">
+        <v>100</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>24</v>
+      </c>
+      <c r="B235">
+        <v>58</v>
+      </c>
+      <c r="C235">
+        <v>0</v>
+      </c>
+      <c r="D235" t="s">
+        <v>201</v>
+      </c>
+      <c r="E235" t="s">
+        <v>207</v>
+      </c>
+      <c r="F235" t="s">
+        <v>28</v>
+      </c>
+      <c r="G235" t="s">
+        <v>205</v>
+      </c>
+      <c r="H235" t="s">
+        <v>200</v>
+      </c>
+      <c r="I235" t="s">
+        <v>18</v>
+      </c>
+      <c r="K235">
+        <v>100</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>26</v>
+      </c>
+      <c r="B236">
+        <v>432</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236" t="s">
+        <v>21</v>
+      </c>
+      <c r="E236" t="s">
+        <v>207</v>
+      </c>
+      <c r="F236" t="s">
+        <v>28</v>
+      </c>
+      <c r="G236" t="s">
+        <v>205</v>
+      </c>
+      <c r="H236" t="s">
+        <v>200</v>
+      </c>
+      <c r="I236" t="s">
+        <v>18</v>
+      </c>
+      <c r="K236">
+        <v>100</v>
+      </c>
+      <c r="L236">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_77DDB655914D040E62355476585DCE3A87458B1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD251EF9-1BEF-42DB-B616-ECD0CCFA4ED9}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_3A3DD0641462DC0F62355476585DCE3A87449165" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B30E714-36A5-4FBD-B1BA-D05CABA1DDC5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3205" uniqueCount="234">
   <si>
     <t>Producto</t>
   </si>
@@ -647,6 +647,81 @@
   </si>
   <si>
     <t>Vacaciones del 26 de jun al 13 de julio</t>
+  </si>
+  <si>
+    <t>21%</t>
+  </si>
+  <si>
+    <t>19%</t>
+  </si>
+  <si>
+    <t>160%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vac del 14 al 31 de julio </t>
+  </si>
+  <si>
+    <t>109%</t>
+  </si>
+  <si>
+    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+  </si>
+  <si>
+    <t>COPACABANA</t>
+  </si>
+  <si>
+    <t>Meta terminales 33</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>Alexandra Patricia Duque</t>
+  </si>
+  <si>
+    <t>Vac del 14 al 31 de julio</t>
+  </si>
+  <si>
+    <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t>34%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vac del 18 de junio al 6 de julio </t>
+  </si>
+  <si>
+    <t>13%</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Ingresa de vac el 4  Meta puntos 890.4      Meta post 12</t>
+  </si>
+  <si>
+    <t>Hogar 1</t>
+  </si>
+  <si>
+    <t>Terminales  24</t>
+  </si>
+  <si>
+    <t>Otros 47</t>
+  </si>
+  <si>
+    <t>CVS PLUS 504</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>26%</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L236"/>
+  <dimension ref="A1:L446"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -9432,6 +9507,7434 @@
         <v>0</v>
       </c>
     </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>12</v>
+      </c>
+      <c r="B237">
+        <v>10</v>
+      </c>
+      <c r="C237">
+        <v>0</v>
+      </c>
+      <c r="D237" t="s">
+        <v>21</v>
+      </c>
+      <c r="E237" t="s">
+        <v>127</v>
+      </c>
+      <c r="F237" t="s">
+        <v>15</v>
+      </c>
+      <c r="G237" t="s">
+        <v>128</v>
+      </c>
+      <c r="H237" t="s">
+        <v>200</v>
+      </c>
+      <c r="I237" t="s">
+        <v>18</v>
+      </c>
+      <c r="K237">
+        <v>100</v>
+      </c>
+      <c r="L237">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>20</v>
+      </c>
+      <c r="B238">
+        <v>3</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238" t="s">
+        <v>21</v>
+      </c>
+      <c r="E238" t="s">
+        <v>127</v>
+      </c>
+      <c r="F238" t="s">
+        <v>15</v>
+      </c>
+      <c r="G238" t="s">
+        <v>128</v>
+      </c>
+      <c r="H238" t="s">
+        <v>200</v>
+      </c>
+      <c r="I238" t="s">
+        <v>18</v>
+      </c>
+      <c r="K238">
+        <v>100</v>
+      </c>
+      <c r="L238">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>22</v>
+      </c>
+      <c r="B239">
+        <v>24</v>
+      </c>
+      <c r="C239">
+        <v>5</v>
+      </c>
+      <c r="D239" t="s">
+        <v>209</v>
+      </c>
+      <c r="E239" t="s">
+        <v>127</v>
+      </c>
+      <c r="F239" t="s">
+        <v>15</v>
+      </c>
+      <c r="G239" t="s">
+        <v>128</v>
+      </c>
+      <c r="H239" t="s">
+        <v>200</v>
+      </c>
+      <c r="I239" t="s">
+        <v>18</v>
+      </c>
+      <c r="K239">
+        <v>100</v>
+      </c>
+      <c r="L239">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>24</v>
+      </c>
+      <c r="B240">
+        <v>32</v>
+      </c>
+      <c r="C240">
+        <v>5</v>
+      </c>
+      <c r="D240" t="s">
+        <v>201</v>
+      </c>
+      <c r="E240" t="s">
+        <v>127</v>
+      </c>
+      <c r="F240" t="s">
+        <v>15</v>
+      </c>
+      <c r="G240" t="s">
+        <v>128</v>
+      </c>
+      <c r="H240" t="s">
+        <v>200</v>
+      </c>
+      <c r="I240" t="s">
+        <v>18</v>
+      </c>
+      <c r="K240">
+        <v>100</v>
+      </c>
+      <c r="L240">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>26</v>
+      </c>
+      <c r="B241">
+        <v>510</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241" t="s">
+        <v>21</v>
+      </c>
+      <c r="E241" t="s">
+        <v>127</v>
+      </c>
+      <c r="F241" t="s">
+        <v>15</v>
+      </c>
+      <c r="G241" t="s">
+        <v>128</v>
+      </c>
+      <c r="H241" t="s">
+        <v>200</v>
+      </c>
+      <c r="I241" t="s">
+        <v>18</v>
+      </c>
+      <c r="K241">
+        <v>100</v>
+      </c>
+      <c r="L241">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>12</v>
+      </c>
+      <c r="B242">
+        <v>15</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+      <c r="D242" t="s">
+        <v>199</v>
+      </c>
+      <c r="E242" t="s">
+        <v>130</v>
+      </c>
+      <c r="F242" t="s">
+        <v>28</v>
+      </c>
+      <c r="G242" t="s">
+        <v>128</v>
+      </c>
+      <c r="H242" t="s">
+        <v>200</v>
+      </c>
+      <c r="I242" t="s">
+        <v>18</v>
+      </c>
+      <c r="K242">
+        <v>100</v>
+      </c>
+      <c r="L242">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>20</v>
+      </c>
+      <c r="B243">
+        <v>5</v>
+      </c>
+      <c r="C243">
+        <v>0</v>
+      </c>
+      <c r="D243" t="s">
+        <v>21</v>
+      </c>
+      <c r="E243" t="s">
+        <v>130</v>
+      </c>
+      <c r="F243" t="s">
+        <v>28</v>
+      </c>
+      <c r="G243" t="s">
+        <v>128</v>
+      </c>
+      <c r="H243" t="s">
+        <v>200</v>
+      </c>
+      <c r="I243" t="s">
+        <v>18</v>
+      </c>
+      <c r="K243">
+        <v>100</v>
+      </c>
+      <c r="L243">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>22</v>
+      </c>
+      <c r="B244">
+        <v>37</v>
+      </c>
+      <c r="C244">
+        <v>7</v>
+      </c>
+      <c r="D244" t="s">
+        <v>210</v>
+      </c>
+      <c r="E244" t="s">
+        <v>130</v>
+      </c>
+      <c r="F244" t="s">
+        <v>28</v>
+      </c>
+      <c r="G244" t="s">
+        <v>128</v>
+      </c>
+      <c r="H244" t="s">
+        <v>200</v>
+      </c>
+      <c r="I244" t="s">
+        <v>18</v>
+      </c>
+      <c r="K244">
+        <v>100</v>
+      </c>
+      <c r="L244">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>24</v>
+      </c>
+      <c r="B245">
+        <v>48</v>
+      </c>
+      <c r="C245">
+        <v>13</v>
+      </c>
+      <c r="D245" t="s">
+        <v>201</v>
+      </c>
+      <c r="E245" t="s">
+        <v>130</v>
+      </c>
+      <c r="F245" t="s">
+        <v>28</v>
+      </c>
+      <c r="G245" t="s">
+        <v>128</v>
+      </c>
+      <c r="H245" t="s">
+        <v>200</v>
+      </c>
+      <c r="I245" t="s">
+        <v>18</v>
+      </c>
+      <c r="K245">
+        <v>100</v>
+      </c>
+      <c r="L245">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>26</v>
+      </c>
+      <c r="B246">
+        <v>765</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246" t="s">
+        <v>21</v>
+      </c>
+      <c r="E246" t="s">
+        <v>130</v>
+      </c>
+      <c r="F246" t="s">
+        <v>28</v>
+      </c>
+      <c r="G246" t="s">
+        <v>128</v>
+      </c>
+      <c r="H246" t="s">
+        <v>200</v>
+      </c>
+      <c r="I246" t="s">
+        <v>18</v>
+      </c>
+      <c r="K246">
+        <v>100</v>
+      </c>
+      <c r="L246">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>12</v>
+      </c>
+      <c r="B247">
+        <v>5</v>
+      </c>
+      <c r="C247">
+        <v>8</v>
+      </c>
+      <c r="D247" t="s">
+        <v>211</v>
+      </c>
+      <c r="E247" t="s">
+        <v>135</v>
+      </c>
+      <c r="F247" t="s">
+        <v>28</v>
+      </c>
+      <c r="G247" t="s">
+        <v>128</v>
+      </c>
+      <c r="H247" t="s">
+        <v>200</v>
+      </c>
+      <c r="I247" t="s">
+        <v>18</v>
+      </c>
+      <c r="J247" t="s">
+        <v>212</v>
+      </c>
+      <c r="K247">
+        <v>100</v>
+      </c>
+      <c r="L247">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>20</v>
+      </c>
+      <c r="B248">
+        <v>2</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248" t="s">
+        <v>21</v>
+      </c>
+      <c r="E248" t="s">
+        <v>135</v>
+      </c>
+      <c r="F248" t="s">
+        <v>28</v>
+      </c>
+      <c r="G248" t="s">
+        <v>128</v>
+      </c>
+      <c r="H248" t="s">
+        <v>200</v>
+      </c>
+      <c r="I248" t="s">
+        <v>18</v>
+      </c>
+      <c r="K248">
+        <v>100</v>
+      </c>
+      <c r="L248">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>22</v>
+      </c>
+      <c r="B249">
+        <v>11</v>
+      </c>
+      <c r="C249">
+        <v>12</v>
+      </c>
+      <c r="D249" t="s">
+        <v>213</v>
+      </c>
+      <c r="E249" t="s">
+        <v>135</v>
+      </c>
+      <c r="F249" t="s">
+        <v>28</v>
+      </c>
+      <c r="G249" t="s">
+        <v>128</v>
+      </c>
+      <c r="H249" t="s">
+        <v>200</v>
+      </c>
+      <c r="I249" t="s">
+        <v>18</v>
+      </c>
+      <c r="K249">
+        <v>100</v>
+      </c>
+      <c r="L249">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>24</v>
+      </c>
+      <c r="B250">
+        <v>14</v>
+      </c>
+      <c r="C250">
+        <v>19</v>
+      </c>
+      <c r="D250" t="s">
+        <v>201</v>
+      </c>
+      <c r="E250" t="s">
+        <v>135</v>
+      </c>
+      <c r="F250" t="s">
+        <v>28</v>
+      </c>
+      <c r="G250" t="s">
+        <v>128</v>
+      </c>
+      <c r="H250" t="s">
+        <v>200</v>
+      </c>
+      <c r="I250" t="s">
+        <v>18</v>
+      </c>
+      <c r="K250">
+        <v>100</v>
+      </c>
+      <c r="L250">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>26</v>
+      </c>
+      <c r="B251">
+        <v>225</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251" t="s">
+        <v>21</v>
+      </c>
+      <c r="E251" t="s">
+        <v>135</v>
+      </c>
+      <c r="F251" t="s">
+        <v>28</v>
+      </c>
+      <c r="G251" t="s">
+        <v>128</v>
+      </c>
+      <c r="H251" t="s">
+        <v>200</v>
+      </c>
+      <c r="I251" t="s">
+        <v>18</v>
+      </c>
+      <c r="K251">
+        <v>100</v>
+      </c>
+      <c r="L251">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>12</v>
+      </c>
+      <c r="B252">
+        <v>19</v>
+      </c>
+      <c r="C252">
+        <v>4</v>
+      </c>
+      <c r="D252" t="s">
+        <v>209</v>
+      </c>
+      <c r="E252" t="s">
+        <v>214</v>
+      </c>
+      <c r="F252" t="s">
+        <v>15</v>
+      </c>
+      <c r="G252" t="s">
+        <v>215</v>
+      </c>
+      <c r="H252" t="s">
+        <v>200</v>
+      </c>
+      <c r="I252" t="s">
+        <v>18</v>
+      </c>
+      <c r="K252">
+        <v>100</v>
+      </c>
+      <c r="L252">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>20</v>
+      </c>
+      <c r="B253">
+        <v>5</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253" t="s">
+        <v>21</v>
+      </c>
+      <c r="E253" t="s">
+        <v>214</v>
+      </c>
+      <c r="F253" t="s">
+        <v>15</v>
+      </c>
+      <c r="G253" t="s">
+        <v>215</v>
+      </c>
+      <c r="H253" t="s">
+        <v>200</v>
+      </c>
+      <c r="I253" t="s">
+        <v>18</v>
+      </c>
+      <c r="K253">
+        <v>100</v>
+      </c>
+      <c r="L253">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>22</v>
+      </c>
+      <c r="B254">
+        <v>32</v>
+      </c>
+      <c r="C254">
+        <v>7</v>
+      </c>
+      <c r="D254" t="s">
+        <v>36</v>
+      </c>
+      <c r="E254" t="s">
+        <v>214</v>
+      </c>
+      <c r="F254" t="s">
+        <v>15</v>
+      </c>
+      <c r="G254" t="s">
+        <v>215</v>
+      </c>
+      <c r="H254" t="s">
+        <v>200</v>
+      </c>
+      <c r="I254" t="s">
+        <v>18</v>
+      </c>
+      <c r="J254" t="s">
+        <v>216</v>
+      </c>
+      <c r="K254">
+        <v>100</v>
+      </c>
+      <c r="L254">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>24</v>
+      </c>
+      <c r="B255">
+        <v>61</v>
+      </c>
+      <c r="C255">
+        <v>8</v>
+      </c>
+      <c r="D255" t="s">
+        <v>201</v>
+      </c>
+      <c r="E255" t="s">
+        <v>214</v>
+      </c>
+      <c r="F255" t="s">
+        <v>15</v>
+      </c>
+      <c r="G255" t="s">
+        <v>215</v>
+      </c>
+      <c r="H255" t="s">
+        <v>200</v>
+      </c>
+      <c r="I255" t="s">
+        <v>18</v>
+      </c>
+      <c r="K255">
+        <v>100</v>
+      </c>
+      <c r="L255">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>26</v>
+      </c>
+      <c r="B256">
+        <v>510</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256" t="s">
+        <v>21</v>
+      </c>
+      <c r="E256" t="s">
+        <v>214</v>
+      </c>
+      <c r="F256" t="s">
+        <v>15</v>
+      </c>
+      <c r="G256" t="s">
+        <v>215</v>
+      </c>
+      <c r="H256" t="s">
+        <v>200</v>
+      </c>
+      <c r="I256" t="s">
+        <v>18</v>
+      </c>
+      <c r="K256">
+        <v>100</v>
+      </c>
+      <c r="L256">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>12</v>
+      </c>
+      <c r="B257">
+        <v>8</v>
+      </c>
+      <c r="C257">
+        <v>12</v>
+      </c>
+      <c r="D257" t="s">
+        <v>217</v>
+      </c>
+      <c r="E257" t="s">
+        <v>218</v>
+      </c>
+      <c r="F257" t="s">
+        <v>28</v>
+      </c>
+      <c r="G257" t="s">
+        <v>215</v>
+      </c>
+      <c r="H257" t="s">
+        <v>200</v>
+      </c>
+      <c r="I257" t="s">
+        <v>18</v>
+      </c>
+      <c r="J257" t="s">
+        <v>219</v>
+      </c>
+      <c r="K257">
+        <v>100</v>
+      </c>
+      <c r="L257">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>20</v>
+      </c>
+      <c r="B258">
+        <v>2</v>
+      </c>
+      <c r="C258">
+        <v>4</v>
+      </c>
+      <c r="D258" t="s">
+        <v>43</v>
+      </c>
+      <c r="E258" t="s">
+        <v>218</v>
+      </c>
+      <c r="F258" t="s">
+        <v>28</v>
+      </c>
+      <c r="G258" t="s">
+        <v>215</v>
+      </c>
+      <c r="H258" t="s">
+        <v>200</v>
+      </c>
+      <c r="I258" t="s">
+        <v>18</v>
+      </c>
+      <c r="K258">
+        <v>100</v>
+      </c>
+      <c r="L258">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>22</v>
+      </c>
+      <c r="B259">
+        <v>14</v>
+      </c>
+      <c r="C259">
+        <v>14</v>
+      </c>
+      <c r="D259" t="s">
+        <v>44</v>
+      </c>
+      <c r="E259" t="s">
+        <v>218</v>
+      </c>
+      <c r="F259" t="s">
+        <v>28</v>
+      </c>
+      <c r="G259" t="s">
+        <v>215</v>
+      </c>
+      <c r="H259" t="s">
+        <v>200</v>
+      </c>
+      <c r="I259" t="s">
+        <v>18</v>
+      </c>
+      <c r="K259">
+        <v>100</v>
+      </c>
+      <c r="L259">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>24</v>
+      </c>
+      <c r="B260">
+        <v>27</v>
+      </c>
+      <c r="C260">
+        <v>31</v>
+      </c>
+      <c r="D260" t="s">
+        <v>55</v>
+      </c>
+      <c r="E260" t="s">
+        <v>218</v>
+      </c>
+      <c r="F260" t="s">
+        <v>28</v>
+      </c>
+      <c r="G260" t="s">
+        <v>215</v>
+      </c>
+      <c r="H260" t="s">
+        <v>200</v>
+      </c>
+      <c r="I260" t="s">
+        <v>18</v>
+      </c>
+      <c r="K260">
+        <v>100</v>
+      </c>
+      <c r="L260">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>26</v>
+      </c>
+      <c r="B261">
+        <v>225</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261" t="s">
+        <v>21</v>
+      </c>
+      <c r="E261" t="s">
+        <v>218</v>
+      </c>
+      <c r="F261" t="s">
+        <v>28</v>
+      </c>
+      <c r="G261" t="s">
+        <v>215</v>
+      </c>
+      <c r="H261" t="s">
+        <v>200</v>
+      </c>
+      <c r="I261" t="s">
+        <v>18</v>
+      </c>
+      <c r="K261">
+        <v>100</v>
+      </c>
+      <c r="L261">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>12</v>
+      </c>
+      <c r="B262">
+        <v>28</v>
+      </c>
+      <c r="C262">
+        <v>7</v>
+      </c>
+      <c r="D262" t="s">
+        <v>71</v>
+      </c>
+      <c r="E262" t="s">
+        <v>220</v>
+      </c>
+      <c r="F262" t="s">
+        <v>28</v>
+      </c>
+      <c r="G262" t="s">
+        <v>215</v>
+      </c>
+      <c r="H262" t="s">
+        <v>200</v>
+      </c>
+      <c r="I262" t="s">
+        <v>18</v>
+      </c>
+      <c r="K262">
+        <v>100</v>
+      </c>
+      <c r="L262">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>20</v>
+      </c>
+      <c r="B263">
+        <v>7</v>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+      <c r="D263" t="s">
+        <v>162</v>
+      </c>
+      <c r="E263" t="s">
+        <v>220</v>
+      </c>
+      <c r="F263" t="s">
+        <v>28</v>
+      </c>
+      <c r="G263" t="s">
+        <v>215</v>
+      </c>
+      <c r="H263" t="s">
+        <v>200</v>
+      </c>
+      <c r="I263" t="s">
+        <v>18</v>
+      </c>
+      <c r="K263">
+        <v>100</v>
+      </c>
+      <c r="L263">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>22</v>
+      </c>
+      <c r="B264">
+        <v>48</v>
+      </c>
+      <c r="C264">
+        <v>12</v>
+      </c>
+      <c r="D264" t="s">
+        <v>71</v>
+      </c>
+      <c r="E264" t="s">
+        <v>220</v>
+      </c>
+      <c r="F264" t="s">
+        <v>28</v>
+      </c>
+      <c r="G264" t="s">
+        <v>215</v>
+      </c>
+      <c r="H264" t="s">
+        <v>200</v>
+      </c>
+      <c r="I264" t="s">
+        <v>18</v>
+      </c>
+      <c r="K264">
+        <v>100</v>
+      </c>
+      <c r="L264">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>24</v>
+      </c>
+      <c r="B265">
+        <v>92</v>
+      </c>
+      <c r="C265">
+        <v>28</v>
+      </c>
+      <c r="D265" t="s">
+        <v>201</v>
+      </c>
+      <c r="E265" t="s">
+        <v>220</v>
+      </c>
+      <c r="F265" t="s">
+        <v>28</v>
+      </c>
+      <c r="G265" t="s">
+        <v>215</v>
+      </c>
+      <c r="H265" t="s">
+        <v>200</v>
+      </c>
+      <c r="I265" t="s">
+        <v>18</v>
+      </c>
+      <c r="K265">
+        <v>100</v>
+      </c>
+      <c r="L265">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>26</v>
+      </c>
+      <c r="B266">
+        <v>765</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266" t="s">
+        <v>21</v>
+      </c>
+      <c r="E266" t="s">
+        <v>220</v>
+      </c>
+      <c r="F266" t="s">
+        <v>28</v>
+      </c>
+      <c r="G266" t="s">
+        <v>215</v>
+      </c>
+      <c r="H266" t="s">
+        <v>200</v>
+      </c>
+      <c r="I266" t="s">
+        <v>18</v>
+      </c>
+      <c r="K266">
+        <v>100</v>
+      </c>
+      <c r="L266">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>12</v>
+      </c>
+      <c r="B267">
+        <v>28</v>
+      </c>
+      <c r="C267">
+        <v>2</v>
+      </c>
+      <c r="D267" t="s">
+        <v>199</v>
+      </c>
+      <c r="E267" t="s">
+        <v>32</v>
+      </c>
+      <c r="F267" t="s">
+        <v>15</v>
+      </c>
+      <c r="G267" t="s">
+        <v>33</v>
+      </c>
+      <c r="H267" t="s">
+        <v>200</v>
+      </c>
+      <c r="I267" t="s">
+        <v>18</v>
+      </c>
+      <c r="K267">
+        <v>100</v>
+      </c>
+      <c r="L267">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>20</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268" t="s">
+        <v>21</v>
+      </c>
+      <c r="E268" t="s">
+        <v>32</v>
+      </c>
+      <c r="F268" t="s">
+        <v>15</v>
+      </c>
+      <c r="G268" t="s">
+        <v>33</v>
+      </c>
+      <c r="H268" t="s">
+        <v>200</v>
+      </c>
+      <c r="I268" t="s">
+        <v>18</v>
+      </c>
+      <c r="K268">
+        <v>100</v>
+      </c>
+      <c r="L268">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>22</v>
+      </c>
+      <c r="B269">
+        <v>34</v>
+      </c>
+      <c r="C269">
+        <v>4</v>
+      </c>
+      <c r="D269" t="s">
+        <v>169</v>
+      </c>
+      <c r="E269" t="s">
+        <v>32</v>
+      </c>
+      <c r="F269" t="s">
+        <v>15</v>
+      </c>
+      <c r="G269" t="s">
+        <v>33</v>
+      </c>
+      <c r="H269" t="s">
+        <v>200</v>
+      </c>
+      <c r="I269" t="s">
+        <v>18</v>
+      </c>
+      <c r="K269">
+        <v>100</v>
+      </c>
+      <c r="L269">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>24</v>
+      </c>
+      <c r="B270">
+        <v>61</v>
+      </c>
+      <c r="C270">
+        <v>14</v>
+      </c>
+      <c r="D270" t="s">
+        <v>201</v>
+      </c>
+      <c r="E270" t="s">
+        <v>32</v>
+      </c>
+      <c r="F270" t="s">
+        <v>15</v>
+      </c>
+      <c r="G270" t="s">
+        <v>33</v>
+      </c>
+      <c r="H270" t="s">
+        <v>200</v>
+      </c>
+      <c r="I270" t="s">
+        <v>18</v>
+      </c>
+      <c r="K270">
+        <v>100</v>
+      </c>
+      <c r="L270">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>26</v>
+      </c>
+      <c r="B271">
+        <v>912</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271" t="s">
+        <v>21</v>
+      </c>
+      <c r="E271" t="s">
+        <v>32</v>
+      </c>
+      <c r="F271" t="s">
+        <v>15</v>
+      </c>
+      <c r="G271" t="s">
+        <v>33</v>
+      </c>
+      <c r="H271" t="s">
+        <v>200</v>
+      </c>
+      <c r="I271" t="s">
+        <v>18</v>
+      </c>
+      <c r="K271">
+        <v>100</v>
+      </c>
+      <c r="L271">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>12</v>
+      </c>
+      <c r="B272">
+        <v>9</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272" t="s">
+        <v>21</v>
+      </c>
+      <c r="E272" t="s">
+        <v>38</v>
+      </c>
+      <c r="F272" t="s">
+        <v>28</v>
+      </c>
+      <c r="G272" t="s">
+        <v>33</v>
+      </c>
+      <c r="H272" t="s">
+        <v>200</v>
+      </c>
+      <c r="I272" t="s">
+        <v>18</v>
+      </c>
+      <c r="J272" t="s">
+        <v>202</v>
+      </c>
+      <c r="K272">
+        <v>100</v>
+      </c>
+      <c r="L272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>20</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273" t="s">
+        <v>21</v>
+      </c>
+      <c r="E273" t="s">
+        <v>38</v>
+      </c>
+      <c r="F273" t="s">
+        <v>28</v>
+      </c>
+      <c r="G273" t="s">
+        <v>33</v>
+      </c>
+      <c r="H273" t="s">
+        <v>200</v>
+      </c>
+      <c r="I273" t="s">
+        <v>18</v>
+      </c>
+      <c r="K273">
+        <v>100</v>
+      </c>
+      <c r="L273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>22</v>
+      </c>
+      <c r="B274">
+        <v>11</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274" t="s">
+        <v>21</v>
+      </c>
+      <c r="E274" t="s">
+        <v>38</v>
+      </c>
+      <c r="F274" t="s">
+        <v>28</v>
+      </c>
+      <c r="G274" t="s">
+        <v>33</v>
+      </c>
+      <c r="H274" t="s">
+        <v>200</v>
+      </c>
+      <c r="I274" t="s">
+        <v>18</v>
+      </c>
+      <c r="K274">
+        <v>100</v>
+      </c>
+      <c r="L274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>24</v>
+      </c>
+      <c r="B275">
+        <v>19</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275" t="s">
+        <v>201</v>
+      </c>
+      <c r="E275" t="s">
+        <v>38</v>
+      </c>
+      <c r="F275" t="s">
+        <v>28</v>
+      </c>
+      <c r="G275" t="s">
+        <v>33</v>
+      </c>
+      <c r="H275" t="s">
+        <v>200</v>
+      </c>
+      <c r="I275" t="s">
+        <v>18</v>
+      </c>
+      <c r="K275">
+        <v>100</v>
+      </c>
+      <c r="L275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>26</v>
+      </c>
+      <c r="B276">
+        <v>288</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276" t="s">
+        <v>21</v>
+      </c>
+      <c r="E276" t="s">
+        <v>38</v>
+      </c>
+      <c r="F276" t="s">
+        <v>28</v>
+      </c>
+      <c r="G276" t="s">
+        <v>33</v>
+      </c>
+      <c r="H276" t="s">
+        <v>200</v>
+      </c>
+      <c r="I276" t="s">
+        <v>18</v>
+      </c>
+      <c r="K276">
+        <v>100</v>
+      </c>
+      <c r="L276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>12</v>
+      </c>
+      <c r="B277">
+        <v>19</v>
+      </c>
+      <c r="C277">
+        <v>9</v>
+      </c>
+      <c r="D277" t="s">
+        <v>203</v>
+      </c>
+      <c r="E277" t="s">
+        <v>204</v>
+      </c>
+      <c r="F277" t="s">
+        <v>15</v>
+      </c>
+      <c r="G277" t="s">
+        <v>205</v>
+      </c>
+      <c r="H277" t="s">
+        <v>200</v>
+      </c>
+      <c r="I277" t="s">
+        <v>18</v>
+      </c>
+      <c r="K277">
+        <v>100</v>
+      </c>
+      <c r="L277">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>20</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278" t="s">
+        <v>21</v>
+      </c>
+      <c r="E278" t="s">
+        <v>204</v>
+      </c>
+      <c r="F278" t="s">
+        <v>15</v>
+      </c>
+      <c r="G278" t="s">
+        <v>205</v>
+      </c>
+      <c r="H278" t="s">
+        <v>200</v>
+      </c>
+      <c r="I278" t="s">
+        <v>18</v>
+      </c>
+      <c r="K278">
+        <v>100</v>
+      </c>
+      <c r="L278">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>22</v>
+      </c>
+      <c r="B279">
+        <v>35</v>
+      </c>
+      <c r="C279">
+        <v>11</v>
+      </c>
+      <c r="D279" t="s">
+        <v>206</v>
+      </c>
+      <c r="E279" t="s">
+        <v>204</v>
+      </c>
+      <c r="F279" t="s">
+        <v>15</v>
+      </c>
+      <c r="G279" t="s">
+        <v>205</v>
+      </c>
+      <c r="H279" t="s">
+        <v>200</v>
+      </c>
+      <c r="I279" t="s">
+        <v>18</v>
+      </c>
+      <c r="K279">
+        <v>100</v>
+      </c>
+      <c r="L279">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>24</v>
+      </c>
+      <c r="B280">
+        <v>102</v>
+      </c>
+      <c r="C280">
+        <v>39</v>
+      </c>
+      <c r="D280" t="s">
+        <v>201</v>
+      </c>
+      <c r="E280" t="s">
+        <v>204</v>
+      </c>
+      <c r="F280" t="s">
+        <v>15</v>
+      </c>
+      <c r="G280" t="s">
+        <v>205</v>
+      </c>
+      <c r="H280" t="s">
+        <v>200</v>
+      </c>
+      <c r="I280" t="s">
+        <v>18</v>
+      </c>
+      <c r="K280">
+        <v>100</v>
+      </c>
+      <c r="L280">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>26</v>
+      </c>
+      <c r="B281">
+        <v>768</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281" t="s">
+        <v>21</v>
+      </c>
+      <c r="E281" t="s">
+        <v>204</v>
+      </c>
+      <c r="F281" t="s">
+        <v>15</v>
+      </c>
+      <c r="G281" t="s">
+        <v>205</v>
+      </c>
+      <c r="H281" t="s">
+        <v>200</v>
+      </c>
+      <c r="I281" t="s">
+        <v>18</v>
+      </c>
+      <c r="K281">
+        <v>100</v>
+      </c>
+      <c r="L281">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>12</v>
+      </c>
+      <c r="B282">
+        <v>11</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282" t="s">
+        <v>21</v>
+      </c>
+      <c r="E282" t="s">
+        <v>207</v>
+      </c>
+      <c r="F282" t="s">
+        <v>28</v>
+      </c>
+      <c r="G282" t="s">
+        <v>205</v>
+      </c>
+      <c r="H282" t="s">
+        <v>200</v>
+      </c>
+      <c r="I282" t="s">
+        <v>18</v>
+      </c>
+      <c r="J282" t="s">
+        <v>208</v>
+      </c>
+      <c r="K282">
+        <v>100</v>
+      </c>
+      <c r="L282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>20</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283" t="s">
+        <v>21</v>
+      </c>
+      <c r="E283" t="s">
+        <v>207</v>
+      </c>
+      <c r="F283" t="s">
+        <v>28</v>
+      </c>
+      <c r="G283" t="s">
+        <v>205</v>
+      </c>
+      <c r="H283" t="s">
+        <v>200</v>
+      </c>
+      <c r="I283" t="s">
+        <v>18</v>
+      </c>
+      <c r="K283">
+        <v>100</v>
+      </c>
+      <c r="L283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>22</v>
+      </c>
+      <c r="B284">
+        <v>20</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284" t="s">
+        <v>21</v>
+      </c>
+      <c r="E284" t="s">
+        <v>207</v>
+      </c>
+      <c r="F284" t="s">
+        <v>28</v>
+      </c>
+      <c r="G284" t="s">
+        <v>205</v>
+      </c>
+      <c r="H284" t="s">
+        <v>200</v>
+      </c>
+      <c r="I284" t="s">
+        <v>18</v>
+      </c>
+      <c r="K284">
+        <v>100</v>
+      </c>
+      <c r="L284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>24</v>
+      </c>
+      <c r="B285">
+        <v>58</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285" t="s">
+        <v>201</v>
+      </c>
+      <c r="E285" t="s">
+        <v>207</v>
+      </c>
+      <c r="F285" t="s">
+        <v>28</v>
+      </c>
+      <c r="G285" t="s">
+        <v>205</v>
+      </c>
+      <c r="H285" t="s">
+        <v>200</v>
+      </c>
+      <c r="I285" t="s">
+        <v>18</v>
+      </c>
+      <c r="K285">
+        <v>100</v>
+      </c>
+      <c r="L285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>26</v>
+      </c>
+      <c r="B286">
+        <v>432</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286" t="s">
+        <v>21</v>
+      </c>
+      <c r="E286" t="s">
+        <v>207</v>
+      </c>
+      <c r="F286" t="s">
+        <v>28</v>
+      </c>
+      <c r="G286" t="s">
+        <v>205</v>
+      </c>
+      <c r="H286" t="s">
+        <v>200</v>
+      </c>
+      <c r="I286" t="s">
+        <v>18</v>
+      </c>
+      <c r="K286">
+        <v>100</v>
+      </c>
+      <c r="L286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>12</v>
+      </c>
+      <c r="B287">
+        <v>10</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287" t="s">
+        <v>21</v>
+      </c>
+      <c r="E287" t="s">
+        <v>127</v>
+      </c>
+      <c r="F287" t="s">
+        <v>15</v>
+      </c>
+      <c r="G287" t="s">
+        <v>128</v>
+      </c>
+      <c r="H287" t="s">
+        <v>200</v>
+      </c>
+      <c r="I287" t="s">
+        <v>18</v>
+      </c>
+      <c r="K287">
+        <v>100</v>
+      </c>
+      <c r="L287">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>20</v>
+      </c>
+      <c r="B288">
+        <v>3</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288" t="s">
+        <v>21</v>
+      </c>
+      <c r="E288" t="s">
+        <v>127</v>
+      </c>
+      <c r="F288" t="s">
+        <v>15</v>
+      </c>
+      <c r="G288" t="s">
+        <v>128</v>
+      </c>
+      <c r="H288" t="s">
+        <v>200</v>
+      </c>
+      <c r="I288" t="s">
+        <v>18</v>
+      </c>
+      <c r="K288">
+        <v>100</v>
+      </c>
+      <c r="L288">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>22</v>
+      </c>
+      <c r="B289">
+        <v>24</v>
+      </c>
+      <c r="C289">
+        <v>5</v>
+      </c>
+      <c r="D289" t="s">
+        <v>209</v>
+      </c>
+      <c r="E289" t="s">
+        <v>127</v>
+      </c>
+      <c r="F289" t="s">
+        <v>15</v>
+      </c>
+      <c r="G289" t="s">
+        <v>128</v>
+      </c>
+      <c r="H289" t="s">
+        <v>200</v>
+      </c>
+      <c r="I289" t="s">
+        <v>18</v>
+      </c>
+      <c r="K289">
+        <v>100</v>
+      </c>
+      <c r="L289">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>24</v>
+      </c>
+      <c r="B290">
+        <v>32</v>
+      </c>
+      <c r="C290">
+        <v>5</v>
+      </c>
+      <c r="D290" t="s">
+        <v>201</v>
+      </c>
+      <c r="E290" t="s">
+        <v>127</v>
+      </c>
+      <c r="F290" t="s">
+        <v>15</v>
+      </c>
+      <c r="G290" t="s">
+        <v>128</v>
+      </c>
+      <c r="H290" t="s">
+        <v>200</v>
+      </c>
+      <c r="I290" t="s">
+        <v>18</v>
+      </c>
+      <c r="K290">
+        <v>100</v>
+      </c>
+      <c r="L290">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>26</v>
+      </c>
+      <c r="B291">
+        <v>510</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291" t="s">
+        <v>21</v>
+      </c>
+      <c r="E291" t="s">
+        <v>127</v>
+      </c>
+      <c r="F291" t="s">
+        <v>15</v>
+      </c>
+      <c r="G291" t="s">
+        <v>128</v>
+      </c>
+      <c r="H291" t="s">
+        <v>200</v>
+      </c>
+      <c r="I291" t="s">
+        <v>18</v>
+      </c>
+      <c r="K291">
+        <v>100</v>
+      </c>
+      <c r="L291">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>12</v>
+      </c>
+      <c r="B292">
+        <v>15</v>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="D292" t="s">
+        <v>199</v>
+      </c>
+      <c r="E292" t="s">
+        <v>130</v>
+      </c>
+      <c r="F292" t="s">
+        <v>28</v>
+      </c>
+      <c r="G292" t="s">
+        <v>128</v>
+      </c>
+      <c r="H292" t="s">
+        <v>200</v>
+      </c>
+      <c r="I292" t="s">
+        <v>18</v>
+      </c>
+      <c r="K292">
+        <v>100</v>
+      </c>
+      <c r="L292">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>20</v>
+      </c>
+      <c r="B293">
+        <v>5</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293" t="s">
+        <v>21</v>
+      </c>
+      <c r="E293" t="s">
+        <v>130</v>
+      </c>
+      <c r="F293" t="s">
+        <v>28</v>
+      </c>
+      <c r="G293" t="s">
+        <v>128</v>
+      </c>
+      <c r="H293" t="s">
+        <v>200</v>
+      </c>
+      <c r="I293" t="s">
+        <v>18</v>
+      </c>
+      <c r="K293">
+        <v>100</v>
+      </c>
+      <c r="L293">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>22</v>
+      </c>
+      <c r="B294">
+        <v>37</v>
+      </c>
+      <c r="C294">
+        <v>7</v>
+      </c>
+      <c r="D294" t="s">
+        <v>210</v>
+      </c>
+      <c r="E294" t="s">
+        <v>130</v>
+      </c>
+      <c r="F294" t="s">
+        <v>28</v>
+      </c>
+      <c r="G294" t="s">
+        <v>128</v>
+      </c>
+      <c r="H294" t="s">
+        <v>200</v>
+      </c>
+      <c r="I294" t="s">
+        <v>18</v>
+      </c>
+      <c r="K294">
+        <v>100</v>
+      </c>
+      <c r="L294">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>24</v>
+      </c>
+      <c r="B295">
+        <v>48</v>
+      </c>
+      <c r="C295">
+        <v>13</v>
+      </c>
+      <c r="D295" t="s">
+        <v>201</v>
+      </c>
+      <c r="E295" t="s">
+        <v>130</v>
+      </c>
+      <c r="F295" t="s">
+        <v>28</v>
+      </c>
+      <c r="G295" t="s">
+        <v>128</v>
+      </c>
+      <c r="H295" t="s">
+        <v>200</v>
+      </c>
+      <c r="I295" t="s">
+        <v>18</v>
+      </c>
+      <c r="K295">
+        <v>100</v>
+      </c>
+      <c r="L295">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>26</v>
+      </c>
+      <c r="B296">
+        <v>765</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296" t="s">
+        <v>21</v>
+      </c>
+      <c r="E296" t="s">
+        <v>130</v>
+      </c>
+      <c r="F296" t="s">
+        <v>28</v>
+      </c>
+      <c r="G296" t="s">
+        <v>128</v>
+      </c>
+      <c r="H296" t="s">
+        <v>200</v>
+      </c>
+      <c r="I296" t="s">
+        <v>18</v>
+      </c>
+      <c r="K296">
+        <v>100</v>
+      </c>
+      <c r="L296">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>12</v>
+      </c>
+      <c r="B297">
+        <v>5</v>
+      </c>
+      <c r="C297">
+        <v>8</v>
+      </c>
+      <c r="D297" t="s">
+        <v>211</v>
+      </c>
+      <c r="E297" t="s">
+        <v>135</v>
+      </c>
+      <c r="F297" t="s">
+        <v>28</v>
+      </c>
+      <c r="G297" t="s">
+        <v>128</v>
+      </c>
+      <c r="H297" t="s">
+        <v>200</v>
+      </c>
+      <c r="I297" t="s">
+        <v>18</v>
+      </c>
+      <c r="J297" t="s">
+        <v>212</v>
+      </c>
+      <c r="K297">
+        <v>100</v>
+      </c>
+      <c r="L297">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>20</v>
+      </c>
+      <c r="B298">
+        <v>2</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298" t="s">
+        <v>21</v>
+      </c>
+      <c r="E298" t="s">
+        <v>135</v>
+      </c>
+      <c r="F298" t="s">
+        <v>28</v>
+      </c>
+      <c r="G298" t="s">
+        <v>128</v>
+      </c>
+      <c r="H298" t="s">
+        <v>200</v>
+      </c>
+      <c r="I298" t="s">
+        <v>18</v>
+      </c>
+      <c r="K298">
+        <v>100</v>
+      </c>
+      <c r="L298">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>22</v>
+      </c>
+      <c r="B299">
+        <v>11</v>
+      </c>
+      <c r="C299">
+        <v>12</v>
+      </c>
+      <c r="D299" t="s">
+        <v>213</v>
+      </c>
+      <c r="E299" t="s">
+        <v>135</v>
+      </c>
+      <c r="F299" t="s">
+        <v>28</v>
+      </c>
+      <c r="G299" t="s">
+        <v>128</v>
+      </c>
+      <c r="H299" t="s">
+        <v>200</v>
+      </c>
+      <c r="I299" t="s">
+        <v>18</v>
+      </c>
+      <c r="K299">
+        <v>100</v>
+      </c>
+      <c r="L299">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>24</v>
+      </c>
+      <c r="B300">
+        <v>14</v>
+      </c>
+      <c r="C300">
+        <v>19</v>
+      </c>
+      <c r="D300" t="s">
+        <v>201</v>
+      </c>
+      <c r="E300" t="s">
+        <v>135</v>
+      </c>
+      <c r="F300" t="s">
+        <v>28</v>
+      </c>
+      <c r="G300" t="s">
+        <v>128</v>
+      </c>
+      <c r="H300" t="s">
+        <v>200</v>
+      </c>
+      <c r="I300" t="s">
+        <v>18</v>
+      </c>
+      <c r="K300">
+        <v>100</v>
+      </c>
+      <c r="L300">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>26</v>
+      </c>
+      <c r="B301">
+        <v>225</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301" t="s">
+        <v>21</v>
+      </c>
+      <c r="E301" t="s">
+        <v>135</v>
+      </c>
+      <c r="F301" t="s">
+        <v>28</v>
+      </c>
+      <c r="G301" t="s">
+        <v>128</v>
+      </c>
+      <c r="H301" t="s">
+        <v>200</v>
+      </c>
+      <c r="I301" t="s">
+        <v>18</v>
+      </c>
+      <c r="K301">
+        <v>100</v>
+      </c>
+      <c r="L301">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>12</v>
+      </c>
+      <c r="B302">
+        <v>20</v>
+      </c>
+      <c r="C302">
+        <v>10</v>
+      </c>
+      <c r="D302" t="s">
+        <v>150</v>
+      </c>
+      <c r="E302" t="s">
+        <v>188</v>
+      </c>
+      <c r="F302" t="s">
+        <v>15</v>
+      </c>
+      <c r="G302" t="s">
+        <v>189</v>
+      </c>
+      <c r="H302" t="s">
+        <v>200</v>
+      </c>
+      <c r="I302" t="s">
+        <v>18</v>
+      </c>
+      <c r="K302">
+        <v>100</v>
+      </c>
+      <c r="L302">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>20</v>
+      </c>
+      <c r="B303">
+        <v>3</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303" t="s">
+        <v>21</v>
+      </c>
+      <c r="E303" t="s">
+        <v>188</v>
+      </c>
+      <c r="F303" t="s">
+        <v>15</v>
+      </c>
+      <c r="G303" t="s">
+        <v>189</v>
+      </c>
+      <c r="H303" t="s">
+        <v>200</v>
+      </c>
+      <c r="I303" t="s">
+        <v>18</v>
+      </c>
+      <c r="K303">
+        <v>100</v>
+      </c>
+      <c r="L303">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>22</v>
+      </c>
+      <c r="B304">
+        <v>35</v>
+      </c>
+      <c r="C304">
+        <v>19</v>
+      </c>
+      <c r="D304" t="s">
+        <v>221</v>
+      </c>
+      <c r="E304" t="s">
+        <v>188</v>
+      </c>
+      <c r="F304" t="s">
+        <v>15</v>
+      </c>
+      <c r="G304" t="s">
+        <v>189</v>
+      </c>
+      <c r="H304" t="s">
+        <v>200</v>
+      </c>
+      <c r="I304" t="s">
+        <v>18</v>
+      </c>
+      <c r="K304">
+        <v>100</v>
+      </c>
+      <c r="L304">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>24</v>
+      </c>
+      <c r="B305">
+        <v>62</v>
+      </c>
+      <c r="C305">
+        <v>47</v>
+      </c>
+      <c r="D305" t="s">
+        <v>201</v>
+      </c>
+      <c r="E305" t="s">
+        <v>188</v>
+      </c>
+      <c r="F305" t="s">
+        <v>15</v>
+      </c>
+      <c r="G305" t="s">
+        <v>189</v>
+      </c>
+      <c r="H305" t="s">
+        <v>200</v>
+      </c>
+      <c r="I305" t="s">
+        <v>18</v>
+      </c>
+      <c r="K305">
+        <v>100</v>
+      </c>
+      <c r="L305">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>26</v>
+      </c>
+      <c r="B306">
+        <v>420</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306" t="s">
+        <v>21</v>
+      </c>
+      <c r="E306" t="s">
+        <v>188</v>
+      </c>
+      <c r="F306" t="s">
+        <v>15</v>
+      </c>
+      <c r="G306" t="s">
+        <v>189</v>
+      </c>
+      <c r="H306" t="s">
+        <v>200</v>
+      </c>
+      <c r="I306" t="s">
+        <v>18</v>
+      </c>
+      <c r="K306">
+        <v>100</v>
+      </c>
+      <c r="L306">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>12</v>
+      </c>
+      <c r="B307">
+        <v>29</v>
+      </c>
+      <c r="C307">
+        <v>11</v>
+      </c>
+      <c r="D307" t="s">
+        <v>37</v>
+      </c>
+      <c r="E307" t="s">
+        <v>222</v>
+      </c>
+      <c r="F307" t="s">
+        <v>28</v>
+      </c>
+      <c r="G307" t="s">
+        <v>189</v>
+      </c>
+      <c r="H307" t="s">
+        <v>200</v>
+      </c>
+      <c r="I307" t="s">
+        <v>18</v>
+      </c>
+      <c r="K307">
+        <v>100</v>
+      </c>
+      <c r="L307">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>20</v>
+      </c>
+      <c r="B308">
+        <v>4</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308" t="s">
+        <v>21</v>
+      </c>
+      <c r="E308" t="s">
+        <v>222</v>
+      </c>
+      <c r="F308" t="s">
+        <v>28</v>
+      </c>
+      <c r="G308" t="s">
+        <v>189</v>
+      </c>
+      <c r="H308" t="s">
+        <v>200</v>
+      </c>
+      <c r="I308" t="s">
+        <v>18</v>
+      </c>
+      <c r="K308">
+        <v>100</v>
+      </c>
+      <c r="L308">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>22</v>
+      </c>
+      <c r="B309">
+        <v>53</v>
+      </c>
+      <c r="C309">
+        <v>18</v>
+      </c>
+      <c r="D309" t="s">
+        <v>223</v>
+      </c>
+      <c r="E309" t="s">
+        <v>222</v>
+      </c>
+      <c r="F309" t="s">
+        <v>28</v>
+      </c>
+      <c r="G309" t="s">
+        <v>189</v>
+      </c>
+      <c r="H309" t="s">
+        <v>200</v>
+      </c>
+      <c r="I309" t="s">
+        <v>18</v>
+      </c>
+      <c r="K309">
+        <v>100</v>
+      </c>
+      <c r="L309">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>24</v>
+      </c>
+      <c r="B310">
+        <v>92</v>
+      </c>
+      <c r="C310">
+        <v>27</v>
+      </c>
+      <c r="D310" t="s">
+        <v>201</v>
+      </c>
+      <c r="E310" t="s">
+        <v>222</v>
+      </c>
+      <c r="F310" t="s">
+        <v>28</v>
+      </c>
+      <c r="G310" t="s">
+        <v>189</v>
+      </c>
+      <c r="H310" t="s">
+        <v>200</v>
+      </c>
+      <c r="I310" t="s">
+        <v>18</v>
+      </c>
+      <c r="K310">
+        <v>100</v>
+      </c>
+      <c r="L310">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>26</v>
+      </c>
+      <c r="B311">
+        <v>630</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311" t="s">
+        <v>21</v>
+      </c>
+      <c r="E311" t="s">
+        <v>222</v>
+      </c>
+      <c r="F311" t="s">
+        <v>28</v>
+      </c>
+      <c r="G311" t="s">
+        <v>189</v>
+      </c>
+      <c r="H311" t="s">
+        <v>200</v>
+      </c>
+      <c r="I311" t="s">
+        <v>18</v>
+      </c>
+      <c r="K311">
+        <v>100</v>
+      </c>
+      <c r="L311">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>12</v>
+      </c>
+      <c r="B312">
+        <v>21</v>
+      </c>
+      <c r="C312">
+        <v>5</v>
+      </c>
+      <c r="D312" t="s">
+        <v>110</v>
+      </c>
+      <c r="E312" t="s">
+        <v>192</v>
+      </c>
+      <c r="F312" t="s">
+        <v>28</v>
+      </c>
+      <c r="G312" t="s">
+        <v>189</v>
+      </c>
+      <c r="H312" t="s">
+        <v>200</v>
+      </c>
+      <c r="I312" t="s">
+        <v>18</v>
+      </c>
+      <c r="J312" t="s">
+        <v>224</v>
+      </c>
+      <c r="K312">
+        <v>100</v>
+      </c>
+      <c r="L312">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>20</v>
+      </c>
+      <c r="B313">
+        <v>3</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313" t="s">
+        <v>21</v>
+      </c>
+      <c r="E313" t="s">
+        <v>192</v>
+      </c>
+      <c r="F313" t="s">
+        <v>28</v>
+      </c>
+      <c r="G313" t="s">
+        <v>189</v>
+      </c>
+      <c r="H313" t="s">
+        <v>200</v>
+      </c>
+      <c r="I313" t="s">
+        <v>18</v>
+      </c>
+      <c r="K313">
+        <v>100</v>
+      </c>
+      <c r="L313">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>22</v>
+      </c>
+      <c r="B314">
+        <v>38</v>
+      </c>
+      <c r="C314">
+        <v>5</v>
+      </c>
+      <c r="D314" t="s">
+        <v>225</v>
+      </c>
+      <c r="E314" t="s">
+        <v>192</v>
+      </c>
+      <c r="F314" t="s">
+        <v>28</v>
+      </c>
+      <c r="G314" t="s">
+        <v>189</v>
+      </c>
+      <c r="H314" t="s">
+        <v>200</v>
+      </c>
+      <c r="I314" t="s">
+        <v>18</v>
+      </c>
+      <c r="K314">
+        <v>100</v>
+      </c>
+      <c r="L314">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>24</v>
+      </c>
+      <c r="B315">
+        <v>66</v>
+      </c>
+      <c r="C315">
+        <v>4</v>
+      </c>
+      <c r="D315" t="s">
+        <v>201</v>
+      </c>
+      <c r="E315" t="s">
+        <v>192</v>
+      </c>
+      <c r="F315" t="s">
+        <v>28</v>
+      </c>
+      <c r="G315" t="s">
+        <v>189</v>
+      </c>
+      <c r="H315" t="s">
+        <v>200</v>
+      </c>
+      <c r="I315" t="s">
+        <v>18</v>
+      </c>
+      <c r="K315">
+        <v>100</v>
+      </c>
+      <c r="L315">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>26</v>
+      </c>
+      <c r="B316">
+        <v>450</v>
+      </c>
+      <c r="C316">
+        <v>0</v>
+      </c>
+      <c r="D316" t="s">
+        <v>21</v>
+      </c>
+      <c r="E316" t="s">
+        <v>192</v>
+      </c>
+      <c r="F316" t="s">
+        <v>28</v>
+      </c>
+      <c r="G316" t="s">
+        <v>189</v>
+      </c>
+      <c r="H316" t="s">
+        <v>200</v>
+      </c>
+      <c r="I316" t="s">
+        <v>18</v>
+      </c>
+      <c r="K316">
+        <v>100</v>
+      </c>
+      <c r="L316">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>12</v>
+      </c>
+      <c r="B317">
+        <v>14</v>
+      </c>
+      <c r="C317">
+        <v>5</v>
+      </c>
+      <c r="D317" t="s">
+        <v>226</v>
+      </c>
+      <c r="E317" t="s">
+        <v>173</v>
+      </c>
+      <c r="F317" t="s">
+        <v>15</v>
+      </c>
+      <c r="G317" t="s">
+        <v>174</v>
+      </c>
+      <c r="H317" t="s">
+        <v>200</v>
+      </c>
+      <c r="I317" t="s">
+        <v>18</v>
+      </c>
+      <c r="J317" t="s">
+        <v>227</v>
+      </c>
+      <c r="K317">
+        <v>100</v>
+      </c>
+      <c r="L317">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>20</v>
+      </c>
+      <c r="B318">
+        <v>1</v>
+      </c>
+      <c r="C318">
+        <v>0</v>
+      </c>
+      <c r="D318" t="s">
+        <v>21</v>
+      </c>
+      <c r="E318" t="s">
+        <v>173</v>
+      </c>
+      <c r="F318" t="s">
+        <v>15</v>
+      </c>
+      <c r="G318" t="s">
+        <v>174</v>
+      </c>
+      <c r="H318" t="s">
+        <v>200</v>
+      </c>
+      <c r="I318" t="s">
+        <v>18</v>
+      </c>
+      <c r="J318" t="s">
+        <v>228</v>
+      </c>
+      <c r="K318">
+        <v>100</v>
+      </c>
+      <c r="L318">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>22</v>
+      </c>
+      <c r="B319">
+        <v>28</v>
+      </c>
+      <c r="C319">
+        <v>6</v>
+      </c>
+      <c r="D319" t="s">
+        <v>209</v>
+      </c>
+      <c r="E319" t="s">
+        <v>173</v>
+      </c>
+      <c r="F319" t="s">
+        <v>15</v>
+      </c>
+      <c r="G319" t="s">
+        <v>174</v>
+      </c>
+      <c r="H319" t="s">
+        <v>200</v>
+      </c>
+      <c r="I319" t="s">
+        <v>18</v>
+      </c>
+      <c r="J319" t="s">
+        <v>229</v>
+      </c>
+      <c r="K319">
+        <v>100</v>
+      </c>
+      <c r="L319">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>24</v>
+      </c>
+      <c r="B320">
+        <v>56</v>
+      </c>
+      <c r="C320">
+        <v>14</v>
+      </c>
+      <c r="D320" t="s">
+        <v>71</v>
+      </c>
+      <c r="E320" t="s">
+        <v>173</v>
+      </c>
+      <c r="F320" t="s">
+        <v>15</v>
+      </c>
+      <c r="G320" t="s">
+        <v>174</v>
+      </c>
+      <c r="H320" t="s">
+        <v>200</v>
+      </c>
+      <c r="I320" t="s">
+        <v>18</v>
+      </c>
+      <c r="J320" t="s">
+        <v>230</v>
+      </c>
+      <c r="K320">
+        <v>100</v>
+      </c>
+      <c r="L320">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>26</v>
+      </c>
+      <c r="B321">
+        <v>600</v>
+      </c>
+      <c r="C321">
+        <v>0</v>
+      </c>
+      <c r="D321" t="s">
+        <v>21</v>
+      </c>
+      <c r="E321" t="s">
+        <v>173</v>
+      </c>
+      <c r="F321" t="s">
+        <v>15</v>
+      </c>
+      <c r="G321" t="s">
+        <v>174</v>
+      </c>
+      <c r="H321" t="s">
+        <v>200</v>
+      </c>
+      <c r="I321" t="s">
+        <v>18</v>
+      </c>
+      <c r="J321" t="s">
+        <v>231</v>
+      </c>
+      <c r="K321">
+        <v>100</v>
+      </c>
+      <c r="L321">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>12</v>
+      </c>
+      <c r="B322">
+        <v>21</v>
+      </c>
+      <c r="C322">
+        <v>10</v>
+      </c>
+      <c r="D322" t="s">
+        <v>232</v>
+      </c>
+      <c r="E322" t="s">
+        <v>123</v>
+      </c>
+      <c r="F322" t="s">
+        <v>28</v>
+      </c>
+      <c r="G322" t="s">
+        <v>174</v>
+      </c>
+      <c r="H322" t="s">
+        <v>200</v>
+      </c>
+      <c r="I322" t="s">
+        <v>18</v>
+      </c>
+      <c r="K322">
+        <v>100</v>
+      </c>
+      <c r="L322">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>20</v>
+      </c>
+      <c r="B323">
+        <v>2</v>
+      </c>
+      <c r="C323">
+        <v>0</v>
+      </c>
+      <c r="D323" t="s">
+        <v>21</v>
+      </c>
+      <c r="E323" t="s">
+        <v>123</v>
+      </c>
+      <c r="F323" t="s">
+        <v>28</v>
+      </c>
+      <c r="G323" t="s">
+        <v>174</v>
+      </c>
+      <c r="H323" t="s">
+        <v>200</v>
+      </c>
+      <c r="I323" t="s">
+        <v>18</v>
+      </c>
+      <c r="K323">
+        <v>100</v>
+      </c>
+      <c r="L323">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>22</v>
+      </c>
+      <c r="B324">
+        <v>42</v>
+      </c>
+      <c r="C324">
+        <v>17</v>
+      </c>
+      <c r="D324" t="s">
+        <v>90</v>
+      </c>
+      <c r="E324" t="s">
+        <v>123</v>
+      </c>
+      <c r="F324" t="s">
+        <v>28</v>
+      </c>
+      <c r="G324" t="s">
+        <v>174</v>
+      </c>
+      <c r="H324" t="s">
+        <v>200</v>
+      </c>
+      <c r="I324" t="s">
+        <v>18</v>
+      </c>
+      <c r="K324">
+        <v>100</v>
+      </c>
+      <c r="L324">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>24</v>
+      </c>
+      <c r="B325">
+        <v>84</v>
+      </c>
+      <c r="C325">
+        <v>40</v>
+      </c>
+      <c r="D325" t="s">
+        <v>201</v>
+      </c>
+      <c r="E325" t="s">
+        <v>123</v>
+      </c>
+      <c r="F325" t="s">
+        <v>28</v>
+      </c>
+      <c r="G325" t="s">
+        <v>174</v>
+      </c>
+      <c r="H325" t="s">
+        <v>200</v>
+      </c>
+      <c r="I325" t="s">
+        <v>18</v>
+      </c>
+      <c r="K325">
+        <v>100</v>
+      </c>
+      <c r="L325">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>26</v>
+      </c>
+      <c r="B326">
+        <v>900</v>
+      </c>
+      <c r="C326">
+        <v>0</v>
+      </c>
+      <c r="D326" t="s">
+        <v>21</v>
+      </c>
+      <c r="E326" t="s">
+        <v>123</v>
+      </c>
+      <c r="F326" t="s">
+        <v>28</v>
+      </c>
+      <c r="G326" t="s">
+        <v>174</v>
+      </c>
+      <c r="H326" t="s">
+        <v>200</v>
+      </c>
+      <c r="I326" t="s">
+        <v>18</v>
+      </c>
+      <c r="K326">
+        <v>100</v>
+      </c>
+      <c r="L326">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>12</v>
+      </c>
+      <c r="B327">
+        <v>21</v>
+      </c>
+      <c r="C327">
+        <v>3</v>
+      </c>
+      <c r="D327" t="s">
+        <v>162</v>
+      </c>
+      <c r="E327" t="s">
+        <v>69</v>
+      </c>
+      <c r="F327" t="s">
+        <v>63</v>
+      </c>
+      <c r="G327" t="s">
+        <v>174</v>
+      </c>
+      <c r="H327" t="s">
+        <v>200</v>
+      </c>
+      <c r="I327" t="s">
+        <v>18</v>
+      </c>
+      <c r="K327">
+        <v>100</v>
+      </c>
+      <c r="L327">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>20</v>
+      </c>
+      <c r="B328">
+        <v>2</v>
+      </c>
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328" t="s">
+        <v>21</v>
+      </c>
+      <c r="E328" t="s">
+        <v>69</v>
+      </c>
+      <c r="F328" t="s">
+        <v>63</v>
+      </c>
+      <c r="G328" t="s">
+        <v>174</v>
+      </c>
+      <c r="H328" t="s">
+        <v>200</v>
+      </c>
+      <c r="I328" t="s">
+        <v>18</v>
+      </c>
+      <c r="K328">
+        <v>100</v>
+      </c>
+      <c r="L328">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>22</v>
+      </c>
+      <c r="B329">
+        <v>42</v>
+      </c>
+      <c r="C329">
+        <v>11</v>
+      </c>
+      <c r="D329" t="s">
+        <v>233</v>
+      </c>
+      <c r="E329" t="s">
+        <v>69</v>
+      </c>
+      <c r="F329" t="s">
+        <v>63</v>
+      </c>
+      <c r="G329" t="s">
+        <v>174</v>
+      </c>
+      <c r="H329" t="s">
+        <v>200</v>
+      </c>
+      <c r="I329" t="s">
+        <v>18</v>
+      </c>
+      <c r="K329">
+        <v>100</v>
+      </c>
+      <c r="L329">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>24</v>
+      </c>
+      <c r="B330">
+        <v>84</v>
+      </c>
+      <c r="C330">
+        <v>6</v>
+      </c>
+      <c r="D330" t="s">
+        <v>201</v>
+      </c>
+      <c r="E330" t="s">
+        <v>69</v>
+      </c>
+      <c r="F330" t="s">
+        <v>63</v>
+      </c>
+      <c r="G330" t="s">
+        <v>174</v>
+      </c>
+      <c r="H330" t="s">
+        <v>200</v>
+      </c>
+      <c r="I330" t="s">
+        <v>18</v>
+      </c>
+      <c r="K330">
+        <v>100</v>
+      </c>
+      <c r="L330">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>26</v>
+      </c>
+      <c r="B331">
+        <v>900</v>
+      </c>
+      <c r="C331">
+        <v>0</v>
+      </c>
+      <c r="D331" t="s">
+        <v>21</v>
+      </c>
+      <c r="E331" t="s">
+        <v>69</v>
+      </c>
+      <c r="F331" t="s">
+        <v>63</v>
+      </c>
+      <c r="G331" t="s">
+        <v>174</v>
+      </c>
+      <c r="H331" t="s">
+        <v>200</v>
+      </c>
+      <c r="I331" t="s">
+        <v>18</v>
+      </c>
+      <c r="K331">
+        <v>100</v>
+      </c>
+      <c r="L331">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>12</v>
+      </c>
+      <c r="B332">
+        <v>28</v>
+      </c>
+      <c r="C332">
+        <v>2</v>
+      </c>
+      <c r="D332" t="s">
+        <v>199</v>
+      </c>
+      <c r="E332" t="s">
+        <v>32</v>
+      </c>
+      <c r="F332" t="s">
+        <v>15</v>
+      </c>
+      <c r="G332" t="s">
+        <v>33</v>
+      </c>
+      <c r="H332" t="s">
+        <v>200</v>
+      </c>
+      <c r="I332" t="s">
+        <v>18</v>
+      </c>
+      <c r="K332">
+        <v>100</v>
+      </c>
+      <c r="L332">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>20</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333" t="s">
+        <v>21</v>
+      </c>
+      <c r="E333" t="s">
+        <v>32</v>
+      </c>
+      <c r="F333" t="s">
+        <v>15</v>
+      </c>
+      <c r="G333" t="s">
+        <v>33</v>
+      </c>
+      <c r="H333" t="s">
+        <v>200</v>
+      </c>
+      <c r="I333" t="s">
+        <v>18</v>
+      </c>
+      <c r="K333">
+        <v>100</v>
+      </c>
+      <c r="L333">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>22</v>
+      </c>
+      <c r="B334">
+        <v>34</v>
+      </c>
+      <c r="C334">
+        <v>4</v>
+      </c>
+      <c r="D334" t="s">
+        <v>169</v>
+      </c>
+      <c r="E334" t="s">
+        <v>32</v>
+      </c>
+      <c r="F334" t="s">
+        <v>15</v>
+      </c>
+      <c r="G334" t="s">
+        <v>33</v>
+      </c>
+      <c r="H334" t="s">
+        <v>200</v>
+      </c>
+      <c r="I334" t="s">
+        <v>18</v>
+      </c>
+      <c r="K334">
+        <v>100</v>
+      </c>
+      <c r="L334">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>24</v>
+      </c>
+      <c r="B335">
+        <v>61</v>
+      </c>
+      <c r="C335">
+        <v>14</v>
+      </c>
+      <c r="D335" t="s">
+        <v>201</v>
+      </c>
+      <c r="E335" t="s">
+        <v>32</v>
+      </c>
+      <c r="F335" t="s">
+        <v>15</v>
+      </c>
+      <c r="G335" t="s">
+        <v>33</v>
+      </c>
+      <c r="H335" t="s">
+        <v>200</v>
+      </c>
+      <c r="I335" t="s">
+        <v>18</v>
+      </c>
+      <c r="K335">
+        <v>100</v>
+      </c>
+      <c r="L335">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>26</v>
+      </c>
+      <c r="B336">
+        <v>912</v>
+      </c>
+      <c r="C336">
+        <v>0</v>
+      </c>
+      <c r="D336" t="s">
+        <v>21</v>
+      </c>
+      <c r="E336" t="s">
+        <v>32</v>
+      </c>
+      <c r="F336" t="s">
+        <v>15</v>
+      </c>
+      <c r="G336" t="s">
+        <v>33</v>
+      </c>
+      <c r="H336" t="s">
+        <v>200</v>
+      </c>
+      <c r="I336" t="s">
+        <v>18</v>
+      </c>
+      <c r="K336">
+        <v>100</v>
+      </c>
+      <c r="L336">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>12</v>
+      </c>
+      <c r="B337">
+        <v>9</v>
+      </c>
+      <c r="C337">
+        <v>0</v>
+      </c>
+      <c r="D337" t="s">
+        <v>21</v>
+      </c>
+      <c r="E337" t="s">
+        <v>38</v>
+      </c>
+      <c r="F337" t="s">
+        <v>28</v>
+      </c>
+      <c r="G337" t="s">
+        <v>33</v>
+      </c>
+      <c r="H337" t="s">
+        <v>200</v>
+      </c>
+      <c r="I337" t="s">
+        <v>18</v>
+      </c>
+      <c r="J337" t="s">
+        <v>202</v>
+      </c>
+      <c r="K337">
+        <v>100</v>
+      </c>
+      <c r="L337">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>20</v>
+      </c>
+      <c r="B338">
+        <v>0</v>
+      </c>
+      <c r="C338">
+        <v>0</v>
+      </c>
+      <c r="D338" t="s">
+        <v>21</v>
+      </c>
+      <c r="E338" t="s">
+        <v>38</v>
+      </c>
+      <c r="F338" t="s">
+        <v>28</v>
+      </c>
+      <c r="G338" t="s">
+        <v>33</v>
+      </c>
+      <c r="H338" t="s">
+        <v>200</v>
+      </c>
+      <c r="I338" t="s">
+        <v>18</v>
+      </c>
+      <c r="K338">
+        <v>100</v>
+      </c>
+      <c r="L338">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>22</v>
+      </c>
+      <c r="B339">
+        <v>11</v>
+      </c>
+      <c r="C339">
+        <v>0</v>
+      </c>
+      <c r="D339" t="s">
+        <v>21</v>
+      </c>
+      <c r="E339" t="s">
+        <v>38</v>
+      </c>
+      <c r="F339" t="s">
+        <v>28</v>
+      </c>
+      <c r="G339" t="s">
+        <v>33</v>
+      </c>
+      <c r="H339" t="s">
+        <v>200</v>
+      </c>
+      <c r="I339" t="s">
+        <v>18</v>
+      </c>
+      <c r="K339">
+        <v>100</v>
+      </c>
+      <c r="L339">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>24</v>
+      </c>
+      <c r="B340">
+        <v>19</v>
+      </c>
+      <c r="C340">
+        <v>0</v>
+      </c>
+      <c r="D340" t="s">
+        <v>201</v>
+      </c>
+      <c r="E340" t="s">
+        <v>38</v>
+      </c>
+      <c r="F340" t="s">
+        <v>28</v>
+      </c>
+      <c r="G340" t="s">
+        <v>33</v>
+      </c>
+      <c r="H340" t="s">
+        <v>200</v>
+      </c>
+      <c r="I340" t="s">
+        <v>18</v>
+      </c>
+      <c r="K340">
+        <v>100</v>
+      </c>
+      <c r="L340">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>26</v>
+      </c>
+      <c r="B341">
+        <v>288</v>
+      </c>
+      <c r="C341">
+        <v>0</v>
+      </c>
+      <c r="D341" t="s">
+        <v>21</v>
+      </c>
+      <c r="E341" t="s">
+        <v>38</v>
+      </c>
+      <c r="F341" t="s">
+        <v>28</v>
+      </c>
+      <c r="G341" t="s">
+        <v>33</v>
+      </c>
+      <c r="H341" t="s">
+        <v>200</v>
+      </c>
+      <c r="I341" t="s">
+        <v>18</v>
+      </c>
+      <c r="K341">
+        <v>100</v>
+      </c>
+      <c r="L341">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>12</v>
+      </c>
+      <c r="B342">
+        <v>19</v>
+      </c>
+      <c r="C342">
+        <v>9</v>
+      </c>
+      <c r="D342" t="s">
+        <v>203</v>
+      </c>
+      <c r="E342" t="s">
+        <v>204</v>
+      </c>
+      <c r="F342" t="s">
+        <v>15</v>
+      </c>
+      <c r="G342" t="s">
+        <v>205</v>
+      </c>
+      <c r="H342" t="s">
+        <v>200</v>
+      </c>
+      <c r="I342" t="s">
+        <v>18</v>
+      </c>
+      <c r="K342">
+        <v>100</v>
+      </c>
+      <c r="L342">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>20</v>
+      </c>
+      <c r="B343">
+        <v>0</v>
+      </c>
+      <c r="C343">
+        <v>0</v>
+      </c>
+      <c r="D343" t="s">
+        <v>21</v>
+      </c>
+      <c r="E343" t="s">
+        <v>204</v>
+      </c>
+      <c r="F343" t="s">
+        <v>15</v>
+      </c>
+      <c r="G343" t="s">
+        <v>205</v>
+      </c>
+      <c r="H343" t="s">
+        <v>200</v>
+      </c>
+      <c r="I343" t="s">
+        <v>18</v>
+      </c>
+      <c r="K343">
+        <v>100</v>
+      </c>
+      <c r="L343">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>22</v>
+      </c>
+      <c r="B344">
+        <v>35</v>
+      </c>
+      <c r="C344">
+        <v>11</v>
+      </c>
+      <c r="D344" t="s">
+        <v>206</v>
+      </c>
+      <c r="E344" t="s">
+        <v>204</v>
+      </c>
+      <c r="F344" t="s">
+        <v>15</v>
+      </c>
+      <c r="G344" t="s">
+        <v>205</v>
+      </c>
+      <c r="H344" t="s">
+        <v>200</v>
+      </c>
+      <c r="I344" t="s">
+        <v>18</v>
+      </c>
+      <c r="K344">
+        <v>100</v>
+      </c>
+      <c r="L344">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>24</v>
+      </c>
+      <c r="B345">
+        <v>102</v>
+      </c>
+      <c r="C345">
+        <v>39</v>
+      </c>
+      <c r="D345" t="s">
+        <v>201</v>
+      </c>
+      <c r="E345" t="s">
+        <v>204</v>
+      </c>
+      <c r="F345" t="s">
+        <v>15</v>
+      </c>
+      <c r="G345" t="s">
+        <v>205</v>
+      </c>
+      <c r="H345" t="s">
+        <v>200</v>
+      </c>
+      <c r="I345" t="s">
+        <v>18</v>
+      </c>
+      <c r="K345">
+        <v>100</v>
+      </c>
+      <c r="L345">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>26</v>
+      </c>
+      <c r="B346">
+        <v>768</v>
+      </c>
+      <c r="C346">
+        <v>0</v>
+      </c>
+      <c r="D346" t="s">
+        <v>21</v>
+      </c>
+      <c r="E346" t="s">
+        <v>204</v>
+      </c>
+      <c r="F346" t="s">
+        <v>15</v>
+      </c>
+      <c r="G346" t="s">
+        <v>205</v>
+      </c>
+      <c r="H346" t="s">
+        <v>200</v>
+      </c>
+      <c r="I346" t="s">
+        <v>18</v>
+      </c>
+      <c r="K346">
+        <v>100</v>
+      </c>
+      <c r="L346">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>12</v>
+      </c>
+      <c r="B347">
+        <v>11</v>
+      </c>
+      <c r="C347">
+        <v>0</v>
+      </c>
+      <c r="D347" t="s">
+        <v>21</v>
+      </c>
+      <c r="E347" t="s">
+        <v>207</v>
+      </c>
+      <c r="F347" t="s">
+        <v>28</v>
+      </c>
+      <c r="G347" t="s">
+        <v>205</v>
+      </c>
+      <c r="H347" t="s">
+        <v>200</v>
+      </c>
+      <c r="I347" t="s">
+        <v>18</v>
+      </c>
+      <c r="J347" t="s">
+        <v>208</v>
+      </c>
+      <c r="K347">
+        <v>100</v>
+      </c>
+      <c r="L347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>20</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>0</v>
+      </c>
+      <c r="D348" t="s">
+        <v>21</v>
+      </c>
+      <c r="E348" t="s">
+        <v>207</v>
+      </c>
+      <c r="F348" t="s">
+        <v>28</v>
+      </c>
+      <c r="G348" t="s">
+        <v>205</v>
+      </c>
+      <c r="H348" t="s">
+        <v>200</v>
+      </c>
+      <c r="I348" t="s">
+        <v>18</v>
+      </c>
+      <c r="K348">
+        <v>100</v>
+      </c>
+      <c r="L348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>22</v>
+      </c>
+      <c r="B349">
+        <v>20</v>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+      <c r="D349" t="s">
+        <v>21</v>
+      </c>
+      <c r="E349" t="s">
+        <v>207</v>
+      </c>
+      <c r="F349" t="s">
+        <v>28</v>
+      </c>
+      <c r="G349" t="s">
+        <v>205</v>
+      </c>
+      <c r="H349" t="s">
+        <v>200</v>
+      </c>
+      <c r="I349" t="s">
+        <v>18</v>
+      </c>
+      <c r="K349">
+        <v>100</v>
+      </c>
+      <c r="L349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>24</v>
+      </c>
+      <c r="B350">
+        <v>58</v>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+      <c r="D350" t="s">
+        <v>201</v>
+      </c>
+      <c r="E350" t="s">
+        <v>207</v>
+      </c>
+      <c r="F350" t="s">
+        <v>28</v>
+      </c>
+      <c r="G350" t="s">
+        <v>205</v>
+      </c>
+      <c r="H350" t="s">
+        <v>200</v>
+      </c>
+      <c r="I350" t="s">
+        <v>18</v>
+      </c>
+      <c r="K350">
+        <v>100</v>
+      </c>
+      <c r="L350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>26</v>
+      </c>
+      <c r="B351">
+        <v>432</v>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+      <c r="D351" t="s">
+        <v>21</v>
+      </c>
+      <c r="E351" t="s">
+        <v>207</v>
+      </c>
+      <c r="F351" t="s">
+        <v>28</v>
+      </c>
+      <c r="G351" t="s">
+        <v>205</v>
+      </c>
+      <c r="H351" t="s">
+        <v>200</v>
+      </c>
+      <c r="I351" t="s">
+        <v>18</v>
+      </c>
+      <c r="K351">
+        <v>100</v>
+      </c>
+      <c r="L351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>12</v>
+      </c>
+      <c r="B352">
+        <v>10</v>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+      <c r="D352" t="s">
+        <v>21</v>
+      </c>
+      <c r="E352" t="s">
+        <v>127</v>
+      </c>
+      <c r="F352" t="s">
+        <v>15</v>
+      </c>
+      <c r="G352" t="s">
+        <v>128</v>
+      </c>
+      <c r="H352" t="s">
+        <v>200</v>
+      </c>
+      <c r="I352" t="s">
+        <v>18</v>
+      </c>
+      <c r="K352">
+        <v>100</v>
+      </c>
+      <c r="L352">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>20</v>
+      </c>
+      <c r="B353">
+        <v>3</v>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+      <c r="D353" t="s">
+        <v>21</v>
+      </c>
+      <c r="E353" t="s">
+        <v>127</v>
+      </c>
+      <c r="F353" t="s">
+        <v>15</v>
+      </c>
+      <c r="G353" t="s">
+        <v>128</v>
+      </c>
+      <c r="H353" t="s">
+        <v>200</v>
+      </c>
+      <c r="I353" t="s">
+        <v>18</v>
+      </c>
+      <c r="K353">
+        <v>100</v>
+      </c>
+      <c r="L353">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>22</v>
+      </c>
+      <c r="B354">
+        <v>24</v>
+      </c>
+      <c r="C354">
+        <v>5</v>
+      </c>
+      <c r="D354" t="s">
+        <v>209</v>
+      </c>
+      <c r="E354" t="s">
+        <v>127</v>
+      </c>
+      <c r="F354" t="s">
+        <v>15</v>
+      </c>
+      <c r="G354" t="s">
+        <v>128</v>
+      </c>
+      <c r="H354" t="s">
+        <v>200</v>
+      </c>
+      <c r="I354" t="s">
+        <v>18</v>
+      </c>
+      <c r="K354">
+        <v>100</v>
+      </c>
+      <c r="L354">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>24</v>
+      </c>
+      <c r="B355">
+        <v>32</v>
+      </c>
+      <c r="C355">
+        <v>5</v>
+      </c>
+      <c r="D355" t="s">
+        <v>201</v>
+      </c>
+      <c r="E355" t="s">
+        <v>127</v>
+      </c>
+      <c r="F355" t="s">
+        <v>15</v>
+      </c>
+      <c r="G355" t="s">
+        <v>128</v>
+      </c>
+      <c r="H355" t="s">
+        <v>200</v>
+      </c>
+      <c r="I355" t="s">
+        <v>18</v>
+      </c>
+      <c r="K355">
+        <v>100</v>
+      </c>
+      <c r="L355">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>26</v>
+      </c>
+      <c r="B356">
+        <v>510</v>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+      <c r="D356" t="s">
+        <v>21</v>
+      </c>
+      <c r="E356" t="s">
+        <v>127</v>
+      </c>
+      <c r="F356" t="s">
+        <v>15</v>
+      </c>
+      <c r="G356" t="s">
+        <v>128</v>
+      </c>
+      <c r="H356" t="s">
+        <v>200</v>
+      </c>
+      <c r="I356" t="s">
+        <v>18</v>
+      </c>
+      <c r="K356">
+        <v>100</v>
+      </c>
+      <c r="L356">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>12</v>
+      </c>
+      <c r="B357">
+        <v>15</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+      <c r="D357" t="s">
+        <v>199</v>
+      </c>
+      <c r="E357" t="s">
+        <v>130</v>
+      </c>
+      <c r="F357" t="s">
+        <v>28</v>
+      </c>
+      <c r="G357" t="s">
+        <v>128</v>
+      </c>
+      <c r="H357" t="s">
+        <v>200</v>
+      </c>
+      <c r="I357" t="s">
+        <v>18</v>
+      </c>
+      <c r="K357">
+        <v>100</v>
+      </c>
+      <c r="L357">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>20</v>
+      </c>
+      <c r="B358">
+        <v>5</v>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+      <c r="D358" t="s">
+        <v>21</v>
+      </c>
+      <c r="E358" t="s">
+        <v>130</v>
+      </c>
+      <c r="F358" t="s">
+        <v>28</v>
+      </c>
+      <c r="G358" t="s">
+        <v>128</v>
+      </c>
+      <c r="H358" t="s">
+        <v>200</v>
+      </c>
+      <c r="I358" t="s">
+        <v>18</v>
+      </c>
+      <c r="K358">
+        <v>100</v>
+      </c>
+      <c r="L358">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>22</v>
+      </c>
+      <c r="B359">
+        <v>37</v>
+      </c>
+      <c r="C359">
+        <v>7</v>
+      </c>
+      <c r="D359" t="s">
+        <v>210</v>
+      </c>
+      <c r="E359" t="s">
+        <v>130</v>
+      </c>
+      <c r="F359" t="s">
+        <v>28</v>
+      </c>
+      <c r="G359" t="s">
+        <v>128</v>
+      </c>
+      <c r="H359" t="s">
+        <v>200</v>
+      </c>
+      <c r="I359" t="s">
+        <v>18</v>
+      </c>
+      <c r="K359">
+        <v>100</v>
+      </c>
+      <c r="L359">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>24</v>
+      </c>
+      <c r="B360">
+        <v>48</v>
+      </c>
+      <c r="C360">
+        <v>13</v>
+      </c>
+      <c r="D360" t="s">
+        <v>201</v>
+      </c>
+      <c r="E360" t="s">
+        <v>130</v>
+      </c>
+      <c r="F360" t="s">
+        <v>28</v>
+      </c>
+      <c r="G360" t="s">
+        <v>128</v>
+      </c>
+      <c r="H360" t="s">
+        <v>200</v>
+      </c>
+      <c r="I360" t="s">
+        <v>18</v>
+      </c>
+      <c r="K360">
+        <v>100</v>
+      </c>
+      <c r="L360">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>26</v>
+      </c>
+      <c r="B361">
+        <v>765</v>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+      <c r="D361" t="s">
+        <v>21</v>
+      </c>
+      <c r="E361" t="s">
+        <v>130</v>
+      </c>
+      <c r="F361" t="s">
+        <v>28</v>
+      </c>
+      <c r="G361" t="s">
+        <v>128</v>
+      </c>
+      <c r="H361" t="s">
+        <v>200</v>
+      </c>
+      <c r="I361" t="s">
+        <v>18</v>
+      </c>
+      <c r="K361">
+        <v>100</v>
+      </c>
+      <c r="L361">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>12</v>
+      </c>
+      <c r="B362">
+        <v>5</v>
+      </c>
+      <c r="C362">
+        <v>8</v>
+      </c>
+      <c r="D362" t="s">
+        <v>211</v>
+      </c>
+      <c r="E362" t="s">
+        <v>135</v>
+      </c>
+      <c r="F362" t="s">
+        <v>28</v>
+      </c>
+      <c r="G362" t="s">
+        <v>128</v>
+      </c>
+      <c r="H362" t="s">
+        <v>200</v>
+      </c>
+      <c r="I362" t="s">
+        <v>18</v>
+      </c>
+      <c r="J362" t="s">
+        <v>212</v>
+      </c>
+      <c r="K362">
+        <v>100</v>
+      </c>
+      <c r="L362">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>20</v>
+      </c>
+      <c r="B363">
+        <v>2</v>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+      <c r="D363" t="s">
+        <v>21</v>
+      </c>
+      <c r="E363" t="s">
+        <v>135</v>
+      </c>
+      <c r="F363" t="s">
+        <v>28</v>
+      </c>
+      <c r="G363" t="s">
+        <v>128</v>
+      </c>
+      <c r="H363" t="s">
+        <v>200</v>
+      </c>
+      <c r="I363" t="s">
+        <v>18</v>
+      </c>
+      <c r="K363">
+        <v>100</v>
+      </c>
+      <c r="L363">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>22</v>
+      </c>
+      <c r="B364">
+        <v>11</v>
+      </c>
+      <c r="C364">
+        <v>12</v>
+      </c>
+      <c r="D364" t="s">
+        <v>213</v>
+      </c>
+      <c r="E364" t="s">
+        <v>135</v>
+      </c>
+      <c r="F364" t="s">
+        <v>28</v>
+      </c>
+      <c r="G364" t="s">
+        <v>128</v>
+      </c>
+      <c r="H364" t="s">
+        <v>200</v>
+      </c>
+      <c r="I364" t="s">
+        <v>18</v>
+      </c>
+      <c r="K364">
+        <v>100</v>
+      </c>
+      <c r="L364">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>24</v>
+      </c>
+      <c r="B365">
+        <v>14</v>
+      </c>
+      <c r="C365">
+        <v>19</v>
+      </c>
+      <c r="D365" t="s">
+        <v>201</v>
+      </c>
+      <c r="E365" t="s">
+        <v>135</v>
+      </c>
+      <c r="F365" t="s">
+        <v>28</v>
+      </c>
+      <c r="G365" t="s">
+        <v>128</v>
+      </c>
+      <c r="H365" t="s">
+        <v>200</v>
+      </c>
+      <c r="I365" t="s">
+        <v>18</v>
+      </c>
+      <c r="K365">
+        <v>100</v>
+      </c>
+      <c r="L365">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>26</v>
+      </c>
+      <c r="B366">
+        <v>225</v>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+      <c r="D366" t="s">
+        <v>21</v>
+      </c>
+      <c r="E366" t="s">
+        <v>135</v>
+      </c>
+      <c r="F366" t="s">
+        <v>28</v>
+      </c>
+      <c r="G366" t="s">
+        <v>128</v>
+      </c>
+      <c r="H366" t="s">
+        <v>200</v>
+      </c>
+      <c r="I366" t="s">
+        <v>18</v>
+      </c>
+      <c r="K366">
+        <v>100</v>
+      </c>
+      <c r="L366">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>12</v>
+      </c>
+      <c r="B367">
+        <v>19</v>
+      </c>
+      <c r="C367">
+        <v>4</v>
+      </c>
+      <c r="D367" t="s">
+        <v>209</v>
+      </c>
+      <c r="E367" t="s">
+        <v>214</v>
+      </c>
+      <c r="F367" t="s">
+        <v>15</v>
+      </c>
+      <c r="G367" t="s">
+        <v>215</v>
+      </c>
+      <c r="H367" t="s">
+        <v>200</v>
+      </c>
+      <c r="I367" t="s">
+        <v>18</v>
+      </c>
+      <c r="K367">
+        <v>100</v>
+      </c>
+      <c r="L367">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>20</v>
+      </c>
+      <c r="B368">
+        <v>5</v>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+      <c r="D368" t="s">
+        <v>21</v>
+      </c>
+      <c r="E368" t="s">
+        <v>214</v>
+      </c>
+      <c r="F368" t="s">
+        <v>15</v>
+      </c>
+      <c r="G368" t="s">
+        <v>215</v>
+      </c>
+      <c r="H368" t="s">
+        <v>200</v>
+      </c>
+      <c r="I368" t="s">
+        <v>18</v>
+      </c>
+      <c r="K368">
+        <v>100</v>
+      </c>
+      <c r="L368">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>22</v>
+      </c>
+      <c r="B369">
+        <v>32</v>
+      </c>
+      <c r="C369">
+        <v>7</v>
+      </c>
+      <c r="D369" t="s">
+        <v>36</v>
+      </c>
+      <c r="E369" t="s">
+        <v>214</v>
+      </c>
+      <c r="F369" t="s">
+        <v>15</v>
+      </c>
+      <c r="G369" t="s">
+        <v>215</v>
+      </c>
+      <c r="H369" t="s">
+        <v>200</v>
+      </c>
+      <c r="I369" t="s">
+        <v>18</v>
+      </c>
+      <c r="J369" t="s">
+        <v>216</v>
+      </c>
+      <c r="K369">
+        <v>100</v>
+      </c>
+      <c r="L369">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>24</v>
+      </c>
+      <c r="B370">
+        <v>61</v>
+      </c>
+      <c r="C370">
+        <v>8</v>
+      </c>
+      <c r="D370" t="s">
+        <v>201</v>
+      </c>
+      <c r="E370" t="s">
+        <v>214</v>
+      </c>
+      <c r="F370" t="s">
+        <v>15</v>
+      </c>
+      <c r="G370" t="s">
+        <v>215</v>
+      </c>
+      <c r="H370" t="s">
+        <v>200</v>
+      </c>
+      <c r="I370" t="s">
+        <v>18</v>
+      </c>
+      <c r="K370">
+        <v>100</v>
+      </c>
+      <c r="L370">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>26</v>
+      </c>
+      <c r="B371">
+        <v>510</v>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+      <c r="D371" t="s">
+        <v>21</v>
+      </c>
+      <c r="E371" t="s">
+        <v>214</v>
+      </c>
+      <c r="F371" t="s">
+        <v>15</v>
+      </c>
+      <c r="G371" t="s">
+        <v>215</v>
+      </c>
+      <c r="H371" t="s">
+        <v>200</v>
+      </c>
+      <c r="I371" t="s">
+        <v>18</v>
+      </c>
+      <c r="K371">
+        <v>100</v>
+      </c>
+      <c r="L371">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>12</v>
+      </c>
+      <c r="B372">
+        <v>8</v>
+      </c>
+      <c r="C372">
+        <v>12</v>
+      </c>
+      <c r="D372" t="s">
+        <v>217</v>
+      </c>
+      <c r="E372" t="s">
+        <v>218</v>
+      </c>
+      <c r="F372" t="s">
+        <v>28</v>
+      </c>
+      <c r="G372" t="s">
+        <v>215</v>
+      </c>
+      <c r="H372" t="s">
+        <v>200</v>
+      </c>
+      <c r="I372" t="s">
+        <v>18</v>
+      </c>
+      <c r="J372" t="s">
+        <v>219</v>
+      </c>
+      <c r="K372">
+        <v>100</v>
+      </c>
+      <c r="L372">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>20</v>
+      </c>
+      <c r="B373">
+        <v>2</v>
+      </c>
+      <c r="C373">
+        <v>4</v>
+      </c>
+      <c r="D373" t="s">
+        <v>43</v>
+      </c>
+      <c r="E373" t="s">
+        <v>218</v>
+      </c>
+      <c r="F373" t="s">
+        <v>28</v>
+      </c>
+      <c r="G373" t="s">
+        <v>215</v>
+      </c>
+      <c r="H373" t="s">
+        <v>200</v>
+      </c>
+      <c r="I373" t="s">
+        <v>18</v>
+      </c>
+      <c r="K373">
+        <v>100</v>
+      </c>
+      <c r="L373">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>22</v>
+      </c>
+      <c r="B374">
+        <v>14</v>
+      </c>
+      <c r="C374">
+        <v>14</v>
+      </c>
+      <c r="D374" t="s">
+        <v>44</v>
+      </c>
+      <c r="E374" t="s">
+        <v>218</v>
+      </c>
+      <c r="F374" t="s">
+        <v>28</v>
+      </c>
+      <c r="G374" t="s">
+        <v>215</v>
+      </c>
+      <c r="H374" t="s">
+        <v>200</v>
+      </c>
+      <c r="I374" t="s">
+        <v>18</v>
+      </c>
+      <c r="K374">
+        <v>100</v>
+      </c>
+      <c r="L374">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>24</v>
+      </c>
+      <c r="B375">
+        <v>27</v>
+      </c>
+      <c r="C375">
+        <v>31</v>
+      </c>
+      <c r="D375" t="s">
+        <v>55</v>
+      </c>
+      <c r="E375" t="s">
+        <v>218</v>
+      </c>
+      <c r="F375" t="s">
+        <v>28</v>
+      </c>
+      <c r="G375" t="s">
+        <v>215</v>
+      </c>
+      <c r="H375" t="s">
+        <v>200</v>
+      </c>
+      <c r="I375" t="s">
+        <v>18</v>
+      </c>
+      <c r="K375">
+        <v>100</v>
+      </c>
+      <c r="L375">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>26</v>
+      </c>
+      <c r="B376">
+        <v>225</v>
+      </c>
+      <c r="C376">
+        <v>0</v>
+      </c>
+      <c r="D376" t="s">
+        <v>21</v>
+      </c>
+      <c r="E376" t="s">
+        <v>218</v>
+      </c>
+      <c r="F376" t="s">
+        <v>28</v>
+      </c>
+      <c r="G376" t="s">
+        <v>215</v>
+      </c>
+      <c r="H376" t="s">
+        <v>200</v>
+      </c>
+      <c r="I376" t="s">
+        <v>18</v>
+      </c>
+      <c r="K376">
+        <v>100</v>
+      </c>
+      <c r="L376">
+        <v>99.2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>12</v>
+      </c>
+      <c r="B377">
+        <v>28</v>
+      </c>
+      <c r="C377">
+        <v>7</v>
+      </c>
+      <c r="D377" t="s">
+        <v>71</v>
+      </c>
+      <c r="E377" t="s">
+        <v>220</v>
+      </c>
+      <c r="F377" t="s">
+        <v>28</v>
+      </c>
+      <c r="G377" t="s">
+        <v>215</v>
+      </c>
+      <c r="H377" t="s">
+        <v>200</v>
+      </c>
+      <c r="I377" t="s">
+        <v>18</v>
+      </c>
+      <c r="K377">
+        <v>100</v>
+      </c>
+      <c r="L377">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>20</v>
+      </c>
+      <c r="B378">
+        <v>7</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+      <c r="D378" t="s">
+        <v>162</v>
+      </c>
+      <c r="E378" t="s">
+        <v>220</v>
+      </c>
+      <c r="F378" t="s">
+        <v>28</v>
+      </c>
+      <c r="G378" t="s">
+        <v>215</v>
+      </c>
+      <c r="H378" t="s">
+        <v>200</v>
+      </c>
+      <c r="I378" t="s">
+        <v>18</v>
+      </c>
+      <c r="K378">
+        <v>100</v>
+      </c>
+      <c r="L378">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>22</v>
+      </c>
+      <c r="B379">
+        <v>48</v>
+      </c>
+      <c r="C379">
+        <v>12</v>
+      </c>
+      <c r="D379" t="s">
+        <v>71</v>
+      </c>
+      <c r="E379" t="s">
+        <v>220</v>
+      </c>
+      <c r="F379" t="s">
+        <v>28</v>
+      </c>
+      <c r="G379" t="s">
+        <v>215</v>
+      </c>
+      <c r="H379" t="s">
+        <v>200</v>
+      </c>
+      <c r="I379" t="s">
+        <v>18</v>
+      </c>
+      <c r="K379">
+        <v>100</v>
+      </c>
+      <c r="L379">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>24</v>
+      </c>
+      <c r="B380">
+        <v>92</v>
+      </c>
+      <c r="C380">
+        <v>28</v>
+      </c>
+      <c r="D380" t="s">
+        <v>201</v>
+      </c>
+      <c r="E380" t="s">
+        <v>220</v>
+      </c>
+      <c r="F380" t="s">
+        <v>28</v>
+      </c>
+      <c r="G380" t="s">
+        <v>215</v>
+      </c>
+      <c r="H380" t="s">
+        <v>200</v>
+      </c>
+      <c r="I380" t="s">
+        <v>18</v>
+      </c>
+      <c r="K380">
+        <v>100</v>
+      </c>
+      <c r="L380">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>26</v>
+      </c>
+      <c r="B381">
+        <v>765</v>
+      </c>
+      <c r="C381">
+        <v>0</v>
+      </c>
+      <c r="D381" t="s">
+        <v>21</v>
+      </c>
+      <c r="E381" t="s">
+        <v>220</v>
+      </c>
+      <c r="F381" t="s">
+        <v>28</v>
+      </c>
+      <c r="G381" t="s">
+        <v>215</v>
+      </c>
+      <c r="H381" t="s">
+        <v>200</v>
+      </c>
+      <c r="I381" t="s">
+        <v>18</v>
+      </c>
+      <c r="K381">
+        <v>100</v>
+      </c>
+      <c r="L381">
+        <v>21.8</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>12</v>
+      </c>
+      <c r="B382">
+        <v>28</v>
+      </c>
+      <c r="C382">
+        <v>2</v>
+      </c>
+      <c r="D382" t="s">
+        <v>199</v>
+      </c>
+      <c r="E382" t="s">
+        <v>32</v>
+      </c>
+      <c r="F382" t="s">
+        <v>15</v>
+      </c>
+      <c r="G382" t="s">
+        <v>33</v>
+      </c>
+      <c r="H382" t="s">
+        <v>200</v>
+      </c>
+      <c r="I382" t="s">
+        <v>18</v>
+      </c>
+      <c r="K382">
+        <v>100</v>
+      </c>
+      <c r="L382">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>20</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>0</v>
+      </c>
+      <c r="D383" t="s">
+        <v>21</v>
+      </c>
+      <c r="E383" t="s">
+        <v>32</v>
+      </c>
+      <c r="F383" t="s">
+        <v>15</v>
+      </c>
+      <c r="G383" t="s">
+        <v>33</v>
+      </c>
+      <c r="H383" t="s">
+        <v>200</v>
+      </c>
+      <c r="I383" t="s">
+        <v>18</v>
+      </c>
+      <c r="K383">
+        <v>100</v>
+      </c>
+      <c r="L383">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>22</v>
+      </c>
+      <c r="B384">
+        <v>34</v>
+      </c>
+      <c r="C384">
+        <v>4</v>
+      </c>
+      <c r="D384" t="s">
+        <v>169</v>
+      </c>
+      <c r="E384" t="s">
+        <v>32</v>
+      </c>
+      <c r="F384" t="s">
+        <v>15</v>
+      </c>
+      <c r="G384" t="s">
+        <v>33</v>
+      </c>
+      <c r="H384" t="s">
+        <v>200</v>
+      </c>
+      <c r="I384" t="s">
+        <v>18</v>
+      </c>
+      <c r="K384">
+        <v>100</v>
+      </c>
+      <c r="L384">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>24</v>
+      </c>
+      <c r="B385">
+        <v>61</v>
+      </c>
+      <c r="C385">
+        <v>14</v>
+      </c>
+      <c r="D385" t="s">
+        <v>201</v>
+      </c>
+      <c r="E385" t="s">
+        <v>32</v>
+      </c>
+      <c r="F385" t="s">
+        <v>15</v>
+      </c>
+      <c r="G385" t="s">
+        <v>33</v>
+      </c>
+      <c r="H385" t="s">
+        <v>200</v>
+      </c>
+      <c r="I385" t="s">
+        <v>18</v>
+      </c>
+      <c r="K385">
+        <v>100</v>
+      </c>
+      <c r="L385">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>26</v>
+      </c>
+      <c r="B386">
+        <v>912</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386" t="s">
+        <v>21</v>
+      </c>
+      <c r="E386" t="s">
+        <v>32</v>
+      </c>
+      <c r="F386" t="s">
+        <v>15</v>
+      </c>
+      <c r="G386" t="s">
+        <v>33</v>
+      </c>
+      <c r="H386" t="s">
+        <v>200</v>
+      </c>
+      <c r="I386" t="s">
+        <v>18</v>
+      </c>
+      <c r="K386">
+        <v>100</v>
+      </c>
+      <c r="L386">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>12</v>
+      </c>
+      <c r="B387">
+        <v>9</v>
+      </c>
+      <c r="C387">
+        <v>0</v>
+      </c>
+      <c r="D387" t="s">
+        <v>21</v>
+      </c>
+      <c r="E387" t="s">
+        <v>38</v>
+      </c>
+      <c r="F387" t="s">
+        <v>28</v>
+      </c>
+      <c r="G387" t="s">
+        <v>33</v>
+      </c>
+      <c r="H387" t="s">
+        <v>200</v>
+      </c>
+      <c r="I387" t="s">
+        <v>18</v>
+      </c>
+      <c r="J387" t="s">
+        <v>202</v>
+      </c>
+      <c r="K387">
+        <v>100</v>
+      </c>
+      <c r="L387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>20</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>0</v>
+      </c>
+      <c r="D388" t="s">
+        <v>21</v>
+      </c>
+      <c r="E388" t="s">
+        <v>38</v>
+      </c>
+      <c r="F388" t="s">
+        <v>28</v>
+      </c>
+      <c r="G388" t="s">
+        <v>33</v>
+      </c>
+      <c r="H388" t="s">
+        <v>200</v>
+      </c>
+      <c r="I388" t="s">
+        <v>18</v>
+      </c>
+      <c r="K388">
+        <v>100</v>
+      </c>
+      <c r="L388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>22</v>
+      </c>
+      <c r="B389">
+        <v>11</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+      <c r="D389" t="s">
+        <v>21</v>
+      </c>
+      <c r="E389" t="s">
+        <v>38</v>
+      </c>
+      <c r="F389" t="s">
+        <v>28</v>
+      </c>
+      <c r="G389" t="s">
+        <v>33</v>
+      </c>
+      <c r="H389" t="s">
+        <v>200</v>
+      </c>
+      <c r="I389" t="s">
+        <v>18</v>
+      </c>
+      <c r="K389">
+        <v>100</v>
+      </c>
+      <c r="L389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>24</v>
+      </c>
+      <c r="B390">
+        <v>19</v>
+      </c>
+      <c r="C390">
+        <v>0</v>
+      </c>
+      <c r="D390" t="s">
+        <v>201</v>
+      </c>
+      <c r="E390" t="s">
+        <v>38</v>
+      </c>
+      <c r="F390" t="s">
+        <v>28</v>
+      </c>
+      <c r="G390" t="s">
+        <v>33</v>
+      </c>
+      <c r="H390" t="s">
+        <v>200</v>
+      </c>
+      <c r="I390" t="s">
+        <v>18</v>
+      </c>
+      <c r="K390">
+        <v>100</v>
+      </c>
+      <c r="L390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>26</v>
+      </c>
+      <c r="B391">
+        <v>288</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+      <c r="D391" t="s">
+        <v>21</v>
+      </c>
+      <c r="E391" t="s">
+        <v>38</v>
+      </c>
+      <c r="F391" t="s">
+        <v>28</v>
+      </c>
+      <c r="G391" t="s">
+        <v>33</v>
+      </c>
+      <c r="H391" t="s">
+        <v>200</v>
+      </c>
+      <c r="I391" t="s">
+        <v>18</v>
+      </c>
+      <c r="K391">
+        <v>100</v>
+      </c>
+      <c r="L391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>12</v>
+      </c>
+      <c r="B392">
+        <v>19</v>
+      </c>
+      <c r="C392">
+        <v>9</v>
+      </c>
+      <c r="D392" t="s">
+        <v>203</v>
+      </c>
+      <c r="E392" t="s">
+        <v>204</v>
+      </c>
+      <c r="F392" t="s">
+        <v>15</v>
+      </c>
+      <c r="G392" t="s">
+        <v>205</v>
+      </c>
+      <c r="H392" t="s">
+        <v>200</v>
+      </c>
+      <c r="I392" t="s">
+        <v>18</v>
+      </c>
+      <c r="K392">
+        <v>100</v>
+      </c>
+      <c r="L392">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>20</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393" t="s">
+        <v>21</v>
+      </c>
+      <c r="E393" t="s">
+        <v>204</v>
+      </c>
+      <c r="F393" t="s">
+        <v>15</v>
+      </c>
+      <c r="G393" t="s">
+        <v>205</v>
+      </c>
+      <c r="H393" t="s">
+        <v>200</v>
+      </c>
+      <c r="I393" t="s">
+        <v>18</v>
+      </c>
+      <c r="K393">
+        <v>100</v>
+      </c>
+      <c r="L393">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>22</v>
+      </c>
+      <c r="B394">
+        <v>35</v>
+      </c>
+      <c r="C394">
+        <v>11</v>
+      </c>
+      <c r="D394" t="s">
+        <v>206</v>
+      </c>
+      <c r="E394" t="s">
+        <v>204</v>
+      </c>
+      <c r="F394" t="s">
+        <v>15</v>
+      </c>
+      <c r="G394" t="s">
+        <v>205</v>
+      </c>
+      <c r="H394" t="s">
+        <v>200</v>
+      </c>
+      <c r="I394" t="s">
+        <v>18</v>
+      </c>
+      <c r="K394">
+        <v>100</v>
+      </c>
+      <c r="L394">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>24</v>
+      </c>
+      <c r="B395">
+        <v>102</v>
+      </c>
+      <c r="C395">
+        <v>39</v>
+      </c>
+      <c r="D395" t="s">
+        <v>201</v>
+      </c>
+      <c r="E395" t="s">
+        <v>204</v>
+      </c>
+      <c r="F395" t="s">
+        <v>15</v>
+      </c>
+      <c r="G395" t="s">
+        <v>205</v>
+      </c>
+      <c r="H395" t="s">
+        <v>200</v>
+      </c>
+      <c r="I395" t="s">
+        <v>18</v>
+      </c>
+      <c r="K395">
+        <v>100</v>
+      </c>
+      <c r="L395">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>26</v>
+      </c>
+      <c r="B396">
+        <v>768</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396" t="s">
+        <v>21</v>
+      </c>
+      <c r="E396" t="s">
+        <v>204</v>
+      </c>
+      <c r="F396" t="s">
+        <v>15</v>
+      </c>
+      <c r="G396" t="s">
+        <v>205</v>
+      </c>
+      <c r="H396" t="s">
+        <v>200</v>
+      </c>
+      <c r="I396" t="s">
+        <v>18</v>
+      </c>
+      <c r="K396">
+        <v>100</v>
+      </c>
+      <c r="L396">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>12</v>
+      </c>
+      <c r="B397">
+        <v>11</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397" t="s">
+        <v>21</v>
+      </c>
+      <c r="E397" t="s">
+        <v>207</v>
+      </c>
+      <c r="F397" t="s">
+        <v>28</v>
+      </c>
+      <c r="G397" t="s">
+        <v>205</v>
+      </c>
+      <c r="H397" t="s">
+        <v>200</v>
+      </c>
+      <c r="I397" t="s">
+        <v>18</v>
+      </c>
+      <c r="J397" t="s">
+        <v>208</v>
+      </c>
+      <c r="K397">
+        <v>100</v>
+      </c>
+      <c r="L397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>20</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>0</v>
+      </c>
+      <c r="D398" t="s">
+        <v>21</v>
+      </c>
+      <c r="E398" t="s">
+        <v>207</v>
+      </c>
+      <c r="F398" t="s">
+        <v>28</v>
+      </c>
+      <c r="G398" t="s">
+        <v>205</v>
+      </c>
+      <c r="H398" t="s">
+        <v>200</v>
+      </c>
+      <c r="I398" t="s">
+        <v>18</v>
+      </c>
+      <c r="K398">
+        <v>100</v>
+      </c>
+      <c r="L398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>22</v>
+      </c>
+      <c r="B399">
+        <v>20</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399" t="s">
+        <v>21</v>
+      </c>
+      <c r="E399" t="s">
+        <v>207</v>
+      </c>
+      <c r="F399" t="s">
+        <v>28</v>
+      </c>
+      <c r="G399" t="s">
+        <v>205</v>
+      </c>
+      <c r="H399" t="s">
+        <v>200</v>
+      </c>
+      <c r="I399" t="s">
+        <v>18</v>
+      </c>
+      <c r="K399">
+        <v>100</v>
+      </c>
+      <c r="L399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>24</v>
+      </c>
+      <c r="B400">
+        <v>58</v>
+      </c>
+      <c r="C400">
+        <v>0</v>
+      </c>
+      <c r="D400" t="s">
+        <v>201</v>
+      </c>
+      <c r="E400" t="s">
+        <v>207</v>
+      </c>
+      <c r="F400" t="s">
+        <v>28</v>
+      </c>
+      <c r="G400" t="s">
+        <v>205</v>
+      </c>
+      <c r="H400" t="s">
+        <v>200</v>
+      </c>
+      <c r="I400" t="s">
+        <v>18</v>
+      </c>
+      <c r="K400">
+        <v>100</v>
+      </c>
+      <c r="L400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>26</v>
+      </c>
+      <c r="B401">
+        <v>432</v>
+      </c>
+      <c r="C401">
+        <v>0</v>
+      </c>
+      <c r="D401" t="s">
+        <v>21</v>
+      </c>
+      <c r="E401" t="s">
+        <v>207</v>
+      </c>
+      <c r="F401" t="s">
+        <v>28</v>
+      </c>
+      <c r="G401" t="s">
+        <v>205</v>
+      </c>
+      <c r="H401" t="s">
+        <v>200</v>
+      </c>
+      <c r="I401" t="s">
+        <v>18</v>
+      </c>
+      <c r="K401">
+        <v>100</v>
+      </c>
+      <c r="L401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>12</v>
+      </c>
+      <c r="B402">
+        <v>10</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402" t="s">
+        <v>21</v>
+      </c>
+      <c r="E402" t="s">
+        <v>127</v>
+      </c>
+      <c r="F402" t="s">
+        <v>15</v>
+      </c>
+      <c r="G402" t="s">
+        <v>128</v>
+      </c>
+      <c r="H402" t="s">
+        <v>200</v>
+      </c>
+      <c r="I402" t="s">
+        <v>18</v>
+      </c>
+      <c r="K402">
+        <v>100</v>
+      </c>
+      <c r="L402">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="403" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>20</v>
+      </c>
+      <c r="B403">
+        <v>3</v>
+      </c>
+      <c r="C403">
+        <v>0</v>
+      </c>
+      <c r="D403" t="s">
+        <v>21</v>
+      </c>
+      <c r="E403" t="s">
+        <v>127</v>
+      </c>
+      <c r="F403" t="s">
+        <v>15</v>
+      </c>
+      <c r="G403" t="s">
+        <v>128</v>
+      </c>
+      <c r="H403" t="s">
+        <v>200</v>
+      </c>
+      <c r="I403" t="s">
+        <v>18</v>
+      </c>
+      <c r="K403">
+        <v>100</v>
+      </c>
+      <c r="L403">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="404" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>22</v>
+      </c>
+      <c r="B404">
+        <v>24</v>
+      </c>
+      <c r="C404">
+        <v>5</v>
+      </c>
+      <c r="D404" t="s">
+        <v>209</v>
+      </c>
+      <c r="E404" t="s">
+        <v>127</v>
+      </c>
+      <c r="F404" t="s">
+        <v>15</v>
+      </c>
+      <c r="G404" t="s">
+        <v>128</v>
+      </c>
+      <c r="H404" t="s">
+        <v>200</v>
+      </c>
+      <c r="I404" t="s">
+        <v>18</v>
+      </c>
+      <c r="K404">
+        <v>100</v>
+      </c>
+      <c r="L404">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="405" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>24</v>
+      </c>
+      <c r="B405">
+        <v>32</v>
+      </c>
+      <c r="C405">
+        <v>5</v>
+      </c>
+      <c r="D405" t="s">
+        <v>201</v>
+      </c>
+      <c r="E405" t="s">
+        <v>127</v>
+      </c>
+      <c r="F405" t="s">
+        <v>15</v>
+      </c>
+      <c r="G405" t="s">
+        <v>128</v>
+      </c>
+      <c r="H405" t="s">
+        <v>200</v>
+      </c>
+      <c r="I405" t="s">
+        <v>18</v>
+      </c>
+      <c r="K405">
+        <v>100</v>
+      </c>
+      <c r="L405">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="406" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>26</v>
+      </c>
+      <c r="B406">
+        <v>510</v>
+      </c>
+      <c r="C406">
+        <v>0</v>
+      </c>
+      <c r="D406" t="s">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>127</v>
+      </c>
+      <c r="F406" t="s">
+        <v>15</v>
+      </c>
+      <c r="G406" t="s">
+        <v>128</v>
+      </c>
+      <c r="H406" t="s">
+        <v>200</v>
+      </c>
+      <c r="I406" t="s">
+        <v>18</v>
+      </c>
+      <c r="K406">
+        <v>100</v>
+      </c>
+      <c r="L406">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>12</v>
+      </c>
+      <c r="B407">
+        <v>15</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407" t="s">
+        <v>199</v>
+      </c>
+      <c r="E407" t="s">
+        <v>130</v>
+      </c>
+      <c r="F407" t="s">
+        <v>28</v>
+      </c>
+      <c r="G407" t="s">
+        <v>128</v>
+      </c>
+      <c r="H407" t="s">
+        <v>200</v>
+      </c>
+      <c r="I407" t="s">
+        <v>18</v>
+      </c>
+      <c r="K407">
+        <v>100</v>
+      </c>
+      <c r="L407">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="408" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>20</v>
+      </c>
+      <c r="B408">
+        <v>5</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408" t="s">
+        <v>21</v>
+      </c>
+      <c r="E408" t="s">
+        <v>130</v>
+      </c>
+      <c r="F408" t="s">
+        <v>28</v>
+      </c>
+      <c r="G408" t="s">
+        <v>128</v>
+      </c>
+      <c r="H408" t="s">
+        <v>200</v>
+      </c>
+      <c r="I408" t="s">
+        <v>18</v>
+      </c>
+      <c r="K408">
+        <v>100</v>
+      </c>
+      <c r="L408">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="409" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>22</v>
+      </c>
+      <c r="B409">
+        <v>37</v>
+      </c>
+      <c r="C409">
+        <v>7</v>
+      </c>
+      <c r="D409" t="s">
+        <v>210</v>
+      </c>
+      <c r="E409" t="s">
+        <v>130</v>
+      </c>
+      <c r="F409" t="s">
+        <v>28</v>
+      </c>
+      <c r="G409" t="s">
+        <v>128</v>
+      </c>
+      <c r="H409" t="s">
+        <v>200</v>
+      </c>
+      <c r="I409" t="s">
+        <v>18</v>
+      </c>
+      <c r="K409">
+        <v>100</v>
+      </c>
+      <c r="L409">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="410" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>24</v>
+      </c>
+      <c r="B410">
+        <v>48</v>
+      </c>
+      <c r="C410">
+        <v>13</v>
+      </c>
+      <c r="D410" t="s">
+        <v>201</v>
+      </c>
+      <c r="E410" t="s">
+        <v>130</v>
+      </c>
+      <c r="F410" t="s">
+        <v>28</v>
+      </c>
+      <c r="G410" t="s">
+        <v>128</v>
+      </c>
+      <c r="H410" t="s">
+        <v>200</v>
+      </c>
+      <c r="I410" t="s">
+        <v>18</v>
+      </c>
+      <c r="K410">
+        <v>100</v>
+      </c>
+      <c r="L410">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="411" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>26</v>
+      </c>
+      <c r="B411">
+        <v>765</v>
+      </c>
+      <c r="C411">
+        <v>0</v>
+      </c>
+      <c r="D411" t="s">
+        <v>21</v>
+      </c>
+      <c r="E411" t="s">
+        <v>130</v>
+      </c>
+      <c r="F411" t="s">
+        <v>28</v>
+      </c>
+      <c r="G411" t="s">
+        <v>128</v>
+      </c>
+      <c r="H411" t="s">
+        <v>200</v>
+      </c>
+      <c r="I411" t="s">
+        <v>18</v>
+      </c>
+      <c r="K411">
+        <v>100</v>
+      </c>
+      <c r="L411">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>12</v>
+      </c>
+      <c r="B412">
+        <v>5</v>
+      </c>
+      <c r="C412">
+        <v>8</v>
+      </c>
+      <c r="D412" t="s">
+        <v>211</v>
+      </c>
+      <c r="E412" t="s">
+        <v>135</v>
+      </c>
+      <c r="F412" t="s">
+        <v>28</v>
+      </c>
+      <c r="G412" t="s">
+        <v>128</v>
+      </c>
+      <c r="H412" t="s">
+        <v>200</v>
+      </c>
+      <c r="I412" t="s">
+        <v>18</v>
+      </c>
+      <c r="J412" t="s">
+        <v>212</v>
+      </c>
+      <c r="K412">
+        <v>100</v>
+      </c>
+      <c r="L412">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>20</v>
+      </c>
+      <c r="B413">
+        <v>2</v>
+      </c>
+      <c r="C413">
+        <v>0</v>
+      </c>
+      <c r="D413" t="s">
+        <v>21</v>
+      </c>
+      <c r="E413" t="s">
+        <v>135</v>
+      </c>
+      <c r="F413" t="s">
+        <v>28</v>
+      </c>
+      <c r="G413" t="s">
+        <v>128</v>
+      </c>
+      <c r="H413" t="s">
+        <v>200</v>
+      </c>
+      <c r="I413" t="s">
+        <v>18</v>
+      </c>
+      <c r="K413">
+        <v>100</v>
+      </c>
+      <c r="L413">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>22</v>
+      </c>
+      <c r="B414">
+        <v>11</v>
+      </c>
+      <c r="C414">
+        <v>12</v>
+      </c>
+      <c r="D414" t="s">
+        <v>213</v>
+      </c>
+      <c r="E414" t="s">
+        <v>135</v>
+      </c>
+      <c r="F414" t="s">
+        <v>28</v>
+      </c>
+      <c r="G414" t="s">
+        <v>128</v>
+      </c>
+      <c r="H414" t="s">
+        <v>200</v>
+      </c>
+      <c r="I414" t="s">
+        <v>18</v>
+      </c>
+      <c r="K414">
+        <v>100</v>
+      </c>
+      <c r="L414">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>24</v>
+      </c>
+      <c r="B415">
+        <v>14</v>
+      </c>
+      <c r="C415">
+        <v>19</v>
+      </c>
+      <c r="D415" t="s">
+        <v>201</v>
+      </c>
+      <c r="E415" t="s">
+        <v>135</v>
+      </c>
+      <c r="F415" t="s">
+        <v>28</v>
+      </c>
+      <c r="G415" t="s">
+        <v>128</v>
+      </c>
+      <c r="H415" t="s">
+        <v>200</v>
+      </c>
+      <c r="I415" t="s">
+        <v>18</v>
+      </c>
+      <c r="K415">
+        <v>100</v>
+      </c>
+      <c r="L415">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>26</v>
+      </c>
+      <c r="B416">
+        <v>225</v>
+      </c>
+      <c r="C416">
+        <v>0</v>
+      </c>
+      <c r="D416" t="s">
+        <v>21</v>
+      </c>
+      <c r="E416" t="s">
+        <v>135</v>
+      </c>
+      <c r="F416" t="s">
+        <v>28</v>
+      </c>
+      <c r="G416" t="s">
+        <v>128</v>
+      </c>
+      <c r="H416" t="s">
+        <v>200</v>
+      </c>
+      <c r="I416" t="s">
+        <v>18</v>
+      </c>
+      <c r="K416">
+        <v>100</v>
+      </c>
+      <c r="L416">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>12</v>
+      </c>
+      <c r="B417">
+        <v>20</v>
+      </c>
+      <c r="C417">
+        <v>10</v>
+      </c>
+      <c r="D417" t="s">
+        <v>150</v>
+      </c>
+      <c r="E417" t="s">
+        <v>188</v>
+      </c>
+      <c r="F417" t="s">
+        <v>15</v>
+      </c>
+      <c r="G417" t="s">
+        <v>189</v>
+      </c>
+      <c r="H417" t="s">
+        <v>200</v>
+      </c>
+      <c r="I417" t="s">
+        <v>18</v>
+      </c>
+      <c r="K417">
+        <v>100</v>
+      </c>
+      <c r="L417">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>20</v>
+      </c>
+      <c r="B418">
+        <v>3</v>
+      </c>
+      <c r="C418">
+        <v>0</v>
+      </c>
+      <c r="D418" t="s">
+        <v>21</v>
+      </c>
+      <c r="E418" t="s">
+        <v>188</v>
+      </c>
+      <c r="F418" t="s">
+        <v>15</v>
+      </c>
+      <c r="G418" t="s">
+        <v>189</v>
+      </c>
+      <c r="H418" t="s">
+        <v>200</v>
+      </c>
+      <c r="I418" t="s">
+        <v>18</v>
+      </c>
+      <c r="K418">
+        <v>100</v>
+      </c>
+      <c r="L418">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>22</v>
+      </c>
+      <c r="B419">
+        <v>35</v>
+      </c>
+      <c r="C419">
+        <v>19</v>
+      </c>
+      <c r="D419" t="s">
+        <v>221</v>
+      </c>
+      <c r="E419" t="s">
+        <v>188</v>
+      </c>
+      <c r="F419" t="s">
+        <v>15</v>
+      </c>
+      <c r="G419" t="s">
+        <v>189</v>
+      </c>
+      <c r="H419" t="s">
+        <v>200</v>
+      </c>
+      <c r="I419" t="s">
+        <v>18</v>
+      </c>
+      <c r="K419">
+        <v>100</v>
+      </c>
+      <c r="L419">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>24</v>
+      </c>
+      <c r="B420">
+        <v>62</v>
+      </c>
+      <c r="C420">
+        <v>47</v>
+      </c>
+      <c r="D420" t="s">
+        <v>201</v>
+      </c>
+      <c r="E420" t="s">
+        <v>188</v>
+      </c>
+      <c r="F420" t="s">
+        <v>15</v>
+      </c>
+      <c r="G420" t="s">
+        <v>189</v>
+      </c>
+      <c r="H420" t="s">
+        <v>200</v>
+      </c>
+      <c r="I420" t="s">
+        <v>18</v>
+      </c>
+      <c r="K420">
+        <v>100</v>
+      </c>
+      <c r="L420">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>26</v>
+      </c>
+      <c r="B421">
+        <v>420</v>
+      </c>
+      <c r="C421">
+        <v>0</v>
+      </c>
+      <c r="D421" t="s">
+        <v>21</v>
+      </c>
+      <c r="E421" t="s">
+        <v>188</v>
+      </c>
+      <c r="F421" t="s">
+        <v>15</v>
+      </c>
+      <c r="G421" t="s">
+        <v>189</v>
+      </c>
+      <c r="H421" t="s">
+        <v>200</v>
+      </c>
+      <c r="I421" t="s">
+        <v>18</v>
+      </c>
+      <c r="K421">
+        <v>100</v>
+      </c>
+      <c r="L421">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>12</v>
+      </c>
+      <c r="B422">
+        <v>29</v>
+      </c>
+      <c r="C422">
+        <v>11</v>
+      </c>
+      <c r="D422" t="s">
+        <v>37</v>
+      </c>
+      <c r="E422" t="s">
+        <v>222</v>
+      </c>
+      <c r="F422" t="s">
+        <v>28</v>
+      </c>
+      <c r="G422" t="s">
+        <v>189</v>
+      </c>
+      <c r="H422" t="s">
+        <v>200</v>
+      </c>
+      <c r="I422" t="s">
+        <v>18</v>
+      </c>
+      <c r="K422">
+        <v>100</v>
+      </c>
+      <c r="L422">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>20</v>
+      </c>
+      <c r="B423">
+        <v>4</v>
+      </c>
+      <c r="C423">
+        <v>0</v>
+      </c>
+      <c r="D423" t="s">
+        <v>21</v>
+      </c>
+      <c r="E423" t="s">
+        <v>222</v>
+      </c>
+      <c r="F423" t="s">
+        <v>28</v>
+      </c>
+      <c r="G423" t="s">
+        <v>189</v>
+      </c>
+      <c r="H423" t="s">
+        <v>200</v>
+      </c>
+      <c r="I423" t="s">
+        <v>18</v>
+      </c>
+      <c r="K423">
+        <v>100</v>
+      </c>
+      <c r="L423">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>22</v>
+      </c>
+      <c r="B424">
+        <v>53</v>
+      </c>
+      <c r="C424">
+        <v>18</v>
+      </c>
+      <c r="D424" t="s">
+        <v>223</v>
+      </c>
+      <c r="E424" t="s">
+        <v>222</v>
+      </c>
+      <c r="F424" t="s">
+        <v>28</v>
+      </c>
+      <c r="G424" t="s">
+        <v>189</v>
+      </c>
+      <c r="H424" t="s">
+        <v>200</v>
+      </c>
+      <c r="I424" t="s">
+        <v>18</v>
+      </c>
+      <c r="K424">
+        <v>100</v>
+      </c>
+      <c r="L424">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>24</v>
+      </c>
+      <c r="B425">
+        <v>92</v>
+      </c>
+      <c r="C425">
+        <v>27</v>
+      </c>
+      <c r="D425" t="s">
+        <v>201</v>
+      </c>
+      <c r="E425" t="s">
+        <v>222</v>
+      </c>
+      <c r="F425" t="s">
+        <v>28</v>
+      </c>
+      <c r="G425" t="s">
+        <v>189</v>
+      </c>
+      <c r="H425" t="s">
+        <v>200</v>
+      </c>
+      <c r="I425" t="s">
+        <v>18</v>
+      </c>
+      <c r="K425">
+        <v>100</v>
+      </c>
+      <c r="L425">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>26</v>
+      </c>
+      <c r="B426">
+        <v>630</v>
+      </c>
+      <c r="C426">
+        <v>0</v>
+      </c>
+      <c r="D426" t="s">
+        <v>21</v>
+      </c>
+      <c r="E426" t="s">
+        <v>222</v>
+      </c>
+      <c r="F426" t="s">
+        <v>28</v>
+      </c>
+      <c r="G426" t="s">
+        <v>189</v>
+      </c>
+      <c r="H426" t="s">
+        <v>200</v>
+      </c>
+      <c r="I426" t="s">
+        <v>18</v>
+      </c>
+      <c r="K426">
+        <v>100</v>
+      </c>
+      <c r="L426">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>12</v>
+      </c>
+      <c r="B427">
+        <v>21</v>
+      </c>
+      <c r="C427">
+        <v>5</v>
+      </c>
+      <c r="D427" t="s">
+        <v>110</v>
+      </c>
+      <c r="E427" t="s">
+        <v>192</v>
+      </c>
+      <c r="F427" t="s">
+        <v>28</v>
+      </c>
+      <c r="G427" t="s">
+        <v>189</v>
+      </c>
+      <c r="H427" t="s">
+        <v>200</v>
+      </c>
+      <c r="I427" t="s">
+        <v>18</v>
+      </c>
+      <c r="J427" t="s">
+        <v>224</v>
+      </c>
+      <c r="K427">
+        <v>100</v>
+      </c>
+      <c r="L427">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>20</v>
+      </c>
+      <c r="B428">
+        <v>3</v>
+      </c>
+      <c r="C428">
+        <v>0</v>
+      </c>
+      <c r="D428" t="s">
+        <v>21</v>
+      </c>
+      <c r="E428" t="s">
+        <v>192</v>
+      </c>
+      <c r="F428" t="s">
+        <v>28</v>
+      </c>
+      <c r="G428" t="s">
+        <v>189</v>
+      </c>
+      <c r="H428" t="s">
+        <v>200</v>
+      </c>
+      <c r="I428" t="s">
+        <v>18</v>
+      </c>
+      <c r="K428">
+        <v>100</v>
+      </c>
+      <c r="L428">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>22</v>
+      </c>
+      <c r="B429">
+        <v>38</v>
+      </c>
+      <c r="C429">
+        <v>5</v>
+      </c>
+      <c r="D429" t="s">
+        <v>225</v>
+      </c>
+      <c r="E429" t="s">
+        <v>192</v>
+      </c>
+      <c r="F429" t="s">
+        <v>28</v>
+      </c>
+      <c r="G429" t="s">
+        <v>189</v>
+      </c>
+      <c r="H429" t="s">
+        <v>200</v>
+      </c>
+      <c r="I429" t="s">
+        <v>18</v>
+      </c>
+      <c r="K429">
+        <v>100</v>
+      </c>
+      <c r="L429">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>24</v>
+      </c>
+      <c r="B430">
+        <v>66</v>
+      </c>
+      <c r="C430">
+        <v>4</v>
+      </c>
+      <c r="D430" t="s">
+        <v>201</v>
+      </c>
+      <c r="E430" t="s">
+        <v>192</v>
+      </c>
+      <c r="F430" t="s">
+        <v>28</v>
+      </c>
+      <c r="G430" t="s">
+        <v>189</v>
+      </c>
+      <c r="H430" t="s">
+        <v>200</v>
+      </c>
+      <c r="I430" t="s">
+        <v>18</v>
+      </c>
+      <c r="K430">
+        <v>100</v>
+      </c>
+      <c r="L430">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>26</v>
+      </c>
+      <c r="B431">
+        <v>450</v>
+      </c>
+      <c r="C431">
+        <v>0</v>
+      </c>
+      <c r="D431" t="s">
+        <v>21</v>
+      </c>
+      <c r="E431" t="s">
+        <v>192</v>
+      </c>
+      <c r="F431" t="s">
+        <v>28</v>
+      </c>
+      <c r="G431" t="s">
+        <v>189</v>
+      </c>
+      <c r="H431" t="s">
+        <v>200</v>
+      </c>
+      <c r="I431" t="s">
+        <v>18</v>
+      </c>
+      <c r="K431">
+        <v>100</v>
+      </c>
+      <c r="L431">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>12</v>
+      </c>
+      <c r="B432">
+        <v>14</v>
+      </c>
+      <c r="C432">
+        <v>5</v>
+      </c>
+      <c r="D432" t="s">
+        <v>226</v>
+      </c>
+      <c r="E432" t="s">
+        <v>173</v>
+      </c>
+      <c r="F432" t="s">
+        <v>15</v>
+      </c>
+      <c r="G432" t="s">
+        <v>174</v>
+      </c>
+      <c r="H432" t="s">
+        <v>200</v>
+      </c>
+      <c r="I432" t="s">
+        <v>18</v>
+      </c>
+      <c r="J432" t="s">
+        <v>227</v>
+      </c>
+      <c r="K432">
+        <v>100</v>
+      </c>
+      <c r="L432">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="433" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>20</v>
+      </c>
+      <c r="B433">
+        <v>1</v>
+      </c>
+      <c r="C433">
+        <v>0</v>
+      </c>
+      <c r="D433" t="s">
+        <v>21</v>
+      </c>
+      <c r="E433" t="s">
+        <v>173</v>
+      </c>
+      <c r="F433" t="s">
+        <v>15</v>
+      </c>
+      <c r="G433" t="s">
+        <v>174</v>
+      </c>
+      <c r="H433" t="s">
+        <v>200</v>
+      </c>
+      <c r="I433" t="s">
+        <v>18</v>
+      </c>
+      <c r="J433" t="s">
+        <v>228</v>
+      </c>
+      <c r="K433">
+        <v>100</v>
+      </c>
+      <c r="L433">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="434" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>22</v>
+      </c>
+      <c r="B434">
+        <v>28</v>
+      </c>
+      <c r="C434">
+        <v>6</v>
+      </c>
+      <c r="D434" t="s">
+        <v>209</v>
+      </c>
+      <c r="E434" t="s">
+        <v>173</v>
+      </c>
+      <c r="F434" t="s">
+        <v>15</v>
+      </c>
+      <c r="G434" t="s">
+        <v>174</v>
+      </c>
+      <c r="H434" t="s">
+        <v>200</v>
+      </c>
+      <c r="I434" t="s">
+        <v>18</v>
+      </c>
+      <c r="J434" t="s">
+        <v>229</v>
+      </c>
+      <c r="K434">
+        <v>100</v>
+      </c>
+      <c r="L434">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="435" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>24</v>
+      </c>
+      <c r="B435">
+        <v>56</v>
+      </c>
+      <c r="C435">
+        <v>14</v>
+      </c>
+      <c r="D435" t="s">
+        <v>71</v>
+      </c>
+      <c r="E435" t="s">
+        <v>173</v>
+      </c>
+      <c r="F435" t="s">
+        <v>15</v>
+      </c>
+      <c r="G435" t="s">
+        <v>174</v>
+      </c>
+      <c r="H435" t="s">
+        <v>200</v>
+      </c>
+      <c r="I435" t="s">
+        <v>18</v>
+      </c>
+      <c r="J435" t="s">
+        <v>230</v>
+      </c>
+      <c r="K435">
+        <v>100</v>
+      </c>
+      <c r="L435">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="436" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>26</v>
+      </c>
+      <c r="B436">
+        <v>600</v>
+      </c>
+      <c r="C436">
+        <v>0</v>
+      </c>
+      <c r="D436" t="s">
+        <v>21</v>
+      </c>
+      <c r="E436" t="s">
+        <v>173</v>
+      </c>
+      <c r="F436" t="s">
+        <v>15</v>
+      </c>
+      <c r="G436" t="s">
+        <v>174</v>
+      </c>
+      <c r="H436" t="s">
+        <v>200</v>
+      </c>
+      <c r="I436" t="s">
+        <v>18</v>
+      </c>
+      <c r="J436" t="s">
+        <v>231</v>
+      </c>
+      <c r="K436">
+        <v>100</v>
+      </c>
+      <c r="L436">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="437" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>12</v>
+      </c>
+      <c r="B437">
+        <v>21</v>
+      </c>
+      <c r="C437">
+        <v>10</v>
+      </c>
+      <c r="D437" t="s">
+        <v>232</v>
+      </c>
+      <c r="E437" t="s">
+        <v>123</v>
+      </c>
+      <c r="F437" t="s">
+        <v>28</v>
+      </c>
+      <c r="G437" t="s">
+        <v>174</v>
+      </c>
+      <c r="H437" t="s">
+        <v>200</v>
+      </c>
+      <c r="I437" t="s">
+        <v>18</v>
+      </c>
+      <c r="K437">
+        <v>100</v>
+      </c>
+      <c r="L437">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="438" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>20</v>
+      </c>
+      <c r="B438">
+        <v>2</v>
+      </c>
+      <c r="C438">
+        <v>0</v>
+      </c>
+      <c r="D438" t="s">
+        <v>21</v>
+      </c>
+      <c r="E438" t="s">
+        <v>123</v>
+      </c>
+      <c r="F438" t="s">
+        <v>28</v>
+      </c>
+      <c r="G438" t="s">
+        <v>174</v>
+      </c>
+      <c r="H438" t="s">
+        <v>200</v>
+      </c>
+      <c r="I438" t="s">
+        <v>18</v>
+      </c>
+      <c r="K438">
+        <v>100</v>
+      </c>
+      <c r="L438">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="439" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>22</v>
+      </c>
+      <c r="B439">
+        <v>42</v>
+      </c>
+      <c r="C439">
+        <v>17</v>
+      </c>
+      <c r="D439" t="s">
+        <v>90</v>
+      </c>
+      <c r="E439" t="s">
+        <v>123</v>
+      </c>
+      <c r="F439" t="s">
+        <v>28</v>
+      </c>
+      <c r="G439" t="s">
+        <v>174</v>
+      </c>
+      <c r="H439" t="s">
+        <v>200</v>
+      </c>
+      <c r="I439" t="s">
+        <v>18</v>
+      </c>
+      <c r="K439">
+        <v>100</v>
+      </c>
+      <c r="L439">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="440" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>24</v>
+      </c>
+      <c r="B440">
+        <v>84</v>
+      </c>
+      <c r="C440">
+        <v>40</v>
+      </c>
+      <c r="D440" t="s">
+        <v>201</v>
+      </c>
+      <c r="E440" t="s">
+        <v>123</v>
+      </c>
+      <c r="F440" t="s">
+        <v>28</v>
+      </c>
+      <c r="G440" t="s">
+        <v>174</v>
+      </c>
+      <c r="H440" t="s">
+        <v>200</v>
+      </c>
+      <c r="I440" t="s">
+        <v>18</v>
+      </c>
+      <c r="K440">
+        <v>100</v>
+      </c>
+      <c r="L440">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="441" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>26</v>
+      </c>
+      <c r="B441">
+        <v>900</v>
+      </c>
+      <c r="C441">
+        <v>0</v>
+      </c>
+      <c r="D441" t="s">
+        <v>21</v>
+      </c>
+      <c r="E441" t="s">
+        <v>123</v>
+      </c>
+      <c r="F441" t="s">
+        <v>28</v>
+      </c>
+      <c r="G441" t="s">
+        <v>174</v>
+      </c>
+      <c r="H441" t="s">
+        <v>200</v>
+      </c>
+      <c r="I441" t="s">
+        <v>18</v>
+      </c>
+      <c r="K441">
+        <v>100</v>
+      </c>
+      <c r="L441">
+        <v>27.2</v>
+      </c>
+    </row>
+    <row r="442" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>12</v>
+      </c>
+      <c r="B442">
+        <v>21</v>
+      </c>
+      <c r="C442">
+        <v>3</v>
+      </c>
+      <c r="D442" t="s">
+        <v>162</v>
+      </c>
+      <c r="E442" t="s">
+        <v>69</v>
+      </c>
+      <c r="F442" t="s">
+        <v>63</v>
+      </c>
+      <c r="G442" t="s">
+        <v>174</v>
+      </c>
+      <c r="H442" t="s">
+        <v>200</v>
+      </c>
+      <c r="I442" t="s">
+        <v>18</v>
+      </c>
+      <c r="K442">
+        <v>100</v>
+      </c>
+      <c r="L442">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="443" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>20</v>
+      </c>
+      <c r="B443">
+        <v>2</v>
+      </c>
+      <c r="C443">
+        <v>0</v>
+      </c>
+      <c r="D443" t="s">
+        <v>21</v>
+      </c>
+      <c r="E443" t="s">
+        <v>69</v>
+      </c>
+      <c r="F443" t="s">
+        <v>63</v>
+      </c>
+      <c r="G443" t="s">
+        <v>174</v>
+      </c>
+      <c r="H443" t="s">
+        <v>200</v>
+      </c>
+      <c r="I443" t="s">
+        <v>18</v>
+      </c>
+      <c r="K443">
+        <v>100</v>
+      </c>
+      <c r="L443">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="444" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>22</v>
+      </c>
+      <c r="B444">
+        <v>42</v>
+      </c>
+      <c r="C444">
+        <v>11</v>
+      </c>
+      <c r="D444" t="s">
+        <v>233</v>
+      </c>
+      <c r="E444" t="s">
+        <v>69</v>
+      </c>
+      <c r="F444" t="s">
+        <v>63</v>
+      </c>
+      <c r="G444" t="s">
+        <v>174</v>
+      </c>
+      <c r="H444" t="s">
+        <v>200</v>
+      </c>
+      <c r="I444" t="s">
+        <v>18</v>
+      </c>
+      <c r="K444">
+        <v>100</v>
+      </c>
+      <c r="L444">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="445" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>24</v>
+      </c>
+      <c r="B445">
+        <v>84</v>
+      </c>
+      <c r="C445">
+        <v>6</v>
+      </c>
+      <c r="D445" t="s">
+        <v>201</v>
+      </c>
+      <c r="E445" t="s">
+        <v>69</v>
+      </c>
+      <c r="F445" t="s">
+        <v>63</v>
+      </c>
+      <c r="G445" t="s">
+        <v>174</v>
+      </c>
+      <c r="H445" t="s">
+        <v>200</v>
+      </c>
+      <c r="I445" t="s">
+        <v>18</v>
+      </c>
+      <c r="K445">
+        <v>100</v>
+      </c>
+      <c r="L445">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="446" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>26</v>
+      </c>
+      <c r="B446">
+        <v>900</v>
+      </c>
+      <c r="C446">
+        <v>0</v>
+      </c>
+      <c r="D446" t="s">
+        <v>21</v>
+      </c>
+      <c r="E446" t="s">
+        <v>69</v>
+      </c>
+      <c r="F446" t="s">
+        <v>63</v>
+      </c>
+      <c r="G446" t="s">
+        <v>174</v>
+      </c>
+      <c r="H446" t="s">
+        <v>200</v>
+      </c>
+      <c r="I446" t="s">
+        <v>18</v>
+      </c>
+      <c r="K446">
+        <v>100</v>
+      </c>
+      <c r="L446">
+        <v>17.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,22 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_3A3DD0641462DC0F62355476585DCE3A87449165" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A1CC77F-32F7-4FF8-B943-CF926F0C1630}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C18536F-092E-4829-B955-5BB013648117}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$230</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="98">
   <si>
     <t>Producto</t>
   </si>
@@ -64,9 +61,21 @@
     <t>POSTPAGO</t>
   </si>
   <si>
+    <t>7%</t>
+  </si>
+  <si>
+    <t>Lider Don Matias Diana Ruiz</t>
+  </si>
+  <si>
     <t>LIDER</t>
   </si>
   <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>Sin pago (0%)</t>
   </si>
   <si>
@@ -79,196 +88,232 @@
     <t>TERMINALES</t>
   </si>
   <si>
+    <t>12%</t>
+  </si>
+  <si>
     <t>OTROS</t>
   </si>
   <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
     <t>CVS PLUS</t>
   </si>
   <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
+  </si>
+  <si>
     <t>ASESOR</t>
   </si>
   <si>
-    <t>Lider Don Matias Diana Ruiz</t>
-  </si>
-  <si>
-    <t>DON MATIAS</t>
+    <t>Vacaciones del 3 al 22 de julio</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Vacaciones del 26 de jun al 13 de julio</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>21%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>19%</t>
+  </si>
+  <si>
+    <t>160%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vac del 14 al 31 de julio </t>
+  </si>
+  <si>
+    <t>109%</t>
+  </si>
+  <si>
+    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+  </si>
+  <si>
+    <t>COPACABANA</t>
   </si>
   <si>
     <t>22%</t>
   </si>
   <si>
+    <t>Meta terminales 33</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>Alexandra Patricia Duque</t>
+  </si>
+  <si>
+    <t>Vac del 14 al 31 de julio</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
     <t>38%</t>
   </si>
   <si>
-    <t>Evelyn Daniela Lopera Lopera</t>
-  </si>
-  <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>115%</t>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t>34%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vac del 18 de junio al 6 de julio </t>
+  </si>
+  <si>
+    <t>13%</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>Ingresa de vac el 4  Meta puntos 890.4      Meta post 12</t>
+  </si>
+  <si>
+    <t>Hogar 1</t>
+  </si>
+  <si>
+    <t>Terminales  24</t>
+  </si>
+  <si>
+    <t>Otros 47</t>
+  </si>
+  <si>
+    <t>CVS PLUS 504</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
   </si>
   <si>
     <t>SUPERNUMERARIO</t>
   </si>
   <si>
-    <t>Sara Julieth Acevedo Gutierrez</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Posada Galeano</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
-  </si>
-  <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>Evelis Mary Ojeda Baldovino</t>
-  </si>
-  <si>
-    <t>Sene Del Socorro Suarez Torres</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>Lider Luz Stella Serna</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
-    <t>Lider Yolima Mesa Zapata</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>Pendiente 4 porta pre</t>
-  </si>
-  <si>
-    <t>Vacaciones del 3 al 22 de julio</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>Lider Geraldin Angulo Jaramillo</t>
-  </si>
-  <si>
-    <t>YARUMAL</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>Laura Carolina Chavarria Amariles</t>
-  </si>
-  <si>
-    <t>Vacaciones del 26 de jun al 13 de julio</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>19%</t>
-  </si>
-  <si>
-    <t>160%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vac del 14 al 31 de julio </t>
-  </si>
-  <si>
-    <t>109%</t>
-  </si>
-  <si>
-    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
-  </si>
-  <si>
-    <t>COPACABANA</t>
-  </si>
-  <si>
-    <t>Meta terminales 33</t>
-  </si>
-  <si>
-    <t>150%</t>
-  </si>
-  <si>
-    <t>Alexandra Patricia Duque</t>
-  </si>
-  <si>
-    <t>Vac del 14 al 31 de julio</t>
-  </si>
-  <si>
-    <t>Bibiana Farley Rios Agudelo</t>
-  </si>
-  <si>
-    <t>54%</t>
-  </si>
-  <si>
-    <t>Darinela  Chavarria Carvajal</t>
-  </si>
-  <si>
-    <t>34%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vac del 18 de junio al 6 de julio </t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
-    <t>Ingresa de vac el 4  Meta puntos 890.4      Meta post 12</t>
-  </si>
-  <si>
-    <t>Hogar 1</t>
-  </si>
-  <si>
-    <t>Terminales  24</t>
-  </si>
-  <si>
-    <t>Otros 47</t>
-  </si>
-  <si>
-    <t>CVS PLUS 504</t>
-  </si>
-  <si>
-    <t>48%</t>
-  </si>
-  <si>
     <t>26%</t>
+  </si>
+  <si>
+    <t>68%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>Vac del 16 de junio al 3 de julio</t>
+  </si>
+  <si>
+    <t>32%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>129%</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Maria Camila Arango VÃ©lez</t>
+  </si>
+  <si>
+    <t>Le finalizaron el 18 elabora - 15 días</t>
+  </si>
+  <si>
+    <t>57%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>Johan Daniel Herrera Mazo</t>
   </si>
 </sst>
 </file>
@@ -632,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -684,22 +729,22 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>100</v>
@@ -710,31 +755,31 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K3">
         <v>100</v>
@@ -745,7 +790,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>34</v>
@@ -754,22 +799,22 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -780,7 +825,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>61</v>
@@ -789,22 +834,22 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -815,7 +860,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>912</v>
@@ -824,22 +869,22 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -859,25 +904,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -888,7 +933,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -897,22 +942,22 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -923,7 +968,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>11</v>
@@ -932,22 +977,22 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -958,7 +1003,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>19</v>
@@ -967,22 +1012,22 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -993,7 +1038,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>288</v>
@@ -1002,22 +1047,22 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>22</v>
-      </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -1037,22 +1082,22 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -1063,31 +1108,31 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -1098,7 +1143,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -1107,22 +1152,22 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -1133,7 +1178,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>102</v>
@@ -1142,22 +1187,22 @@
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -1168,7 +1213,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>768</v>
@@ -1177,22 +1222,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -1212,25 +1257,25 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -1241,7 +1286,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1250,22 +1295,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -1276,7 +1321,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>20</v>
@@ -1285,22 +1330,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -1311,7 +1356,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>58</v>
@@ -1320,22 +1365,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -1346,7 +1391,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>432</v>
@@ -1355,22 +1400,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -1390,22 +1435,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -1416,7 +1461,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -1425,22 +1470,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
         <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -1451,7 +1496,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>24</v>
@@ -1460,22 +1505,22 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
         <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -1486,7 +1531,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>32</v>
@@ -1495,22 +1540,22 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
         <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
         <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -1521,7 +1566,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>510</v>
@@ -1530,22 +1575,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
         <v>35</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -1565,22 +1610,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G27" t="s">
         <v>36</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -1591,7 +1636,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -1600,22 +1645,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
         <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -1626,7 +1671,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B29">
         <v>37</v>
@@ -1635,22 +1680,22 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G29" t="s">
         <v>36</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -1661,7 +1706,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B30">
         <v>48</v>
@@ -1670,22 +1715,22 @@
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
         <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -1696,7 +1741,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B31">
         <v>765</v>
@@ -1705,22 +1750,22 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G31" t="s">
         <v>36</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -1740,25 +1785,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
         <v>36</v>
       </c>
       <c r="H32" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -1769,7 +1814,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1778,22 +1823,22 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
         <v>36</v>
       </c>
       <c r="H33" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -1804,7 +1849,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B34">
         <v>11</v>
@@ -1813,22 +1858,22 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
         <v>36</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -1839,7 +1884,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>14</v>
@@ -1848,22 +1893,22 @@
         <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
         <v>36</v>
       </c>
       <c r="H35" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -1874,7 +1919,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B36">
         <v>225</v>
@@ -1883,22 +1928,22 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G36" t="s">
         <v>36</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -1918,22 +1963,22 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H37" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -1944,7 +1989,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -1953,22 +1998,22 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -1979,7 +2024,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>32</v>
@@ -1988,25 +2033,25 @@
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -2017,7 +2062,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B40">
         <v>61</v>
@@ -2026,22 +2071,22 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H40" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -2052,7 +2097,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B41">
         <v>510</v>
@@ -2061,22 +2106,22 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -2096,25 +2141,25 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -2125,7 +2170,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2134,22 +2179,22 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H43" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K43">
         <v>100</v>
@@ -2160,7 +2205,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B44">
         <v>14</v>
@@ -2169,22 +2214,22 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H44" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -2195,7 +2240,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B45">
         <v>27</v>
@@ -2204,22 +2249,22 @@
         <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H45" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K45">
         <v>100</v>
@@ -2230,7 +2275,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>225</v>
@@ -2239,22 +2284,22 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H46" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K46">
         <v>100</v>
@@ -2274,22 +2319,22 @@
         <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H47" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -2300,7 +2345,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B48">
         <v>7</v>
@@ -2309,22 +2354,22 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H48" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K48">
         <v>100</v>
@@ -2335,7 +2380,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -2344,22 +2389,22 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H49" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K49">
         <v>100</v>
@@ -2370,7 +2415,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B50">
         <v>92</v>
@@ -2379,22 +2424,22 @@
         <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H50" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K50">
         <v>100</v>
@@ -2405,7 +2450,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>765</v>
@@ -2414,22 +2459,22 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H51" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K51">
         <v>100</v>
@@ -2449,22 +2494,22 @@
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K52">
         <v>100</v>
@@ -2475,31 +2520,31 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
         <v>15</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="G53" t="s">
         <v>16</v>
       </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" t="s">
-        <v>22</v>
-      </c>
       <c r="H53" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K53">
         <v>100</v>
@@ -2510,7 +2555,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B54">
         <v>34</v>
@@ -2519,22 +2564,22 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K54">
         <v>100</v>
@@ -2545,7 +2590,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B55">
         <v>61</v>
@@ -2554,22 +2599,22 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H55" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K55">
         <v>100</v>
@@ -2580,7 +2625,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B56">
         <v>912</v>
@@ -2589,22 +2634,22 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
         <v>16</v>
       </c>
-      <c r="E56" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" t="s">
-        <v>22</v>
-      </c>
       <c r="H56" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K56">
         <v>100</v>
@@ -2624,25 +2669,25 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" t="s">
         <v>16</v>
       </c>
-      <c r="E57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" t="s">
-        <v>22</v>
-      </c>
       <c r="H57" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -2653,7 +2698,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -2662,22 +2707,22 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" t="s">
         <v>16</v>
       </c>
-      <c r="E58" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" t="s">
-        <v>22</v>
-      </c>
       <c r="H58" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K58">
         <v>100</v>
@@ -2688,7 +2733,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B59">
         <v>11</v>
@@ -2697,22 +2742,22 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" t="s">
         <v>16</v>
       </c>
-      <c r="E59" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" t="s">
-        <v>22</v>
-      </c>
       <c r="H59" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I59" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K59">
         <v>100</v>
@@ -2723,7 +2768,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B60">
         <v>19</v>
@@ -2732,22 +2777,22 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K60">
         <v>100</v>
@@ -2758,7 +2803,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B61">
         <v>288</v>
@@ -2767,22 +2812,22 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" t="s">
         <v>16</v>
       </c>
-      <c r="E61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" t="s">
-        <v>22</v>
-      </c>
       <c r="H61" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K61">
         <v>100</v>
@@ -2802,22 +2847,22 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -2828,31 +2873,31 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" t="s">
         <v>15</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" t="s">
-        <v>52</v>
-      </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
       <c r="G63" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -2863,7 +2908,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B64">
         <v>35</v>
@@ -2872,22 +2917,22 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -2898,7 +2943,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B65">
         <v>102</v>
@@ -2907,22 +2952,22 @@
         <v>39</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K65">
         <v>100</v>
@@ -2933,7 +2978,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B66">
         <v>768</v>
@@ -2942,22 +2987,22 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -2977,25 +3022,25 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -3006,7 +3051,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3015,22 +3060,22 @@
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -3041,7 +3086,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B69">
         <v>20</v>
@@ -3050,22 +3095,22 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G69" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -3076,7 +3121,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B70">
         <v>58</v>
@@ -3085,22 +3130,22 @@
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -3111,7 +3156,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B71">
         <v>432</v>
@@ -3120,22 +3165,22 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -3155,22 +3200,22 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
         <v>35</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
         <v>36</v>
       </c>
       <c r="H72" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -3181,7 +3226,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B73">
         <v>3</v>
@@ -3190,22 +3235,22 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
         <v>35</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G73" t="s">
         <v>36</v>
       </c>
       <c r="H73" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -3216,7 +3261,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B74">
         <v>24</v>
@@ -3225,22 +3270,22 @@
         <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E74" t="s">
         <v>35</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
         <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -3251,7 +3296,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B75">
         <v>32</v>
@@ -3260,22 +3305,22 @@
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E75" t="s">
         <v>35</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
         <v>36</v>
       </c>
       <c r="H75" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -3286,7 +3331,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B76">
         <v>510</v>
@@ -3295,22 +3340,22 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
         <v>35</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
         <v>36</v>
       </c>
       <c r="H76" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -3330,22 +3375,22 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
         <v>36</v>
       </c>
       <c r="H77" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -3356,7 +3401,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B78">
         <v>5</v>
@@ -3365,22 +3410,22 @@
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
         <v>36</v>
       </c>
       <c r="H78" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -3391,7 +3436,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B79">
         <v>37</v>
@@ -3400,22 +3445,22 @@
         <v>7</v>
       </c>
       <c r="D79" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G79" t="s">
         <v>36</v>
       </c>
       <c r="H79" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -3426,7 +3471,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B80">
         <v>48</v>
@@ -3435,22 +3480,22 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F80" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G80" t="s">
         <v>36</v>
       </c>
       <c r="H80" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -3461,7 +3506,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B81">
         <v>765</v>
@@ -3470,22 +3515,22 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G81" t="s">
         <v>36</v>
       </c>
       <c r="H81" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K81">
         <v>100</v>
@@ -3505,25 +3550,25 @@
         <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G82" t="s">
         <v>36</v>
       </c>
       <c r="H82" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="K82">
         <v>100</v>
@@ -3534,7 +3579,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -3543,22 +3588,22 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G83" t="s">
         <v>36</v>
       </c>
       <c r="H83" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K83">
         <v>100</v>
@@ -3569,7 +3614,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B84">
         <v>11</v>
@@ -3578,22 +3623,22 @@
         <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
         <v>36</v>
       </c>
       <c r="H84" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K84">
         <v>100</v>
@@ -3604,7 +3649,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B85">
         <v>14</v>
@@ -3613,22 +3658,22 @@
         <v>19</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
         <v>36</v>
       </c>
       <c r="H85" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K85">
         <v>100</v>
@@ -3639,7 +3684,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B86">
         <v>225</v>
@@ -3648,22 +3693,22 @@
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G86" t="s">
         <v>36</v>
       </c>
       <c r="H86" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K86">
         <v>100</v>
@@ -3683,22 +3728,22 @@
         <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H87" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K87">
         <v>100</v>
@@ -3709,7 +3754,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -3718,22 +3763,22 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H88" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K88">
         <v>100</v>
@@ -3744,7 +3789,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B89">
         <v>35</v>
@@ -3753,22 +3798,22 @@
         <v>19</v>
       </c>
       <c r="D89" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E89" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H89" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K89">
         <v>100</v>
@@ -3779,7 +3824,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B90">
         <v>62</v>
@@ -3788,22 +3833,22 @@
         <v>47</v>
       </c>
       <c r="D90" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H90" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K90">
         <v>100</v>
@@ -3814,7 +3859,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B91">
         <v>420</v>
@@ -3823,22 +3868,22 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H91" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K91">
         <v>100</v>
@@ -3858,22 +3903,22 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E92" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G92" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H92" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K92">
         <v>100</v>
@@ -3884,7 +3929,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B93">
         <v>4</v>
@@ -3893,22 +3938,22 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G93" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I93" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K93">
         <v>100</v>
@@ -3919,7 +3964,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B94">
         <v>53</v>
@@ -3928,22 +3973,22 @@
         <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E94" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G94" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H94" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K94">
         <v>100</v>
@@ -3954,7 +3999,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B95">
         <v>92</v>
@@ -3963,22 +4008,22 @@
         <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G95" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H95" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K95">
         <v>100</v>
@@ -3989,7 +4034,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B96">
         <v>630</v>
@@ -3998,22 +4043,22 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E96" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G96" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H96" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K96">
         <v>100</v>
@@ -4033,25 +4078,25 @@
         <v>5</v>
       </c>
       <c r="D97" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E97" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H97" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K97">
         <v>100</v>
@@ -4062,7 +4107,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B98">
         <v>3</v>
@@ -4071,22 +4116,22 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H98" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K98">
         <v>100</v>
@@ -4097,7 +4142,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B99">
         <v>38</v>
@@ -4106,22 +4151,22 @@
         <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H99" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K99">
         <v>100</v>
@@ -4132,7 +4177,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B100">
         <v>66</v>
@@ -4141,22 +4186,22 @@
         <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H100" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I100" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K100">
         <v>100</v>
@@ -4167,7 +4212,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B101">
         <v>450</v>
@@ -4176,22 +4221,22 @@
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H101" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I101" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K101">
         <v>100</v>
@@ -4211,25 +4256,25 @@
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H102" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I102" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K102">
         <v>100</v>
@@ -4240,7 +4285,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -4249,25 +4294,25 @@
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H103" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I103" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J103" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K103">
         <v>100</v>
@@ -4278,7 +4323,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B104">
         <v>28</v>
@@ -4287,25 +4332,25 @@
         <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H104" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I104" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J104" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K104">
         <v>100</v>
@@ -4316,7 +4361,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B105">
         <v>56</v>
@@ -4325,25 +4370,25 @@
         <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F105" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H105" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I105" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J105" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K105">
         <v>100</v>
@@ -4354,7 +4399,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B106">
         <v>600</v>
@@ -4363,25 +4408,25 @@
         <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H106" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I106" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J106" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K106">
         <v>100</v>
@@ -4401,22 +4446,22 @@
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E107" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G107" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H107" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I107" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K107">
         <v>100</v>
@@ -4427,7 +4472,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -4436,22 +4481,22 @@
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G108" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H108" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I108" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K108">
         <v>100</v>
@@ -4462,7 +4507,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B109">
         <v>42</v>
@@ -4471,22 +4516,22 @@
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E109" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G109" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H109" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I109" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K109">
         <v>100</v>
@@ -4497,7 +4542,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B110">
         <v>84</v>
@@ -4506,22 +4551,22 @@
         <v>40</v>
       </c>
       <c r="D110" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H110" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I110" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K110">
         <v>100</v>
@@ -4532,7 +4577,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B111">
         <v>900</v>
@@ -4541,22 +4586,22 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G111" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H111" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I111" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K111">
         <v>100</v>
@@ -4576,22 +4621,22 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E112" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F112" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H112" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I112" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K112">
         <v>100</v>
@@ -4602,7 +4647,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -4611,22 +4656,22 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F113" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H113" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I113" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K113">
         <v>100</v>
@@ -4637,7 +4682,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B114">
         <v>42</v>
@@ -4649,19 +4694,19 @@
         <v>81</v>
       </c>
       <c r="E114" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F114" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H114" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I114" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K114">
         <v>100</v>
@@ -4672,7 +4717,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B115">
         <v>84</v>
@@ -4681,22 +4726,22 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F115" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H115" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I115" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K115">
         <v>100</v>
@@ -4707,7 +4752,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B116">
         <v>900</v>
@@ -4716,22 +4761,22 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F116" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G116" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H116" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I116" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K116">
         <v>100</v>
@@ -4740,8 +4785,713 @@
         <v>17.8</v>
       </c>
     </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117">
+        <v>19</v>
+      </c>
+      <c r="C117">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>82</v>
+      </c>
+      <c r="E117" t="s">
+        <v>83</v>
+      </c>
+      <c r="F117" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>84</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" t="s">
+        <v>85</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118">
+        <v>4</v>
+      </c>
+      <c r="C118">
+        <v>2</v>
+      </c>
+      <c r="D118" t="s">
+        <v>57</v>
+      </c>
+      <c r="E118" t="s">
+        <v>83</v>
+      </c>
+      <c r="F118" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>84</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118">
+        <v>100</v>
+      </c>
+      <c r="L118">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>21</v>
+      </c>
+      <c r="B119">
+        <v>19</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>86</v>
+      </c>
+      <c r="E119" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>84</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119">
+        <v>100</v>
+      </c>
+      <c r="L119">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120">
+        <v>65</v>
+      </c>
+      <c r="C120">
+        <v>32</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" t="s">
+        <v>83</v>
+      </c>
+      <c r="F120" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>84</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120">
+        <v>100</v>
+      </c>
+      <c r="L120">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121">
+        <v>465</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121" t="s">
+        <v>83</v>
+      </c>
+      <c r="F121" t="s">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>84</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122">
+        <v>29</v>
+      </c>
+      <c r="C122">
+        <v>30</v>
+      </c>
+      <c r="D122" t="s">
+        <v>87</v>
+      </c>
+      <c r="E122" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G122" t="s">
+        <v>84</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122">
+        <v>100</v>
+      </c>
+      <c r="L122">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123">
+        <v>7</v>
+      </c>
+      <c r="C123">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>89</v>
+      </c>
+      <c r="E123" t="s">
+        <v>88</v>
+      </c>
+      <c r="F123" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" t="s">
+        <v>84</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123">
+        <v>100</v>
+      </c>
+      <c r="L123">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124">
+        <v>28</v>
+      </c>
+      <c r="C124">
+        <v>20</v>
+      </c>
+      <c r="D124" t="s">
+        <v>90</v>
+      </c>
+      <c r="E124" t="s">
+        <v>88</v>
+      </c>
+      <c r="F124" t="s">
+        <v>27</v>
+      </c>
+      <c r="G124" t="s">
+        <v>84</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124">
+        <v>100</v>
+      </c>
+      <c r="L124">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>23</v>
+      </c>
+      <c r="B125">
+        <v>98</v>
+      </c>
+      <c r="C125">
+        <v>79</v>
+      </c>
+      <c r="D125" t="s">
+        <v>91</v>
+      </c>
+      <c r="E125" t="s">
+        <v>88</v>
+      </c>
+      <c r="F125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G125" t="s">
+        <v>84</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125">
+        <v>100</v>
+      </c>
+      <c r="L125">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126">
+        <v>698</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" t="s">
+        <v>88</v>
+      </c>
+      <c r="F126" t="s">
+        <v>27</v>
+      </c>
+      <c r="G126" t="s">
+        <v>84</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126">
+        <v>100</v>
+      </c>
+      <c r="L126">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127">
+        <v>14</v>
+      </c>
+      <c r="C127">
+        <v>4</v>
+      </c>
+      <c r="D127" t="s">
+        <v>92</v>
+      </c>
+      <c r="E127" t="s">
+        <v>93</v>
+      </c>
+      <c r="F127" t="s">
+        <v>27</v>
+      </c>
+      <c r="G127" t="s">
+        <v>84</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" t="s">
+        <v>94</v>
+      </c>
+      <c r="K127">
+        <v>100</v>
+      </c>
+      <c r="L127">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128" t="s">
+        <v>93</v>
+      </c>
+      <c r="F128" t="s">
+        <v>27</v>
+      </c>
+      <c r="G128" t="s">
+        <v>84</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="K128">
+        <v>100</v>
+      </c>
+      <c r="L128">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>21</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="C129">
+        <v>8</v>
+      </c>
+      <c r="D129" t="s">
+        <v>95</v>
+      </c>
+      <c r="E129" t="s">
+        <v>93</v>
+      </c>
+      <c r="F129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G129" t="s">
+        <v>84</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129">
+        <v>100</v>
+      </c>
+      <c r="L129">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>23</v>
+      </c>
+      <c r="B130">
+        <v>47</v>
+      </c>
+      <c r="C130">
+        <v>35</v>
+      </c>
+      <c r="D130" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130" t="s">
+        <v>93</v>
+      </c>
+      <c r="F130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G130" t="s">
+        <v>84</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130">
+        <v>100</v>
+      </c>
+      <c r="L130">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131">
+        <v>338</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" t="s">
+        <v>93</v>
+      </c>
+      <c r="F131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G131" t="s">
+        <v>84</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131">
+        <v>100</v>
+      </c>
+      <c r="L131">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132">
+        <v>23</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132" t="s">
+        <v>96</v>
+      </c>
+      <c r="E132" t="s">
+        <v>97</v>
+      </c>
+      <c r="F132" t="s">
+        <v>80</v>
+      </c>
+      <c r="G132" t="s">
+        <v>84</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132">
+        <v>100</v>
+      </c>
+      <c r="L132">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133" t="s">
+        <v>78</v>
+      </c>
+      <c r="E133" t="s">
+        <v>97</v>
+      </c>
+      <c r="F133" t="s">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s">
+        <v>84</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133">
+        <v>100</v>
+      </c>
+      <c r="L133">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B134">
+        <v>23</v>
+      </c>
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>46</v>
+      </c>
+      <c r="E134" t="s">
+        <v>97</v>
+      </c>
+      <c r="F134" t="s">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s">
+        <v>84</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134">
+        <v>100</v>
+      </c>
+      <c r="L134">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135">
+        <v>79</v>
+      </c>
+      <c r="C135">
+        <v>8</v>
+      </c>
+      <c r="D135" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" t="s">
+        <v>97</v>
+      </c>
+      <c r="F135" t="s">
+        <v>80</v>
+      </c>
+      <c r="G135" t="s">
+        <v>84</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+      <c r="K135">
+        <v>100</v>
+      </c>
+      <c r="L135">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136">
+        <v>563</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136" t="s">
+        <v>97</v>
+      </c>
+      <c r="F136" t="s">
+        <v>80</v>
+      </c>
+      <c r="G136" t="s">
+        <v>84</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136">
+        <v>100</v>
+      </c>
+      <c r="L136">
+        <v>13.9</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C18536F-092E-4829-B955-5BB013648117}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{961B8A04-CE07-424F-AC65-25F6401EAF43}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -5492,6 +5495,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{961B8A04-CE07-424F-AC65-25F6401EAF43}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30FADAC5-54D2-4BA3-9155-37417AC802E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="136">
   <si>
     <t>Producto</t>
   </si>
@@ -317,6 +317,120 @@
   </si>
   <si>
     <t>Johan Daniel Herrera Mazo</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>8%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>Meta 352</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>Meta otros 106</t>
+  </si>
+  <si>
+    <t>Meta terminales 52</t>
+  </si>
+  <si>
+    <t>Meta Hogar 3</t>
+  </si>
+  <si>
+    <t>Meta puntos 1595          - meta post 33</t>
+  </si>
+  <si>
+    <t>86%</t>
+  </si>
+  <si>
+    <t>Nasly Johanna Martinez Ocampo</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>225%</t>
+  </si>
+  <si>
+    <t>154%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>136%</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>132%</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>Calamidad 3 días</t>
+  </si>
+  <si>
+    <t>123%</t>
+  </si>
+  <si>
+    <t>Luz Enith Sanchez Galeano</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>131%</t>
+  </si>
+  <si>
+    <t>Lider Paola Andrea Clavijo</t>
+  </si>
+  <si>
+    <t>122%</t>
+  </si>
+  <si>
+    <t>80%</t>
   </si>
 </sst>
 </file>
@@ -680,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:L191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -5492,6 +5606,1949 @@
       </c>
       <c r="L136">
         <v>13.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137">
+        <v>21</v>
+      </c>
+      <c r="C137">
+        <v>27</v>
+      </c>
+      <c r="D137" t="s">
+        <v>89</v>
+      </c>
+      <c r="E137" t="s">
+        <v>133</v>
+      </c>
+      <c r="F137" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" t="s">
+        <v>122</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137">
+        <v>100</v>
+      </c>
+      <c r="L137">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>19</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138">
+        <v>4</v>
+      </c>
+      <c r="D138" t="s">
+        <v>135</v>
+      </c>
+      <c r="E138" t="s">
+        <v>133</v>
+      </c>
+      <c r="F138" t="s">
+        <v>15</v>
+      </c>
+      <c r="G138" t="s">
+        <v>122</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138">
+        <v>100</v>
+      </c>
+      <c r="L138">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139">
+        <v>24</v>
+      </c>
+      <c r="C139">
+        <v>13</v>
+      </c>
+      <c r="D139" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" t="s">
+        <v>133</v>
+      </c>
+      <c r="F139" t="s">
+        <v>15</v>
+      </c>
+      <c r="G139" t="s">
+        <v>122</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139">
+        <v>100</v>
+      </c>
+      <c r="L139">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>23</v>
+      </c>
+      <c r="B140">
+        <v>51</v>
+      </c>
+      <c r="C140">
+        <v>62</v>
+      </c>
+      <c r="D140" t="s">
+        <v>134</v>
+      </c>
+      <c r="E140" t="s">
+        <v>133</v>
+      </c>
+      <c r="F140" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" t="s">
+        <v>122</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>18</v>
+      </c>
+      <c r="K140">
+        <v>100</v>
+      </c>
+      <c r="L140">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141">
+        <v>402</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>20</v>
+      </c>
+      <c r="E141" t="s">
+        <v>133</v>
+      </c>
+      <c r="F141" t="s">
+        <v>15</v>
+      </c>
+      <c r="G141" t="s">
+        <v>122</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141">
+        <v>100</v>
+      </c>
+      <c r="L141">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142">
+        <v>32</v>
+      </c>
+      <c r="C142">
+        <v>42</v>
+      </c>
+      <c r="D142" t="s">
+        <v>132</v>
+      </c>
+      <c r="E142" t="s">
+        <v>129</v>
+      </c>
+      <c r="F142" t="s">
+        <v>27</v>
+      </c>
+      <c r="G142" t="s">
+        <v>122</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142">
+        <v>100</v>
+      </c>
+      <c r="L142">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143">
+        <v>8</v>
+      </c>
+      <c r="C143">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>131</v>
+      </c>
+      <c r="E143" t="s">
+        <v>129</v>
+      </c>
+      <c r="F143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G143" t="s">
+        <v>122</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143">
+        <v>100</v>
+      </c>
+      <c r="L143">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>21</v>
+      </c>
+      <c r="B144">
+        <v>36</v>
+      </c>
+      <c r="C144">
+        <v>31</v>
+      </c>
+      <c r="D144" t="s">
+        <v>108</v>
+      </c>
+      <c r="E144" t="s">
+        <v>129</v>
+      </c>
+      <c r="F144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G144" t="s">
+        <v>122</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144">
+        <v>100</v>
+      </c>
+      <c r="L144">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>23</v>
+      </c>
+      <c r="B145">
+        <v>76</v>
+      </c>
+      <c r="C145">
+        <v>85</v>
+      </c>
+      <c r="D145" t="s">
+        <v>130</v>
+      </c>
+      <c r="E145" t="s">
+        <v>129</v>
+      </c>
+      <c r="F145" t="s">
+        <v>27</v>
+      </c>
+      <c r="G145" t="s">
+        <v>122</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145">
+        <v>100</v>
+      </c>
+      <c r="L145">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146">
+        <v>603</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146" t="s">
+        <v>20</v>
+      </c>
+      <c r="E146" t="s">
+        <v>129</v>
+      </c>
+      <c r="F146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G146" t="s">
+        <v>122</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146">
+        <v>100</v>
+      </c>
+      <c r="L146">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147">
+        <v>26</v>
+      </c>
+      <c r="C147">
+        <v>32</v>
+      </c>
+      <c r="D147" t="s">
+        <v>128</v>
+      </c>
+      <c r="E147" t="s">
+        <v>124</v>
+      </c>
+      <c r="F147" t="s">
+        <v>27</v>
+      </c>
+      <c r="G147" t="s">
+        <v>122</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" t="s">
+        <v>127</v>
+      </c>
+      <c r="K147">
+        <v>100</v>
+      </c>
+      <c r="L147">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>19</v>
+      </c>
+      <c r="B148">
+        <v>7</v>
+      </c>
+      <c r="C148">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>108</v>
+      </c>
+      <c r="E148" t="s">
+        <v>124</v>
+      </c>
+      <c r="F148" t="s">
+        <v>27</v>
+      </c>
+      <c r="G148" t="s">
+        <v>122</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148">
+        <v>100</v>
+      </c>
+      <c r="L148">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>21</v>
+      </c>
+      <c r="B149">
+        <v>30</v>
+      </c>
+      <c r="C149">
+        <v>18</v>
+      </c>
+      <c r="D149" t="s">
+        <v>126</v>
+      </c>
+      <c r="E149" t="s">
+        <v>124</v>
+      </c>
+      <c r="F149" t="s">
+        <v>27</v>
+      </c>
+      <c r="G149" t="s">
+        <v>122</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149">
+        <v>100</v>
+      </c>
+      <c r="L149">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>23</v>
+      </c>
+      <c r="B150">
+        <v>63</v>
+      </c>
+      <c r="C150">
+        <v>83</v>
+      </c>
+      <c r="D150" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" t="s">
+        <v>124</v>
+      </c>
+      <c r="F150" t="s">
+        <v>27</v>
+      </c>
+      <c r="G150" t="s">
+        <v>122</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150">
+        <v>100</v>
+      </c>
+      <c r="L150">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151">
+        <v>495</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151" t="s">
+        <v>20</v>
+      </c>
+      <c r="E151" t="s">
+        <v>124</v>
+      </c>
+      <c r="F151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G151" t="s">
+        <v>122</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151">
+        <v>100</v>
+      </c>
+      <c r="L151">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152">
+        <v>30</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152" t="s">
+        <v>20</v>
+      </c>
+      <c r="E152" t="s">
+        <v>101</v>
+      </c>
+      <c r="F152" t="s">
+        <v>80</v>
+      </c>
+      <c r="G152" t="s">
+        <v>122</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>18</v>
+      </c>
+      <c r="K152">
+        <v>100</v>
+      </c>
+      <c r="L152">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>19</v>
+      </c>
+      <c r="B153">
+        <v>8</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" t="s">
+        <v>101</v>
+      </c>
+      <c r="F153" t="s">
+        <v>80</v>
+      </c>
+      <c r="G153" t="s">
+        <v>122</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153">
+        <v>100</v>
+      </c>
+      <c r="L153">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>21</v>
+      </c>
+      <c r="B154">
+        <v>34</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154" t="s">
+        <v>20</v>
+      </c>
+      <c r="E154" t="s">
+        <v>101</v>
+      </c>
+      <c r="F154" t="s">
+        <v>80</v>
+      </c>
+      <c r="G154" t="s">
+        <v>122</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154">
+        <v>100</v>
+      </c>
+      <c r="L154">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>23</v>
+      </c>
+      <c r="B155">
+        <v>71</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" t="s">
+        <v>101</v>
+      </c>
+      <c r="F155" t="s">
+        <v>80</v>
+      </c>
+      <c r="G155" t="s">
+        <v>122</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" t="s">
+        <v>18</v>
+      </c>
+      <c r="K155">
+        <v>100</v>
+      </c>
+      <c r="L155">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B156">
+        <v>563</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>20</v>
+      </c>
+      <c r="E156" t="s">
+        <v>101</v>
+      </c>
+      <c r="F156" t="s">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s">
+        <v>122</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156">
+        <v>100</v>
+      </c>
+      <c r="L156">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157">
+        <v>30</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157" t="s">
+        <v>20</v>
+      </c>
+      <c r="E157" t="s">
+        <v>79</v>
+      </c>
+      <c r="F157" t="s">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s">
+        <v>122</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157">
+        <v>100</v>
+      </c>
+      <c r="L157">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>19</v>
+      </c>
+      <c r="B158">
+        <v>8</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158" t="s">
+        <v>20</v>
+      </c>
+      <c r="E158" t="s">
+        <v>79</v>
+      </c>
+      <c r="F158" t="s">
+        <v>80</v>
+      </c>
+      <c r="G158" t="s">
+        <v>122</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158">
+        <v>100</v>
+      </c>
+      <c r="L158">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159">
+        <v>34</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+      <c r="D159" t="s">
+        <v>123</v>
+      </c>
+      <c r="E159" t="s">
+        <v>79</v>
+      </c>
+      <c r="F159" t="s">
+        <v>80</v>
+      </c>
+      <c r="G159" t="s">
+        <v>122</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159">
+        <v>100</v>
+      </c>
+      <c r="L159">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>23</v>
+      </c>
+      <c r="B160">
+        <v>71</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" t="s">
+        <v>79</v>
+      </c>
+      <c r="F160" t="s">
+        <v>80</v>
+      </c>
+      <c r="G160" t="s">
+        <v>122</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160">
+        <v>100</v>
+      </c>
+      <c r="L160">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="B161">
+        <v>563</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>20</v>
+      </c>
+      <c r="E161" t="s">
+        <v>79</v>
+      </c>
+      <c r="F161" t="s">
+        <v>80</v>
+      </c>
+      <c r="G161" t="s">
+        <v>122</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161">
+        <v>100</v>
+      </c>
+      <c r="L161">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162">
+        <v>28</v>
+      </c>
+      <c r="C162">
+        <v>38</v>
+      </c>
+      <c r="D162" t="s">
+        <v>121</v>
+      </c>
+      <c r="E162" t="s">
+        <v>118</v>
+      </c>
+      <c r="F162" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" t="s">
+        <v>98</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162">
+        <v>100</v>
+      </c>
+      <c r="L162">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>19</v>
+      </c>
+      <c r="B163">
+        <v>3</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
+        <v>120</v>
+      </c>
+      <c r="E163" t="s">
+        <v>118</v>
+      </c>
+      <c r="F163" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" t="s">
+        <v>98</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163">
+        <v>100</v>
+      </c>
+      <c r="L163">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164">
+        <v>44</v>
+      </c>
+      <c r="C164">
+        <v>33</v>
+      </c>
+      <c r="D164" t="s">
+        <v>119</v>
+      </c>
+      <c r="E164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F164" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" t="s">
+        <v>98</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164">
+        <v>100</v>
+      </c>
+      <c r="L164">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>23</v>
+      </c>
+      <c r="B165">
+        <v>90</v>
+      </c>
+      <c r="C165">
+        <v>180</v>
+      </c>
+      <c r="D165" t="s">
+        <v>51</v>
+      </c>
+      <c r="E165" t="s">
+        <v>118</v>
+      </c>
+      <c r="F165" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" t="s">
+        <v>98</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165">
+        <v>100</v>
+      </c>
+      <c r="L165">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166">
+        <v>300</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>20</v>
+      </c>
+      <c r="E166" t="s">
+        <v>118</v>
+      </c>
+      <c r="F166" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" t="s">
+        <v>98</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166">
+        <v>100</v>
+      </c>
+      <c r="L166">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>12</v>
+      </c>
+      <c r="B167">
+        <v>37</v>
+      </c>
+      <c r="C167">
+        <v>41</v>
+      </c>
+      <c r="D167" t="s">
+        <v>117</v>
+      </c>
+      <c r="E167" t="s">
+        <v>114</v>
+      </c>
+      <c r="F167" t="s">
+        <v>27</v>
+      </c>
+      <c r="G167" t="s">
+        <v>98</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167">
+        <v>100</v>
+      </c>
+      <c r="L167">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168">
+        <v>4</v>
+      </c>
+      <c r="D168" t="s">
+        <v>52</v>
+      </c>
+      <c r="E168" t="s">
+        <v>114</v>
+      </c>
+      <c r="F168" t="s">
+        <v>27</v>
+      </c>
+      <c r="G168" t="s">
+        <v>98</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168">
+        <v>100</v>
+      </c>
+      <c r="L168">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>21</v>
+      </c>
+      <c r="B169">
+        <v>59</v>
+      </c>
+      <c r="C169">
+        <v>53</v>
+      </c>
+      <c r="D169" t="s">
+        <v>116</v>
+      </c>
+      <c r="E169" t="s">
+        <v>114</v>
+      </c>
+      <c r="F169" t="s">
+        <v>27</v>
+      </c>
+      <c r="G169" t="s">
+        <v>98</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169">
+        <v>100</v>
+      </c>
+      <c r="L169">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>23</v>
+      </c>
+      <c r="B170">
+        <v>120</v>
+      </c>
+      <c r="C170">
+        <v>115</v>
+      </c>
+      <c r="D170" t="s">
+        <v>115</v>
+      </c>
+      <c r="E170" t="s">
+        <v>114</v>
+      </c>
+      <c r="F170" t="s">
+        <v>27</v>
+      </c>
+      <c r="G170" t="s">
+        <v>98</v>
+      </c>
+      <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170">
+        <v>100</v>
+      </c>
+      <c r="L170">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171">
+        <v>399</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>20</v>
+      </c>
+      <c r="E171" t="s">
+        <v>114</v>
+      </c>
+      <c r="F171" t="s">
+        <v>27</v>
+      </c>
+      <c r="G171" t="s">
+        <v>98</v>
+      </c>
+      <c r="H171" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171">
+        <v>100</v>
+      </c>
+      <c r="L171">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B172">
+        <v>37</v>
+      </c>
+      <c r="C172">
+        <v>57</v>
+      </c>
+      <c r="D172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E172" t="s">
+        <v>109</v>
+      </c>
+      <c r="F172" t="s">
+        <v>27</v>
+      </c>
+      <c r="G172" t="s">
+        <v>98</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172">
+        <v>100</v>
+      </c>
+      <c r="L172">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>19</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173">
+        <v>9</v>
+      </c>
+      <c r="D173" t="s">
+        <v>112</v>
+      </c>
+      <c r="E173" t="s">
+        <v>109</v>
+      </c>
+      <c r="F173" t="s">
+        <v>27</v>
+      </c>
+      <c r="G173" t="s">
+        <v>98</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173">
+        <v>100</v>
+      </c>
+      <c r="L173">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174">
+        <v>59</v>
+      </c>
+      <c r="C174">
+        <v>58</v>
+      </c>
+      <c r="D174" t="s">
+        <v>111</v>
+      </c>
+      <c r="E174" t="s">
+        <v>109</v>
+      </c>
+      <c r="F174" t="s">
+        <v>27</v>
+      </c>
+      <c r="G174" t="s">
+        <v>98</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174">
+        <v>100</v>
+      </c>
+      <c r="L174">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>23</v>
+      </c>
+      <c r="B175">
+        <v>120</v>
+      </c>
+      <c r="C175">
+        <v>141</v>
+      </c>
+      <c r="D175" t="s">
+        <v>110</v>
+      </c>
+      <c r="E175" t="s">
+        <v>109</v>
+      </c>
+      <c r="F175" t="s">
+        <v>27</v>
+      </c>
+      <c r="G175" t="s">
+        <v>98</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175">
+        <v>100</v>
+      </c>
+      <c r="L175">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>25</v>
+      </c>
+      <c r="B176">
+        <v>399</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>20</v>
+      </c>
+      <c r="E176" t="s">
+        <v>109</v>
+      </c>
+      <c r="F176" t="s">
+        <v>27</v>
+      </c>
+      <c r="G176" t="s">
+        <v>98</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176">
+        <v>100</v>
+      </c>
+      <c r="L176">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>12</v>
+      </c>
+      <c r="B177">
+        <v>37</v>
+      </c>
+      <c r="C177">
+        <v>32</v>
+      </c>
+      <c r="D177" t="s">
+        <v>108</v>
+      </c>
+      <c r="E177" t="s">
+        <v>103</v>
+      </c>
+      <c r="F177" t="s">
+        <v>27</v>
+      </c>
+      <c r="G177" t="s">
+        <v>98</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" t="s">
+        <v>107</v>
+      </c>
+      <c r="K177">
+        <v>100</v>
+      </c>
+      <c r="L177">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>19</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
+        <v>54</v>
+      </c>
+      <c r="E178" t="s">
+        <v>103</v>
+      </c>
+      <c r="F178" t="s">
+        <v>27</v>
+      </c>
+      <c r="G178" t="s">
+        <v>98</v>
+      </c>
+      <c r="H178" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" t="s">
+        <v>106</v>
+      </c>
+      <c r="K178">
+        <v>100</v>
+      </c>
+      <c r="L178">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>21</v>
+      </c>
+      <c r="B179">
+        <v>59</v>
+      </c>
+      <c r="C179">
+        <v>40</v>
+      </c>
+      <c r="D179" t="s">
+        <v>82</v>
+      </c>
+      <c r="E179" t="s">
+        <v>103</v>
+      </c>
+      <c r="F179" t="s">
+        <v>27</v>
+      </c>
+      <c r="G179" t="s">
+        <v>98</v>
+      </c>
+      <c r="H179" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" t="s">
+        <v>105</v>
+      </c>
+      <c r="K179">
+        <v>100</v>
+      </c>
+      <c r="L179">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>23</v>
+      </c>
+      <c r="B180">
+        <v>120</v>
+      </c>
+      <c r="C180">
+        <v>116</v>
+      </c>
+      <c r="D180" t="s">
+        <v>24</v>
+      </c>
+      <c r="E180" t="s">
+        <v>103</v>
+      </c>
+      <c r="F180" t="s">
+        <v>27</v>
+      </c>
+      <c r="G180" t="s">
+        <v>98</v>
+      </c>
+      <c r="H180" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" t="s">
+        <v>18</v>
+      </c>
+      <c r="J180" t="s">
+        <v>104</v>
+      </c>
+      <c r="K180">
+        <v>100</v>
+      </c>
+      <c r="L180">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>25</v>
+      </c>
+      <c r="B181">
+        <v>399</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181" t="s">
+        <v>20</v>
+      </c>
+      <c r="E181" t="s">
+        <v>103</v>
+      </c>
+      <c r="F181" t="s">
+        <v>27</v>
+      </c>
+      <c r="G181" t="s">
+        <v>98</v>
+      </c>
+      <c r="H181" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" t="s">
+        <v>102</v>
+      </c>
+      <c r="K181">
+        <v>100</v>
+      </c>
+      <c r="L181">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182">
+        <v>37</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182" t="s">
+        <v>20</v>
+      </c>
+      <c r="E182" t="s">
+        <v>101</v>
+      </c>
+      <c r="F182" t="s">
+        <v>80</v>
+      </c>
+      <c r="G182" t="s">
+        <v>98</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182" t="s">
+        <v>18</v>
+      </c>
+      <c r="K182">
+        <v>100</v>
+      </c>
+      <c r="L182">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183" t="s">
+        <v>20</v>
+      </c>
+      <c r="E183" t="s">
+        <v>101</v>
+      </c>
+      <c r="F183" t="s">
+        <v>80</v>
+      </c>
+      <c r="G183" t="s">
+        <v>98</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" t="s">
+        <v>18</v>
+      </c>
+      <c r="K183">
+        <v>100</v>
+      </c>
+      <c r="L183">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>21</v>
+      </c>
+      <c r="B184">
+        <v>59</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184" t="s">
+        <v>20</v>
+      </c>
+      <c r="E184" t="s">
+        <v>101</v>
+      </c>
+      <c r="F184" t="s">
+        <v>80</v>
+      </c>
+      <c r="G184" t="s">
+        <v>98</v>
+      </c>
+      <c r="H184" t="s">
+        <v>17</v>
+      </c>
+      <c r="I184" t="s">
+        <v>18</v>
+      </c>
+      <c r="K184">
+        <v>100</v>
+      </c>
+      <c r="L184">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>23</v>
+      </c>
+      <c r="B185">
+        <v>120</v>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+      <c r="D185" t="s">
+        <v>24</v>
+      </c>
+      <c r="E185" t="s">
+        <v>101</v>
+      </c>
+      <c r="F185" t="s">
+        <v>80</v>
+      </c>
+      <c r="G185" t="s">
+        <v>98</v>
+      </c>
+      <c r="H185" t="s">
+        <v>17</v>
+      </c>
+      <c r="I185" t="s">
+        <v>18</v>
+      </c>
+      <c r="K185">
+        <v>100</v>
+      </c>
+      <c r="L185">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>25</v>
+      </c>
+      <c r="B186">
+        <v>399</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>20</v>
+      </c>
+      <c r="E186" t="s">
+        <v>101</v>
+      </c>
+      <c r="F186" t="s">
+        <v>80</v>
+      </c>
+      <c r="G186" t="s">
+        <v>98</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186" t="s">
+        <v>18</v>
+      </c>
+      <c r="K186">
+        <v>100</v>
+      </c>
+      <c r="L186">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>12</v>
+      </c>
+      <c r="B187">
+        <v>37</v>
+      </c>
+      <c r="C187">
+        <v>4</v>
+      </c>
+      <c r="D187" t="s">
+        <v>100</v>
+      </c>
+      <c r="E187" t="s">
+        <v>79</v>
+      </c>
+      <c r="F187" t="s">
+        <v>80</v>
+      </c>
+      <c r="G187" t="s">
+        <v>98</v>
+      </c>
+      <c r="H187" t="s">
+        <v>17</v>
+      </c>
+      <c r="I187" t="s">
+        <v>18</v>
+      </c>
+      <c r="K187">
+        <v>100</v>
+      </c>
+      <c r="L187">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>19</v>
+      </c>
+      <c r="B188">
+        <v>4</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>54</v>
+      </c>
+      <c r="E188" t="s">
+        <v>79</v>
+      </c>
+      <c r="F188" t="s">
+        <v>80</v>
+      </c>
+      <c r="G188" t="s">
+        <v>98</v>
+      </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
+      <c r="I188" t="s">
+        <v>18</v>
+      </c>
+      <c r="K188">
+        <v>100</v>
+      </c>
+      <c r="L188">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189">
+        <v>59</v>
+      </c>
+      <c r="C189">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>99</v>
+      </c>
+      <c r="E189" t="s">
+        <v>79</v>
+      </c>
+      <c r="F189" t="s">
+        <v>80</v>
+      </c>
+      <c r="G189" t="s">
+        <v>98</v>
+      </c>
+      <c r="H189" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189">
+        <v>100</v>
+      </c>
+      <c r="L189">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>23</v>
+      </c>
+      <c r="B190">
+        <v>120</v>
+      </c>
+      <c r="C190">
+        <v>4</v>
+      </c>
+      <c r="D190" t="s">
+        <v>24</v>
+      </c>
+      <c r="E190" t="s">
+        <v>79</v>
+      </c>
+      <c r="F190" t="s">
+        <v>80</v>
+      </c>
+      <c r="G190" t="s">
+        <v>98</v>
+      </c>
+      <c r="H190" t="s">
+        <v>17</v>
+      </c>
+      <c r="I190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190">
+        <v>100</v>
+      </c>
+      <c r="L190">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>25</v>
+      </c>
+      <c r="B191">
+        <v>399</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191" t="s">
+        <v>20</v>
+      </c>
+      <c r="E191" t="s">
+        <v>79</v>
+      </c>
+      <c r="F191" t="s">
+        <v>80</v>
+      </c>
+      <c r="G191" t="s">
+        <v>98</v>
+      </c>
+      <c r="H191" t="s">
+        <v>17</v>
+      </c>
+      <c r="I191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191">
+        <v>100</v>
+      </c>
+      <c r="L191">
+        <v>8.3000000000000007</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_3A3DD0641462DC0F62355476585DCE3A87449165" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A1CC77F-32F7-4FF8-B943-CF926F0C1630}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30FADAC5-54D2-4BA3-9155-37417AC802E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$230</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="831" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="136">
   <si>
     <t>Producto</t>
   </si>
@@ -64,9 +64,21 @@
     <t>POSTPAGO</t>
   </si>
   <si>
+    <t>7%</t>
+  </si>
+  <si>
+    <t>Lider Don Matias Diana Ruiz</t>
+  </si>
+  <si>
     <t>LIDER</t>
   </si>
   <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
     <t>Sin pago (0%)</t>
   </si>
   <si>
@@ -79,196 +91,346 @@
     <t>TERMINALES</t>
   </si>
   <si>
+    <t>12%</t>
+  </si>
+  <si>
     <t>OTROS</t>
   </si>
   <si>
+    <t>Pendiente 4 porta pre</t>
+  </si>
+  <si>
     <t>CVS PLUS</t>
   </si>
   <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
+  </si>
+  <si>
     <t>ASESOR</t>
   </si>
   <si>
-    <t>Lider Don Matias Diana Ruiz</t>
-  </si>
-  <si>
-    <t>DON MATIAS</t>
+    <t>Vacaciones del 3 al 22 de julio</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>Vacaciones del 26 de jun al 13 de julio</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>21%</t>
+  </si>
+  <si>
+    <t>Evelis Mary Ojeda Baldovino</t>
+  </si>
+  <si>
+    <t>19%</t>
+  </si>
+  <si>
+    <t>160%</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vac del 14 al 31 de julio </t>
+  </si>
+  <si>
+    <t>109%</t>
+  </si>
+  <si>
+    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+  </si>
+  <si>
+    <t>COPACABANA</t>
   </si>
   <si>
     <t>22%</t>
   </si>
   <si>
+    <t>Meta terminales 33</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>Alexandra Patricia Duque</t>
+  </si>
+  <si>
+    <t>Vac del 14 al 31 de julio</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>25%</t>
+  </si>
+  <si>
+    <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>14%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
     <t>38%</t>
   </si>
   <si>
-    <t>Evelyn Daniela Lopera Lopera</t>
-  </si>
-  <si>
-    <t>200%</t>
-  </si>
-  <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>115%</t>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t>34%</t>
+  </si>
+  <si>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vac del 18 de junio al 6 de julio </t>
+  </si>
+  <si>
+    <t>13%</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>Ingresa de vac el 4  Meta puntos 890.4      Meta post 12</t>
+  </si>
+  <si>
+    <t>Hogar 1</t>
+  </si>
+  <si>
+    <t>Terminales  24</t>
+  </si>
+  <si>
+    <t>Otros 47</t>
+  </si>
+  <si>
+    <t>CVS PLUS 504</t>
+  </si>
+  <si>
+    <t>48%</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Posada Galeano</t>
+  </si>
+  <si>
+    <t>40%</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
   </si>
   <si>
     <t>SUPERNUMERARIO</t>
   </si>
   <si>
-    <t>Sara Julieth Acevedo Gutierrez</t>
-  </si>
-  <si>
-    <t>25%</t>
-  </si>
-  <si>
-    <t>40%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>Maria Fernanda Posada Galeano</t>
-  </si>
-  <si>
-    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
-  </si>
-  <si>
-    <t>BARBOSA</t>
-  </si>
-  <si>
-    <t>Evelis Mary Ojeda Baldovino</t>
-  </si>
-  <si>
-    <t>Sene Del Socorro Suarez Torres</t>
-  </si>
-  <si>
-    <t>50%</t>
-  </si>
-  <si>
-    <t>14%</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>Lider Luz Stella Serna</t>
-  </si>
-  <si>
-    <t>TERMINAL NORTE</t>
-  </si>
-  <si>
-    <t>Lider Yolima Mesa Zapata</t>
-  </si>
-  <si>
-    <t>CALDAS</t>
-  </si>
-  <si>
-    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>2026-07</t>
-  </si>
-  <si>
-    <t>Pendiente 4 porta pre</t>
-  </si>
-  <si>
-    <t>Vacaciones del 3 al 22 de julio</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>Lider Geraldin Angulo Jaramillo</t>
-  </si>
-  <si>
-    <t>YARUMAL</t>
-  </si>
-  <si>
-    <t>31%</t>
-  </si>
-  <si>
-    <t>Laura Carolina Chavarria Amariles</t>
-  </si>
-  <si>
-    <t>Vacaciones del 26 de jun al 13 de julio</t>
-  </si>
-  <si>
-    <t>21%</t>
-  </si>
-  <si>
-    <t>19%</t>
-  </si>
-  <si>
-    <t>160%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vac del 14 al 31 de julio </t>
-  </si>
-  <si>
-    <t>109%</t>
-  </si>
-  <si>
-    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
-  </si>
-  <si>
-    <t>COPACABANA</t>
-  </si>
-  <si>
-    <t>Meta terminales 33</t>
-  </si>
-  <si>
-    <t>150%</t>
-  </si>
-  <si>
-    <t>Alexandra Patricia Duque</t>
-  </si>
-  <si>
-    <t>Vac del 14 al 31 de julio</t>
-  </si>
-  <si>
-    <t>Bibiana Farley Rios Agudelo</t>
-  </si>
-  <si>
-    <t>54%</t>
-  </si>
-  <si>
-    <t>Darinela  Chavarria Carvajal</t>
-  </si>
-  <si>
-    <t>34%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vac del 18 de junio al 6 de julio </t>
-  </si>
-  <si>
-    <t>13%</t>
-  </si>
-  <si>
-    <t>36%</t>
-  </si>
-  <si>
-    <t>Ingresa de vac el 4  Meta puntos 890.4      Meta post 12</t>
-  </si>
-  <si>
-    <t>Hogar 1</t>
-  </si>
-  <si>
-    <t>Terminales  24</t>
-  </si>
-  <si>
-    <t>Otros 47</t>
-  </si>
-  <si>
-    <t>CVS PLUS 504</t>
-  </si>
-  <si>
-    <t>48%</t>
-  </si>
-  <si>
     <t>26%</t>
+  </si>
+  <si>
+    <t>68%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>Vac del 16 de junio al 3 de julio</t>
+  </si>
+  <si>
+    <t>32%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>129%</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Maria Camila Arango VÃ©lez</t>
+  </si>
+  <si>
+    <t>Le finalizaron el 18 elabora - 15 días</t>
+  </si>
+  <si>
+    <t>57%</t>
+  </si>
+  <si>
+    <t>4%</t>
+  </si>
+  <si>
+    <t>Johan Daniel Herrera Mazo</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>8%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>Meta 352</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>Meta otros 106</t>
+  </si>
+  <si>
+    <t>Meta terminales 52</t>
+  </si>
+  <si>
+    <t>Meta Hogar 3</t>
+  </si>
+  <si>
+    <t>Meta puntos 1595          - meta post 33</t>
+  </si>
+  <si>
+    <t>86%</t>
+  </si>
+  <si>
+    <t>Nasly Johanna Martinez Ocampo</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>225%</t>
+  </si>
+  <si>
+    <t>154%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>136%</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>6%</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>132%</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>Calamidad 3 días</t>
+  </si>
+  <si>
+    <t>123%</t>
+  </si>
+  <si>
+    <t>Luz Enith Sanchez Galeano</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>131%</t>
+  </si>
+  <si>
+    <t>Lider Paola Andrea Clavijo</t>
+  </si>
+  <si>
+    <t>122%</t>
+  </si>
+  <si>
+    <t>80%</t>
   </si>
 </sst>
 </file>
@@ -632,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L191"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -684,22 +846,22 @@
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K2">
         <v>100</v>
@@ -710,31 +872,31 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>22</v>
-      </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K3">
         <v>100</v>
@@ -745,7 +907,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4">
         <v>34</v>
@@ -754,22 +916,22 @@
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K4">
         <v>100</v>
@@ -780,7 +942,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>61</v>
@@ -789,22 +951,22 @@
         <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K5">
         <v>100</v>
@@ -815,7 +977,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>912</v>
@@ -824,22 +986,22 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -859,25 +1021,25 @@
         <v>0</v>
       </c>
       <c r="D7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="G7" t="s">
-        <v>22</v>
-      </c>
       <c r="H7" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K7">
         <v>100</v>
@@ -888,7 +1050,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -897,22 +1059,22 @@
         <v>0</v>
       </c>
       <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
       <c r="H8" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K8">
         <v>100</v>
@@ -923,7 +1085,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>11</v>
@@ -932,22 +1094,22 @@
         <v>0</v>
       </c>
       <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
       <c r="H9" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K9">
         <v>100</v>
@@ -958,7 +1120,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B10">
         <v>19</v>
@@ -967,22 +1129,22 @@
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K10">
         <v>100</v>
@@ -993,7 +1155,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B11">
         <v>288</v>
@@ -1002,22 +1164,22 @@
         <v>0</v>
       </c>
       <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
         <v>16</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" t="s">
-        <v>22</v>
-      </c>
       <c r="H11" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -1037,22 +1199,22 @@
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -1063,31 +1225,31 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F13" t="s">
-        <v>13</v>
-      </c>
       <c r="G13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K13">
         <v>100</v>
@@ -1098,7 +1260,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B14">
         <v>35</v>
@@ -1107,22 +1269,22 @@
         <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K14">
         <v>100</v>
@@ -1133,7 +1295,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>102</v>
@@ -1142,22 +1304,22 @@
         <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -1168,7 +1330,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B16">
         <v>768</v>
@@ -1177,22 +1339,22 @@
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>100</v>
@@ -1212,25 +1374,25 @@
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J17" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -1241,7 +1403,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1250,22 +1412,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -1276,7 +1438,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>20</v>
@@ -1285,22 +1447,22 @@
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K19">
         <v>100</v>
@@ -1311,7 +1473,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B20">
         <v>58</v>
@@ -1320,22 +1482,22 @@
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -1346,7 +1508,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21">
         <v>432</v>
@@ -1355,22 +1517,22 @@
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -1390,22 +1552,22 @@
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G22" t="s">
         <v>36</v>
       </c>
       <c r="H22" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K22">
         <v>100</v>
@@ -1416,7 +1578,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B23">
         <v>3</v>
@@ -1425,22 +1587,22 @@
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G23" t="s">
         <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K23">
         <v>100</v>
@@ -1451,7 +1613,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B24">
         <v>24</v>
@@ -1460,22 +1622,22 @@
         <v>5</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
         <v>36</v>
       </c>
       <c r="H24" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K24">
         <v>100</v>
@@ -1486,7 +1648,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B25">
         <v>32</v>
@@ -1495,22 +1657,22 @@
         <v>5</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E25" t="s">
         <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
         <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K25">
         <v>100</v>
@@ -1521,7 +1683,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B26">
         <v>510</v>
@@ -1530,22 +1692,22 @@
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
         <v>35</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26" t="s">
         <v>36</v>
       </c>
       <c r="H26" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -1565,22 +1727,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G27" t="s">
         <v>36</v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K27">
         <v>100</v>
@@ -1591,7 +1753,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -1600,22 +1762,22 @@
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G28" t="s">
         <v>36</v>
       </c>
       <c r="H28" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K28">
         <v>100</v>
@@ -1626,7 +1788,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B29">
         <v>37</v>
@@ -1635,22 +1797,22 @@
         <v>7</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E29" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G29" t="s">
         <v>36</v>
       </c>
       <c r="H29" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K29">
         <v>100</v>
@@ -1661,7 +1823,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B30">
         <v>48</v>
@@ -1670,22 +1832,22 @@
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
         <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K30">
         <v>100</v>
@@ -1696,7 +1858,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B31">
         <v>765</v>
@@ -1705,22 +1867,22 @@
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G31" t="s">
         <v>36</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I31" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K31">
         <v>100</v>
@@ -1740,25 +1902,25 @@
         <v>8</v>
       </c>
       <c r="D32" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E32" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
         <v>36</v>
       </c>
       <c r="H32" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J32" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="K32">
         <v>100</v>
@@ -1769,7 +1931,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B33">
         <v>2</v>
@@ -1778,22 +1940,22 @@
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E33" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
         <v>36</v>
       </c>
       <c r="H33" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I33" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K33">
         <v>100</v>
@@ -1804,7 +1966,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B34">
         <v>11</v>
@@ -1813,22 +1975,22 @@
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
         <v>36</v>
       </c>
       <c r="H34" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I34" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -1839,7 +2001,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B35">
         <v>14</v>
@@ -1848,22 +2010,22 @@
         <v>19</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
         <v>36</v>
       </c>
       <c r="H35" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I35" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K35">
         <v>100</v>
@@ -1874,7 +2036,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B36">
         <v>225</v>
@@ -1883,22 +2045,22 @@
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G36" t="s">
         <v>36</v>
       </c>
       <c r="H36" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I36" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K36">
         <v>100</v>
@@ -1918,22 +2080,22 @@
         <v>4</v>
       </c>
       <c r="D37" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E37" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H37" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I37" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -1944,7 +2106,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B38">
         <v>5</v>
@@ -1953,22 +2115,22 @@
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H38" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -1979,7 +2141,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B39">
         <v>32</v>
@@ -1988,25 +2150,25 @@
         <v>7</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H39" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J39" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -2017,7 +2179,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B40">
         <v>61</v>
@@ -2026,22 +2188,22 @@
         <v>8</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H40" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -2052,7 +2214,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B41">
         <v>510</v>
@@ -2061,22 +2223,22 @@
         <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H41" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K41">
         <v>100</v>
@@ -2096,25 +2258,25 @@
         <v>12</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H42" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J42" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="K42">
         <v>100</v>
@@ -2125,7 +2287,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B43">
         <v>2</v>
@@ -2134,22 +2296,22 @@
         <v>4</v>
       </c>
       <c r="D43" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H43" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K43">
         <v>100</v>
@@ -2160,7 +2322,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B44">
         <v>14</v>
@@ -2169,22 +2331,22 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H44" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K44">
         <v>100</v>
@@ -2195,7 +2357,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B45">
         <v>27</v>
@@ -2204,22 +2366,22 @@
         <v>31</v>
       </c>
       <c r="D45" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H45" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K45">
         <v>100</v>
@@ -2230,7 +2392,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B46">
         <v>225</v>
@@ -2239,22 +2401,22 @@
         <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H46" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I46" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K46">
         <v>100</v>
@@ -2274,22 +2436,22 @@
         <v>7</v>
       </c>
       <c r="D47" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E47" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H47" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -2300,7 +2462,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B48">
         <v>7</v>
@@ -2309,22 +2471,22 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E48" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H48" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I48" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K48">
         <v>100</v>
@@ -2335,7 +2497,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B49">
         <v>48</v>
@@ -2344,22 +2506,22 @@
         <v>12</v>
       </c>
       <c r="D49" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E49" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G49" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H49" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I49" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K49">
         <v>100</v>
@@ -2370,7 +2532,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B50">
         <v>92</v>
@@ -2379,22 +2541,22 @@
         <v>28</v>
       </c>
       <c r="D50" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F50" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H50" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K50">
         <v>100</v>
@@ -2405,7 +2567,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B51">
         <v>765</v>
@@ -2414,22 +2576,22 @@
         <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G51" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="H51" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I51" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K51">
         <v>100</v>
@@ -2449,22 +2611,22 @@
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E52" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H52" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I52" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K52">
         <v>100</v>
@@ -2475,31 +2637,31 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>19</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53" t="s">
         <v>15</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
-        <v>0</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="G53" t="s">
         <v>16</v>
       </c>
-      <c r="E53" t="s">
-        <v>21</v>
-      </c>
-      <c r="F53" t="s">
-        <v>13</v>
-      </c>
-      <c r="G53" t="s">
-        <v>22</v>
-      </c>
       <c r="H53" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K53">
         <v>100</v>
@@ -2510,7 +2672,7 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B54">
         <v>34</v>
@@ -2519,22 +2681,22 @@
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E54" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K54">
         <v>100</v>
@@ -2545,7 +2707,7 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B55">
         <v>61</v>
@@ -2554,22 +2716,22 @@
         <v>14</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H55" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I55" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K55">
         <v>100</v>
@@ -2580,7 +2742,7 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B56">
         <v>912</v>
@@ -2589,22 +2751,22 @@
         <v>0</v>
       </c>
       <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" t="s">
         <v>16</v>
       </c>
-      <c r="E56" t="s">
-        <v>21</v>
-      </c>
-      <c r="F56" t="s">
-        <v>13</v>
-      </c>
-      <c r="G56" t="s">
-        <v>22</v>
-      </c>
       <c r="H56" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K56">
         <v>100</v>
@@ -2624,25 +2786,25 @@
         <v>0</v>
       </c>
       <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>26</v>
+      </c>
+      <c r="F57" t="s">
+        <v>27</v>
+      </c>
+      <c r="G57" t="s">
         <v>16</v>
       </c>
-      <c r="E57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" t="s">
-        <v>20</v>
-      </c>
-      <c r="G57" t="s">
-        <v>22</v>
-      </c>
       <c r="H57" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I57" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J57" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -2653,7 +2815,7 @@
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -2662,22 +2824,22 @@
         <v>0</v>
       </c>
       <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>26</v>
+      </c>
+      <c r="F58" t="s">
+        <v>27</v>
+      </c>
+      <c r="G58" t="s">
         <v>16</v>
       </c>
-      <c r="E58" t="s">
-        <v>25</v>
-      </c>
-      <c r="F58" t="s">
-        <v>20</v>
-      </c>
-      <c r="G58" t="s">
-        <v>22</v>
-      </c>
       <c r="H58" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I58" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K58">
         <v>100</v>
@@ -2688,7 +2850,7 @@
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B59">
         <v>11</v>
@@ -2697,22 +2859,22 @@
         <v>0</v>
       </c>
       <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" t="s">
         <v>16</v>
       </c>
-      <c r="E59" t="s">
-        <v>25</v>
-      </c>
-      <c r="F59" t="s">
-        <v>20</v>
-      </c>
-      <c r="G59" t="s">
-        <v>22</v>
-      </c>
       <c r="H59" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I59" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K59">
         <v>100</v>
@@ -2723,7 +2885,7 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B60">
         <v>19</v>
@@ -2732,22 +2894,22 @@
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F60" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H60" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K60">
         <v>100</v>
@@ -2758,7 +2920,7 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B61">
         <v>288</v>
@@ -2767,22 +2929,22 @@
         <v>0</v>
       </c>
       <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>26</v>
+      </c>
+      <c r="F61" t="s">
+        <v>27</v>
+      </c>
+      <c r="G61" t="s">
         <v>16</v>
       </c>
-      <c r="E61" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" t="s">
-        <v>20</v>
-      </c>
-      <c r="G61" t="s">
-        <v>22</v>
-      </c>
       <c r="H61" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K61">
         <v>100</v>
@@ -2802,22 +2964,22 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="E62" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K62">
         <v>100</v>
@@ -2828,31 +2990,31 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>19</v>
+      </c>
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" t="s">
         <v>15</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
-      <c r="D63" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" t="s">
-        <v>52</v>
-      </c>
-      <c r="F63" t="s">
-        <v>13</v>
-      </c>
       <c r="G63" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K63">
         <v>100</v>
@@ -2863,7 +3025,7 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B64">
         <v>35</v>
@@ -2872,22 +3034,22 @@
         <v>11</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E64" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K64">
         <v>100</v>
@@ -2898,7 +3060,7 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B65">
         <v>102</v>
@@ -2907,22 +3069,22 @@
         <v>39</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F65" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I65" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K65">
         <v>100</v>
@@ -2933,7 +3095,7 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B66">
         <v>768</v>
@@ -2942,22 +3104,22 @@
         <v>0</v>
       </c>
       <c r="D66" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I66" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K66">
         <v>100</v>
@@ -2977,25 +3139,25 @@
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F67" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="K67">
         <v>100</v>
@@ -3006,7 +3168,7 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -3015,22 +3177,22 @@
         <v>0</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K68">
         <v>100</v>
@@ -3041,7 +3203,7 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B69">
         <v>20</v>
@@ -3050,22 +3212,22 @@
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F69" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G69" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K69">
         <v>100</v>
@@ -3076,7 +3238,7 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B70">
         <v>58</v>
@@ -3085,22 +3247,22 @@
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I70" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K70">
         <v>100</v>
@@ -3111,7 +3273,7 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B71">
         <v>432</v>
@@ -3120,22 +3282,22 @@
         <v>0</v>
       </c>
       <c r="D71" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="F71" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I71" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K71">
         <v>100</v>
@@ -3155,22 +3317,22 @@
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
         <v>35</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
         <v>36</v>
       </c>
       <c r="H72" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I72" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K72">
         <v>100</v>
@@ -3181,7 +3343,7 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B73">
         <v>3</v>
@@ -3190,22 +3352,22 @@
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
         <v>35</v>
       </c>
       <c r="F73" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G73" t="s">
         <v>36</v>
       </c>
       <c r="H73" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K73">
         <v>100</v>
@@ -3216,7 +3378,7 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B74">
         <v>24</v>
@@ -3225,22 +3387,22 @@
         <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E74" t="s">
         <v>35</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G74" t="s">
         <v>36</v>
       </c>
       <c r="H74" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I74" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K74">
         <v>100</v>
@@ -3251,7 +3413,7 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B75">
         <v>32</v>
@@ -3260,22 +3422,22 @@
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E75" t="s">
         <v>35</v>
       </c>
       <c r="F75" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G75" t="s">
         <v>36</v>
       </c>
       <c r="H75" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K75">
         <v>100</v>
@@ -3286,7 +3448,7 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B76">
         <v>510</v>
@@ -3295,22 +3457,22 @@
         <v>0</v>
       </c>
       <c r="D76" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
         <v>35</v>
       </c>
       <c r="F76" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G76" t="s">
         <v>36</v>
       </c>
       <c r="H76" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I76" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K76">
         <v>100</v>
@@ -3330,22 +3492,22 @@
         <v>1</v>
       </c>
       <c r="D77" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F77" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
         <v>36</v>
       </c>
       <c r="H77" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K77">
         <v>100</v>
@@ -3356,7 +3518,7 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B78">
         <v>5</v>
@@ -3365,22 +3527,22 @@
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G78" t="s">
         <v>36</v>
       </c>
       <c r="H78" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I78" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K78">
         <v>100</v>
@@ -3391,7 +3553,7 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B79">
         <v>37</v>
@@ -3400,22 +3562,22 @@
         <v>7</v>
       </c>
       <c r="D79" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F79" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G79" t="s">
         <v>36</v>
       </c>
       <c r="H79" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I79" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K79">
         <v>100</v>
@@ -3426,7 +3588,7 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B80">
         <v>48</v>
@@ -3435,22 +3597,22 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F80" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G80" t="s">
         <v>36</v>
       </c>
       <c r="H80" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K80">
         <v>100</v>
@@ -3461,7 +3623,7 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B81">
         <v>765</v>
@@ -3470,22 +3632,22 @@
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F81" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G81" t="s">
         <v>36</v>
       </c>
       <c r="H81" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I81" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K81">
         <v>100</v>
@@ -3505,25 +3667,25 @@
         <v>8</v>
       </c>
       <c r="D82" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="E82" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G82" t="s">
         <v>36</v>
       </c>
       <c r="H82" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I82" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J82" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="K82">
         <v>100</v>
@@ -3534,7 +3696,7 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -3543,22 +3705,22 @@
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G83" t="s">
         <v>36</v>
       </c>
       <c r="H83" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K83">
         <v>100</v>
@@ -3569,7 +3731,7 @@
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B84">
         <v>11</v>
@@ -3578,22 +3740,22 @@
         <v>12</v>
       </c>
       <c r="D84" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E84" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F84" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
         <v>36</v>
       </c>
       <c r="H84" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I84" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K84">
         <v>100</v>
@@ -3604,7 +3766,7 @@
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B85">
         <v>14</v>
@@ -3613,22 +3775,22 @@
         <v>19</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F85" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
         <v>36</v>
       </c>
       <c r="H85" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K85">
         <v>100</v>
@@ -3639,7 +3801,7 @@
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B86">
         <v>225</v>
@@ -3648,22 +3810,22 @@
         <v>0</v>
       </c>
       <c r="D86" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G86" t="s">
         <v>36</v>
       </c>
       <c r="H86" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K86">
         <v>100</v>
@@ -3683,22 +3845,22 @@
         <v>10</v>
       </c>
       <c r="D87" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E87" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H87" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I87" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K87">
         <v>100</v>
@@ -3709,7 +3871,7 @@
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B88">
         <v>3</v>
@@ -3718,22 +3880,22 @@
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E88" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H88" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K88">
         <v>100</v>
@@ -3744,7 +3906,7 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B89">
         <v>35</v>
@@ -3753,22 +3915,22 @@
         <v>19</v>
       </c>
       <c r="D89" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E89" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H89" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I89" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K89">
         <v>100</v>
@@ -3779,7 +3941,7 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B90">
         <v>62</v>
@@ -3788,22 +3950,22 @@
         <v>47</v>
       </c>
       <c r="D90" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H90" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I90" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K90">
         <v>100</v>
@@ -3814,7 +3976,7 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B91">
         <v>420</v>
@@ -3823,22 +3985,22 @@
         <v>0</v>
       </c>
       <c r="D91" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E91" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H91" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I91" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K91">
         <v>100</v>
@@ -3858,22 +4020,22 @@
         <v>11</v>
       </c>
       <c r="D92" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="E92" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F92" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G92" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H92" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I92" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K92">
         <v>100</v>
@@ -3884,7 +4046,7 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B93">
         <v>4</v>
@@ -3893,22 +4055,22 @@
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E93" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F93" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G93" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H93" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I93" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K93">
         <v>100</v>
@@ -3919,7 +4081,7 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B94">
         <v>53</v>
@@ -3928,22 +4090,22 @@
         <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E94" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F94" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G94" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H94" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K94">
         <v>100</v>
@@ -3954,7 +4116,7 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B95">
         <v>92</v>
@@ -3963,22 +4125,22 @@
         <v>27</v>
       </c>
       <c r="D95" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E95" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G95" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H95" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I95" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K95">
         <v>100</v>
@@ -3989,7 +4151,7 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B96">
         <v>630</v>
@@ -3998,22 +4160,22 @@
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E96" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F96" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G96" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H96" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I96" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K96">
         <v>100</v>
@@ -4033,25 +4195,25 @@
         <v>5</v>
       </c>
       <c r="D97" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="E97" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F97" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H97" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I97" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="K97">
         <v>100</v>
@@ -4062,7 +4224,7 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B98">
         <v>3</v>
@@ -4071,22 +4233,22 @@
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F98" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H98" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I98" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K98">
         <v>100</v>
@@ -4097,7 +4259,7 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B99">
         <v>38</v>
@@ -4106,22 +4268,22 @@
         <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E99" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H99" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I99" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K99">
         <v>100</v>
@@ -4132,7 +4294,7 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B100">
         <v>66</v>
@@ -4141,22 +4303,22 @@
         <v>4</v>
       </c>
       <c r="D100" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F100" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H100" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I100" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K100">
         <v>100</v>
@@ -4167,7 +4329,7 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B101">
         <v>450</v>
@@ -4176,22 +4338,22 @@
         <v>0</v>
       </c>
       <c r="D101" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="H101" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I101" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K101">
         <v>100</v>
@@ -4211,25 +4373,25 @@
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E102" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F102" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H102" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I102" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J102" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K102">
         <v>100</v>
@@ -4240,7 +4402,7 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -4249,25 +4411,25 @@
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E103" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F103" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H103" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I103" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J103" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="K103">
         <v>100</v>
@@ -4278,7 +4440,7 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B104">
         <v>28</v>
@@ -4287,25 +4449,25 @@
         <v>6</v>
       </c>
       <c r="D104" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="E104" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F104" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H104" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I104" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J104" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K104">
         <v>100</v>
@@ -4316,7 +4478,7 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B105">
         <v>56</v>
@@ -4325,25 +4487,25 @@
         <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E105" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F105" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H105" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I105" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J105" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K105">
         <v>100</v>
@@ -4354,7 +4516,7 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B106">
         <v>600</v>
@@ -4363,25 +4525,25 @@
         <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="F106" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H106" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I106" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J106" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K106">
         <v>100</v>
@@ -4401,22 +4563,22 @@
         <v>10</v>
       </c>
       <c r="D107" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E107" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G107" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H107" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I107" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K107">
         <v>100</v>
@@ -4427,7 +4589,7 @@
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -4436,22 +4598,22 @@
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E108" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F108" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G108" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H108" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I108" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K108">
         <v>100</v>
@@ -4462,7 +4624,7 @@
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B109">
         <v>42</v>
@@ -4471,22 +4633,22 @@
         <v>17</v>
       </c>
       <c r="D109" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="E109" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G109" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H109" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I109" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K109">
         <v>100</v>
@@ -4497,7 +4659,7 @@
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B110">
         <v>84</v>
@@ -4506,22 +4668,22 @@
         <v>40</v>
       </c>
       <c r="D110" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F110" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H110" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I110" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K110">
         <v>100</v>
@@ -4532,7 +4694,7 @@
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B111">
         <v>900</v>
@@ -4541,22 +4703,22 @@
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F111" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G111" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H111" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I111" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K111">
         <v>100</v>
@@ -4576,22 +4738,22 @@
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E112" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F112" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G112" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H112" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I112" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K112">
         <v>100</v>
@@ -4602,7 +4764,7 @@
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -4611,22 +4773,22 @@
         <v>0</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E113" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F113" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H113" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I113" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K113">
         <v>100</v>
@@ -4637,7 +4799,7 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B114">
         <v>42</v>
@@ -4649,19 +4811,19 @@
         <v>81</v>
       </c>
       <c r="E114" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F114" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G114" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H114" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I114" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K114">
         <v>100</v>
@@ -4672,7 +4834,7 @@
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B115">
         <v>84</v>
@@ -4681,22 +4843,22 @@
         <v>6</v>
       </c>
       <c r="D115" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="E115" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F115" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H115" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I115" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K115">
         <v>100</v>
@@ -4707,7 +4869,7 @@
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B116">
         <v>900</v>
@@ -4716,22 +4878,22 @@
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="F116" t="s">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="G116" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="H116" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="I116" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K116">
         <v>100</v>
@@ -4740,8 +4902,2657 @@
         <v>17.8</v>
       </c>
     </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>12</v>
+      </c>
+      <c r="B117">
+        <v>19</v>
+      </c>
+      <c r="C117">
+        <v>13</v>
+      </c>
+      <c r="D117" t="s">
+        <v>82</v>
+      </c>
+      <c r="E117" t="s">
+        <v>83</v>
+      </c>
+      <c r="F117" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" t="s">
+        <v>84</v>
+      </c>
+      <c r="H117" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" t="s">
+        <v>18</v>
+      </c>
+      <c r="J117" t="s">
+        <v>85</v>
+      </c>
+      <c r="K117">
+        <v>100</v>
+      </c>
+      <c r="L117">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>19</v>
+      </c>
+      <c r="B118">
+        <v>4</v>
+      </c>
+      <c r="C118">
+        <v>2</v>
+      </c>
+      <c r="D118" t="s">
+        <v>57</v>
+      </c>
+      <c r="E118" t="s">
+        <v>83</v>
+      </c>
+      <c r="F118" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" t="s">
+        <v>84</v>
+      </c>
+      <c r="H118" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118">
+        <v>100</v>
+      </c>
+      <c r="L118">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>21</v>
+      </c>
+      <c r="B119">
+        <v>19</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>86</v>
+      </c>
+      <c r="E119" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119" t="s">
+        <v>15</v>
+      </c>
+      <c r="G119" t="s">
+        <v>84</v>
+      </c>
+      <c r="H119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119">
+        <v>100</v>
+      </c>
+      <c r="L119">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>23</v>
+      </c>
+      <c r="B120">
+        <v>65</v>
+      </c>
+      <c r="C120">
+        <v>32</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" t="s">
+        <v>83</v>
+      </c>
+      <c r="F120" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" t="s">
+        <v>84</v>
+      </c>
+      <c r="H120" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120">
+        <v>100</v>
+      </c>
+      <c r="L120">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121">
+        <v>465</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>20</v>
+      </c>
+      <c r="E121" t="s">
+        <v>83</v>
+      </c>
+      <c r="F121" t="s">
+        <v>15</v>
+      </c>
+      <c r="G121" t="s">
+        <v>84</v>
+      </c>
+      <c r="H121" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121">
+        <v>100</v>
+      </c>
+      <c r="L121">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>12</v>
+      </c>
+      <c r="B122">
+        <v>29</v>
+      </c>
+      <c r="C122">
+        <v>30</v>
+      </c>
+      <c r="D122" t="s">
+        <v>87</v>
+      </c>
+      <c r="E122" t="s">
+        <v>88</v>
+      </c>
+      <c r="F122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G122" t="s">
+        <v>84</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122">
+        <v>100</v>
+      </c>
+      <c r="L122">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>19</v>
+      </c>
+      <c r="B123">
+        <v>7</v>
+      </c>
+      <c r="C123">
+        <v>9</v>
+      </c>
+      <c r="D123" t="s">
+        <v>89</v>
+      </c>
+      <c r="E123" t="s">
+        <v>88</v>
+      </c>
+      <c r="F123" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" t="s">
+        <v>84</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123">
+        <v>100</v>
+      </c>
+      <c r="L123">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>21</v>
+      </c>
+      <c r="B124">
+        <v>28</v>
+      </c>
+      <c r="C124">
+        <v>20</v>
+      </c>
+      <c r="D124" t="s">
+        <v>90</v>
+      </c>
+      <c r="E124" t="s">
+        <v>88</v>
+      </c>
+      <c r="F124" t="s">
+        <v>27</v>
+      </c>
+      <c r="G124" t="s">
+        <v>84</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124">
+        <v>100</v>
+      </c>
+      <c r="L124">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>23</v>
+      </c>
+      <c r="B125">
+        <v>98</v>
+      </c>
+      <c r="C125">
+        <v>79</v>
+      </c>
+      <c r="D125" t="s">
+        <v>91</v>
+      </c>
+      <c r="E125" t="s">
+        <v>88</v>
+      </c>
+      <c r="F125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G125" t="s">
+        <v>84</v>
+      </c>
+      <c r="H125" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" t="s">
+        <v>18</v>
+      </c>
+      <c r="K125">
+        <v>100</v>
+      </c>
+      <c r="L125">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126">
+        <v>698</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" t="s">
+        <v>88</v>
+      </c>
+      <c r="F126" t="s">
+        <v>27</v>
+      </c>
+      <c r="G126" t="s">
+        <v>84</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126">
+        <v>100</v>
+      </c>
+      <c r="L126">
+        <v>85.7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>12</v>
+      </c>
+      <c r="B127">
+        <v>14</v>
+      </c>
+      <c r="C127">
+        <v>4</v>
+      </c>
+      <c r="D127" t="s">
+        <v>92</v>
+      </c>
+      <c r="E127" t="s">
+        <v>93</v>
+      </c>
+      <c r="F127" t="s">
+        <v>27</v>
+      </c>
+      <c r="G127" t="s">
+        <v>84</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" t="s">
+        <v>18</v>
+      </c>
+      <c r="J127" t="s">
+        <v>94</v>
+      </c>
+      <c r="K127">
+        <v>100</v>
+      </c>
+      <c r="L127">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>19</v>
+      </c>
+      <c r="B128">
+        <v>3</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128" t="s">
+        <v>93</v>
+      </c>
+      <c r="F128" t="s">
+        <v>27</v>
+      </c>
+      <c r="G128" t="s">
+        <v>84</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" t="s">
+        <v>18</v>
+      </c>
+      <c r="K128">
+        <v>100</v>
+      </c>
+      <c r="L128">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>21</v>
+      </c>
+      <c r="B129">
+        <v>14</v>
+      </c>
+      <c r="C129">
+        <v>8</v>
+      </c>
+      <c r="D129" t="s">
+        <v>95</v>
+      </c>
+      <c r="E129" t="s">
+        <v>93</v>
+      </c>
+      <c r="F129" t="s">
+        <v>27</v>
+      </c>
+      <c r="G129" t="s">
+        <v>84</v>
+      </c>
+      <c r="H129" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129">
+        <v>100</v>
+      </c>
+      <c r="L129">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>23</v>
+      </c>
+      <c r="B130">
+        <v>47</v>
+      </c>
+      <c r="C130">
+        <v>35</v>
+      </c>
+      <c r="D130" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130" t="s">
+        <v>93</v>
+      </c>
+      <c r="F130" t="s">
+        <v>27</v>
+      </c>
+      <c r="G130" t="s">
+        <v>84</v>
+      </c>
+      <c r="H130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130">
+        <v>100</v>
+      </c>
+      <c r="L130">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>25</v>
+      </c>
+      <c r="B131">
+        <v>338</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>20</v>
+      </c>
+      <c r="E131" t="s">
+        <v>93</v>
+      </c>
+      <c r="F131" t="s">
+        <v>27</v>
+      </c>
+      <c r="G131" t="s">
+        <v>84</v>
+      </c>
+      <c r="H131" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" t="s">
+        <v>18</v>
+      </c>
+      <c r="K131">
+        <v>100</v>
+      </c>
+      <c r="L131">
+        <v>47.3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>12</v>
+      </c>
+      <c r="B132">
+        <v>23</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132" t="s">
+        <v>96</v>
+      </c>
+      <c r="E132" t="s">
+        <v>97</v>
+      </c>
+      <c r="F132" t="s">
+        <v>80</v>
+      </c>
+      <c r="G132" t="s">
+        <v>84</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132">
+        <v>100</v>
+      </c>
+      <c r="L132">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>19</v>
+      </c>
+      <c r="B133">
+        <v>5</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133" t="s">
+        <v>78</v>
+      </c>
+      <c r="E133" t="s">
+        <v>97</v>
+      </c>
+      <c r="F133" t="s">
+        <v>80</v>
+      </c>
+      <c r="G133" t="s">
+        <v>84</v>
+      </c>
+      <c r="H133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" t="s">
+        <v>18</v>
+      </c>
+      <c r="K133">
+        <v>100</v>
+      </c>
+      <c r="L133">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>21</v>
+      </c>
+      <c r="B134">
+        <v>23</v>
+      </c>
+      <c r="C134">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>46</v>
+      </c>
+      <c r="E134" t="s">
+        <v>97</v>
+      </c>
+      <c r="F134" t="s">
+        <v>80</v>
+      </c>
+      <c r="G134" t="s">
+        <v>84</v>
+      </c>
+      <c r="H134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134">
+        <v>100</v>
+      </c>
+      <c r="L134">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>23</v>
+      </c>
+      <c r="B135">
+        <v>79</v>
+      </c>
+      <c r="C135">
+        <v>8</v>
+      </c>
+      <c r="D135" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" t="s">
+        <v>97</v>
+      </c>
+      <c r="F135" t="s">
+        <v>80</v>
+      </c>
+      <c r="G135" t="s">
+        <v>84</v>
+      </c>
+      <c r="H135" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" t="s">
+        <v>18</v>
+      </c>
+      <c r="K135">
+        <v>100</v>
+      </c>
+      <c r="L135">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>25</v>
+      </c>
+      <c r="B136">
+        <v>563</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136" t="s">
+        <v>20</v>
+      </c>
+      <c r="E136" t="s">
+        <v>97</v>
+      </c>
+      <c r="F136" t="s">
+        <v>80</v>
+      </c>
+      <c r="G136" t="s">
+        <v>84</v>
+      </c>
+      <c r="H136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" t="s">
+        <v>18</v>
+      </c>
+      <c r="K136">
+        <v>100</v>
+      </c>
+      <c r="L136">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>12</v>
+      </c>
+      <c r="B137">
+        <v>21</v>
+      </c>
+      <c r="C137">
+        <v>27</v>
+      </c>
+      <c r="D137" t="s">
+        <v>89</v>
+      </c>
+      <c r="E137" t="s">
+        <v>133</v>
+      </c>
+      <c r="F137" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" t="s">
+        <v>122</v>
+      </c>
+      <c r="H137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137">
+        <v>100</v>
+      </c>
+      <c r="L137">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>19</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+      <c r="C138">
+        <v>4</v>
+      </c>
+      <c r="D138" t="s">
+        <v>135</v>
+      </c>
+      <c r="E138" t="s">
+        <v>133</v>
+      </c>
+      <c r="F138" t="s">
+        <v>15</v>
+      </c>
+      <c r="G138" t="s">
+        <v>122</v>
+      </c>
+      <c r="H138" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138">
+        <v>100</v>
+      </c>
+      <c r="L138">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>21</v>
+      </c>
+      <c r="B139">
+        <v>24</v>
+      </c>
+      <c r="C139">
+        <v>13</v>
+      </c>
+      <c r="D139" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" t="s">
+        <v>133</v>
+      </c>
+      <c r="F139" t="s">
+        <v>15</v>
+      </c>
+      <c r="G139" t="s">
+        <v>122</v>
+      </c>
+      <c r="H139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139">
+        <v>100</v>
+      </c>
+      <c r="L139">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>23</v>
+      </c>
+      <c r="B140">
+        <v>51</v>
+      </c>
+      <c r="C140">
+        <v>62</v>
+      </c>
+      <c r="D140" t="s">
+        <v>134</v>
+      </c>
+      <c r="E140" t="s">
+        <v>133</v>
+      </c>
+      <c r="F140" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" t="s">
+        <v>122</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" t="s">
+        <v>18</v>
+      </c>
+      <c r="K140">
+        <v>100</v>
+      </c>
+      <c r="L140">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>25</v>
+      </c>
+      <c r="B141">
+        <v>402</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>20</v>
+      </c>
+      <c r="E141" t="s">
+        <v>133</v>
+      </c>
+      <c r="F141" t="s">
+        <v>15</v>
+      </c>
+      <c r="G141" t="s">
+        <v>122</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141">
+        <v>100</v>
+      </c>
+      <c r="L141">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B142">
+        <v>32</v>
+      </c>
+      <c r="C142">
+        <v>42</v>
+      </c>
+      <c r="D142" t="s">
+        <v>132</v>
+      </c>
+      <c r="E142" t="s">
+        <v>129</v>
+      </c>
+      <c r="F142" t="s">
+        <v>27</v>
+      </c>
+      <c r="G142" t="s">
+        <v>122</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142">
+        <v>100</v>
+      </c>
+      <c r="L142">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>19</v>
+      </c>
+      <c r="B143">
+        <v>8</v>
+      </c>
+      <c r="C143">
+        <v>5</v>
+      </c>
+      <c r="D143" t="s">
+        <v>131</v>
+      </c>
+      <c r="E143" t="s">
+        <v>129</v>
+      </c>
+      <c r="F143" t="s">
+        <v>27</v>
+      </c>
+      <c r="G143" t="s">
+        <v>122</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143">
+        <v>100</v>
+      </c>
+      <c r="L143">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>21</v>
+      </c>
+      <c r="B144">
+        <v>36</v>
+      </c>
+      <c r="C144">
+        <v>31</v>
+      </c>
+      <c r="D144" t="s">
+        <v>108</v>
+      </c>
+      <c r="E144" t="s">
+        <v>129</v>
+      </c>
+      <c r="F144" t="s">
+        <v>27</v>
+      </c>
+      <c r="G144" t="s">
+        <v>122</v>
+      </c>
+      <c r="H144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" t="s">
+        <v>18</v>
+      </c>
+      <c r="K144">
+        <v>100</v>
+      </c>
+      <c r="L144">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>23</v>
+      </c>
+      <c r="B145">
+        <v>76</v>
+      </c>
+      <c r="C145">
+        <v>85</v>
+      </c>
+      <c r="D145" t="s">
+        <v>130</v>
+      </c>
+      <c r="E145" t="s">
+        <v>129</v>
+      </c>
+      <c r="F145" t="s">
+        <v>27</v>
+      </c>
+      <c r="G145" t="s">
+        <v>122</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145">
+        <v>100</v>
+      </c>
+      <c r="L145">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146">
+        <v>603</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146" t="s">
+        <v>20</v>
+      </c>
+      <c r="E146" t="s">
+        <v>129</v>
+      </c>
+      <c r="F146" t="s">
+        <v>27</v>
+      </c>
+      <c r="G146" t="s">
+        <v>122</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146">
+        <v>100</v>
+      </c>
+      <c r="L146">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>12</v>
+      </c>
+      <c r="B147">
+        <v>26</v>
+      </c>
+      <c r="C147">
+        <v>32</v>
+      </c>
+      <c r="D147" t="s">
+        <v>128</v>
+      </c>
+      <c r="E147" t="s">
+        <v>124</v>
+      </c>
+      <c r="F147" t="s">
+        <v>27</v>
+      </c>
+      <c r="G147" t="s">
+        <v>122</v>
+      </c>
+      <c r="H147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" t="s">
+        <v>18</v>
+      </c>
+      <c r="J147" t="s">
+        <v>127</v>
+      </c>
+      <c r="K147">
+        <v>100</v>
+      </c>
+      <c r="L147">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>19</v>
+      </c>
+      <c r="B148">
+        <v>7</v>
+      </c>
+      <c r="C148">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>108</v>
+      </c>
+      <c r="E148" t="s">
+        <v>124</v>
+      </c>
+      <c r="F148" t="s">
+        <v>27</v>
+      </c>
+      <c r="G148" t="s">
+        <v>122</v>
+      </c>
+      <c r="H148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" t="s">
+        <v>18</v>
+      </c>
+      <c r="K148">
+        <v>100</v>
+      </c>
+      <c r="L148">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>21</v>
+      </c>
+      <c r="B149">
+        <v>30</v>
+      </c>
+      <c r="C149">
+        <v>18</v>
+      </c>
+      <c r="D149" t="s">
+        <v>126</v>
+      </c>
+      <c r="E149" t="s">
+        <v>124</v>
+      </c>
+      <c r="F149" t="s">
+        <v>27</v>
+      </c>
+      <c r="G149" t="s">
+        <v>122</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149">
+        <v>100</v>
+      </c>
+      <c r="L149">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>23</v>
+      </c>
+      <c r="B150">
+        <v>63</v>
+      </c>
+      <c r="C150">
+        <v>83</v>
+      </c>
+      <c r="D150" t="s">
+        <v>125</v>
+      </c>
+      <c r="E150" t="s">
+        <v>124</v>
+      </c>
+      <c r="F150" t="s">
+        <v>27</v>
+      </c>
+      <c r="G150" t="s">
+        <v>122</v>
+      </c>
+      <c r="H150" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150">
+        <v>100</v>
+      </c>
+      <c r="L150">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151">
+        <v>495</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151" t="s">
+        <v>20</v>
+      </c>
+      <c r="E151" t="s">
+        <v>124</v>
+      </c>
+      <c r="F151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G151" t="s">
+        <v>122</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151">
+        <v>100</v>
+      </c>
+      <c r="L151">
+        <v>84.1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>12</v>
+      </c>
+      <c r="B152">
+        <v>30</v>
+      </c>
+      <c r="C152">
+        <v>0</v>
+      </c>
+      <c r="D152" t="s">
+        <v>20</v>
+      </c>
+      <c r="E152" t="s">
+        <v>101</v>
+      </c>
+      <c r="F152" t="s">
+        <v>80</v>
+      </c>
+      <c r="G152" t="s">
+        <v>122</v>
+      </c>
+      <c r="H152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I152" t="s">
+        <v>18</v>
+      </c>
+      <c r="K152">
+        <v>100</v>
+      </c>
+      <c r="L152">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>19</v>
+      </c>
+      <c r="B153">
+        <v>8</v>
+      </c>
+      <c r="C153">
+        <v>0</v>
+      </c>
+      <c r="D153" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" t="s">
+        <v>101</v>
+      </c>
+      <c r="F153" t="s">
+        <v>80</v>
+      </c>
+      <c r="G153" t="s">
+        <v>122</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153">
+        <v>100</v>
+      </c>
+      <c r="L153">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>21</v>
+      </c>
+      <c r="B154">
+        <v>34</v>
+      </c>
+      <c r="C154">
+        <v>0</v>
+      </c>
+      <c r="D154" t="s">
+        <v>20</v>
+      </c>
+      <c r="E154" t="s">
+        <v>101</v>
+      </c>
+      <c r="F154" t="s">
+        <v>80</v>
+      </c>
+      <c r="G154" t="s">
+        <v>122</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154">
+        <v>100</v>
+      </c>
+      <c r="L154">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>23</v>
+      </c>
+      <c r="B155">
+        <v>71</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" t="s">
+        <v>101</v>
+      </c>
+      <c r="F155" t="s">
+        <v>80</v>
+      </c>
+      <c r="G155" t="s">
+        <v>122</v>
+      </c>
+      <c r="H155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I155" t="s">
+        <v>18</v>
+      </c>
+      <c r="K155">
+        <v>100</v>
+      </c>
+      <c r="L155">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B156">
+        <v>563</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>20</v>
+      </c>
+      <c r="E156" t="s">
+        <v>101</v>
+      </c>
+      <c r="F156" t="s">
+        <v>80</v>
+      </c>
+      <c r="G156" t="s">
+        <v>122</v>
+      </c>
+      <c r="H156" t="s">
+        <v>17</v>
+      </c>
+      <c r="I156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156">
+        <v>100</v>
+      </c>
+      <c r="L156">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157">
+        <v>30</v>
+      </c>
+      <c r="C157">
+        <v>0</v>
+      </c>
+      <c r="D157" t="s">
+        <v>20</v>
+      </c>
+      <c r="E157" t="s">
+        <v>79</v>
+      </c>
+      <c r="F157" t="s">
+        <v>80</v>
+      </c>
+      <c r="G157" t="s">
+        <v>122</v>
+      </c>
+      <c r="H157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157">
+        <v>100</v>
+      </c>
+      <c r="L157">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>19</v>
+      </c>
+      <c r="B158">
+        <v>8</v>
+      </c>
+      <c r="C158">
+        <v>0</v>
+      </c>
+      <c r="D158" t="s">
+        <v>20</v>
+      </c>
+      <c r="E158" t="s">
+        <v>79</v>
+      </c>
+      <c r="F158" t="s">
+        <v>80</v>
+      </c>
+      <c r="G158" t="s">
+        <v>122</v>
+      </c>
+      <c r="H158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158">
+        <v>100</v>
+      </c>
+      <c r="L158">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>21</v>
+      </c>
+      <c r="B159">
+        <v>34</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+      <c r="D159" t="s">
+        <v>123</v>
+      </c>
+      <c r="E159" t="s">
+        <v>79</v>
+      </c>
+      <c r="F159" t="s">
+        <v>80</v>
+      </c>
+      <c r="G159" t="s">
+        <v>122</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159">
+        <v>100</v>
+      </c>
+      <c r="L159">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>23</v>
+      </c>
+      <c r="B160">
+        <v>71</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" t="s">
+        <v>79</v>
+      </c>
+      <c r="F160" t="s">
+        <v>80</v>
+      </c>
+      <c r="G160" t="s">
+        <v>122</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160">
+        <v>100</v>
+      </c>
+      <c r="L160">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="B161">
+        <v>563</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>20</v>
+      </c>
+      <c r="E161" t="s">
+        <v>79</v>
+      </c>
+      <c r="F161" t="s">
+        <v>80</v>
+      </c>
+      <c r="G161" t="s">
+        <v>122</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161">
+        <v>100</v>
+      </c>
+      <c r="L161">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>12</v>
+      </c>
+      <c r="B162">
+        <v>28</v>
+      </c>
+      <c r="C162">
+        <v>38</v>
+      </c>
+      <c r="D162" t="s">
+        <v>121</v>
+      </c>
+      <c r="E162" t="s">
+        <v>118</v>
+      </c>
+      <c r="F162" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" t="s">
+        <v>98</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162">
+        <v>100</v>
+      </c>
+      <c r="L162">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>19</v>
+      </c>
+      <c r="B163">
+        <v>3</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163" t="s">
+        <v>120</v>
+      </c>
+      <c r="E163" t="s">
+        <v>118</v>
+      </c>
+      <c r="F163" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" t="s">
+        <v>98</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163">
+        <v>100</v>
+      </c>
+      <c r="L163">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>21</v>
+      </c>
+      <c r="B164">
+        <v>44</v>
+      </c>
+      <c r="C164">
+        <v>33</v>
+      </c>
+      <c r="D164" t="s">
+        <v>119</v>
+      </c>
+      <c r="E164" t="s">
+        <v>118</v>
+      </c>
+      <c r="F164" t="s">
+        <v>15</v>
+      </c>
+      <c r="G164" t="s">
+        <v>98</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164">
+        <v>100</v>
+      </c>
+      <c r="L164">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>23</v>
+      </c>
+      <c r="B165">
+        <v>90</v>
+      </c>
+      <c r="C165">
+        <v>180</v>
+      </c>
+      <c r="D165" t="s">
+        <v>51</v>
+      </c>
+      <c r="E165" t="s">
+        <v>118</v>
+      </c>
+      <c r="F165" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" t="s">
+        <v>98</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165">
+        <v>100</v>
+      </c>
+      <c r="L165">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166">
+        <v>300</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>20</v>
+      </c>
+      <c r="E166" t="s">
+        <v>118</v>
+      </c>
+      <c r="F166" t="s">
+        <v>15</v>
+      </c>
+      <c r="G166" t="s">
+        <v>98</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166">
+        <v>100</v>
+      </c>
+      <c r="L166">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>12</v>
+      </c>
+      <c r="B167">
+        <v>37</v>
+      </c>
+      <c r="C167">
+        <v>41</v>
+      </c>
+      <c r="D167" t="s">
+        <v>117</v>
+      </c>
+      <c r="E167" t="s">
+        <v>114</v>
+      </c>
+      <c r="F167" t="s">
+        <v>27</v>
+      </c>
+      <c r="G167" t="s">
+        <v>98</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167">
+        <v>100</v>
+      </c>
+      <c r="L167">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>19</v>
+      </c>
+      <c r="B168">
+        <v>4</v>
+      </c>
+      <c r="C168">
+        <v>4</v>
+      </c>
+      <c r="D168" t="s">
+        <v>52</v>
+      </c>
+      <c r="E168" t="s">
+        <v>114</v>
+      </c>
+      <c r="F168" t="s">
+        <v>27</v>
+      </c>
+      <c r="G168" t="s">
+        <v>98</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168">
+        <v>100</v>
+      </c>
+      <c r="L168">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>21</v>
+      </c>
+      <c r="B169">
+        <v>59</v>
+      </c>
+      <c r="C169">
+        <v>53</v>
+      </c>
+      <c r="D169" t="s">
+        <v>116</v>
+      </c>
+      <c r="E169" t="s">
+        <v>114</v>
+      </c>
+      <c r="F169" t="s">
+        <v>27</v>
+      </c>
+      <c r="G169" t="s">
+        <v>98</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169">
+        <v>100</v>
+      </c>
+      <c r="L169">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>23</v>
+      </c>
+      <c r="B170">
+        <v>120</v>
+      </c>
+      <c r="C170">
+        <v>115</v>
+      </c>
+      <c r="D170" t="s">
+        <v>115</v>
+      </c>
+      <c r="E170" t="s">
+        <v>114</v>
+      </c>
+      <c r="F170" t="s">
+        <v>27</v>
+      </c>
+      <c r="G170" t="s">
+        <v>98</v>
+      </c>
+      <c r="H170" t="s">
+        <v>17</v>
+      </c>
+      <c r="I170" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170">
+        <v>100</v>
+      </c>
+      <c r="L170">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171">
+        <v>399</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>20</v>
+      </c>
+      <c r="E171" t="s">
+        <v>114</v>
+      </c>
+      <c r="F171" t="s">
+        <v>27</v>
+      </c>
+      <c r="G171" t="s">
+        <v>98</v>
+      </c>
+      <c r="H171" t="s">
+        <v>17</v>
+      </c>
+      <c r="I171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171">
+        <v>100</v>
+      </c>
+      <c r="L171">
+        <v>89.3</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B172">
+        <v>37</v>
+      </c>
+      <c r="C172">
+        <v>57</v>
+      </c>
+      <c r="D172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E172" t="s">
+        <v>109</v>
+      </c>
+      <c r="F172" t="s">
+        <v>27</v>
+      </c>
+      <c r="G172" t="s">
+        <v>98</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172">
+        <v>100</v>
+      </c>
+      <c r="L172">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>19</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173">
+        <v>9</v>
+      </c>
+      <c r="D173" t="s">
+        <v>112</v>
+      </c>
+      <c r="E173" t="s">
+        <v>109</v>
+      </c>
+      <c r="F173" t="s">
+        <v>27</v>
+      </c>
+      <c r="G173" t="s">
+        <v>98</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173">
+        <v>100</v>
+      </c>
+      <c r="L173">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174">
+        <v>59</v>
+      </c>
+      <c r="C174">
+        <v>58</v>
+      </c>
+      <c r="D174" t="s">
+        <v>111</v>
+      </c>
+      <c r="E174" t="s">
+        <v>109</v>
+      </c>
+      <c r="F174" t="s">
+        <v>27</v>
+      </c>
+      <c r="G174" t="s">
+        <v>98</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174">
+        <v>100</v>
+      </c>
+      <c r="L174">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>23</v>
+      </c>
+      <c r="B175">
+        <v>120</v>
+      </c>
+      <c r="C175">
+        <v>141</v>
+      </c>
+      <c r="D175" t="s">
+        <v>110</v>
+      </c>
+      <c r="E175" t="s">
+        <v>109</v>
+      </c>
+      <c r="F175" t="s">
+        <v>27</v>
+      </c>
+      <c r="G175" t="s">
+        <v>98</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175">
+        <v>100</v>
+      </c>
+      <c r="L175">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>25</v>
+      </c>
+      <c r="B176">
+        <v>399</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>20</v>
+      </c>
+      <c r="E176" t="s">
+        <v>109</v>
+      </c>
+      <c r="F176" t="s">
+        <v>27</v>
+      </c>
+      <c r="G176" t="s">
+        <v>98</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176">
+        <v>100</v>
+      </c>
+      <c r="L176">
+        <v>115.3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>12</v>
+      </c>
+      <c r="B177">
+        <v>37</v>
+      </c>
+      <c r="C177">
+        <v>32</v>
+      </c>
+      <c r="D177" t="s">
+        <v>108</v>
+      </c>
+      <c r="E177" t="s">
+        <v>103</v>
+      </c>
+      <c r="F177" t="s">
+        <v>27</v>
+      </c>
+      <c r="G177" t="s">
+        <v>98</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177" t="s">
+        <v>18</v>
+      </c>
+      <c r="J177" t="s">
+        <v>107</v>
+      </c>
+      <c r="K177">
+        <v>100</v>
+      </c>
+      <c r="L177">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>19</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
+        <v>54</v>
+      </c>
+      <c r="E178" t="s">
+        <v>103</v>
+      </c>
+      <c r="F178" t="s">
+        <v>27</v>
+      </c>
+      <c r="G178" t="s">
+        <v>98</v>
+      </c>
+      <c r="H178" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" t="s">
+        <v>106</v>
+      </c>
+      <c r="K178">
+        <v>100</v>
+      </c>
+      <c r="L178">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>21</v>
+      </c>
+      <c r="B179">
+        <v>59</v>
+      </c>
+      <c r="C179">
+        <v>40</v>
+      </c>
+      <c r="D179" t="s">
+        <v>82</v>
+      </c>
+      <c r="E179" t="s">
+        <v>103</v>
+      </c>
+      <c r="F179" t="s">
+        <v>27</v>
+      </c>
+      <c r="G179" t="s">
+        <v>98</v>
+      </c>
+      <c r="H179" t="s">
+        <v>17</v>
+      </c>
+      <c r="I179" t="s">
+        <v>18</v>
+      </c>
+      <c r="J179" t="s">
+        <v>105</v>
+      </c>
+      <c r="K179">
+        <v>100</v>
+      </c>
+      <c r="L179">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>23</v>
+      </c>
+      <c r="B180">
+        <v>120</v>
+      </c>
+      <c r="C180">
+        <v>116</v>
+      </c>
+      <c r="D180" t="s">
+        <v>24</v>
+      </c>
+      <c r="E180" t="s">
+        <v>103</v>
+      </c>
+      <c r="F180" t="s">
+        <v>27</v>
+      </c>
+      <c r="G180" t="s">
+        <v>98</v>
+      </c>
+      <c r="H180" t="s">
+        <v>17</v>
+      </c>
+      <c r="I180" t="s">
+        <v>18</v>
+      </c>
+      <c r="J180" t="s">
+        <v>104</v>
+      </c>
+      <c r="K180">
+        <v>100</v>
+      </c>
+      <c r="L180">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>25</v>
+      </c>
+      <c r="B181">
+        <v>399</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181" t="s">
+        <v>20</v>
+      </c>
+      <c r="E181" t="s">
+        <v>103</v>
+      </c>
+      <c r="F181" t="s">
+        <v>27</v>
+      </c>
+      <c r="G181" t="s">
+        <v>98</v>
+      </c>
+      <c r="H181" t="s">
+        <v>17</v>
+      </c>
+      <c r="I181" t="s">
+        <v>18</v>
+      </c>
+      <c r="J181" t="s">
+        <v>102</v>
+      </c>
+      <c r="K181">
+        <v>100</v>
+      </c>
+      <c r="L181">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>12</v>
+      </c>
+      <c r="B182">
+        <v>37</v>
+      </c>
+      <c r="C182">
+        <v>0</v>
+      </c>
+      <c r="D182" t="s">
+        <v>20</v>
+      </c>
+      <c r="E182" t="s">
+        <v>101</v>
+      </c>
+      <c r="F182" t="s">
+        <v>80</v>
+      </c>
+      <c r="G182" t="s">
+        <v>98</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182" t="s">
+        <v>18</v>
+      </c>
+      <c r="K182">
+        <v>100</v>
+      </c>
+      <c r="L182">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
+      </c>
+      <c r="C183">
+        <v>0</v>
+      </c>
+      <c r="D183" t="s">
+        <v>20</v>
+      </c>
+      <c r="E183" t="s">
+        <v>101</v>
+      </c>
+      <c r="F183" t="s">
+        <v>80</v>
+      </c>
+      <c r="G183" t="s">
+        <v>98</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183" t="s">
+        <v>18</v>
+      </c>
+      <c r="K183">
+        <v>100</v>
+      </c>
+      <c r="L183">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>21</v>
+      </c>
+      <c r="B184">
+        <v>59</v>
+      </c>
+      <c r="C184">
+        <v>0</v>
+      </c>
+      <c r="D184" t="s">
+        <v>20</v>
+      </c>
+      <c r="E184" t="s">
+        <v>101</v>
+      </c>
+      <c r="F184" t="s">
+        <v>80</v>
+      </c>
+      <c r="G184" t="s">
+        <v>98</v>
+      </c>
+      <c r="H184" t="s">
+        <v>17</v>
+      </c>
+      <c r="I184" t="s">
+        <v>18</v>
+      </c>
+      <c r="K184">
+        <v>100</v>
+      </c>
+      <c r="L184">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>23</v>
+      </c>
+      <c r="B185">
+        <v>120</v>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+      <c r="D185" t="s">
+        <v>24</v>
+      </c>
+      <c r="E185" t="s">
+        <v>101</v>
+      </c>
+      <c r="F185" t="s">
+        <v>80</v>
+      </c>
+      <c r="G185" t="s">
+        <v>98</v>
+      </c>
+      <c r="H185" t="s">
+        <v>17</v>
+      </c>
+      <c r="I185" t="s">
+        <v>18</v>
+      </c>
+      <c r="K185">
+        <v>100</v>
+      </c>
+      <c r="L185">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>25</v>
+      </c>
+      <c r="B186">
+        <v>399</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>20</v>
+      </c>
+      <c r="E186" t="s">
+        <v>101</v>
+      </c>
+      <c r="F186" t="s">
+        <v>80</v>
+      </c>
+      <c r="G186" t="s">
+        <v>98</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186" t="s">
+        <v>18</v>
+      </c>
+      <c r="K186">
+        <v>100</v>
+      </c>
+      <c r="L186">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>12</v>
+      </c>
+      <c r="B187">
+        <v>37</v>
+      </c>
+      <c r="C187">
+        <v>4</v>
+      </c>
+      <c r="D187" t="s">
+        <v>100</v>
+      </c>
+      <c r="E187" t="s">
+        <v>79</v>
+      </c>
+      <c r="F187" t="s">
+        <v>80</v>
+      </c>
+      <c r="G187" t="s">
+        <v>98</v>
+      </c>
+      <c r="H187" t="s">
+        <v>17</v>
+      </c>
+      <c r="I187" t="s">
+        <v>18</v>
+      </c>
+      <c r="K187">
+        <v>100</v>
+      </c>
+      <c r="L187">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>19</v>
+      </c>
+      <c r="B188">
+        <v>4</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188" t="s">
+        <v>54</v>
+      </c>
+      <c r="E188" t="s">
+        <v>79</v>
+      </c>
+      <c r="F188" t="s">
+        <v>80</v>
+      </c>
+      <c r="G188" t="s">
+        <v>98</v>
+      </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
+      <c r="I188" t="s">
+        <v>18</v>
+      </c>
+      <c r="K188">
+        <v>100</v>
+      </c>
+      <c r="L188">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189">
+        <v>59</v>
+      </c>
+      <c r="C189">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>99</v>
+      </c>
+      <c r="E189" t="s">
+        <v>79</v>
+      </c>
+      <c r="F189" t="s">
+        <v>80</v>
+      </c>
+      <c r="G189" t="s">
+        <v>98</v>
+      </c>
+      <c r="H189" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189">
+        <v>100</v>
+      </c>
+      <c r="L189">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>23</v>
+      </c>
+      <c r="B190">
+        <v>120</v>
+      </c>
+      <c r="C190">
+        <v>4</v>
+      </c>
+      <c r="D190" t="s">
+        <v>24</v>
+      </c>
+      <c r="E190" t="s">
+        <v>79</v>
+      </c>
+      <c r="F190" t="s">
+        <v>80</v>
+      </c>
+      <c r="G190" t="s">
+        <v>98</v>
+      </c>
+      <c r="H190" t="s">
+        <v>17</v>
+      </c>
+      <c r="I190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190">
+        <v>100</v>
+      </c>
+      <c r="L190">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>25</v>
+      </c>
+      <c r="B191">
+        <v>399</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191" t="s">
+        <v>20</v>
+      </c>
+      <c r="E191" t="s">
+        <v>79</v>
+      </c>
+      <c r="F191" t="s">
+        <v>80</v>
+      </c>
+      <c r="G191" t="s">
+        <v>98</v>
+      </c>
+      <c r="H191" t="s">
+        <v>17</v>
+      </c>
+      <c r="I191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191">
+        <v>100</v>
+      </c>
+      <c r="L191">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L230" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvs -actualizado/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30FADAC5-54D2-4BA3-9155-37417AC802E9}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_3B992E025660C00F62355476585DCE3A87467095" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1895ED-FC91-4295-8E34-EF2886DA07E1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="144">
   <si>
     <t>Producto</t>
   </si>
@@ -142,21 +142,12 @@
     <t>Evelis Mary Ojeda Baldovino</t>
   </si>
   <si>
-    <t>19%</t>
-  </si>
-  <si>
-    <t>160%</t>
-  </si>
-  <si>
     <t>Sene Del Socorro Suarez Torres</t>
   </si>
   <si>
     <t xml:space="preserve">Vac del 14 al 31 de julio </t>
   </si>
   <si>
-    <t>109%</t>
-  </si>
-  <si>
     <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
   </si>
   <si>
@@ -431,6 +422,39 @@
   </si>
   <si>
     <t>80%</t>
+  </si>
+  <si>
+    <t>Incap 5 días  Meta puntos 653  cump                       Meta postpago 8</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>Meta Hogar 2</t>
+  </si>
+  <si>
+    <t>Meta Terminales  19</t>
+  </si>
+  <si>
+    <t>69%</t>
+  </si>
+  <si>
+    <t>Meta Otros 26</t>
+  </si>
+  <si>
+    <t>Meta CVS PLUS 408</t>
+  </si>
+  <si>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>179%</t>
+  </si>
+  <si>
+    <t>180%</t>
+  </si>
+  <si>
+    <t>27%</t>
   </si>
 </sst>
 </file>
@@ -794,7 +818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L191"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -1546,22 +1570,22 @@
         <v>12</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D22" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E22" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H22" t="s">
         <v>17</v>
@@ -1573,7 +1597,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
@@ -1581,7 +1605,7 @@
         <v>19</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1590,13 +1614,13 @@
         <v>20</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H23" t="s">
         <v>17</v>
@@ -1608,7 +1632,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
@@ -1616,22 +1640,22 @@
         <v>21</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H24" t="s">
         <v>17</v>
@@ -1639,11 +1663,14 @@
       <c r="I24" t="s">
         <v>18</v>
       </c>
+      <c r="J24" t="s">
+        <v>44</v>
+      </c>
       <c r="K24">
         <v>100</v>
       </c>
       <c r="L24">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
@@ -1651,22 +1678,22 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="C25">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H25" t="s">
         <v>17</v>
@@ -1678,7 +1705,7 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
@@ -1695,13 +1722,13 @@
         <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H26" t="s">
         <v>17</v>
@@ -1713,7 +1740,7 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>14.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
@@ -1721,22 +1748,22 @@
         <v>12</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
         <v>27</v>
       </c>
       <c r="G27" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H27" t="s">
         <v>17</v>
@@ -1744,11 +1771,14 @@
       <c r="I27" t="s">
         <v>18</v>
       </c>
+      <c r="J27" t="s">
+        <v>47</v>
+      </c>
       <c r="K27">
         <v>100</v>
       </c>
       <c r="L27">
-        <v>13.4</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
@@ -1756,22 +1786,22 @@
         <v>19</v>
       </c>
       <c r="B28">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="E28" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
         <v>27</v>
       </c>
       <c r="G28" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H28" t="s">
         <v>17</v>
@@ -1783,7 +1813,7 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>13.4</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -1791,22 +1821,22 @@
         <v>21</v>
       </c>
       <c r="B29">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="C29">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
         <v>27</v>
       </c>
       <c r="G29" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H29" t="s">
         <v>17</v>
@@ -1818,7 +1848,7 @@
         <v>100</v>
       </c>
       <c r="L29">
-        <v>13.4</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
@@ -1826,22 +1856,22 @@
         <v>23</v>
       </c>
       <c r="B30">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E30" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
         <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H30" t="s">
         <v>17</v>
@@ -1853,7 +1883,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>13.4</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
@@ -1861,7 +1891,7 @@
         <v>25</v>
       </c>
       <c r="B31">
-        <v>765</v>
+        <v>225</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1870,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
         <v>27</v>
       </c>
       <c r="G31" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H31" t="s">
         <v>17</v>
@@ -1888,7 +1918,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>13.4</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
@@ -1896,22 +1926,22 @@
         <v>12</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F32" t="s">
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H32" t="s">
         <v>17</v>
@@ -1919,14 +1949,11 @@
       <c r="I32" t="s">
         <v>18</v>
       </c>
-      <c r="J32" t="s">
-        <v>42</v>
-      </c>
       <c r="K32">
         <v>100</v>
       </c>
       <c r="L32">
-        <v>113</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
@@ -1934,22 +1961,22 @@
         <v>19</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="E33" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F33" t="s">
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H33" t="s">
         <v>17</v>
@@ -1961,7 +1988,7 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>113</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
@@ -1969,22 +1996,22 @@
         <v>21</v>
       </c>
       <c r="B34">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="C34">
         <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F34" t="s">
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H34" t="s">
         <v>17</v>
@@ -1996,7 +2023,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>113</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
@@ -2004,22 +2031,22 @@
         <v>23</v>
       </c>
       <c r="B35">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="C35">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D35" t="s">
         <v>24</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F35" t="s">
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H35" t="s">
         <v>17</v>
@@ -2031,7 +2058,7 @@
         <v>100</v>
       </c>
       <c r="L35">
-        <v>113</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
@@ -2039,7 +2066,7 @@
         <v>25</v>
       </c>
       <c r="B36">
-        <v>225</v>
+        <v>765</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2048,13 +2075,13 @@
         <v>20</v>
       </c>
       <c r="E36" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F36" t="s">
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H36" t="s">
         <v>17</v>
@@ -2066,7 +2093,7 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>113</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
@@ -2074,22 +2101,22 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F37" t="s">
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H37" t="s">
         <v>17</v>
@@ -2101,7 +2128,7 @@
         <v>100</v>
       </c>
       <c r="L37">
-        <v>17.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
@@ -2109,7 +2136,7 @@
         <v>19</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C38">
         <v>0</v>
@@ -2118,13 +2145,13 @@
         <v>20</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F38" t="s">
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H38" t="s">
         <v>17</v>
@@ -2136,7 +2163,7 @@
         <v>100</v>
       </c>
       <c r="L38">
-        <v>17.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -2144,22 +2171,22 @@
         <v>21</v>
       </c>
       <c r="B39">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F39" t="s">
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H39" t="s">
         <v>17</v>
@@ -2167,14 +2194,11 @@
       <c r="I39" t="s">
         <v>18</v>
       </c>
-      <c r="J39" t="s">
-        <v>47</v>
-      </c>
       <c r="K39">
         <v>100</v>
       </c>
       <c r="L39">
-        <v>17.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
@@ -2185,19 +2209,19 @@
         <v>61</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F40" t="s">
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H40" t="s">
         <v>17</v>
@@ -2209,7 +2233,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>17.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
@@ -2217,7 +2241,7 @@
         <v>25</v>
       </c>
       <c r="B41">
-        <v>510</v>
+        <v>912</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -2226,13 +2250,13 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F41" t="s">
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H41" t="s">
         <v>17</v>
@@ -2244,7 +2268,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>17.5</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
@@ -2252,22 +2276,22 @@
         <v>12</v>
       </c>
       <c r="B42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C42">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F42" t="s">
         <v>27</v>
       </c>
       <c r="G42" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H42" t="s">
         <v>17</v>
@@ -2276,13 +2300,13 @@
         <v>18</v>
       </c>
       <c r="J42" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="K42">
         <v>100</v>
       </c>
       <c r="L42">
-        <v>99.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
@@ -2290,22 +2314,22 @@
         <v>19</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E43" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F43" t="s">
         <v>27</v>
       </c>
       <c r="G43" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H43" t="s">
         <v>17</v>
@@ -2317,7 +2341,7 @@
         <v>100</v>
       </c>
       <c r="L43">
-        <v>99.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
@@ -2325,22 +2349,22 @@
         <v>21</v>
       </c>
       <c r="B44">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F44" t="s">
         <v>27</v>
       </c>
       <c r="G44" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H44" t="s">
         <v>17</v>
@@ -2352,7 +2376,7 @@
         <v>100</v>
       </c>
       <c r="L44">
-        <v>99.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
@@ -2360,22 +2384,22 @@
         <v>23</v>
       </c>
       <c r="B45">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C45">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F45" t="s">
         <v>27</v>
       </c>
       <c r="G45" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H45" t="s">
         <v>17</v>
@@ -2387,7 +2411,7 @@
         <v>100</v>
       </c>
       <c r="L45">
-        <v>99.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
@@ -2395,7 +2419,7 @@
         <v>25</v>
       </c>
       <c r="B46">
-        <v>225</v>
+        <v>288</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -2404,13 +2428,13 @@
         <v>20</v>
       </c>
       <c r="E46" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="F46" t="s">
         <v>27</v>
       </c>
       <c r="G46" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2422,7 +2446,7 @@
         <v>100</v>
       </c>
       <c r="L46">
-        <v>99.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
@@ -2430,22 +2454,22 @@
         <v>12</v>
       </c>
       <c r="B47">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C47">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2457,7 +2481,7 @@
         <v>100</v>
       </c>
       <c r="L47">
-        <v>21.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2465,22 +2489,22 @@
         <v>19</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H48" t="s">
         <v>17</v>
@@ -2492,7 +2516,7 @@
         <v>100</v>
       </c>
       <c r="L48">
-        <v>21.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
@@ -2500,22 +2524,22 @@
         <v>21</v>
       </c>
       <c r="B49">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C49">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="E49" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2527,7 +2551,7 @@
         <v>100</v>
       </c>
       <c r="L49">
-        <v>21.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
@@ -2535,22 +2559,22 @@
         <v>23</v>
       </c>
       <c r="B50">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="D50" t="s">
         <v>24</v>
       </c>
       <c r="E50" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
         <v>17</v>
@@ -2562,7 +2586,7 @@
         <v>100</v>
       </c>
       <c r="L50">
-        <v>21.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
@@ -2570,7 +2594,7 @@
         <v>25</v>
       </c>
       <c r="B51">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2579,13 +2603,13 @@
         <v>20</v>
       </c>
       <c r="E51" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H51" t="s">
         <v>17</v>
@@ -2597,7 +2621,7 @@
         <v>100</v>
       </c>
       <c r="L51">
-        <v>21.8</v>
+        <v>25.9</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
@@ -2605,22 +2629,22 @@
         <v>12</v>
       </c>
       <c r="B52">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F52" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H52" t="s">
         <v>17</v>
@@ -2628,11 +2652,14 @@
       <c r="I52" t="s">
         <v>18</v>
       </c>
+      <c r="J52" t="s">
+        <v>34</v>
+      </c>
       <c r="K52">
         <v>100</v>
       </c>
       <c r="L52">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
@@ -2649,13 +2676,13 @@
         <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F53" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H53" t="s">
         <v>17</v>
@@ -2667,7 +2694,7 @@
         <v>100</v>
       </c>
       <c r="L53">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
@@ -2675,22 +2702,22 @@
         <v>21</v>
       </c>
       <c r="B54">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -2702,7 +2729,7 @@
         <v>100</v>
       </c>
       <c r="L54">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -2710,22 +2737,22 @@
         <v>23</v>
       </c>
       <c r="B55">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C55">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D55" t="s">
         <v>24</v>
       </c>
       <c r="E55" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F55" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H55" t="s">
         <v>17</v>
@@ -2737,7 +2764,7 @@
         <v>100</v>
       </c>
       <c r="L55">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
@@ -2745,7 +2772,7 @@
         <v>25</v>
       </c>
       <c r="B56">
-        <v>912</v>
+        <v>432</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2754,13 +2781,13 @@
         <v>20</v>
       </c>
       <c r="E56" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="F56" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
         <v>17</v>
@@ -2772,7 +2799,7 @@
         <v>100</v>
       </c>
       <c r="L56">
-        <v>10.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
@@ -2780,22 +2807,22 @@
         <v>12</v>
       </c>
       <c r="B57">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="E57" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F57" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="H57" t="s">
         <v>17</v>
@@ -2803,14 +2830,11 @@
       <c r="I57" t="s">
         <v>18</v>
       </c>
-      <c r="J57" t="s">
-        <v>28</v>
-      </c>
       <c r="K57">
         <v>100</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
@@ -2818,7 +2842,7 @@
         <v>19</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2827,13 +2851,13 @@
         <v>20</v>
       </c>
       <c r="E58" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F58" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="H58" t="s">
         <v>17</v>
@@ -2845,7 +2869,7 @@
         <v>100</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
@@ -2853,22 +2877,22 @@
         <v>21</v>
       </c>
       <c r="B59">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="E59" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F59" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="H59" t="s">
         <v>17</v>
@@ -2880,7 +2904,7 @@
         <v>100</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
@@ -2888,22 +2912,22 @@
         <v>23</v>
       </c>
       <c r="B60">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D60" t="s">
         <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F60" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
@@ -2915,7 +2939,7 @@
         <v>100</v>
       </c>
       <c r="L60">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
@@ -2923,7 +2947,7 @@
         <v>25</v>
       </c>
       <c r="B61">
-        <v>288</v>
+        <v>420</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2932,13 +2956,13 @@
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="F61" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="H61" t="s">
         <v>17</v>
@@ -2950,7 +2974,7 @@
         <v>100</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
@@ -2958,22 +2982,22 @@
         <v>12</v>
       </c>
       <c r="B62">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C62">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="E62" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -2985,7 +3009,7 @@
         <v>100</v>
       </c>
       <c r="L62">
-        <v>25.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
@@ -2993,7 +3017,7 @@
         <v>19</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -3002,13 +3026,13 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F63" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
@@ -3020,7 +3044,7 @@
         <v>100</v>
       </c>
       <c r="L63">
-        <v>25.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
@@ -3028,22 +3052,22 @@
         <v>21</v>
       </c>
       <c r="B64">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C64">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F64" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H64" t="s">
         <v>17</v>
@@ -3055,7 +3079,7 @@
         <v>100</v>
       </c>
       <c r="L64">
-        <v>25.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.25">
@@ -3063,22 +3087,22 @@
         <v>23</v>
       </c>
       <c r="B65">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C65">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F65" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H65" t="s">
         <v>17</v>
@@ -3090,7 +3114,7 @@
         <v>100</v>
       </c>
       <c r="L65">
-        <v>25.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.25">
@@ -3098,7 +3122,7 @@
         <v>25</v>
       </c>
       <c r="B66">
-        <v>768</v>
+        <v>630</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3107,13 +3131,13 @@
         <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="F66" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H66" t="s">
         <v>17</v>
@@ -3125,7 +3149,7 @@
         <v>100</v>
       </c>
       <c r="L66">
-        <v>25.9</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.25">
@@ -3133,22 +3157,22 @@
         <v>12</v>
       </c>
       <c r="B67">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D67" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="E67" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F67" t="s">
         <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H67" t="s">
         <v>17</v>
@@ -3157,13 +3181,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="K67">
         <v>100</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
@@ -3171,7 +3195,7 @@
         <v>19</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -3180,13 +3204,13 @@
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F68" t="s">
         <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
@@ -3198,7 +3222,7 @@
         <v>100</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
@@ -3206,22 +3230,22 @@
         <v>21</v>
       </c>
       <c r="B69">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D69" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="E69" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F69" t="s">
         <v>27</v>
       </c>
       <c r="G69" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H69" t="s">
         <v>17</v>
@@ -3233,7 +3257,7 @@
         <v>100</v>
       </c>
       <c r="L69">
-        <v>0</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
@@ -3241,22 +3265,22 @@
         <v>23</v>
       </c>
       <c r="B70">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H70" t="s">
         <v>17</v>
@@ -3268,7 +3292,7 @@
         <v>100</v>
       </c>
       <c r="L70">
-        <v>0</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
@@ -3276,7 +3300,7 @@
         <v>25</v>
       </c>
       <c r="B71">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3285,13 +3309,13 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="F71" t="s">
         <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="H71" t="s">
         <v>17</v>
@@ -3303,7 +3327,7 @@
         <v>100</v>
       </c>
       <c r="L71">
-        <v>0</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
@@ -3311,22 +3335,22 @@
         <v>12</v>
       </c>
       <c r="B72">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D72" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E72" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F72" t="s">
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H72" t="s">
         <v>17</v>
@@ -3334,11 +3358,14 @@
       <c r="I72" t="s">
         <v>18</v>
       </c>
+      <c r="J72" t="s">
+        <v>68</v>
+      </c>
       <c r="K72">
         <v>100</v>
       </c>
       <c r="L72">
-        <v>14.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
@@ -3346,7 +3373,7 @@
         <v>19</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -3355,13 +3382,13 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F73" t="s">
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H73" t="s">
         <v>17</v>
@@ -3369,11 +3396,14 @@
       <c r="I73" t="s">
         <v>18</v>
       </c>
+      <c r="J73" t="s">
+        <v>69</v>
+      </c>
       <c r="K73">
         <v>100</v>
       </c>
       <c r="L73">
-        <v>14.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
@@ -3381,22 +3411,22 @@
         <v>21</v>
       </c>
       <c r="B74">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D74" t="s">
         <v>37</v>
       </c>
       <c r="E74" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F74" t="s">
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H74" t="s">
         <v>17</v>
@@ -3404,11 +3434,14 @@
       <c r="I74" t="s">
         <v>18</v>
       </c>
+      <c r="J74" t="s">
+        <v>70</v>
+      </c>
       <c r="K74">
         <v>100</v>
       </c>
       <c r="L74">
-        <v>14.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
@@ -3416,22 +3449,22 @@
         <v>23</v>
       </c>
       <c r="B75">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C75">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E75" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F75" t="s">
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H75" t="s">
         <v>17</v>
@@ -3439,11 +3472,14 @@
       <c r="I75" t="s">
         <v>18</v>
       </c>
+      <c r="J75" t="s">
+        <v>71</v>
+      </c>
       <c r="K75">
         <v>100</v>
       </c>
       <c r="L75">
-        <v>14.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
@@ -3451,7 +3487,7 @@
         <v>25</v>
       </c>
       <c r="B76">
-        <v>510</v>
+        <v>600</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3460,13 +3496,13 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="F76" t="s">
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H76" t="s">
         <v>17</v>
@@ -3474,11 +3510,14 @@
       <c r="I76" t="s">
         <v>18</v>
       </c>
+      <c r="J76" t="s">
+        <v>72</v>
+      </c>
       <c r="K76">
         <v>100</v>
       </c>
       <c r="L76">
-        <v>14.2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
@@ -3486,22 +3525,22 @@
         <v>12</v>
       </c>
       <c r="B77">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D77" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="E77" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F77" t="s">
         <v>27</v>
       </c>
       <c r="G77" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
@@ -3513,7 +3552,7 @@
         <v>100</v>
       </c>
       <c r="L77">
-        <v>13.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
@@ -3521,7 +3560,7 @@
         <v>19</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3530,13 +3569,13 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F78" t="s">
         <v>27</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -3548,7 +3587,7 @@
         <v>100</v>
       </c>
       <c r="L78">
-        <v>13.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
@@ -3556,22 +3595,22 @@
         <v>21</v>
       </c>
       <c r="B79">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C79">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="E79" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F79" t="s">
         <v>27</v>
       </c>
       <c r="G79" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H79" t="s">
         <v>17</v>
@@ -3583,7 +3622,7 @@
         <v>100</v>
       </c>
       <c r="L79">
-        <v>13.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
@@ -3591,22 +3630,22 @@
         <v>23</v>
       </c>
       <c r="B80">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C80">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F80" t="s">
         <v>27</v>
       </c>
       <c r="G80" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H80" t="s">
         <v>17</v>
@@ -3618,7 +3657,7 @@
         <v>100</v>
       </c>
       <c r="L80">
-        <v>13.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
@@ -3626,7 +3665,7 @@
         <v>25</v>
       </c>
       <c r="B81">
-        <v>765</v>
+        <v>900</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3635,13 +3674,13 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="F81" t="s">
         <v>27</v>
       </c>
       <c r="G81" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -3653,7 +3692,7 @@
         <v>100</v>
       </c>
       <c r="L81">
-        <v>13.4</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
@@ -3661,22 +3700,22 @@
         <v>12</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C82">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E82" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F82" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G82" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -3684,14 +3723,11 @@
       <c r="I82" t="s">
         <v>18</v>
       </c>
-      <c r="J82" t="s">
-        <v>42</v>
-      </c>
       <c r="K82">
         <v>100</v>
       </c>
       <c r="L82">
-        <v>113</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
@@ -3708,13 +3744,13 @@
         <v>20</v>
       </c>
       <c r="E83" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F83" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G83" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H83" t="s">
         <v>17</v>
@@ -3726,7 +3762,7 @@
         <v>100</v>
       </c>
       <c r="L83">
-        <v>113</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
@@ -3734,22 +3770,22 @@
         <v>21</v>
       </c>
       <c r="B84">
+        <v>42</v>
+      </c>
+      <c r="C84">
         <v>11</v>
       </c>
-      <c r="C84">
-        <v>12</v>
-      </c>
       <c r="D84" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="E84" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F84" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G84" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -3761,7 +3797,7 @@
         <v>100</v>
       </c>
       <c r="L84">
-        <v>113</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
@@ -3769,22 +3805,22 @@
         <v>23</v>
       </c>
       <c r="B85">
-        <v>14</v>
+        <v>84</v>
       </c>
       <c r="C85">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D85" t="s">
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F85" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G85" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
@@ -3796,7 +3832,7 @@
         <v>100</v>
       </c>
       <c r="L85">
-        <v>113</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
@@ -3804,7 +3840,7 @@
         <v>25</v>
       </c>
       <c r="B86">
-        <v>225</v>
+        <v>900</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3813,13 +3849,13 @@
         <v>20</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="F86" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G86" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="H86" t="s">
         <v>17</v>
@@ -3831,7 +3867,7 @@
         <v>100</v>
       </c>
       <c r="L86">
-        <v>113</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
@@ -3839,22 +3875,22 @@
         <v>12</v>
       </c>
       <c r="B87">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C87">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E87" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F87" t="s">
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s">
         <v>17</v>
@@ -3862,11 +3898,14 @@
       <c r="I87" t="s">
         <v>18</v>
       </c>
+      <c r="J87" t="s">
+        <v>82</v>
+      </c>
       <c r="K87">
         <v>100</v>
       </c>
       <c r="L87">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
@@ -3874,22 +3913,22 @@
         <v>19</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="E88" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F88" t="s">
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -3901,7 +3940,7 @@
         <v>100</v>
       </c>
       <c r="L88">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
@@ -3909,22 +3948,22 @@
         <v>21</v>
       </c>
       <c r="B89">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="C89">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D89" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="E89" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F89" t="s">
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s">
         <v>17</v>
@@ -3936,7 +3975,7 @@
         <v>100</v>
       </c>
       <c r="L89">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
@@ -3944,22 +3983,22 @@
         <v>23</v>
       </c>
       <c r="B90">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C90">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D90" t="s">
         <v>24</v>
       </c>
       <c r="E90" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F90" t="s">
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s">
         <v>17</v>
@@ -3971,7 +4010,7 @@
         <v>100</v>
       </c>
       <c r="L90">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
@@ -3979,7 +4018,7 @@
         <v>25</v>
       </c>
       <c r="B91">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3988,13 +4027,13 @@
         <v>20</v>
       </c>
       <c r="E91" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F91" t="s">
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H91" t="s">
         <v>17</v>
@@ -4006,7 +4045,7 @@
         <v>100</v>
       </c>
       <c r="L91">
-        <v>42.1</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
@@ -4017,19 +4056,19 @@
         <v>29</v>
       </c>
       <c r="C92">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D92" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E92" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F92" t="s">
         <v>27</v>
       </c>
       <c r="G92" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -4041,7 +4080,7 @@
         <v>100</v>
       </c>
       <c r="L92">
-        <v>29.1</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
@@ -4049,22 +4088,22 @@
         <v>19</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>20</v>
+        <v>86</v>
       </c>
       <c r="E93" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F93" t="s">
         <v>27</v>
       </c>
       <c r="G93" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -4076,7 +4115,7 @@
         <v>100</v>
       </c>
       <c r="L93">
-        <v>29.1</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
@@ -4084,22 +4123,22 @@
         <v>21</v>
       </c>
       <c r="B94">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C94">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D94" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="E94" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F94" t="s">
         <v>27</v>
       </c>
       <c r="G94" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H94" t="s">
         <v>17</v>
@@ -4111,7 +4150,7 @@
         <v>100</v>
       </c>
       <c r="L94">
-        <v>29.1</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
@@ -4119,22 +4158,22 @@
         <v>23</v>
       </c>
       <c r="B95">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C95">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="D95" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="E95" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F95" t="s">
         <v>27</v>
       </c>
       <c r="G95" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s">
         <v>17</v>
@@ -4146,7 +4185,7 @@
         <v>100</v>
       </c>
       <c r="L95">
-        <v>29.1</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -4154,7 +4193,7 @@
         <v>25</v>
       </c>
       <c r="B96">
-        <v>630</v>
+        <v>698</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4163,13 +4202,13 @@
         <v>20</v>
       </c>
       <c r="E96" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="F96" t="s">
         <v>27</v>
       </c>
       <c r="G96" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s">
         <v>17</v>
@@ -4181,7 +4220,7 @@
         <v>100</v>
       </c>
       <c r="L96">
-        <v>29.1</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.25">
@@ -4189,22 +4228,22 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D97" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="E97" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F97" t="s">
         <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s">
         <v>17</v>
@@ -4213,13 +4252,13 @@
         <v>18</v>
       </c>
       <c r="J97" t="s">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="K97">
         <v>100</v>
       </c>
       <c r="L97">
-        <v>13.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4236,13 +4275,13 @@
         <v>20</v>
       </c>
       <c r="E98" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F98" t="s">
         <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s">
         <v>17</v>
@@ -4254,7 +4293,7 @@
         <v>100</v>
       </c>
       <c r="L98">
-        <v>13.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4262,22 +4301,22 @@
         <v>21</v>
       </c>
       <c r="B99">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="C99">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D99" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="E99" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F99" t="s">
         <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s">
         <v>17</v>
@@ -4289,7 +4328,7 @@
         <v>100</v>
       </c>
       <c r="L99">
-        <v>13.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4297,22 +4336,22 @@
         <v>23</v>
       </c>
       <c r="B100">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="C100">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D100" t="s">
         <v>24</v>
       </c>
       <c r="E100" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F100" t="s">
         <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s">
         <v>17</v>
@@ -4324,7 +4363,7 @@
         <v>100</v>
       </c>
       <c r="L100">
-        <v>13.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4332,7 +4371,7 @@
         <v>25</v>
       </c>
       <c r="B101">
-        <v>450</v>
+        <v>338</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4341,13 +4380,13 @@
         <v>20</v>
       </c>
       <c r="E101" t="s">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="F101" t="s">
         <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s">
         <v>17</v>
@@ -4359,7 +4398,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>13.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4367,22 +4406,22 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C102">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D102" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E102" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F102" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G102" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s">
         <v>17</v>
@@ -4390,14 +4429,11 @@
       <c r="I102" t="s">
         <v>18</v>
       </c>
-      <c r="J102" t="s">
-        <v>71</v>
-      </c>
       <c r="K102">
         <v>100</v>
       </c>
       <c r="L102">
-        <v>13</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4405,22 +4441,22 @@
         <v>19</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E103" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F103" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G103" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -4428,14 +4464,11 @@
       <c r="I103" t="s">
         <v>18</v>
       </c>
-      <c r="J103" t="s">
-        <v>72</v>
-      </c>
       <c r="K103">
         <v>100</v>
       </c>
       <c r="L103">
-        <v>13</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4443,22 +4476,22 @@
         <v>21</v>
       </c>
       <c r="B104">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C104">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D104" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E104" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F104" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G104" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s">
         <v>17</v>
@@ -4466,14 +4499,11 @@
       <c r="I104" t="s">
         <v>18</v>
       </c>
-      <c r="J104" t="s">
-        <v>73</v>
-      </c>
       <c r="K104">
         <v>100</v>
       </c>
       <c r="L104">
-        <v>13</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4481,22 +4511,22 @@
         <v>23</v>
       </c>
       <c r="B105">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C105">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D105" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="E105" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F105" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G105" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s">
         <v>17</v>
@@ -4504,14 +4534,11 @@
       <c r="I105" t="s">
         <v>18</v>
       </c>
-      <c r="J105" t="s">
-        <v>74</v>
-      </c>
       <c r="K105">
         <v>100</v>
       </c>
       <c r="L105">
-        <v>13</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4519,7 +4546,7 @@
         <v>25</v>
       </c>
       <c r="B106">
-        <v>600</v>
+        <v>563</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4528,13 +4555,13 @@
         <v>20</v>
       </c>
       <c r="E106" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="F106" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="G106" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s">
         <v>17</v>
@@ -4542,14 +4569,11 @@
       <c r="I106" t="s">
         <v>18</v>
       </c>
-      <c r="J106" t="s">
-        <v>75</v>
-      </c>
       <c r="K106">
         <v>100</v>
       </c>
       <c r="L106">
-        <v>13</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4560,19 +4584,19 @@
         <v>21</v>
       </c>
       <c r="C107">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E107" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F107" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H107" t="s">
         <v>17</v>
@@ -4584,7 +4608,7 @@
         <v>100</v>
       </c>
       <c r="L107">
-        <v>27.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4592,22 +4616,22 @@
         <v>19</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="E108" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F108" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G108" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -4619,7 +4643,7 @@
         <v>100</v>
       </c>
       <c r="L108">
-        <v>27.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4627,22 +4651,22 @@
         <v>21</v>
       </c>
       <c r="B109">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C109">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="E109" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F109" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G109" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H109" t="s">
         <v>17</v>
@@ -4654,7 +4678,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>27.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -4662,22 +4686,22 @@
         <v>23</v>
       </c>
       <c r="B110">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="C110">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="D110" t="s">
-        <v>24</v>
+        <v>131</v>
       </c>
       <c r="E110" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F110" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H110" t="s">
         <v>17</v>
@@ -4689,7 +4713,7 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>27.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -4697,7 +4721,7 @@
         <v>25</v>
       </c>
       <c r="B111">
-        <v>900</v>
+        <v>402</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4706,13 +4730,13 @@
         <v>20</v>
       </c>
       <c r="E111" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="F111" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="G111" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -4724,7 +4748,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>27.2</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -4732,22 +4756,22 @@
         <v>12</v>
       </c>
       <c r="B112">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D112" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="E112" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F112" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="G112" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H112" t="s">
         <v>17</v>
@@ -4759,7 +4783,7 @@
         <v>100</v>
       </c>
       <c r="L112">
-        <v>17.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -4767,22 +4791,22 @@
         <v>19</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>20</v>
+        <v>128</v>
       </c>
       <c r="E113" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F113" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H113" t="s">
         <v>17</v>
@@ -4794,7 +4818,7 @@
         <v>100</v>
       </c>
       <c r="L113">
-        <v>17.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -4802,22 +4826,22 @@
         <v>21</v>
       </c>
       <c r="B114">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C114">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E114" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F114" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
         <v>17</v>
@@ -4829,7 +4853,7 @@
         <v>100</v>
       </c>
       <c r="L114">
-        <v>17.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -4837,22 +4861,22 @@
         <v>23</v>
       </c>
       <c r="B115">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C115">
-        <v>6</v>
+        <v>85</v>
       </c>
       <c r="D115" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="E115" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F115" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H115" t="s">
         <v>17</v>
@@ -4864,7 +4888,7 @@
         <v>100</v>
       </c>
       <c r="L115">
-        <v>17.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -4872,7 +4896,7 @@
         <v>25</v>
       </c>
       <c r="B116">
-        <v>900</v>
+        <v>603</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -4881,13 +4905,13 @@
         <v>20</v>
       </c>
       <c r="E116" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="F116" t="s">
-        <v>80</v>
+        <v>27</v>
       </c>
       <c r="G116" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="H116" t="s">
         <v>17</v>
@@ -4899,7 +4923,7 @@
         <v>100</v>
       </c>
       <c r="L116">
-        <v>17.8</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -4907,22 +4931,22 @@
         <v>12</v>
       </c>
       <c r="B117">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C117">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D117" t="s">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="E117" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F117" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H117" t="s">
         <v>17</v>
@@ -4931,13 +4955,13 @@
         <v>18</v>
       </c>
       <c r="J117" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="K117">
         <v>100</v>
       </c>
       <c r="L117">
-        <v>42</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -4945,22 +4969,22 @@
         <v>19</v>
       </c>
       <c r="B118">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C118">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D118" t="s">
-        <v>57</v>
+        <v>105</v>
       </c>
       <c r="E118" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F118" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G118" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H118" t="s">
         <v>17</v>
@@ -4972,7 +4996,7 @@
         <v>100</v>
       </c>
       <c r="L118">
-        <v>42</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -4980,22 +5004,22 @@
         <v>21</v>
       </c>
       <c r="B119">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C119">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="E119" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F119" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G119" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H119" t="s">
         <v>17</v>
@@ -5007,7 +5031,7 @@
         <v>100</v>
       </c>
       <c r="L119">
-        <v>42</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5015,22 +5039,22 @@
         <v>23</v>
       </c>
       <c r="B120">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C120">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="D120" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="E120" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F120" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G120" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H120" t="s">
         <v>17</v>
@@ -5042,7 +5066,7 @@
         <v>100</v>
       </c>
       <c r="L120">
-        <v>42</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5050,7 +5074,7 @@
         <v>25</v>
       </c>
       <c r="B121">
-        <v>465</v>
+        <v>495</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5059,13 +5083,13 @@
         <v>20</v>
       </c>
       <c r="E121" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="F121" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G121" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H121" t="s">
         <v>17</v>
@@ -5077,7 +5101,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>42</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5085,22 +5109,22 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C122">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>87</v>
+        <v>20</v>
       </c>
       <c r="E122" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F122" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G122" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H122" t="s">
         <v>17</v>
@@ -5112,7 +5136,7 @@
         <v>100</v>
       </c>
       <c r="L122">
-        <v>85.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5120,22 +5144,22 @@
         <v>19</v>
       </c>
       <c r="B123">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C123">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="E123" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F123" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G123" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H123" t="s">
         <v>17</v>
@@ -5147,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="L123">
-        <v>85.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5155,22 +5179,22 @@
         <v>21</v>
       </c>
       <c r="B124">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124" t="s">
         <v>20</v>
       </c>
-      <c r="D124" t="s">
-        <v>90</v>
-      </c>
       <c r="E124" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F124" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G124" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H124" t="s">
         <v>17</v>
@@ -5182,7 +5206,7 @@
         <v>100</v>
       </c>
       <c r="L124">
-        <v>85.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5190,22 +5214,22 @@
         <v>23</v>
       </c>
       <c r="B125">
+        <v>71</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" t="s">
         <v>98</v>
       </c>
-      <c r="C125">
-        <v>79</v>
-      </c>
-      <c r="D125" t="s">
-        <v>91</v>
-      </c>
-      <c r="E125" t="s">
-        <v>88</v>
-      </c>
       <c r="F125" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G125" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H125" t="s">
         <v>17</v>
@@ -5217,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="L125">
-        <v>85.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5225,7 +5249,7 @@
         <v>25</v>
       </c>
       <c r="B126">
-        <v>698</v>
+        <v>563</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5234,13 +5258,13 @@
         <v>20</v>
       </c>
       <c r="E126" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F126" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G126" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H126" t="s">
         <v>17</v>
@@ -5252,7 +5276,7 @@
         <v>100</v>
       </c>
       <c r="L126">
-        <v>85.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5260,22 +5284,22 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C127">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="E127" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F127" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G127" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H127" t="s">
         <v>17</v>
@@ -5283,14 +5307,11 @@
       <c r="I127" t="s">
         <v>18</v>
       </c>
-      <c r="J127" t="s">
-        <v>94</v>
-      </c>
       <c r="K127">
         <v>100</v>
       </c>
       <c r="L127">
-        <v>47.3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5298,7 +5319,7 @@
         <v>19</v>
       </c>
       <c r="B128">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -5307,13 +5328,13 @@
         <v>20</v>
       </c>
       <c r="E128" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F128" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G128" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H128" t="s">
         <v>17</v>
@@ -5325,7 +5346,7 @@
         <v>100</v>
       </c>
       <c r="L128">
-        <v>47.3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5333,22 +5354,22 @@
         <v>21</v>
       </c>
       <c r="B129">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C129">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E129" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F129" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G129" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H129" t="s">
         <v>17</v>
@@ -5360,7 +5381,7 @@
         <v>100</v>
       </c>
       <c r="L129">
-        <v>47.3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5368,22 +5389,22 @@
         <v>23</v>
       </c>
       <c r="B130">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C130">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D130" t="s">
         <v>24</v>
       </c>
       <c r="E130" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F130" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G130" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H130" t="s">
         <v>17</v>
@@ -5395,7 +5416,7 @@
         <v>100</v>
       </c>
       <c r="L130">
-        <v>47.3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5403,7 +5424,7 @@
         <v>25</v>
       </c>
       <c r="B131">
-        <v>338</v>
+        <v>563</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -5412,13 +5433,13 @@
         <v>20</v>
       </c>
       <c r="E131" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F131" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G131" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H131" t="s">
         <v>17</v>
@@ -5430,7 +5451,7 @@
         <v>100</v>
       </c>
       <c r="L131">
-        <v>47.3</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5438,22 +5459,22 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D132" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E132" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F132" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G132" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H132" t="s">
         <v>17</v>
@@ -5465,7 +5486,7 @@
         <v>100</v>
       </c>
       <c r="L132">
-        <v>13.9</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5473,22 +5494,22 @@
         <v>19</v>
       </c>
       <c r="B133">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D133" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="E133" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F133" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G133" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H133" t="s">
         <v>17</v>
@@ -5500,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>13.9</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5508,22 +5529,22 @@
         <v>21</v>
       </c>
       <c r="B134">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C134">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D134" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="E134" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F134" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G134" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H134" t="s">
         <v>17</v>
@@ -5535,7 +5556,7 @@
         <v>100</v>
       </c>
       <c r="L134">
-        <v>13.9</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5543,22 +5564,22 @@
         <v>23</v>
       </c>
       <c r="B135">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="C135">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="D135" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E135" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F135" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G135" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H135" t="s">
         <v>17</v>
@@ -5570,7 +5591,7 @@
         <v>100</v>
       </c>
       <c r="L135">
-        <v>13.9</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5578,7 +5599,7 @@
         <v>25</v>
       </c>
       <c r="B136">
-        <v>563</v>
+        <v>300</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5587,13 +5608,13 @@
         <v>20</v>
       </c>
       <c r="E136" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="F136" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
       <c r="G136" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H136" t="s">
         <v>17</v>
@@ -5605,7 +5626,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>13.9</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5613,22 +5634,22 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C137">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D137" t="s">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="E137" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F137" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G137" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H137" t="s">
         <v>17</v>
@@ -5640,7 +5661,7 @@
         <v>100</v>
       </c>
       <c r="L137">
-        <v>76.3</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -5648,22 +5669,22 @@
         <v>19</v>
       </c>
       <c r="B138">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C138">
         <v>4</v>
       </c>
       <c r="D138" t="s">
-        <v>135</v>
+        <v>49</v>
       </c>
       <c r="E138" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F138" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G138" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H138" t="s">
         <v>17</v>
@@ -5675,7 +5696,7 @@
         <v>100</v>
       </c>
       <c r="L138">
-        <v>76.3</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -5683,22 +5704,22 @@
         <v>21</v>
       </c>
       <c r="B139">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="C139">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="D139" t="s">
-        <v>60</v>
+        <v>113</v>
       </c>
       <c r="E139" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F139" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G139" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H139" t="s">
         <v>17</v>
@@ -5710,7 +5731,7 @@
         <v>100</v>
       </c>
       <c r="L139">
-        <v>76.3</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -5718,22 +5739,22 @@
         <v>23</v>
       </c>
       <c r="B140">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="C140">
-        <v>62</v>
+        <v>115</v>
       </c>
       <c r="D140" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E140" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F140" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G140" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H140" t="s">
         <v>17</v>
@@ -5745,7 +5766,7 @@
         <v>100</v>
       </c>
       <c r="L140">
-        <v>76.3</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -5753,7 +5774,7 @@
         <v>25</v>
       </c>
       <c r="B141">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5762,13 +5783,13 @@
         <v>20</v>
       </c>
       <c r="E141" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="F141" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G141" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H141" t="s">
         <v>17</v>
@@ -5780,7 +5801,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>76.3</v>
+        <v>89.3</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -5788,22 +5809,22 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C142">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="D142" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="E142" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F142" t="s">
         <v>27</v>
       </c>
       <c r="G142" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H142" t="s">
         <v>17</v>
@@ -5815,7 +5836,7 @@
         <v>100</v>
       </c>
       <c r="L142">
-        <v>83.7</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -5823,22 +5844,22 @@
         <v>19</v>
       </c>
       <c r="B143">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C143">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D143" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="E143" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F143" t="s">
         <v>27</v>
       </c>
       <c r="G143" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H143" t="s">
         <v>17</v>
@@ -5850,7 +5871,7 @@
         <v>100</v>
       </c>
       <c r="L143">
-        <v>83.7</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -5858,22 +5879,22 @@
         <v>21</v>
       </c>
       <c r="B144">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="C144">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="D144" t="s">
         <v>108</v>
       </c>
       <c r="E144" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F144" t="s">
         <v>27</v>
       </c>
       <c r="G144" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H144" t="s">
         <v>17</v>
@@ -5885,7 +5906,7 @@
         <v>100</v>
       </c>
       <c r="L144">
-        <v>83.7</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -5893,22 +5914,22 @@
         <v>23</v>
       </c>
       <c r="B145">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="C145">
-        <v>85</v>
+        <v>141</v>
       </c>
       <c r="D145" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="E145" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F145" t="s">
         <v>27</v>
       </c>
       <c r="G145" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H145" t="s">
         <v>17</v>
@@ -5920,7 +5941,7 @@
         <v>100</v>
       </c>
       <c r="L145">
-        <v>83.7</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -5928,7 +5949,7 @@
         <v>25</v>
       </c>
       <c r="B146">
-        <v>603</v>
+        <v>399</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -5937,13 +5958,13 @@
         <v>20</v>
       </c>
       <c r="E146" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="F146" t="s">
         <v>27</v>
       </c>
       <c r="G146" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H146" t="s">
         <v>17</v>
@@ -5955,7 +5976,7 @@
         <v>100</v>
       </c>
       <c r="L146">
-        <v>83.7</v>
+        <v>115.3</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -5963,22 +5984,22 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C147">
         <v>32</v>
       </c>
       <c r="D147" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="E147" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F147" t="s">
         <v>27</v>
       </c>
       <c r="G147" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H147" t="s">
         <v>17</v>
@@ -5987,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="J147" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="K147">
         <v>100</v>
       </c>
       <c r="L147">
-        <v>84.1</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6001,22 +6022,22 @@
         <v>19</v>
       </c>
       <c r="B148">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C148">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D148" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="E148" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F148" t="s">
         <v>27</v>
       </c>
       <c r="G148" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H148" t="s">
         <v>17</v>
@@ -6024,11 +6045,14 @@
       <c r="I148" t="s">
         <v>18</v>
       </c>
+      <c r="J148" t="s">
+        <v>103</v>
+      </c>
       <c r="K148">
         <v>100</v>
       </c>
       <c r="L148">
-        <v>84.1</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6036,22 +6060,22 @@
         <v>21</v>
       </c>
       <c r="B149">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C149">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D149" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="E149" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F149" t="s">
         <v>27</v>
       </c>
       <c r="G149" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H149" t="s">
         <v>17</v>
@@ -6059,11 +6083,14 @@
       <c r="I149" t="s">
         <v>18</v>
       </c>
+      <c r="J149" t="s">
+        <v>102</v>
+      </c>
       <c r="K149">
         <v>100</v>
       </c>
       <c r="L149">
-        <v>84.1</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6071,22 +6098,22 @@
         <v>23</v>
       </c>
       <c r="B150">
-        <v>63</v>
+        <v>120</v>
       </c>
       <c r="C150">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="D150" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="E150" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F150" t="s">
         <v>27</v>
       </c>
       <c r="G150" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H150" t="s">
         <v>17</v>
@@ -6094,11 +6121,14 @@
       <c r="I150" t="s">
         <v>18</v>
       </c>
+      <c r="J150" t="s">
+        <v>101</v>
+      </c>
       <c r="K150">
         <v>100</v>
       </c>
       <c r="L150">
-        <v>84.1</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6106,7 +6136,7 @@
         <v>25</v>
       </c>
       <c r="B151">
-        <v>495</v>
+        <v>399</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6115,13 +6145,13 @@
         <v>20</v>
       </c>
       <c r="E151" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F151" t="s">
         <v>27</v>
       </c>
       <c r="G151" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H151" t="s">
         <v>17</v>
@@ -6129,11 +6159,14 @@
       <c r="I151" t="s">
         <v>18</v>
       </c>
+      <c r="J151" t="s">
+        <v>99</v>
+      </c>
       <c r="K151">
         <v>100</v>
       </c>
       <c r="L151">
-        <v>84.1</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6141,7 +6174,7 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -6150,13 +6183,13 @@
         <v>20</v>
       </c>
       <c r="E152" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F152" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G152" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H152" t="s">
         <v>17</v>
@@ -6168,7 +6201,7 @@
         <v>100</v>
       </c>
       <c r="L152">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6176,7 +6209,7 @@
         <v>19</v>
       </c>
       <c r="B153">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -6185,13 +6218,13 @@
         <v>20</v>
       </c>
       <c r="E153" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F153" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G153" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H153" t="s">
         <v>17</v>
@@ -6203,7 +6236,7 @@
         <v>100</v>
       </c>
       <c r="L153">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6211,7 +6244,7 @@
         <v>21</v>
       </c>
       <c r="B154">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -6220,13 +6253,13 @@
         <v>20</v>
       </c>
       <c r="E154" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F154" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G154" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H154" t="s">
         <v>17</v>
@@ -6238,7 +6271,7 @@
         <v>100</v>
       </c>
       <c r="L154">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6246,22 +6279,22 @@
         <v>23</v>
       </c>
       <c r="B155">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C155">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D155" t="s">
         <v>24</v>
       </c>
       <c r="E155" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F155" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G155" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H155" t="s">
         <v>17</v>
@@ -6273,7 +6306,7 @@
         <v>100</v>
       </c>
       <c r="L155">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6281,7 +6314,7 @@
         <v>25</v>
       </c>
       <c r="B156">
-        <v>563</v>
+        <v>399</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6290,13 +6323,13 @@
         <v>20</v>
       </c>
       <c r="E156" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F156" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G156" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H156" t="s">
         <v>17</v>
@@ -6308,7 +6341,7 @@
         <v>100</v>
       </c>
       <c r="L156">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6316,22 +6349,22 @@
         <v>12</v>
       </c>
       <c r="B157">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D157" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="E157" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F157" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G157" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H157" t="s">
         <v>17</v>
@@ -6343,7 +6376,7 @@
         <v>100</v>
       </c>
       <c r="L157">
-        <v>2.2000000000000002</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6351,22 +6384,22 @@
         <v>19</v>
       </c>
       <c r="B158">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="E158" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F158" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G158" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H158" t="s">
         <v>17</v>
@@ -6378,7 +6411,7 @@
         <v>100</v>
       </c>
       <c r="L158">
-        <v>2.2000000000000002</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6386,22 +6419,22 @@
         <v>21</v>
       </c>
       <c r="B159">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="C159">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="E159" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F159" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G159" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H159" t="s">
         <v>17</v>
@@ -6413,7 +6446,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>2.2000000000000002</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6421,22 +6454,22 @@
         <v>23</v>
       </c>
       <c r="B160">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="C160">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D160" t="s">
         <v>24</v>
       </c>
       <c r="E160" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F160" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G160" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H160" t="s">
         <v>17</v>
@@ -6448,7 +6481,7 @@
         <v>100</v>
       </c>
       <c r="L160">
-        <v>2.2000000000000002</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6456,7 +6489,7 @@
         <v>25</v>
       </c>
       <c r="B161">
-        <v>563</v>
+        <v>399</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -6465,13 +6498,13 @@
         <v>20</v>
       </c>
       <c r="E161" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F161" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G161" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="H161" t="s">
         <v>17</v>
@@ -6483,7 +6516,7 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>2.2000000000000002</v>
+        <v>8.3000000000000007</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6491,22 +6524,22 @@
         <v>12</v>
       </c>
       <c r="B162">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C162">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D162" t="s">
-        <v>121</v>
+        <v>75</v>
       </c>
       <c r="E162" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F162" t="s">
         <v>15</v>
       </c>
       <c r="G162" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H162" t="s">
         <v>17</v>
@@ -6514,11 +6547,14 @@
       <c r="I162" t="s">
         <v>18</v>
       </c>
+      <c r="J162" t="s">
+        <v>133</v>
+      </c>
       <c r="K162">
         <v>100</v>
       </c>
       <c r="L162">
-        <v>95.5</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6529,19 +6565,19 @@
         <v>3</v>
       </c>
       <c r="C163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D163" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E163" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F163" t="s">
         <v>15</v>
       </c>
       <c r="G163" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H163" t="s">
         <v>17</v>
@@ -6549,11 +6585,14 @@
       <c r="I163" t="s">
         <v>18</v>
       </c>
+      <c r="J163" t="s">
+        <v>135</v>
+      </c>
       <c r="K163">
         <v>100</v>
       </c>
       <c r="L163">
-        <v>95.5</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6561,22 +6600,22 @@
         <v>21</v>
       </c>
       <c r="B164">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="C164">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E164" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F164" t="s">
         <v>15</v>
       </c>
       <c r="G164" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H164" t="s">
         <v>17</v>
@@ -6584,11 +6623,14 @@
       <c r="I164" t="s">
         <v>18</v>
       </c>
+      <c r="J164" t="s">
+        <v>136</v>
+      </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>95.5</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6596,22 +6638,22 @@
         <v>23</v>
       </c>
       <c r="B165">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="C165">
-        <v>180</v>
+        <v>22</v>
       </c>
       <c r="D165" t="s">
-        <v>51</v>
+        <v>137</v>
       </c>
       <c r="E165" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F165" t="s">
         <v>15</v>
       </c>
       <c r="G165" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H165" t="s">
         <v>17</v>
@@ -6619,11 +6661,14 @@
       <c r="I165" t="s">
         <v>18</v>
       </c>
+      <c r="J165" t="s">
+        <v>138</v>
+      </c>
       <c r="K165">
         <v>100</v>
       </c>
       <c r="L165">
-        <v>95.5</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -6631,7 +6676,7 @@
         <v>25</v>
       </c>
       <c r="B166">
-        <v>300</v>
+        <v>510</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6640,13 +6685,13 @@
         <v>20</v>
       </c>
       <c r="E166" t="s">
-        <v>118</v>
+        <v>35</v>
       </c>
       <c r="F166" t="s">
         <v>15</v>
       </c>
       <c r="G166" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H166" t="s">
         <v>17</v>
@@ -6654,11 +6699,14 @@
       <c r="I166" t="s">
         <v>18</v>
       </c>
+      <c r="J166" t="s">
+        <v>139</v>
+      </c>
       <c r="K166">
         <v>100</v>
       </c>
       <c r="L166">
-        <v>95.5</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -6666,22 +6714,22 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C167">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D167" t="s">
-        <v>117</v>
+        <v>140</v>
       </c>
       <c r="E167" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="F167" t="s">
         <v>27</v>
       </c>
       <c r="G167" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H167" t="s">
         <v>17</v>
@@ -6693,7 +6741,7 @@
         <v>100</v>
       </c>
       <c r="L167">
-        <v>89.3</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -6701,22 +6749,22 @@
         <v>19</v>
       </c>
       <c r="B168">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C168">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D168" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="E168" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="F168" t="s">
         <v>27</v>
       </c>
       <c r="G168" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H168" t="s">
         <v>17</v>
@@ -6728,7 +6776,7 @@
         <v>100</v>
       </c>
       <c r="L168">
-        <v>89.3</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -6736,22 +6784,22 @@
         <v>21</v>
       </c>
       <c r="B169">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C169">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D169" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="E169" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="F169" t="s">
         <v>27</v>
       </c>
       <c r="G169" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H169" t="s">
         <v>17</v>
@@ -6763,7 +6811,7 @@
         <v>100</v>
       </c>
       <c r="L169">
-        <v>89.3</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -6771,22 +6819,22 @@
         <v>23</v>
       </c>
       <c r="B170">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="C170">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="D170" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="E170" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="F170" t="s">
         <v>27</v>
       </c>
       <c r="G170" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H170" t="s">
         <v>17</v>
@@ -6798,7 +6846,7 @@
         <v>100</v>
       </c>
       <c r="L170">
-        <v>89.3</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -6806,7 +6854,7 @@
         <v>25</v>
       </c>
       <c r="B171">
-        <v>399</v>
+        <v>765</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -6815,13 +6863,13 @@
         <v>20</v>
       </c>
       <c r="E171" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="F171" t="s">
         <v>27</v>
       </c>
       <c r="G171" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H171" t="s">
         <v>17</v>
@@ -6833,7 +6881,7 @@
         <v>100</v>
       </c>
       <c r="L171">
-        <v>89.3</v>
+        <v>84.1</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -6841,22 +6889,22 @@
         <v>12</v>
       </c>
       <c r="B172">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="C172">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>113</v>
+        <v>142</v>
       </c>
       <c r="E172" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F172" t="s">
         <v>27</v>
       </c>
       <c r="G172" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H172" t="s">
         <v>17</v>
@@ -6864,11 +6912,14 @@
       <c r="I172" t="s">
         <v>18</v>
       </c>
+      <c r="J172" t="s">
+        <v>40</v>
+      </c>
       <c r="K172">
         <v>100</v>
       </c>
       <c r="L172">
-        <v>115.3</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -6876,22 +6927,22 @@
         <v>19</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C173">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="E173" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F173" t="s">
         <v>27</v>
       </c>
       <c r="G173" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H173" t="s">
         <v>17</v>
@@ -6903,7 +6954,7 @@
         <v>100</v>
       </c>
       <c r="L173">
-        <v>115.3</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -6911,22 +6962,22 @@
         <v>21</v>
       </c>
       <c r="B174">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C174">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D174" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E174" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F174" t="s">
         <v>27</v>
       </c>
       <c r="G174" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H174" t="s">
         <v>17</v>
@@ -6938,7 +6989,7 @@
         <v>100</v>
       </c>
       <c r="L174">
-        <v>115.3</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -6946,22 +6997,22 @@
         <v>23</v>
       </c>
       <c r="B175">
-        <v>120</v>
+        <v>14</v>
       </c>
       <c r="C175">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="D175" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="E175" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F175" t="s">
         <v>27</v>
       </c>
       <c r="G175" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H175" t="s">
         <v>17</v>
@@ -6973,7 +7024,7 @@
         <v>100</v>
       </c>
       <c r="L175">
-        <v>115.3</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -6981,7 +7032,7 @@
         <v>25</v>
       </c>
       <c r="B176">
-        <v>399</v>
+        <v>225</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -6990,13 +7041,13 @@
         <v>20</v>
       </c>
       <c r="E176" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="F176" t="s">
         <v>27</v>
       </c>
       <c r="G176" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H176" t="s">
         <v>17</v>
@@ -7008,7 +7059,7 @@
         <v>100</v>
       </c>
       <c r="L176">
-        <v>115.3</v>
+        <v>128.6</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7016,22 +7067,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C177">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="E177" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F177" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G177" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H177" t="s">
         <v>17</v>
@@ -7039,14 +7090,11 @@
       <c r="I177" t="s">
         <v>18</v>
       </c>
-      <c r="J177" t="s">
-        <v>107</v>
-      </c>
       <c r="K177">
         <v>100</v>
       </c>
       <c r="L177">
-        <v>67.5</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7060,16 +7108,16 @@
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E178" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F178" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G178" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H178" t="s">
         <v>17</v>
@@ -7077,14 +7125,11 @@
       <c r="I178" t="s">
         <v>18</v>
       </c>
-      <c r="J178" t="s">
-        <v>106</v>
-      </c>
       <c r="K178">
         <v>100</v>
       </c>
       <c r="L178">
-        <v>67.5</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7092,22 +7137,22 @@
         <v>21</v>
       </c>
       <c r="B179">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C179">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D179" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E179" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F179" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G179" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H179" t="s">
         <v>17</v>
@@ -7115,14 +7160,11 @@
       <c r="I179" t="s">
         <v>18</v>
       </c>
-      <c r="J179" t="s">
-        <v>105</v>
-      </c>
       <c r="K179">
         <v>100</v>
       </c>
       <c r="L179">
-        <v>67.5</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7130,22 +7172,22 @@
         <v>23</v>
       </c>
       <c r="B180">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="C180">
-        <v>116</v>
+        <v>5</v>
       </c>
       <c r="D180" t="s">
         <v>24</v>
       </c>
       <c r="E180" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F180" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G180" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H180" t="s">
         <v>17</v>
@@ -7153,14 +7195,11 @@
       <c r="I180" t="s">
         <v>18</v>
       </c>
-      <c r="J180" t="s">
-        <v>104</v>
-      </c>
       <c r="K180">
         <v>100</v>
       </c>
       <c r="L180">
-        <v>67.5</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7168,7 +7207,7 @@
         <v>25</v>
       </c>
       <c r="B181">
-        <v>399</v>
+        <v>563</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -7177,13 +7216,13 @@
         <v>20</v>
       </c>
       <c r="E181" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="F181" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="G181" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H181" t="s">
         <v>17</v>
@@ -7191,364 +7230,11 @@
       <c r="I181" t="s">
         <v>18</v>
       </c>
-      <c r="J181" t="s">
-        <v>102</v>
-      </c>
       <c r="K181">
         <v>100</v>
       </c>
       <c r="L181">
-        <v>67.5</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>12</v>
-      </c>
-      <c r="B182">
-        <v>37</v>
-      </c>
-      <c r="C182">
-        <v>0</v>
-      </c>
-      <c r="D182" t="s">
-        <v>20</v>
-      </c>
-      <c r="E182" t="s">
-        <v>101</v>
-      </c>
-      <c r="F182" t="s">
-        <v>80</v>
-      </c>
-      <c r="G182" t="s">
-        <v>98</v>
-      </c>
-      <c r="H182" t="s">
-        <v>17</v>
-      </c>
-      <c r="I182" t="s">
-        <v>18</v>
-      </c>
-      <c r="K182">
-        <v>100</v>
-      </c>
-      <c r="L182">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>19</v>
-      </c>
-      <c r="B183">
-        <v>4</v>
-      </c>
-      <c r="C183">
-        <v>0</v>
-      </c>
-      <c r="D183" t="s">
-        <v>20</v>
-      </c>
-      <c r="E183" t="s">
-        <v>101</v>
-      </c>
-      <c r="F183" t="s">
-        <v>80</v>
-      </c>
-      <c r="G183" t="s">
-        <v>98</v>
-      </c>
-      <c r="H183" t="s">
-        <v>17</v>
-      </c>
-      <c r="I183" t="s">
-        <v>18</v>
-      </c>
-      <c r="K183">
-        <v>100</v>
-      </c>
-      <c r="L183">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>21</v>
-      </c>
-      <c r="B184">
-        <v>59</v>
-      </c>
-      <c r="C184">
-        <v>0</v>
-      </c>
-      <c r="D184" t="s">
-        <v>20</v>
-      </c>
-      <c r="E184" t="s">
-        <v>101</v>
-      </c>
-      <c r="F184" t="s">
-        <v>80</v>
-      </c>
-      <c r="G184" t="s">
-        <v>98</v>
-      </c>
-      <c r="H184" t="s">
-        <v>17</v>
-      </c>
-      <c r="I184" t="s">
-        <v>18</v>
-      </c>
-      <c r="K184">
-        <v>100</v>
-      </c>
-      <c r="L184">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>23</v>
-      </c>
-      <c r="B185">
-        <v>120</v>
-      </c>
-      <c r="C185">
-        <v>2</v>
-      </c>
-      <c r="D185" t="s">
-        <v>24</v>
-      </c>
-      <c r="E185" t="s">
-        <v>101</v>
-      </c>
-      <c r="F185" t="s">
-        <v>80</v>
-      </c>
-      <c r="G185" t="s">
-        <v>98</v>
-      </c>
-      <c r="H185" t="s">
-        <v>17</v>
-      </c>
-      <c r="I185" t="s">
-        <v>18</v>
-      </c>
-      <c r="K185">
-        <v>100</v>
-      </c>
-      <c r="L185">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>25</v>
-      </c>
-      <c r="B186">
-        <v>399</v>
-      </c>
-      <c r="C186">
-        <v>0</v>
-      </c>
-      <c r="D186" t="s">
-        <v>20</v>
-      </c>
-      <c r="E186" t="s">
-        <v>101</v>
-      </c>
-      <c r="F186" t="s">
-        <v>80</v>
-      </c>
-      <c r="G186" t="s">
-        <v>98</v>
-      </c>
-      <c r="H186" t="s">
-        <v>17</v>
-      </c>
-      <c r="I186" t="s">
-        <v>18</v>
-      </c>
-      <c r="K186">
-        <v>100</v>
-      </c>
-      <c r="L186">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>12</v>
-      </c>
-      <c r="B187">
-        <v>37</v>
-      </c>
-      <c r="C187">
-        <v>4</v>
-      </c>
-      <c r="D187" t="s">
-        <v>100</v>
-      </c>
-      <c r="E187" t="s">
-        <v>79</v>
-      </c>
-      <c r="F187" t="s">
-        <v>80</v>
-      </c>
-      <c r="G187" t="s">
-        <v>98</v>
-      </c>
-      <c r="H187" t="s">
-        <v>17</v>
-      </c>
-      <c r="I187" t="s">
-        <v>18</v>
-      </c>
-      <c r="K187">
-        <v>100</v>
-      </c>
-      <c r="L187">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>19</v>
-      </c>
-      <c r="B188">
-        <v>4</v>
-      </c>
-      <c r="C188">
-        <v>1</v>
-      </c>
-      <c r="D188" t="s">
-        <v>54</v>
-      </c>
-      <c r="E188" t="s">
-        <v>79</v>
-      </c>
-      <c r="F188" t="s">
-        <v>80</v>
-      </c>
-      <c r="G188" t="s">
-        <v>98</v>
-      </c>
-      <c r="H188" t="s">
-        <v>17</v>
-      </c>
-      <c r="I188" t="s">
-        <v>18</v>
-      </c>
-      <c r="K188">
-        <v>100</v>
-      </c>
-      <c r="L188">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>21</v>
-      </c>
-      <c r="B189">
-        <v>59</v>
-      </c>
-      <c r="C189">
-        <v>5</v>
-      </c>
-      <c r="D189" t="s">
-        <v>99</v>
-      </c>
-      <c r="E189" t="s">
-        <v>79</v>
-      </c>
-      <c r="F189" t="s">
-        <v>80</v>
-      </c>
-      <c r="G189" t="s">
-        <v>98</v>
-      </c>
-      <c r="H189" t="s">
-        <v>17</v>
-      </c>
-      <c r="I189" t="s">
-        <v>18</v>
-      </c>
-      <c r="K189">
-        <v>100</v>
-      </c>
-      <c r="L189">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>23</v>
-      </c>
-      <c r="B190">
-        <v>120</v>
-      </c>
-      <c r="C190">
-        <v>4</v>
-      </c>
-      <c r="D190" t="s">
-        <v>24</v>
-      </c>
-      <c r="E190" t="s">
-        <v>79</v>
-      </c>
-      <c r="F190" t="s">
-        <v>80</v>
-      </c>
-      <c r="G190" t="s">
-        <v>98</v>
-      </c>
-      <c r="H190" t="s">
-        <v>17</v>
-      </c>
-      <c r="I190" t="s">
-        <v>18</v>
-      </c>
-      <c r="K190">
-        <v>100</v>
-      </c>
-      <c r="L190">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>25</v>
-      </c>
-      <c r="B191">
-        <v>399</v>
-      </c>
-      <c r="C191">
-        <v>0</v>
-      </c>
-      <c r="D191" t="s">
-        <v>20</v>
-      </c>
-      <c r="E191" t="s">
-        <v>79</v>
-      </c>
-      <c r="F191" t="s">
-        <v>80</v>
-      </c>
-      <c r="G191" t="s">
-        <v>98</v>
-      </c>
-      <c r="H191" t="s">
-        <v>17</v>
-      </c>
-      <c r="I191" t="s">
-        <v>18</v>
-      </c>
-      <c r="K191">
-        <v>100</v>
-      </c>
-      <c r="L191">
-        <v>8.3000000000000007</v>
+        <v>14.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvsjulio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_295D9EEDD058CA0F62355476585DCE3A87455B01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14C0CE97-C435-4F22-A413-C8F7455F2F0C}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_295D9EEDD058CA0F62355476585DCE3A87455B01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57FD8A5D-5F94-47C3-89CF-41AC0EFE357A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4573,34 +4573,34 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C97">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="E97" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F97" t="s">
         <v>14</v>
       </c>
       <c r="G97" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
       </c>
       <c r="I97" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K97">
         <v>100</v>
       </c>
       <c r="L97">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,22 +4608,22 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C98">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F98" t="s">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -4635,7 +4635,7 @@
         <v>100</v>
       </c>
       <c r="L98">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4643,34 +4643,34 @@
         <v>20</v>
       </c>
       <c r="B99">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C99">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="D99" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E99" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F99" t="s">
         <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
       </c>
       <c r="I99" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K99">
         <v>100</v>
       </c>
       <c r="L99">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4678,34 +4678,34 @@
         <v>21</v>
       </c>
       <c r="B100">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C100">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D100" t="s">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="E100" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
       </c>
       <c r="I100" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K100">
         <v>100</v>
       </c>
       <c r="L100">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4713,34 +4713,34 @@
         <v>23</v>
       </c>
       <c r="B101">
-        <v>402</v>
+        <v>750</v>
       </c>
       <c r="C101">
-        <v>402</v>
+        <v>800</v>
       </c>
       <c r="D101" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="E101" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F101" t="s">
         <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
       </c>
       <c r="I101" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K101">
         <v>100</v>
       </c>
       <c r="L101">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4748,34 +4748,34 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C102">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D102" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="E102" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
       </c>
       <c r="G102" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
       </c>
       <c r="I102" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K102">
         <v>100</v>
       </c>
       <c r="L102">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4783,22 +4783,22 @@
         <v>18</v>
       </c>
       <c r="B103">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
@@ -4810,7 +4810,7 @@
         <v>100</v>
       </c>
       <c r="L103">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4818,22 +4818,22 @@
         <v>20</v>
       </c>
       <c r="B104">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C104">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D104" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="E104" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F104" t="s">
         <v>25</v>
       </c>
       <c r="G104" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -4845,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4853,22 +4853,22 @@
         <v>21</v>
       </c>
       <c r="B105">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C105">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="D105" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F105" t="s">
         <v>25</v>
       </c>
       <c r="G105" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H105" t="s">
         <v>16</v>
@@ -4880,7 +4880,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4888,34 +4888,34 @@
         <v>23</v>
       </c>
       <c r="B106">
-        <v>603</v>
+        <v>750</v>
       </c>
       <c r="C106">
-        <v>603</v>
+        <v>469</v>
       </c>
       <c r="D106" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E106" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F106" t="s">
         <v>25</v>
       </c>
       <c r="G106" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H106" t="s">
         <v>16</v>
       </c>
       <c r="I106" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K106">
         <v>100</v>
       </c>
       <c r="L106">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4923,22 +4923,22 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>26</v>
+        <v>930</v>
       </c>
       <c r="C107">
-        <v>34</v>
+        <v>1107</v>
       </c>
       <c r="D107" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="E107" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F107" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H107" t="s">
         <v>16</v>
@@ -4946,14 +4946,11 @@
       <c r="I107" t="s">
         <v>229</v>
       </c>
-      <c r="J107" t="s">
-        <v>188</v>
-      </c>
       <c r="K107">
         <v>100</v>
       </c>
       <c r="L107">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4961,34 +4958,34 @@
         <v>18</v>
       </c>
       <c r="B108">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="C108">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D108" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="E108" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F108" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
       </c>
       <c r="I108" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K108">
         <v>100</v>
       </c>
       <c r="L108">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4996,22 +4993,22 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>30</v>
+        <v>1712</v>
       </c>
       <c r="C109">
-        <v>20</v>
+        <v>1454</v>
       </c>
       <c r="D109" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="E109" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H109" t="s">
         <v>16</v>
@@ -5023,7 +5020,7 @@
         <v>100</v>
       </c>
       <c r="L109">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5031,22 +5028,22 @@
         <v>21</v>
       </c>
       <c r="B110">
-        <v>63</v>
+        <v>3255</v>
       </c>
       <c r="C110">
-        <v>87</v>
+        <v>3866</v>
       </c>
       <c r="D110" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E110" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H110" t="s">
         <v>16</v>
@@ -5058,7 +5055,7 @@
         <v>100</v>
       </c>
       <c r="L110">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5066,22 +5063,22 @@
         <v>23</v>
       </c>
       <c r="B111">
-        <v>495</v>
+        <v>27700</v>
       </c>
       <c r="C111">
-        <v>507</v>
+        <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F111" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H111" t="s">
         <v>16</v>
@@ -5093,7 +5090,7 @@
         <v>100</v>
       </c>
       <c r="L111">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5101,34 +5098,34 @@
         <v>12</v>
       </c>
       <c r="B112">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E112" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F112" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H112" t="s">
         <v>16</v>
       </c>
       <c r="I112" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K112">
         <v>100</v>
       </c>
       <c r="L112">
-        <v>0.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -5136,34 +5133,34 @@
         <v>18</v>
       </c>
       <c r="B113">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E113" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F113" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H113" t="s">
         <v>16</v>
       </c>
       <c r="I113" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K113">
         <v>100</v>
       </c>
       <c r="L113">
-        <v>0.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5171,22 +5168,22 @@
         <v>20</v>
       </c>
       <c r="B114">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D114" t="s">
-        <v>19</v>
+        <v>169</v>
       </c>
       <c r="E114" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F114" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H114" t="s">
         <v>16</v>
@@ -5198,7 +5195,7 @@
         <v>100</v>
       </c>
       <c r="L114">
-        <v>0.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5206,34 +5203,34 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D115" t="s">
         <v>22</v>
       </c>
       <c r="E115" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F115" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H115" t="s">
         <v>16</v>
       </c>
       <c r="I115" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K115">
         <v>100</v>
       </c>
       <c r="L115">
-        <v>0.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5241,34 +5238,34 @@
         <v>23</v>
       </c>
       <c r="B116">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="D116" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E116" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="F116" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H116" t="s">
         <v>16</v>
       </c>
       <c r="I116" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K116">
         <v>100</v>
       </c>
       <c r="L116">
-        <v>0.3</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5276,37 +5273,34 @@
         <v>12</v>
       </c>
       <c r="B117">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D117" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E117" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="F117" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G117" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
       </c>
       <c r="I117" t="s">
-        <v>17</v>
-      </c>
-      <c r="J117" t="s">
-        <v>189</v>
+        <v>229</v>
       </c>
       <c r="K117">
         <v>100</v>
       </c>
       <c r="L117">
-        <v>2.2000000000000002</v>
+        <v>98</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5314,37 +5308,34 @@
         <v>18</v>
       </c>
       <c r="B118">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E118" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="F118" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G118" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H118" t="s">
         <v>16</v>
       </c>
       <c r="I118" t="s">
-        <v>17</v>
-      </c>
-      <c r="J118" t="s">
-        <v>190</v>
+        <v>229</v>
       </c>
       <c r="K118">
         <v>100</v>
       </c>
       <c r="L118">
-        <v>2.2000000000000002</v>
+        <v>98</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5352,22 +5343,22 @@
         <v>20</v>
       </c>
       <c r="B119">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C119">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D119" t="s">
-        <v>191</v>
+        <v>79</v>
       </c>
       <c r="E119" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="F119" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G119" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H119" t="s">
         <v>16</v>
@@ -5375,14 +5366,11 @@
       <c r="I119" t="s">
         <v>17</v>
       </c>
-      <c r="J119" t="s">
-        <v>192</v>
-      </c>
       <c r="K119">
         <v>100</v>
       </c>
       <c r="L119">
-        <v>2.2000000000000002</v>
+        <v>98</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5390,37 +5378,34 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>91</v>
       </c>
       <c r="D120" t="s">
         <v>22</v>
       </c>
       <c r="E120" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="F120" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G120" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H120" t="s">
         <v>16</v>
       </c>
       <c r="I120" t="s">
-        <v>17</v>
-      </c>
-      <c r="J120" t="s">
-        <v>193</v>
+        <v>231</v>
       </c>
       <c r="K120">
         <v>100</v>
       </c>
       <c r="L120">
-        <v>2.2000000000000002</v>
+        <v>98</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5428,34 +5413,34 @@
         <v>23</v>
       </c>
       <c r="B121">
-        <v>563</v>
+        <v>720</v>
       </c>
       <c r="C121">
-        <v>0</v>
+        <v>733</v>
       </c>
       <c r="D121" t="s">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="E121" t="s">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="F121" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G121" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
       </c>
       <c r="I121" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K121">
         <v>100</v>
       </c>
       <c r="L121">
-        <v>2.2000000000000002</v>
+        <v>98</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5463,34 +5448,37 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C122">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="E122" t="s">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="F122" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G122" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H122" t="s">
         <v>16</v>
       </c>
       <c r="I122" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J122" t="s">
+        <v>171</v>
       </c>
       <c r="K122">
         <v>100</v>
       </c>
       <c r="L122">
-        <v>117.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5498,34 +5486,37 @@
         <v>18</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>19</v>
+        <v>105</v>
       </c>
       <c r="E123" t="s">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="F123" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G123" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H123" t="s">
         <v>16</v>
       </c>
       <c r="I123" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J123" t="s">
+        <v>172</v>
       </c>
       <c r="K123">
         <v>100</v>
       </c>
       <c r="L123">
-        <v>117.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5533,34 +5524,37 @@
         <v>20</v>
       </c>
       <c r="B124">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C124">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>202</v>
+        <v>259</v>
       </c>
       <c r="E124" t="s">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="F124" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G124" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H124" t="s">
         <v>16</v>
       </c>
       <c r="I124" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J124" t="s">
+        <v>173</v>
       </c>
       <c r="K124">
         <v>100</v>
       </c>
       <c r="L124">
-        <v>117.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5568,34 +5562,37 @@
         <v>21</v>
       </c>
       <c r="B125">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C125">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="D125" t="s">
         <v>22</v>
       </c>
       <c r="E125" t="s">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="F125" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G125" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H125" t="s">
         <v>16</v>
       </c>
       <c r="I125" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J125" t="s">
+        <v>174</v>
       </c>
       <c r="K125">
         <v>100</v>
       </c>
       <c r="L125">
-        <v>117.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5603,34 +5600,34 @@
         <v>23</v>
       </c>
       <c r="B126">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C126">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>200</v>
+        <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="F126" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G126" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H126" t="s">
         <v>16</v>
       </c>
       <c r="I126" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K126">
         <v>100</v>
       </c>
       <c r="L126">
-        <v>117.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5638,34 +5635,34 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C127">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D127" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="E127" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="F127" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="H127" t="s">
         <v>16</v>
       </c>
       <c r="I127" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K127">
         <v>100</v>
       </c>
       <c r="L127">
-        <v>64</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5673,34 +5670,34 @@
         <v>18</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="E128" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="F128" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="H128" t="s">
         <v>16</v>
       </c>
       <c r="I128" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K128">
         <v>100</v>
       </c>
       <c r="L128">
-        <v>64</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5708,34 +5705,34 @@
         <v>20</v>
       </c>
       <c r="B129">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C129">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D129" t="s">
-        <v>256</v>
+        <v>63</v>
       </c>
       <c r="E129" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="F129" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="H129" t="s">
         <v>16</v>
       </c>
       <c r="I129" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K129">
         <v>100</v>
       </c>
       <c r="L129">
-        <v>64</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5743,34 +5740,34 @@
         <v>21</v>
       </c>
       <c r="B130">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="C130">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="D130" t="s">
         <v>22</v>
       </c>
       <c r="E130" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="F130" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="H130" t="s">
         <v>16</v>
       </c>
       <c r="I130" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K130">
         <v>100</v>
       </c>
       <c r="L130">
-        <v>64</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5778,34 +5775,34 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>750</v>
+        <v>546</v>
       </c>
       <c r="C131">
-        <v>469</v>
+        <v>546</v>
       </c>
       <c r="D131" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E131" t="s">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="F131" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>254</v>
+        <v>109</v>
       </c>
       <c r="H131" t="s">
         <v>16</v>
       </c>
       <c r="I131" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K131">
         <v>100</v>
       </c>
       <c r="L131">
-        <v>64</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5813,22 +5810,22 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>930</v>
+        <v>12</v>
       </c>
       <c r="C132">
-        <v>1107</v>
+        <v>20</v>
       </c>
       <c r="D132" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E132" t="s">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="F132" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G132" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="H132" t="s">
         <v>16</v>
@@ -5836,11 +5833,14 @@
       <c r="I132" t="s">
         <v>229</v>
       </c>
+      <c r="J132" t="s">
+        <v>112</v>
+      </c>
       <c r="K132">
         <v>100</v>
       </c>
       <c r="L132">
-        <v>86.1</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5848,22 +5848,22 @@
         <v>18</v>
       </c>
       <c r="B133">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="C133">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="E133" t="s">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="F133" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G133" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="H133" t="s">
         <v>16</v>
@@ -5875,7 +5875,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>86.1</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5883,34 +5883,34 @@
         <v>20</v>
       </c>
       <c r="B134">
-        <v>1712</v>
+        <v>18</v>
       </c>
       <c r="C134">
-        <v>1454</v>
+        <v>19</v>
       </c>
       <c r="D134" t="s">
-        <v>230</v>
+        <v>113</v>
       </c>
       <c r="E134" t="s">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="F134" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G134" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="H134" t="s">
         <v>16</v>
       </c>
       <c r="I134" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K134">
         <v>100</v>
       </c>
       <c r="L134">
-        <v>86.1</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5918,34 +5918,34 @@
         <v>21</v>
       </c>
       <c r="B135">
-        <v>3255</v>
+        <v>42</v>
       </c>
       <c r="C135">
-        <v>3866</v>
+        <v>49</v>
       </c>
       <c r="D135" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="E135" t="s">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="F135" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G135" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="H135" t="s">
         <v>16</v>
       </c>
       <c r="I135" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K135">
         <v>100</v>
       </c>
       <c r="L135">
-        <v>86.1</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5953,22 +5953,22 @@
         <v>23</v>
       </c>
       <c r="B136">
-        <v>27700</v>
+        <v>351</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="D136" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="E136" t="s">
-        <v>257</v>
+        <v>111</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G136" t="s">
-        <v>258</v>
+        <v>109</v>
       </c>
       <c r="H136" t="s">
         <v>16</v>
@@ -5980,7 +5980,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>86.1</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5988,34 +5988,37 @@
         <v>12</v>
       </c>
       <c r="B137">
+        <v>20</v>
+      </c>
+      <c r="C137">
         <v>14</v>
       </c>
-      <c r="C137">
-        <v>20</v>
-      </c>
       <c r="D137" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E137" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F137" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G137" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H137" t="s">
         <v>16</v>
       </c>
       <c r="I137" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J137" t="s">
+        <v>117</v>
       </c>
       <c r="K137">
         <v>100</v>
       </c>
       <c r="L137">
-        <v>83.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -6023,34 +6026,34 @@
         <v>18</v>
       </c>
       <c r="B138">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D138" t="s">
-        <v>142</v>
+        <v>37</v>
       </c>
       <c r="E138" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F138" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G138" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H138" t="s">
         <v>16</v>
       </c>
       <c r="I138" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K138">
         <v>100</v>
       </c>
       <c r="L138">
-        <v>83.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -6058,22 +6061,22 @@
         <v>20</v>
       </c>
       <c r="B139">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C139">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D139" t="s">
-        <v>169</v>
+        <v>47</v>
       </c>
       <c r="E139" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F139" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G139" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H139" t="s">
         <v>16</v>
@@ -6085,7 +6088,7 @@
         <v>100</v>
       </c>
       <c r="L139">
-        <v>83.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -6093,34 +6096,34 @@
         <v>21</v>
       </c>
       <c r="B140">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="C140">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D140" t="s">
         <v>22</v>
       </c>
       <c r="E140" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F140" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H140" t="s">
         <v>16</v>
       </c>
       <c r="I140" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K140">
         <v>100</v>
       </c>
       <c r="L140">
-        <v>83.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -6128,22 +6131,22 @@
         <v>23</v>
       </c>
       <c r="B141">
-        <v>480</v>
+        <v>603</v>
       </c>
       <c r="C141">
-        <v>488</v>
+        <v>603</v>
       </c>
       <c r="D141" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E141" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="F141" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G141" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H141" t="s">
         <v>16</v>
@@ -6155,7 +6158,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>83.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -6163,34 +6166,37 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C142">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E142" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="F142" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G142" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H142" t="s">
         <v>16</v>
       </c>
       <c r="I142" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J142" t="s">
+        <v>118</v>
       </c>
       <c r="K142">
         <v>100</v>
       </c>
       <c r="L142">
-        <v>98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -6201,31 +6207,31 @@
         <v>5</v>
       </c>
       <c r="C143">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E143" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="F143" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G143" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H143" t="s">
         <v>16</v>
       </c>
       <c r="I143" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K143">
         <v>100</v>
       </c>
       <c r="L143">
-        <v>98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -6233,22 +6239,22 @@
         <v>20</v>
       </c>
       <c r="B144">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C144">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="E144" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="F144" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G144" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H144" t="s">
         <v>16</v>
@@ -6260,7 +6266,7 @@
         <v>100</v>
       </c>
       <c r="L144">
-        <v>98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -6268,34 +6274,34 @@
         <v>21</v>
       </c>
       <c r="B145">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="C145">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="D145" t="s">
         <v>22</v>
       </c>
       <c r="E145" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="F145" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G145" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H145" t="s">
         <v>16</v>
       </c>
       <c r="I145" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K145">
         <v>100</v>
       </c>
       <c r="L145">
-        <v>98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -6303,34 +6309,34 @@
         <v>23</v>
       </c>
       <c r="B146">
-        <v>720</v>
+        <v>563</v>
       </c>
       <c r="C146">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="D146" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>170</v>
+        <v>102</v>
       </c>
       <c r="F146" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G146" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H146" t="s">
         <v>16</v>
       </c>
       <c r="I146" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K146">
         <v>100</v>
       </c>
       <c r="L146">
-        <v>98</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -6338,37 +6344,34 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D147" t="s">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="E147" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F147" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G147" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="H147" t="s">
         <v>16</v>
       </c>
       <c r="I147" t="s">
-        <v>17</v>
-      </c>
-      <c r="J147" t="s">
-        <v>171</v>
+        <v>229</v>
       </c>
       <c r="K147">
         <v>100</v>
       </c>
       <c r="L147">
-        <v>4.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6376,37 +6379,34 @@
         <v>18</v>
       </c>
       <c r="B148">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="s">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="E148" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F148" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G148" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="H148" t="s">
         <v>16</v>
       </c>
       <c r="I148" t="s">
-        <v>229</v>
-      </c>
-      <c r="J148" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="K148">
         <v>100</v>
       </c>
       <c r="L148">
-        <v>4.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6414,37 +6414,34 @@
         <v>20</v>
       </c>
       <c r="B149">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="D149" t="s">
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="E149" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F149" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G149" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="H149" t="s">
         <v>16</v>
       </c>
       <c r="I149" t="s">
-        <v>17</v>
-      </c>
-      <c r="J149" t="s">
-        <v>173</v>
+        <v>231</v>
       </c>
       <c r="K149">
         <v>100</v>
       </c>
       <c r="L149">
-        <v>4.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6452,37 +6449,34 @@
         <v>21</v>
       </c>
       <c r="B150">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C150">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="D150" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="E150" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F150" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G150" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="H150" t="s">
         <v>16</v>
       </c>
       <c r="I150" t="s">
-        <v>17</v>
-      </c>
-      <c r="J150" t="s">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="K150">
         <v>100</v>
       </c>
       <c r="L150">
-        <v>4.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6490,34 +6484,34 @@
         <v>23</v>
       </c>
       <c r="B151">
-        <v>720</v>
+        <v>300</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D151" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="E151" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F151" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G151" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="H151" t="s">
         <v>16</v>
       </c>
       <c r="I151" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K151">
         <v>100</v>
       </c>
       <c r="L151">
-        <v>4.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6525,22 +6519,22 @@
         <v>12</v>
       </c>
       <c r="B152">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C152">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D152" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="E152" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F152" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G152" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H152" t="s">
         <v>16</v>
@@ -6552,7 +6546,7 @@
         <v>100</v>
       </c>
       <c r="L152">
-        <v>109.2</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6569,13 +6563,13 @@
         <v>71</v>
       </c>
       <c r="E153" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F153" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G153" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H153" t="s">
         <v>16</v>
@@ -6587,7 +6581,7 @@
         <v>100</v>
       </c>
       <c r="L153">
-        <v>109.2</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6595,22 +6589,22 @@
         <v>20</v>
       </c>
       <c r="B154">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C154">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="D154" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E154" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F154" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G154" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H154" t="s">
         <v>16</v>
@@ -6622,7 +6616,7 @@
         <v>100</v>
       </c>
       <c r="L154">
-        <v>109.2</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6630,34 +6624,34 @@
         <v>21</v>
       </c>
       <c r="B155">
-        <v>66</v>
+        <v>120</v>
       </c>
       <c r="C155">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="D155" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="E155" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F155" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G155" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H155" t="s">
         <v>16</v>
       </c>
       <c r="I155" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K155">
         <v>100</v>
       </c>
       <c r="L155">
-        <v>109.2</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6665,22 +6659,22 @@
         <v>23</v>
       </c>
       <c r="B156">
-        <v>546</v>
+        <v>399</v>
       </c>
       <c r="C156">
-        <v>546</v>
+        <v>421</v>
       </c>
       <c r="D156" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E156" t="s">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="F156" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G156" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H156" t="s">
         <v>16</v>
@@ -6692,7 +6686,7 @@
         <v>100</v>
       </c>
       <c r="L156">
-        <v>109.2</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6700,22 +6694,22 @@
         <v>12</v>
       </c>
       <c r="B157">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C157">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D157" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E157" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="F157" t="s">
         <v>25</v>
       </c>
       <c r="G157" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H157" t="s">
         <v>16</v>
@@ -6723,14 +6717,11 @@
       <c r="I157" t="s">
         <v>229</v>
       </c>
-      <c r="J157" t="s">
-        <v>112</v>
-      </c>
       <c r="K157">
         <v>100</v>
       </c>
       <c r="L157">
-        <v>112.7</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6738,34 +6729,34 @@
         <v>18</v>
       </c>
       <c r="B158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D158" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="E158" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="F158" t="s">
         <v>25</v>
       </c>
       <c r="G158" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H158" t="s">
         <v>16</v>
       </c>
       <c r="I158" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K158">
         <v>100</v>
       </c>
       <c r="L158">
-        <v>112.7</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6773,22 +6764,22 @@
         <v>20</v>
       </c>
       <c r="B159">
-        <v>18</v>
+        <v>59</v>
       </c>
       <c r="C159">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="D159" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="E159" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="F159" t="s">
         <v>25</v>
       </c>
       <c r="G159" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H159" t="s">
         <v>16</v>
@@ -6800,7 +6791,7 @@
         <v>100</v>
       </c>
       <c r="L159">
-        <v>112.7</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6808,34 +6799,34 @@
         <v>21</v>
       </c>
       <c r="B160">
-        <v>42</v>
+        <v>120</v>
       </c>
       <c r="C160">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="D160" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="E160" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="F160" t="s">
         <v>25</v>
       </c>
       <c r="G160" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H160" t="s">
         <v>16</v>
       </c>
       <c r="I160" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K160">
         <v>100</v>
       </c>
       <c r="L160">
-        <v>112.7</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6843,22 +6834,22 @@
         <v>23</v>
       </c>
       <c r="B161">
-        <v>351</v>
+        <v>399</v>
       </c>
       <c r="C161">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D161" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E161" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="F161" t="s">
         <v>25</v>
       </c>
       <c r="G161" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H161" t="s">
         <v>16</v>
@@ -6870,7 +6861,7 @@
         <v>100</v>
       </c>
       <c r="L161">
-        <v>112.7</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6878,37 +6869,37 @@
         <v>12</v>
       </c>
       <c r="B162">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C162">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D162" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="E162" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F162" t="s">
         <v>25</v>
       </c>
       <c r="G162" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H162" t="s">
         <v>16</v>
       </c>
       <c r="I162" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="J162" t="s">
-        <v>117</v>
+        <v>152</v>
       </c>
       <c r="K162">
         <v>100</v>
       </c>
       <c r="L162">
-        <v>62.5</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6916,22 +6907,22 @@
         <v>18</v>
       </c>
       <c r="B163">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D163" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E163" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F163" t="s">
         <v>25</v>
       </c>
       <c r="G163" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H163" t="s">
         <v>16</v>
@@ -6939,11 +6930,14 @@
       <c r="I163" t="s">
         <v>17</v>
       </c>
+      <c r="J163" t="s">
+        <v>153</v>
+      </c>
       <c r="K163">
         <v>100</v>
       </c>
       <c r="L163">
-        <v>62.5</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6951,22 +6945,22 @@
         <v>20</v>
       </c>
       <c r="B164">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C164">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D164" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="E164" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F164" t="s">
         <v>25</v>
       </c>
       <c r="G164" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H164" t="s">
         <v>16</v>
@@ -6974,11 +6968,14 @@
       <c r="I164" t="s">
         <v>17</v>
       </c>
+      <c r="J164" t="s">
+        <v>155</v>
+      </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>62.5</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6986,34 +6983,37 @@
         <v>21</v>
       </c>
       <c r="B165">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C165">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D165" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="E165" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F165" t="s">
         <v>25</v>
       </c>
       <c r="G165" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
       </c>
       <c r="I165" t="s">
-        <v>17</v>
+        <v>231</v>
+      </c>
+      <c r="J165" t="s">
+        <v>157</v>
       </c>
       <c r="K165">
         <v>100</v>
       </c>
       <c r="L165">
-        <v>62.5</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -7021,34 +7021,37 @@
         <v>23</v>
       </c>
       <c r="B166">
-        <v>603</v>
+        <v>399</v>
       </c>
       <c r="C166">
-        <v>603</v>
+        <v>421</v>
       </c>
       <c r="D166" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E166" t="s">
-        <v>116</v>
+        <v>151</v>
       </c>
       <c r="F166" t="s">
         <v>25</v>
       </c>
       <c r="G166" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H166" t="s">
         <v>16</v>
       </c>
       <c r="I166" t="s">
-        <v>229</v>
+        <v>231</v>
+      </c>
+      <c r="J166" t="s">
+        <v>158</v>
       </c>
       <c r="K166">
         <v>100</v>
       </c>
       <c r="L166">
-        <v>62.5</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -7056,7 +7059,7 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -7065,13 +7068,13 @@
         <v>19</v>
       </c>
       <c r="E167" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F167" t="s">
         <v>103</v>
       </c>
       <c r="G167" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H167" t="s">
         <v>16</v>
@@ -7080,13 +7083,13 @@
         <v>17</v>
       </c>
       <c r="J167" t="s">
-        <v>118</v>
+        <v>160</v>
       </c>
       <c r="K167">
         <v>100</v>
       </c>
       <c r="L167">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -7094,7 +7097,7 @@
         <v>18</v>
       </c>
       <c r="B168">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -7103,13 +7106,13 @@
         <v>19</v>
       </c>
       <c r="E168" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F168" t="s">
         <v>103</v>
       </c>
       <c r="G168" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H168" t="s">
         <v>16</v>
@@ -7121,7 +7124,7 @@
         <v>100</v>
       </c>
       <c r="L168">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -7129,7 +7132,7 @@
         <v>20</v>
       </c>
       <c r="B169">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -7138,13 +7141,13 @@
         <v>19</v>
       </c>
       <c r="E169" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F169" t="s">
         <v>103</v>
       </c>
       <c r="G169" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H169" t="s">
         <v>16</v>
@@ -7156,7 +7159,7 @@
         <v>100</v>
       </c>
       <c r="L169">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -7164,7 +7167,7 @@
         <v>21</v>
       </c>
       <c r="B170">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C170">
         <v>2</v>
@@ -7173,13 +7176,13 @@
         <v>22</v>
       </c>
       <c r="E170" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F170" t="s">
         <v>103</v>
       </c>
       <c r="G170" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H170" t="s">
         <v>16</v>
@@ -7191,7 +7194,7 @@
         <v>100</v>
       </c>
       <c r="L170">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -7199,7 +7202,7 @@
         <v>23</v>
       </c>
       <c r="B171">
-        <v>563</v>
+        <v>399</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -7208,13 +7211,13 @@
         <v>19</v>
       </c>
       <c r="E171" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F171" t="s">
         <v>103</v>
       </c>
       <c r="G171" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H171" t="s">
         <v>16</v>
@@ -7226,7 +7229,7 @@
         <v>100</v>
       </c>
       <c r="L171">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -7234,19 +7237,19 @@
         <v>12</v>
       </c>
       <c r="B172">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C172">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D172" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E172" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F172" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G172" t="s">
         <v>141</v>
@@ -7257,11 +7260,14 @@
       <c r="I172" t="s">
         <v>229</v>
       </c>
+      <c r="J172" t="s">
+        <v>162</v>
+      </c>
       <c r="K172">
         <v>100</v>
       </c>
       <c r="L172">
-        <v>108.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -7269,19 +7275,19 @@
         <v>18</v>
       </c>
       <c r="B173">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C173">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F173" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G173" t="s">
         <v>141</v>
@@ -7292,11 +7298,14 @@
       <c r="I173" t="s">
         <v>17</v>
       </c>
+      <c r="J173" t="s">
+        <v>163</v>
+      </c>
       <c r="K173">
         <v>100</v>
       </c>
       <c r="L173">
-        <v>108.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -7304,19 +7313,19 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C174">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>87</v>
+        <v>164</v>
       </c>
       <c r="E174" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F174" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G174" t="s">
         <v>141</v>
@@ -7325,13 +7334,16 @@
         <v>16</v>
       </c>
       <c r="I174" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="J174" t="s">
+        <v>165</v>
       </c>
       <c r="K174">
         <v>100</v>
       </c>
       <c r="L174">
-        <v>108.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -7339,19 +7351,19 @@
         <v>21</v>
       </c>
       <c r="B175">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C175">
-        <v>188</v>
+        <v>4</v>
       </c>
       <c r="D175" t="s">
-        <v>143</v>
+        <v>22</v>
       </c>
       <c r="E175" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F175" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G175" t="s">
         <v>141</v>
@@ -7360,13 +7372,16 @@
         <v>16</v>
       </c>
       <c r="I175" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J175" t="s">
+        <v>166</v>
       </c>
       <c r="K175">
         <v>100</v>
       </c>
       <c r="L175">
-        <v>108.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -7374,19 +7389,19 @@
         <v>23</v>
       </c>
       <c r="B176">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="C176">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D176" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E176" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F176" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G176" t="s">
         <v>141</v>
@@ -7395,13 +7410,13 @@
         <v>16</v>
       </c>
       <c r="I176" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K176">
         <v>100</v>
       </c>
       <c r="L176">
-        <v>108.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7409,22 +7424,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C177">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D177" t="s">
-        <v>144</v>
+        <v>260</v>
       </c>
       <c r="E177" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="F177" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G177" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H177" t="s">
         <v>16</v>
@@ -7436,7 +7451,7 @@
         <v>100</v>
       </c>
       <c r="L177">
-        <v>101.2</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7444,22 +7459,22 @@
         <v>18</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C178">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D178" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E178" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="F178" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G178" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H178" t="s">
         <v>16</v>
@@ -7471,7 +7486,7 @@
         <v>100</v>
       </c>
       <c r="L178">
-        <v>101.2</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7479,22 +7494,22 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C179">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="D179" t="s">
         <v>41</v>
       </c>
       <c r="E179" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="F179" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G179" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H179" t="s">
         <v>16</v>
@@ -7506,7 +7521,7 @@
         <v>100</v>
       </c>
       <c r="L179">
-        <v>101.2</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7514,22 +7529,22 @@
         <v>21</v>
       </c>
       <c r="B180">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C180">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="D180" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="E180" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="F180" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G180" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H180" t="s">
         <v>16</v>
@@ -7541,7 +7556,7 @@
         <v>100</v>
       </c>
       <c r="L180">
-        <v>101.2</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7549,22 +7564,22 @@
         <v>23</v>
       </c>
       <c r="B181">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="C181">
-        <v>421</v>
+        <v>1205</v>
       </c>
       <c r="D181" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="E181" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="F181" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G181" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H181" t="s">
         <v>16</v>
@@ -7576,7 +7591,7 @@
         <v>100</v>
       </c>
       <c r="L181">
-        <v>101.2</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -7584,34 +7599,34 @@
         <v>12</v>
       </c>
       <c r="B182">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C182">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D182" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E182" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F182" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G182" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H182" t="s">
         <v>16</v>
       </c>
       <c r="I182" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K182">
         <v>100</v>
       </c>
       <c r="L182">
-        <v>120.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -7619,34 +7634,34 @@
         <v>18</v>
       </c>
       <c r="B183">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C183">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F183" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G183" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H183" t="s">
         <v>16</v>
       </c>
       <c r="I183" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K183">
         <v>100</v>
       </c>
       <c r="L183">
-        <v>120.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -7654,34 +7669,34 @@
         <v>20</v>
       </c>
       <c r="B184">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C184">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>149</v>
+        <v>259</v>
       </c>
       <c r="E184" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F184" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G184" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H184" t="s">
         <v>16</v>
       </c>
       <c r="I184" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K184">
         <v>100</v>
       </c>
       <c r="L184">
-        <v>120.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -7689,34 +7704,34 @@
         <v>21</v>
       </c>
       <c r="B185">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C185">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="E185" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F185" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G185" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H185" t="s">
         <v>16</v>
       </c>
       <c r="I185" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K185">
         <v>100</v>
       </c>
       <c r="L185">
-        <v>120.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -7724,34 +7739,34 @@
         <v>23</v>
       </c>
       <c r="B186">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="C186">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="D186" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E186" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F186" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G186" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H186" t="s">
         <v>16</v>
       </c>
       <c r="I186" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K186">
         <v>100</v>
       </c>
       <c r="L186">
-        <v>120.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -7759,37 +7774,34 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C187">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="D187" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="E187" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="F187" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G187" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H187" t="s">
         <v>16</v>
       </c>
       <c r="I187" t="s">
-        <v>231</v>
-      </c>
-      <c r="J187" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="K187">
         <v>100</v>
       </c>
       <c r="L187">
-        <v>82.9</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7797,22 +7809,22 @@
         <v>18</v>
       </c>
       <c r="B188">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D188" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E188" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="F188" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G188" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H188" t="s">
         <v>16</v>
@@ -7820,14 +7832,11 @@
       <c r="I188" t="s">
         <v>17</v>
       </c>
-      <c r="J188" t="s">
-        <v>153</v>
-      </c>
       <c r="K188">
         <v>100</v>
       </c>
       <c r="L188">
-        <v>82.9</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7835,37 +7844,34 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C189">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D189" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E189" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="F189" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G189" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H189" t="s">
         <v>16</v>
       </c>
       <c r="I189" t="s">
-        <v>17</v>
-      </c>
-      <c r="J189" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="K189">
         <v>100</v>
       </c>
       <c r="L189">
-        <v>82.9</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7873,22 +7879,22 @@
         <v>21</v>
       </c>
       <c r="B190">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="C190">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="D190" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="E190" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="F190" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G190" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H190" t="s">
         <v>16</v>
@@ -7896,14 +7902,11 @@
       <c r="I190" t="s">
         <v>231</v>
       </c>
-      <c r="J190" t="s">
-        <v>157</v>
-      </c>
       <c r="K190">
         <v>100</v>
       </c>
       <c r="L190">
-        <v>82.9</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7911,37 +7914,34 @@
         <v>23</v>
       </c>
       <c r="B191">
-        <v>399</v>
+        <v>320</v>
       </c>
       <c r="C191">
-        <v>421</v>
+        <v>500</v>
       </c>
       <c r="D191" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E191" t="s">
-        <v>151</v>
+        <v>263</v>
       </c>
       <c r="F191" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G191" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H191" t="s">
         <v>16</v>
       </c>
       <c r="I191" t="s">
-        <v>231</v>
-      </c>
-      <c r="J191" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="K191">
         <v>100</v>
       </c>
       <c r="L191">
-        <v>82.9</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7949,37 +7949,34 @@
         <v>12</v>
       </c>
       <c r="B192">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D192" t="s">
-        <v>19</v>
+        <v>183</v>
       </c>
       <c r="E192" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="F192" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G192" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H192" t="s">
         <v>16</v>
       </c>
       <c r="I192" t="s">
-        <v>17</v>
-      </c>
-      <c r="J192" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="K192">
         <v>100</v>
       </c>
       <c r="L192">
-        <v>0.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7987,34 +7984,34 @@
         <v>18</v>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E193" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="F193" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G193" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H193" t="s">
         <v>16</v>
       </c>
       <c r="I193" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K193">
         <v>100</v>
       </c>
       <c r="L193">
-        <v>0.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -8022,34 +8019,34 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="D194" t="s">
-        <v>19</v>
+        <v>238</v>
       </c>
       <c r="E194" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="F194" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G194" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H194" t="s">
         <v>16</v>
       </c>
       <c r="I194" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K194">
         <v>100</v>
       </c>
       <c r="L194">
-        <v>0.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -8057,34 +8054,34 @@
         <v>21</v>
       </c>
       <c r="B195">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="C195">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D195" t="s">
         <v>22</v>
       </c>
       <c r="E195" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="F195" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G195" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H195" t="s">
         <v>16</v>
       </c>
       <c r="I195" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K195">
         <v>100</v>
       </c>
       <c r="L195">
-        <v>0.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -8092,34 +8089,34 @@
         <v>23</v>
       </c>
       <c r="B196">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="C196">
-        <v>0</v>
+        <v>509</v>
       </c>
       <c r="D196" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="E196" t="s">
-        <v>159</v>
+        <v>265</v>
       </c>
       <c r="F196" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G196" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H196" t="s">
         <v>16</v>
       </c>
       <c r="I196" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K196">
         <v>100</v>
       </c>
       <c r="L196">
-        <v>0.1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -8127,37 +8124,34 @@
         <v>12</v>
       </c>
       <c r="B197">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C197">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D197" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="E197" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F197" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G197" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="H197" t="s">
         <v>16</v>
       </c>
       <c r="I197" t="s">
-        <v>229</v>
-      </c>
-      <c r="J197" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="K197">
         <v>100</v>
       </c>
       <c r="L197">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8165,7 +8159,7 @@
         <v>18</v>
       </c>
       <c r="B198">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -8174,13 +8168,13 @@
         <v>19</v>
       </c>
       <c r="E198" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F198" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G198" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="H198" t="s">
         <v>16</v>
@@ -8188,14 +8182,11 @@
       <c r="I198" t="s">
         <v>17</v>
       </c>
-      <c r="J198" t="s">
-        <v>163</v>
-      </c>
       <c r="K198">
         <v>100</v>
       </c>
       <c r="L198">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8203,37 +8194,34 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C199">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>164</v>
+        <v>215</v>
       </c>
       <c r="E199" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F199" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G199" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="H199" t="s">
         <v>16</v>
       </c>
       <c r="I199" t="s">
-        <v>229</v>
-      </c>
-      <c r="J199" t="s">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="K199">
         <v>100</v>
       </c>
       <c r="L199">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8241,7 +8229,7 @@
         <v>21</v>
       </c>
       <c r="B200">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="C200">
         <v>4</v>
@@ -8250,13 +8238,13 @@
         <v>22</v>
       </c>
       <c r="E200" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F200" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G200" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="H200" t="s">
         <v>16</v>
@@ -8264,14 +8252,11 @@
       <c r="I200" t="s">
         <v>17</v>
       </c>
-      <c r="J200" t="s">
-        <v>166</v>
-      </c>
       <c r="K200">
         <v>100</v>
       </c>
       <c r="L200">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8279,7 +8264,7 @@
         <v>23</v>
       </c>
       <c r="B201">
-        <v>399</v>
+        <v>600</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -8288,13 +8273,13 @@
         <v>19</v>
       </c>
       <c r="E201" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="F201" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G201" t="s">
-        <v>141</v>
+        <v>214</v>
       </c>
       <c r="H201" t="s">
         <v>16</v>
@@ -8306,7 +8291,7 @@
         <v>100</v>
       </c>
       <c r="L201">
-        <v>7.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8314,34 +8299,37 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C202">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>260</v>
+        <v>215</v>
       </c>
       <c r="E202" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="F202" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G202" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H202" t="s">
         <v>16</v>
       </c>
       <c r="I202" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J202" t="s">
+        <v>216</v>
       </c>
       <c r="K202">
         <v>100</v>
       </c>
       <c r="L202">
-        <v>98.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8349,34 +8337,37 @@
         <v>18</v>
       </c>
       <c r="B203">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C203">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E203" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="F203" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G203" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H203" t="s">
         <v>16</v>
       </c>
       <c r="I203" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J203" t="s">
+        <v>217</v>
       </c>
       <c r="K203">
         <v>100</v>
       </c>
       <c r="L203">
-        <v>98.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8384,34 +8375,37 @@
         <v>20</v>
       </c>
       <c r="B204">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C204">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D204" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E204" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="F204" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G204" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H204" t="s">
         <v>16</v>
       </c>
       <c r="I204" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J204" t="s">
+        <v>218</v>
       </c>
       <c r="K204">
         <v>100</v>
       </c>
       <c r="L204">
-        <v>98.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8419,34 +8413,37 @@
         <v>21</v>
       </c>
       <c r="B205">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C205">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="D205" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="E205" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="F205" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G205" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H205" t="s">
         <v>16</v>
       </c>
       <c r="I205" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J205" t="s">
+        <v>219</v>
       </c>
       <c r="K205">
         <v>100</v>
       </c>
       <c r="L205">
-        <v>98.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8454,34 +8451,34 @@
         <v>23</v>
       </c>
       <c r="B206">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="C206">
-        <v>1205</v>
+        <v>0</v>
       </c>
       <c r="D206" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>261</v>
+        <v>102</v>
       </c>
       <c r="F206" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G206" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H206" t="s">
         <v>16</v>
       </c>
       <c r="I206" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K206">
         <v>100</v>
       </c>
       <c r="L206">
-        <v>98.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8489,34 +8486,37 @@
         <v>12</v>
       </c>
       <c r="B207">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C207">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D207" t="s">
-        <v>19</v>
+        <v>220</v>
       </c>
       <c r="E207" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F207" t="s">
         <v>103</v>
       </c>
       <c r="G207" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H207" t="s">
         <v>16</v>
       </c>
       <c r="I207" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J207" t="s">
+        <v>221</v>
       </c>
       <c r="K207">
         <v>100</v>
       </c>
       <c r="L207">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8524,22 +8524,22 @@
         <v>18</v>
       </c>
       <c r="B208">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E208" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F208" t="s">
         <v>103</v>
       </c>
       <c r="G208" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H208" t="s">
         <v>16</v>
@@ -8547,11 +8547,14 @@
       <c r="I208" t="s">
         <v>17</v>
       </c>
+      <c r="J208" t="s">
+        <v>222</v>
+      </c>
       <c r="K208">
         <v>100</v>
       </c>
       <c r="L208">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8559,34 +8562,37 @@
         <v>20</v>
       </c>
       <c r="B209">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C209">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D209" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="E209" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F209" t="s">
         <v>103</v>
       </c>
       <c r="G209" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H209" t="s">
         <v>16</v>
       </c>
       <c r="I209" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J209" t="s">
+        <v>224</v>
       </c>
       <c r="K209">
         <v>100</v>
       </c>
       <c r="L209">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8594,22 +8600,22 @@
         <v>21</v>
       </c>
       <c r="B210">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C210">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D210" t="s">
         <v>22</v>
       </c>
       <c r="E210" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F210" t="s">
         <v>103</v>
       </c>
       <c r="G210" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H210" t="s">
         <v>16</v>
@@ -8617,11 +8623,14 @@
       <c r="I210" t="s">
         <v>17</v>
       </c>
+      <c r="J210" t="s">
+        <v>225</v>
+      </c>
       <c r="K210">
         <v>100</v>
       </c>
       <c r="L210">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8629,7 +8638,7 @@
         <v>23</v>
       </c>
       <c r="B211">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -8638,13 +8647,13 @@
         <v>19</v>
       </c>
       <c r="E211" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="F211" t="s">
         <v>103</v>
       </c>
       <c r="G211" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H211" t="s">
         <v>16</v>
@@ -8656,7 +8665,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8664,34 +8673,34 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C212">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D212" t="s">
-        <v>183</v>
+        <v>75</v>
       </c>
       <c r="E212" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="F212" t="s">
         <v>14</v>
       </c>
       <c r="G212" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H212" t="s">
         <v>16</v>
       </c>
       <c r="I212" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>94.8</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8699,34 +8708,34 @@
         <v>18</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D213" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E213" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="F213" t="s">
         <v>14</v>
       </c>
       <c r="G213" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H213" t="s">
         <v>16</v>
       </c>
       <c r="I213" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K213">
         <v>100</v>
       </c>
       <c r="L213">
-        <v>94.8</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8737,31 +8746,31 @@
         <v>30</v>
       </c>
       <c r="C214">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="E214" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="F214" t="s">
         <v>14</v>
       </c>
       <c r="G214" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H214" t="s">
         <v>16</v>
       </c>
       <c r="I214" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>94.8</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8769,22 +8778,22 @@
         <v>21</v>
       </c>
       <c r="B215">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="C215">
-        <v>33</v>
+        <v>105</v>
       </c>
       <c r="D215" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="E215" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="F215" t="s">
         <v>14</v>
       </c>
       <c r="G215" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H215" t="s">
         <v>16</v>
@@ -8796,7 +8805,7 @@
         <v>100</v>
       </c>
       <c r="L215">
-        <v>94.8</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8804,34 +8813,34 @@
         <v>23</v>
       </c>
       <c r="B216">
-        <v>320</v>
+        <v>1200</v>
       </c>
       <c r="C216">
-        <v>500</v>
+        <v>1201</v>
       </c>
       <c r="D216" t="s">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="E216" t="s">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="F216" t="s">
         <v>14</v>
       </c>
       <c r="G216" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H216" t="s">
         <v>16</v>
       </c>
       <c r="I216" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K216">
         <v>100</v>
       </c>
       <c r="L216">
-        <v>94.8</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
@@ -8839,34 +8848,37 @@
         <v>12</v>
       </c>
       <c r="B217">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C217">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D217" t="s">
-        <v>183</v>
+        <v>19</v>
       </c>
       <c r="E217" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F217" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G217" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H217" t="s">
         <v>16</v>
       </c>
       <c r="I217" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J217" t="s">
+        <v>179</v>
       </c>
       <c r="K217">
         <v>100</v>
       </c>
       <c r="L217">
-        <v>90</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
@@ -8874,34 +8886,34 @@
         <v>18</v>
       </c>
       <c r="B218">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E218" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F218" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G218" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H218" t="s">
         <v>16</v>
       </c>
       <c r="I218" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K218">
         <v>100</v>
       </c>
       <c r="L218">
-        <v>90</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
@@ -8909,34 +8921,34 @@
         <v>20</v>
       </c>
       <c r="B219">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C219">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="D219" t="s">
-        <v>238</v>
+        <v>19</v>
       </c>
       <c r="E219" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F219" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G219" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H219" t="s">
         <v>16</v>
       </c>
       <c r="I219" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K219">
         <v>100</v>
       </c>
       <c r="L219">
-        <v>90</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
@@ -8944,34 +8956,34 @@
         <v>21</v>
       </c>
       <c r="B220">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="C220">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="D220" t="s">
         <v>22</v>
       </c>
       <c r="E220" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F220" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G220" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H220" t="s">
         <v>16</v>
       </c>
       <c r="I220" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K220">
         <v>100</v>
       </c>
       <c r="L220">
-        <v>90</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
@@ -8979,34 +8991,34 @@
         <v>23</v>
       </c>
       <c r="B221">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="C221">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="D221" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E221" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F221" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G221" t="s">
-        <v>264</v>
+        <v>176</v>
       </c>
       <c r="H221" t="s">
         <v>16</v>
       </c>
       <c r="I221" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K221">
         <v>100</v>
       </c>
       <c r="L221">
-        <v>90</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
@@ -9014,22 +9026,22 @@
         <v>12</v>
       </c>
       <c r="B222">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D222" t="s">
-        <v>19</v>
+        <v>87</v>
       </c>
       <c r="E222" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F222" t="s">
         <v>14</v>
       </c>
       <c r="G222" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H222" t="s">
         <v>16</v>
@@ -9037,11 +9049,14 @@
       <c r="I222" t="s">
         <v>17</v>
       </c>
+      <c r="J222" t="s">
+        <v>90</v>
+      </c>
       <c r="K222">
         <v>100</v>
       </c>
       <c r="L222">
-        <v>0.1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
@@ -9049,22 +9064,22 @@
         <v>18</v>
       </c>
       <c r="B223">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D223" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E223" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F223" t="s">
         <v>14</v>
       </c>
       <c r="G223" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H223" t="s">
         <v>16</v>
@@ -9076,7 +9091,7 @@
         <v>100</v>
       </c>
       <c r="L223">
-        <v>0.1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
@@ -9084,22 +9099,22 @@
         <v>20</v>
       </c>
       <c r="B224">
+        <v>19</v>
+      </c>
+      <c r="C224">
         <v>10</v>
       </c>
-      <c r="C224">
-        <v>1</v>
-      </c>
       <c r="D224" t="s">
-        <v>215</v>
+        <v>47</v>
       </c>
       <c r="E224" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F224" t="s">
         <v>14</v>
       </c>
       <c r="G224" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H224" t="s">
         <v>16</v>
@@ -9111,7 +9126,7 @@
         <v>100</v>
       </c>
       <c r="L224">
-        <v>0.1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
@@ -9119,22 +9134,22 @@
         <v>21</v>
       </c>
       <c r="B225">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C225">
-        <v>4</v>
+        <v>61</v>
       </c>
       <c r="D225" t="s">
         <v>22</v>
       </c>
       <c r="E225" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F225" t="s">
         <v>14</v>
       </c>
       <c r="G225" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H225" t="s">
         <v>16</v>
@@ -9146,7 +9161,7 @@
         <v>100</v>
       </c>
       <c r="L225">
-        <v>0.1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
@@ -9154,22 +9169,22 @@
         <v>23</v>
       </c>
       <c r="B226">
-        <v>600</v>
+        <v>465</v>
       </c>
       <c r="C226">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="D226" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="E226" t="s">
-        <v>159</v>
+        <v>88</v>
       </c>
       <c r="F226" t="s">
         <v>14</v>
       </c>
       <c r="G226" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H226" t="s">
         <v>16</v>
@@ -9181,7 +9196,7 @@
         <v>100</v>
       </c>
       <c r="L226">
-        <v>0.1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
@@ -9189,37 +9204,34 @@
         <v>12</v>
       </c>
       <c r="B227">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="C227">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D227" t="s">
-        <v>215</v>
+        <v>92</v>
       </c>
       <c r="E227" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F227" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G227" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H227" t="s">
         <v>16</v>
       </c>
       <c r="I227" t="s">
-        <v>17</v>
-      </c>
-      <c r="J227" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="K227">
         <v>100</v>
       </c>
       <c r="L227">
-        <v>0.2</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
@@ -9227,37 +9239,34 @@
         <v>18</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C228">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>40</v>
+        <v>94</v>
       </c>
       <c r="E228" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F228" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G228" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H228" t="s">
         <v>16</v>
       </c>
       <c r="I228" t="s">
-        <v>17</v>
-      </c>
-      <c r="J228" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="K228">
         <v>100</v>
       </c>
       <c r="L228">
-        <v>0.2</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
@@ -9265,37 +9274,34 @@
         <v>20</v>
       </c>
       <c r="B229">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C229">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="D229" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="E229" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F229" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G229" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H229" t="s">
         <v>16</v>
       </c>
       <c r="I229" t="s">
-        <v>17</v>
-      </c>
-      <c r="J229" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="K229">
         <v>100</v>
       </c>
       <c r="L229">
-        <v>0.2</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
@@ -9303,37 +9309,34 @@
         <v>21</v>
       </c>
       <c r="B230">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="C230">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="D230" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="E230" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F230" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G230" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H230" t="s">
         <v>16</v>
       </c>
       <c r="I230" t="s">
-        <v>17</v>
-      </c>
-      <c r="J230" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="K230">
         <v>100</v>
       </c>
       <c r="L230">
-        <v>0.2</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -9341,22 +9344,22 @@
         <v>23</v>
       </c>
       <c r="B231">
-        <v>600</v>
+        <v>698</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="D231" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="E231" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F231" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G231" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H231" t="s">
         <v>16</v>
@@ -9368,7 +9371,7 @@
         <v>100</v>
       </c>
       <c r="L231">
-        <v>0.2</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -9376,37 +9379,37 @@
         <v>12</v>
       </c>
       <c r="B232">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C232">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D232" t="s">
-        <v>220</v>
+        <v>97</v>
       </c>
       <c r="E232" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F232" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G232" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H232" t="s">
         <v>16</v>
       </c>
       <c r="I232" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="J232" t="s">
-        <v>221</v>
+        <v>99</v>
       </c>
       <c r="K232">
         <v>100</v>
       </c>
       <c r="L232">
-        <v>1.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
@@ -9417,19 +9420,19 @@
         <v>3</v>
       </c>
       <c r="C233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D233" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E233" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F233" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G233" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H233" t="s">
         <v>16</v>
@@ -9437,14 +9440,11 @@
       <c r="I233" t="s">
         <v>17</v>
       </c>
-      <c r="J233" t="s">
-        <v>222</v>
-      </c>
       <c r="K233">
         <v>100</v>
       </c>
       <c r="L233">
-        <v>1.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
@@ -9452,37 +9452,34 @@
         <v>20</v>
       </c>
       <c r="B234">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C234">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D234" t="s">
-        <v>223</v>
+        <v>73</v>
       </c>
       <c r="E234" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F234" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G234" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H234" t="s">
         <v>16</v>
       </c>
       <c r="I234" t="s">
-        <v>229</v>
-      </c>
-      <c r="J234" t="s">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="K234">
         <v>100</v>
       </c>
       <c r="L234">
-        <v>1.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
@@ -9490,22 +9487,22 @@
         <v>21</v>
       </c>
       <c r="B235">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C235">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D235" t="s">
         <v>22</v>
       </c>
       <c r="E235" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F235" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G235" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H235" t="s">
         <v>16</v>
@@ -9513,14 +9510,11 @@
       <c r="I235" t="s">
         <v>17</v>
       </c>
-      <c r="J235" t="s">
-        <v>225</v>
-      </c>
       <c r="K235">
         <v>100</v>
       </c>
       <c r="L235">
-        <v>1.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
@@ -9528,22 +9522,22 @@
         <v>23</v>
       </c>
       <c r="B236">
-        <v>600</v>
+        <v>338</v>
       </c>
       <c r="C236">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D236" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="E236" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F236" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G236" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H236" t="s">
         <v>16</v>
@@ -9555,7 +9549,7 @@
         <v>100</v>
       </c>
       <c r="L236">
-        <v>1.3</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
@@ -9563,34 +9557,37 @@
         <v>12</v>
       </c>
       <c r="B237">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C237">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="E237" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="F237" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G237" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H237" t="s">
         <v>16</v>
       </c>
       <c r="I237" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J237" t="s">
+        <v>104</v>
       </c>
       <c r="K237">
         <v>100</v>
       </c>
       <c r="L237">
-        <v>87.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
@@ -9598,34 +9595,34 @@
         <v>18</v>
       </c>
       <c r="B238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C238">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="E238" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="F238" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G238" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H238" t="s">
         <v>16</v>
       </c>
       <c r="I238" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K238">
         <v>100</v>
       </c>
       <c r="L238">
-        <v>87.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
@@ -9633,22 +9630,22 @@
         <v>20</v>
       </c>
       <c r="B239">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C239">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D239" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="E239" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="F239" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G239" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H239" t="s">
         <v>16</v>
@@ -9660,7 +9657,7 @@
         <v>100</v>
       </c>
       <c r="L239">
-        <v>87.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
@@ -9668,34 +9665,34 @@
         <v>21</v>
       </c>
       <c r="B240">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C240">
-        <v>105</v>
+        <v>8</v>
       </c>
       <c r="D240" t="s">
-        <v>178</v>
+        <v>22</v>
       </c>
       <c r="E240" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="F240" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G240" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H240" t="s">
         <v>16</v>
       </c>
       <c r="I240" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K240">
         <v>100</v>
       </c>
       <c r="L240">
-        <v>87.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
@@ -9703,34 +9700,34 @@
         <v>23</v>
       </c>
       <c r="B241">
-        <v>1200</v>
+        <v>563</v>
       </c>
       <c r="C241">
-        <v>1201</v>
+        <v>0</v>
       </c>
       <c r="D241" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E241" t="s">
-        <v>175</v>
+        <v>102</v>
       </c>
       <c r="F241" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G241" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H241" t="s">
         <v>16</v>
       </c>
       <c r="I241" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K241">
         <v>100</v>
       </c>
       <c r="L241">
-        <v>87.8</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
@@ -9738,37 +9735,34 @@
         <v>12</v>
       </c>
       <c r="B242">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C242">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D242" t="s">
-        <v>19</v>
+        <v>205</v>
       </c>
       <c r="E242" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="F242" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G242" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="H242" t="s">
         <v>16</v>
       </c>
       <c r="I242" t="s">
-        <v>17</v>
-      </c>
-      <c r="J242" t="s">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="K242">
         <v>100</v>
       </c>
       <c r="L242">
-        <v>0.1</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
@@ -9779,31 +9773,31 @@
         <v>4</v>
       </c>
       <c r="C243">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D243" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E243" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="F243" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G243" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="H243" t="s">
         <v>16</v>
       </c>
       <c r="I243" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K243">
         <v>100</v>
       </c>
       <c r="L243">
-        <v>0.1</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
@@ -9814,31 +9808,31 @@
         <v>30</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D244" t="s">
-        <v>19</v>
+        <v>268</v>
       </c>
       <c r="E244" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="F244" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G244" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="H244" t="s">
         <v>16</v>
       </c>
       <c r="I244" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K244">
         <v>100</v>
       </c>
       <c r="L244">
-        <v>0.1</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
@@ -9849,31 +9843,31 @@
         <v>70</v>
       </c>
       <c r="C245">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="D245" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="E245" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="F245" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G245" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="H245" t="s">
         <v>16</v>
       </c>
       <c r="I245" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K245">
         <v>100</v>
       </c>
       <c r="L245">
-        <v>0.1</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
@@ -9881,7 +9875,7 @@
         <v>23</v>
       </c>
       <c r="B246">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9890,13 +9884,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>133</v>
+        <v>266</v>
       </c>
       <c r="F246" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G246" t="s">
-        <v>176</v>
+        <v>267</v>
       </c>
       <c r="H246" t="s">
         <v>16</v>
@@ -9908,7 +9902,7 @@
         <v>100</v>
       </c>
       <c r="L246">
-        <v>0.1</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
@@ -9916,22 +9910,22 @@
         <v>12</v>
       </c>
       <c r="B247">
+        <v>14</v>
+      </c>
+      <c r="C247">
         <v>19</v>
       </c>
-      <c r="C247">
-        <v>16</v>
-      </c>
       <c r="D247" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="E247" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="F247" t="s">
         <v>14</v>
       </c>
       <c r="G247" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H247" t="s">
         <v>16</v>
@@ -9940,13 +9934,13 @@
         <v>17</v>
       </c>
       <c r="J247" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="K247">
         <v>100</v>
       </c>
       <c r="L247">
-        <v>65</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
@@ -9954,22 +9948,22 @@
         <v>18</v>
       </c>
       <c r="B248">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C248">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D248" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E248" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="F248" t="s">
         <v>14</v>
       </c>
       <c r="G248" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H248" t="s">
         <v>16</v>
@@ -9977,11 +9971,14 @@
       <c r="I248" t="s">
         <v>17</v>
       </c>
+      <c r="J248" t="s">
+        <v>122</v>
+      </c>
       <c r="K248">
         <v>100</v>
       </c>
       <c r="L248">
-        <v>65</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
@@ -9989,22 +9986,22 @@
         <v>20</v>
       </c>
       <c r="B249">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C249">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D249" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="E249" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="F249" t="s">
         <v>14</v>
       </c>
       <c r="G249" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H249" t="s">
         <v>16</v>
@@ -10012,11 +10009,14 @@
       <c r="I249" t="s">
         <v>17</v>
       </c>
+      <c r="J249" t="s">
+        <v>124</v>
+      </c>
       <c r="K249">
         <v>100</v>
       </c>
       <c r="L249">
-        <v>65</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
@@ -10024,22 +10024,22 @@
         <v>21</v>
       </c>
       <c r="B250">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C250">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="D250" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="E250" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="F250" t="s">
         <v>14</v>
       </c>
       <c r="G250" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H250" t="s">
         <v>16</v>
@@ -10047,11 +10047,14 @@
       <c r="I250" t="s">
         <v>17</v>
       </c>
+      <c r="J250" t="s">
+        <v>126</v>
+      </c>
       <c r="K250">
         <v>100</v>
       </c>
       <c r="L250">
-        <v>65</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
@@ -10059,22 +10062,22 @@
         <v>23</v>
       </c>
       <c r="B251">
-        <v>465</v>
+        <v>600</v>
       </c>
       <c r="C251">
-        <v>645</v>
+        <v>314</v>
       </c>
       <c r="D251" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="E251" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="F251" t="s">
         <v>14</v>
       </c>
       <c r="G251" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H251" t="s">
         <v>16</v>
@@ -10082,11 +10085,14 @@
       <c r="I251" t="s">
         <v>17</v>
       </c>
+      <c r="J251" t="s">
+        <v>128</v>
+      </c>
       <c r="K251">
         <v>100</v>
       </c>
       <c r="L251">
-        <v>65</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
@@ -10094,34 +10100,34 @@
         <v>12</v>
       </c>
       <c r="B252">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C252">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D252" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="E252" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F252" t="s">
         <v>25</v>
       </c>
       <c r="G252" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H252" t="s">
         <v>16</v>
       </c>
       <c r="I252" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K252">
         <v>100</v>
       </c>
       <c r="L252">
-        <v>116.6</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
@@ -10129,34 +10135,34 @@
         <v>18</v>
       </c>
       <c r="B253">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C253">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D253" t="s">
-        <v>94</v>
+        <v>19</v>
       </c>
       <c r="E253" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F253" t="s">
         <v>25</v>
       </c>
       <c r="G253" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H253" t="s">
         <v>16</v>
       </c>
       <c r="I253" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K253">
         <v>100</v>
       </c>
       <c r="L253">
-        <v>116.6</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
@@ -10164,34 +10170,34 @@
         <v>20</v>
       </c>
       <c r="B254">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C254">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D254" t="s">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="E254" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F254" t="s">
         <v>25</v>
       </c>
       <c r="G254" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H254" t="s">
         <v>16</v>
       </c>
       <c r="I254" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K254">
         <v>100</v>
       </c>
       <c r="L254">
-        <v>116.6</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
@@ -10199,34 +10205,34 @@
         <v>21</v>
       </c>
       <c r="B255">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C255">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D255" t="s">
-        <v>64</v>
+        <v>131</v>
       </c>
       <c r="E255" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F255" t="s">
         <v>25</v>
       </c>
       <c r="G255" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H255" t="s">
         <v>16</v>
       </c>
       <c r="I255" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K255">
         <v>100</v>
       </c>
       <c r="L255">
-        <v>116.6</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
@@ -10234,22 +10240,22 @@
         <v>23</v>
       </c>
       <c r="B256">
-        <v>698</v>
+        <v>900</v>
       </c>
       <c r="C256">
-        <v>482</v>
+        <v>46</v>
       </c>
       <c r="D256" t="s">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E256" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="F256" t="s">
         <v>25</v>
       </c>
       <c r="G256" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H256" t="s">
         <v>16</v>
@@ -10261,7 +10267,7 @@
         <v>100</v>
       </c>
       <c r="L256">
-        <v>116.6</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
@@ -10269,37 +10275,37 @@
         <v>12</v>
       </c>
       <c r="B257">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C257">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D257" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="E257" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F257" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G257" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H257" t="s">
         <v>16</v>
       </c>
       <c r="I257" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="J257" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="K257">
         <v>100</v>
       </c>
       <c r="L257">
-        <v>47.3</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
@@ -10307,7 +10313,7 @@
         <v>18</v>
       </c>
       <c r="B258">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -10316,13 +10322,13 @@
         <v>19</v>
       </c>
       <c r="E258" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F258" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G258" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H258" t="s">
         <v>16</v>
@@ -10330,11 +10336,14 @@
       <c r="I258" t="s">
         <v>17</v>
       </c>
+      <c r="J258" t="s">
+        <v>135</v>
+      </c>
       <c r="K258">
         <v>100</v>
       </c>
       <c r="L258">
-        <v>47.3</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
@@ -10342,34 +10351,37 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C259">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D259" t="s">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="E259" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F259" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G259" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H259" t="s">
         <v>16</v>
       </c>
       <c r="I259" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J259" t="s">
+        <v>137</v>
       </c>
       <c r="K259">
         <v>100</v>
       </c>
       <c r="L259">
-        <v>47.3</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
@@ -10377,22 +10389,22 @@
         <v>21</v>
       </c>
       <c r="B260">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C260">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D260" t="s">
         <v>22</v>
       </c>
       <c r="E260" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F260" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G260" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H260" t="s">
         <v>16</v>
@@ -10400,11 +10412,14 @@
       <c r="I260" t="s">
         <v>17</v>
       </c>
+      <c r="J260" t="s">
+        <v>138</v>
+      </c>
       <c r="K260">
         <v>100</v>
       </c>
       <c r="L260">
-        <v>47.3</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
@@ -10412,22 +10427,22 @@
         <v>23</v>
       </c>
       <c r="B261">
-        <v>338</v>
+        <v>900</v>
       </c>
       <c r="C261">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="D261" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="E261" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="F261" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G261" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H261" t="s">
         <v>16</v>
@@ -10439,7 +10454,7 @@
         <v>100</v>
       </c>
       <c r="L261">
-        <v>47.3</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
@@ -10447,22 +10462,22 @@
         <v>12</v>
       </c>
       <c r="B262">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="D262" t="s">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="E262" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="F262" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G262" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="H262" t="s">
         <v>16</v>
@@ -10470,14 +10485,11 @@
       <c r="I262" t="s">
         <v>17</v>
       </c>
-      <c r="J262" t="s">
-        <v>104</v>
-      </c>
       <c r="K262">
         <v>100</v>
       </c>
       <c r="L262">
-        <v>11.7</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
@@ -10488,19 +10500,19 @@
         <v>5</v>
       </c>
       <c r="C263">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D263" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="E263" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="F263" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G263" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="H263" t="s">
         <v>16</v>
@@ -10512,7 +10524,7 @@
         <v>100</v>
       </c>
       <c r="L263">
-        <v>11.7</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
@@ -10520,22 +10532,22 @@
         <v>20</v>
       </c>
       <c r="B264">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C264">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D264" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="E264" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="F264" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G264" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="H264" t="s">
         <v>16</v>
@@ -10547,7 +10559,7 @@
         <v>100</v>
       </c>
       <c r="L264">
-        <v>11.7</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
@@ -10555,22 +10567,22 @@
         <v>21</v>
       </c>
       <c r="B265">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="C265">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D265" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="E265" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="F265" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G265" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="H265" t="s">
         <v>16</v>
@@ -10582,7 +10594,7 @@
         <v>100</v>
       </c>
       <c r="L265">
-        <v>11.7</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
@@ -10590,22 +10602,22 @@
         <v>23</v>
       </c>
       <c r="B266">
-        <v>563</v>
+        <v>768</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="D266" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E266" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="F266" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G266" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="H266" t="s">
         <v>16</v>
@@ -10617,7 +10629,7 @@
         <v>100</v>
       </c>
       <c r="L266">
-        <v>11.7</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
@@ -10625,34 +10637,37 @@
         <v>12</v>
       </c>
       <c r="B267">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C267">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D267" t="s">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="E267" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
       <c r="F267" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G267" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="H267" t="s">
         <v>16</v>
       </c>
       <c r="I267" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J267" t="s">
+        <v>43</v>
       </c>
       <c r="K267">
         <v>100</v>
       </c>
       <c r="L267">
-        <v>89.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
@@ -10660,34 +10675,34 @@
         <v>18</v>
       </c>
       <c r="B268">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C268">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D268" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
       <c r="F268" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G268" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="H268" t="s">
         <v>16</v>
       </c>
       <c r="I268" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K268">
         <v>100</v>
       </c>
       <c r="L268">
-        <v>89.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
@@ -10695,34 +10710,34 @@
         <v>20</v>
       </c>
       <c r="B269">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C269">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>268</v>
+        <v>44</v>
       </c>
       <c r="E269" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
       <c r="F269" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G269" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="H269" t="s">
         <v>16</v>
       </c>
       <c r="I269" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K269">
         <v>100</v>
       </c>
       <c r="L269">
-        <v>89.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
@@ -10730,34 +10745,34 @@
         <v>21</v>
       </c>
       <c r="B270">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C270">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D270" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E270" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
       <c r="F270" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G270" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="H270" t="s">
         <v>16</v>
       </c>
       <c r="I270" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K270">
         <v>100</v>
       </c>
       <c r="L270">
-        <v>89.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
@@ -10765,22 +10780,22 @@
         <v>23</v>
       </c>
       <c r="B271">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="C271">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="D271" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="E271" t="s">
-        <v>266</v>
+        <v>42</v>
       </c>
       <c r="F271" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G271" t="s">
-        <v>267</v>
+        <v>36</v>
       </c>
       <c r="H271" t="s">
         <v>16</v>
@@ -10792,7 +10807,7 @@
         <v>100</v>
       </c>
       <c r="L271">
-        <v>89.7</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
@@ -10800,22 +10815,22 @@
         <v>12</v>
       </c>
       <c r="B272">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C272">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="E272" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="F272" t="s">
         <v>14</v>
       </c>
       <c r="G272" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H272" t="s">
         <v>16</v>
@@ -10824,13 +10839,13 @@
         <v>17</v>
       </c>
       <c r="J272" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="K272">
         <v>100</v>
       </c>
       <c r="L272">
-        <v>71.599999999999994</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
@@ -10838,22 +10853,22 @@
         <v>18</v>
       </c>
       <c r="B273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C273">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D273" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="E273" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="F273" t="s">
         <v>14</v>
       </c>
       <c r="G273" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H273" t="s">
         <v>16</v>
@@ -10861,14 +10876,11 @@
       <c r="I273" t="s">
         <v>17</v>
       </c>
-      <c r="J273" t="s">
-        <v>122</v>
-      </c>
       <c r="K273">
         <v>100</v>
       </c>
       <c r="L273">
-        <v>71.599999999999994</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
@@ -10876,22 +10888,22 @@
         <v>20</v>
       </c>
       <c r="B274">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C274">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D274" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="E274" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="F274" t="s">
         <v>14</v>
       </c>
       <c r="G274" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H274" t="s">
         <v>16</v>
@@ -10899,14 +10911,11 @@
       <c r="I274" t="s">
         <v>17</v>
       </c>
-      <c r="J274" t="s">
-        <v>124</v>
-      </c>
       <c r="K274">
         <v>100</v>
       </c>
       <c r="L274">
-        <v>71.599999999999994</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
@@ -10914,22 +10923,22 @@
         <v>21</v>
       </c>
       <c r="B275">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="C275">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D275" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="E275" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="F275" t="s">
         <v>14</v>
       </c>
       <c r="G275" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H275" t="s">
         <v>16</v>
@@ -10937,14 +10946,11 @@
       <c r="I275" t="s">
         <v>17</v>
       </c>
-      <c r="J275" t="s">
-        <v>126</v>
-      </c>
       <c r="K275">
         <v>100</v>
       </c>
       <c r="L275">
-        <v>71.599999999999994</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
@@ -10952,22 +10958,22 @@
         <v>23</v>
       </c>
       <c r="B276">
-        <v>600</v>
+        <v>211</v>
       </c>
       <c r="C276">
-        <v>314</v>
+        <v>480</v>
       </c>
       <c r="D276" t="s">
-        <v>127</v>
+        <v>70</v>
       </c>
       <c r="E276" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="F276" t="s">
         <v>14</v>
       </c>
       <c r="G276" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H276" t="s">
         <v>16</v>
@@ -10975,14 +10981,11 @@
       <c r="I276" t="s">
         <v>17</v>
       </c>
-      <c r="J276" t="s">
-        <v>128</v>
-      </c>
       <c r="K276">
         <v>100</v>
       </c>
       <c r="L276">
-        <v>71.599999999999994</v>
+        <v>94.2</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
@@ -10990,34 +10993,34 @@
         <v>12</v>
       </c>
       <c r="B277">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C277">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D277" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E277" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="F277" t="s">
         <v>25</v>
       </c>
       <c r="G277" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H277" t="s">
         <v>16</v>
       </c>
       <c r="I277" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K277">
         <v>100</v>
       </c>
       <c r="L277">
-        <v>64.8</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
@@ -11025,7 +11028,7 @@
         <v>18</v>
       </c>
       <c r="B278">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -11034,13 +11037,13 @@
         <v>19</v>
       </c>
       <c r="E278" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="F278" t="s">
         <v>25</v>
       </c>
       <c r="G278" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H278" t="s">
         <v>16</v>
@@ -11052,7 +11055,7 @@
         <v>100</v>
       </c>
       <c r="L278">
-        <v>64.8</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
@@ -11060,22 +11063,22 @@
         <v>20</v>
       </c>
       <c r="B279">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C279">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D279" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="E279" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="F279" t="s">
         <v>25</v>
       </c>
       <c r="G279" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H279" t="s">
         <v>16</v>
@@ -11087,7 +11090,7 @@
         <v>100</v>
       </c>
       <c r="L279">
-        <v>64.8</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
@@ -11095,34 +11098,34 @@
         <v>21</v>
       </c>
       <c r="B280">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C280">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="D280" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="E280" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="F280" t="s">
         <v>25</v>
       </c>
       <c r="G280" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H280" t="s">
         <v>16</v>
       </c>
       <c r="I280" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K280">
         <v>100</v>
       </c>
       <c r="L280">
-        <v>64.8</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
@@ -11130,22 +11133,22 @@
         <v>23</v>
       </c>
       <c r="B281">
-        <v>900</v>
+        <v>989</v>
       </c>
       <c r="C281">
-        <v>46</v>
+        <v>653</v>
       </c>
       <c r="D281" t="s">
-        <v>132</v>
+        <v>74</v>
       </c>
       <c r="E281" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="F281" t="s">
         <v>25</v>
       </c>
       <c r="G281" t="s">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="H281" t="s">
         <v>16</v>
@@ -11157,7 +11160,7 @@
         <v>100</v>
       </c>
       <c r="L281">
-        <v>64.8</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
@@ -11165,37 +11168,37 @@
         <v>12</v>
       </c>
       <c r="B282">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D282" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E282" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F282" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G282" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H282" t="s">
         <v>16</v>
       </c>
       <c r="I282" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J282" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="K282">
         <v>100</v>
       </c>
       <c r="L282">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
@@ -11203,37 +11206,37 @@
         <v>18</v>
       </c>
       <c r="B283">
+        <v>3</v>
+      </c>
+      <c r="C283">
         <v>2</v>
       </c>
-      <c r="C283">
-        <v>0</v>
-      </c>
       <c r="D283" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E283" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F283" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G283" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H283" t="s">
         <v>16</v>
       </c>
       <c r="I283" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="J283" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="K283">
         <v>100</v>
       </c>
       <c r="L283">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
@@ -11241,37 +11244,37 @@
         <v>20</v>
       </c>
       <c r="B284">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C284">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D284" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="E284" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F284" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G284" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H284" t="s">
         <v>16</v>
       </c>
       <c r="I284" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J284" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="K284">
         <v>100</v>
       </c>
       <c r="L284">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
@@ -11279,22 +11282,22 @@
         <v>21</v>
       </c>
       <c r="B285">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C285">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D285" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="E285" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F285" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G285" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H285" t="s">
         <v>16</v>
@@ -11303,13 +11306,13 @@
         <v>17</v>
       </c>
       <c r="J285" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="K285">
         <v>100</v>
       </c>
       <c r="L285">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
@@ -11317,22 +11320,22 @@
         <v>23</v>
       </c>
       <c r="B286">
-        <v>900</v>
+        <v>510</v>
       </c>
       <c r="C286">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="D286" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="E286" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F286" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G286" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H286" t="s">
         <v>16</v>
@@ -11340,11 +11343,14 @@
       <c r="I286" t="s">
         <v>17</v>
       </c>
+      <c r="J286" t="s">
+        <v>201</v>
+      </c>
       <c r="K286">
         <v>100</v>
       </c>
       <c r="L286">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
@@ -11352,34 +11358,34 @@
         <v>12</v>
       </c>
       <c r="B287">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C287">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D287" t="s">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="E287" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F287" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G287" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H287" t="s">
         <v>16</v>
       </c>
       <c r="I287" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K287">
         <v>100</v>
       </c>
       <c r="L287">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
@@ -11390,19 +11396,19 @@
         <v>5</v>
       </c>
       <c r="C288">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D288" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="E288" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F288" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G288" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>16</v>
@@ -11414,7 +11420,7 @@
         <v>100</v>
       </c>
       <c r="L288">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
@@ -11422,22 +11428,22 @@
         <v>20</v>
       </c>
       <c r="B289">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C289">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D289" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E289" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F289" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G289" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H289" t="s">
         <v>16</v>
@@ -11449,7 +11455,7 @@
         <v>100</v>
       </c>
       <c r="L289">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
@@ -11457,34 +11463,34 @@
         <v>21</v>
       </c>
       <c r="B290">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="C290">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="D290" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="E290" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F290" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G290" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H290" t="s">
         <v>16</v>
       </c>
       <c r="I290" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K290">
         <v>100</v>
       </c>
       <c r="L290">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
@@ -11492,34 +11498,34 @@
         <v>23</v>
       </c>
       <c r="B291">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C291">
-        <v>256</v>
+        <v>733</v>
       </c>
       <c r="D291" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E291" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F291" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G291" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H291" t="s">
         <v>16</v>
       </c>
       <c r="I291" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K291">
         <v>100</v>
       </c>
       <c r="L291">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
@@ -11527,37 +11533,37 @@
         <v>12</v>
       </c>
       <c r="B292">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C292">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D292" t="s">
-        <v>41</v>
+        <v>205</v>
       </c>
       <c r="E292" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F292" t="s">
         <v>25</v>
       </c>
       <c r="G292" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H292" t="s">
         <v>16</v>
       </c>
       <c r="I292" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="J292" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="K292">
         <v>100</v>
       </c>
       <c r="L292">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
@@ -11565,22 +11571,22 @@
         <v>18</v>
       </c>
       <c r="B293">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E293" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F293" t="s">
         <v>25</v>
       </c>
       <c r="G293" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H293" t="s">
         <v>16</v>
@@ -11592,7 +11598,7 @@
         <v>100</v>
       </c>
       <c r="L293">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
@@ -11600,34 +11606,34 @@
         <v>20</v>
       </c>
       <c r="B294">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C294">
         <v>11</v>
       </c>
       <c r="D294" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E294" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F294" t="s">
         <v>25</v>
       </c>
       <c r="G294" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H294" t="s">
         <v>16</v>
       </c>
       <c r="I294" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K294">
         <v>100</v>
       </c>
       <c r="L294">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
@@ -11635,22 +11641,22 @@
         <v>21</v>
       </c>
       <c r="B295">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C295">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D295" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E295" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F295" t="s">
         <v>25</v>
       </c>
       <c r="G295" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H295" t="s">
         <v>16</v>
@@ -11662,7 +11668,7 @@
         <v>100</v>
       </c>
       <c r="L295">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
@@ -11670,34 +11676,34 @@
         <v>23</v>
       </c>
       <c r="B296">
-        <v>432</v>
+        <v>225</v>
       </c>
       <c r="C296">
-        <v>171</v>
+        <v>306</v>
       </c>
       <c r="D296" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E296" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F296" t="s">
         <v>25</v>
       </c>
       <c r="G296" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H296" t="s">
         <v>16</v>
       </c>
       <c r="I296" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K296">
         <v>100</v>
       </c>
       <c r="L296">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
@@ -11705,37 +11711,37 @@
         <v>12</v>
       </c>
       <c r="B297">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C297">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D297" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="E297" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F297" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G297" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H297" t="s">
         <v>16</v>
       </c>
       <c r="I297" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="J297" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="K297">
         <v>100</v>
       </c>
       <c r="L297">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
@@ -11743,7 +11749,7 @@
         <v>18</v>
       </c>
       <c r="B298">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -11752,13 +11758,13 @@
         <v>19</v>
       </c>
       <c r="E298" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F298" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G298" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H298" t="s">
         <v>16</v>
@@ -11766,11 +11772,14 @@
       <c r="I298" t="s">
         <v>17</v>
       </c>
+      <c r="J298" t="s">
+        <v>210</v>
+      </c>
       <c r="K298">
         <v>100</v>
       </c>
       <c r="L298">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
@@ -11778,34 +11787,37 @@
         <v>20</v>
       </c>
       <c r="B299">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C299">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D299" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="E299" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F299" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G299" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H299" t="s">
         <v>16</v>
       </c>
       <c r="I299" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J299" t="s">
+        <v>212</v>
       </c>
       <c r="K299">
         <v>100</v>
       </c>
       <c r="L299">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
@@ -11813,34 +11825,37 @@
         <v>21</v>
       </c>
       <c r="B300">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C300">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D300" t="s">
         <v>22</v>
       </c>
       <c r="E300" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F300" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G300" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H300" t="s">
         <v>16</v>
       </c>
       <c r="I300" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J300" t="s">
+        <v>213</v>
       </c>
       <c r="K300">
         <v>100</v>
       </c>
       <c r="L300">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
@@ -11848,22 +11863,22 @@
         <v>23</v>
       </c>
       <c r="B301">
-        <v>211</v>
+        <v>563</v>
       </c>
       <c r="C301">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="D301" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="E301" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F301" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G301" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H301" t="s">
         <v>16</v>
@@ -11875,7 +11890,7 @@
         <v>100</v>
       </c>
       <c r="L301">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
@@ -11883,34 +11898,34 @@
         <v>12</v>
       </c>
       <c r="B302">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C302">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D302" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="E302" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F302" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G302" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H302" t="s">
         <v>16</v>
       </c>
       <c r="I302" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K302">
         <v>100</v>
       </c>
       <c r="L302">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
@@ -11918,34 +11933,34 @@
         <v>18</v>
       </c>
       <c r="B303">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C303">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D303" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E303" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F303" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G303" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H303" t="s">
         <v>16</v>
       </c>
       <c r="I303" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K303">
         <v>100</v>
       </c>
       <c r="L303">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
@@ -11953,22 +11968,22 @@
         <v>20</v>
       </c>
       <c r="B304">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C304">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D304" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="E304" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F304" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G304" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H304" t="s">
         <v>16</v>
@@ -11980,7 +11995,7 @@
         <v>100</v>
       </c>
       <c r="L304">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
@@ -11988,34 +12003,34 @@
         <v>21</v>
       </c>
       <c r="B305">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C305">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D305" t="s">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="E305" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F305" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G305" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H305" t="s">
         <v>16</v>
       </c>
       <c r="I305" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K305">
         <v>100</v>
       </c>
       <c r="L305">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
@@ -12023,34 +12038,34 @@
         <v>23</v>
       </c>
       <c r="B306">
-        <v>989</v>
+        <v>402</v>
       </c>
       <c r="C306">
-        <v>653</v>
+        <v>402</v>
       </c>
       <c r="D306" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E306" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F306" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G306" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H306" t="s">
         <v>16</v>
       </c>
       <c r="I306" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K306">
         <v>100</v>
       </c>
       <c r="L306">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
@@ -12058,22 +12073,22 @@
         <v>12</v>
       </c>
       <c r="B307">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C307">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D307" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E307" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F307" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G307" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H307" t="s">
         <v>16</v>
@@ -12081,14 +12096,11 @@
       <c r="I307" t="s">
         <v>231</v>
       </c>
-      <c r="J307" t="s">
-        <v>196</v>
-      </c>
       <c r="K307">
         <v>100</v>
       </c>
       <c r="L307">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
@@ -12096,37 +12108,34 @@
         <v>18</v>
       </c>
       <c r="B308">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C308">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D308" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="E308" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F308" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G308" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H308" t="s">
         <v>16</v>
       </c>
       <c r="I308" t="s">
-        <v>229</v>
-      </c>
-      <c r="J308" t="s">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="K308">
         <v>100</v>
       </c>
       <c r="L308">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
@@ -12134,37 +12143,34 @@
         <v>20</v>
       </c>
       <c r="B309">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C309">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D309" t="s">
-        <v>51</v>
+        <v>185</v>
       </c>
       <c r="E309" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F309" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G309" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H309" t="s">
         <v>16</v>
       </c>
       <c r="I309" t="s">
-        <v>231</v>
-      </c>
-      <c r="J309" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="K309">
         <v>100</v>
       </c>
       <c r="L309">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
@@ -12172,37 +12178,34 @@
         <v>21</v>
       </c>
       <c r="B310">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="C310">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="D310" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E310" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F310" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G310" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H310" t="s">
         <v>16</v>
       </c>
       <c r="I310" t="s">
-        <v>17</v>
-      </c>
-      <c r="J310" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="K310">
         <v>100</v>
       </c>
       <c r="L310">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
@@ -12210,37 +12213,34 @@
         <v>23</v>
       </c>
       <c r="B311">
-        <v>510</v>
+        <v>603</v>
       </c>
       <c r="C311">
-        <v>547</v>
+        <v>603</v>
       </c>
       <c r="D311" t="s">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="E311" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F311" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G311" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H311" t="s">
         <v>16</v>
       </c>
       <c r="I311" t="s">
-        <v>17</v>
-      </c>
-      <c r="J311" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="K311">
         <v>100</v>
       </c>
       <c r="L311">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
@@ -12248,34 +12248,37 @@
         <v>12</v>
       </c>
       <c r="B312">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C312">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D312" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="E312" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F312" t="s">
         <v>25</v>
       </c>
       <c r="G312" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H312" t="s">
         <v>16</v>
       </c>
       <c r="I312" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="J312" t="s">
+        <v>188</v>
       </c>
       <c r="K312">
         <v>100</v>
       </c>
       <c r="L312">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
@@ -12283,34 +12286,34 @@
         <v>18</v>
       </c>
       <c r="B313">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C313">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D313" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="E313" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F313" t="s">
         <v>25</v>
       </c>
       <c r="G313" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H313" t="s">
         <v>16</v>
       </c>
       <c r="I313" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K313">
         <v>100</v>
       </c>
       <c r="L313">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
@@ -12318,22 +12321,22 @@
         <v>20</v>
       </c>
       <c r="B314">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C314">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D314" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E314" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F314" t="s">
         <v>25</v>
       </c>
       <c r="G314" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H314" t="s">
         <v>16</v>
@@ -12345,7 +12348,7 @@
         <v>100</v>
       </c>
       <c r="L314">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
@@ -12353,34 +12356,34 @@
         <v>21</v>
       </c>
       <c r="B315">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C315">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D315" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="E315" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F315" t="s">
         <v>25</v>
       </c>
       <c r="G315" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H315" t="s">
         <v>16</v>
       </c>
       <c r="I315" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K315">
         <v>100</v>
       </c>
       <c r="L315">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
@@ -12388,34 +12391,34 @@
         <v>23</v>
       </c>
       <c r="B316">
-        <v>765</v>
+        <v>495</v>
       </c>
       <c r="C316">
-        <v>733</v>
+        <v>507</v>
       </c>
       <c r="D316" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E316" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F316" t="s">
         <v>25</v>
       </c>
       <c r="G316" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H316" t="s">
         <v>16</v>
       </c>
       <c r="I316" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K316">
         <v>100</v>
       </c>
       <c r="L316">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
@@ -12423,37 +12426,34 @@
         <v>12</v>
       </c>
       <c r="B317">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C317">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D317" t="s">
-        <v>205</v>
+        <v>19</v>
       </c>
       <c r="E317" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F317" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G317" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H317" t="s">
         <v>16</v>
       </c>
       <c r="I317" t="s">
-        <v>229</v>
-      </c>
-      <c r="J317" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="K317">
         <v>100</v>
       </c>
       <c r="L317">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
@@ -12461,22 +12461,22 @@
         <v>18</v>
       </c>
       <c r="B318">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C318">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D318" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E318" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F318" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G318" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H318" t="s">
         <v>16</v>
@@ -12488,7 +12488,7 @@
         <v>100</v>
       </c>
       <c r="L318">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
@@ -12496,34 +12496,34 @@
         <v>20</v>
       </c>
       <c r="B319">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C319">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D319" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E319" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F319" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G319" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H319" t="s">
         <v>16</v>
       </c>
       <c r="I319" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K319">
         <v>100</v>
       </c>
       <c r="L319">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
@@ -12531,22 +12531,22 @@
         <v>21</v>
       </c>
       <c r="B320">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C320">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D320" t="s">
         <v>22</v>
       </c>
       <c r="E320" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F320" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G320" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H320" t="s">
         <v>16</v>
@@ -12558,7 +12558,7 @@
         <v>100</v>
       </c>
       <c r="L320">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
@@ -12566,34 +12566,34 @@
         <v>23</v>
       </c>
       <c r="B321">
-        <v>225</v>
+        <v>563</v>
       </c>
       <c r="C321">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="D321" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E321" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F321" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G321" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H321" t="s">
         <v>16</v>
       </c>
       <c r="I321" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K321">
         <v>100</v>
       </c>
       <c r="L321">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
@@ -12601,13 +12601,13 @@
         <v>12</v>
       </c>
       <c r="B322">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C322">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D322" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="E322" t="s">
         <v>133</v>
@@ -12616,22 +12616,22 @@
         <v>103</v>
       </c>
       <c r="G322" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H322" t="s">
         <v>16</v>
       </c>
       <c r="I322" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="J322" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="K322">
         <v>100</v>
       </c>
       <c r="L322">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
@@ -12639,7 +12639,7 @@
         <v>18</v>
       </c>
       <c r="B323">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -12654,7 +12654,7 @@
         <v>103</v>
       </c>
       <c r="G323" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H323" t="s">
         <v>16</v>
@@ -12663,13 +12663,13 @@
         <v>17</v>
       </c>
       <c r="J323" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="K323">
         <v>100</v>
       </c>
       <c r="L323">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
@@ -12677,13 +12677,13 @@
         <v>20</v>
       </c>
       <c r="B324">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C324">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D324" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="E324" t="s">
         <v>133</v>
@@ -12692,22 +12692,22 @@
         <v>103</v>
       </c>
       <c r="G324" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H324" t="s">
         <v>16</v>
       </c>
       <c r="I324" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="J324" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="K324">
         <v>100</v>
       </c>
       <c r="L324">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
@@ -12715,10 +12715,10 @@
         <v>21</v>
       </c>
       <c r="B325">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C325">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D325" t="s">
         <v>22</v>
@@ -12730,22 +12730,22 @@
         <v>103</v>
       </c>
       <c r="G325" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H325" t="s">
         <v>16</v>
       </c>
       <c r="I325" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="J325" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="K325">
         <v>100</v>
       </c>
       <c r="L325">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
@@ -12768,7 +12768,7 @@
         <v>103</v>
       </c>
       <c r="G326" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H326" t="s">
         <v>16</v>
@@ -12780,7 +12780,7 @@
         <v>100</v>
       </c>
       <c r="L326">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/07 Julio/Liquidacióncvsjulio/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_295D9EEDD058CA0F62355476585DCE3A87455B01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57FD8A5D-5F94-47C3-89CF-41AC0EFE357A}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_295D9EEDD058CA0F62355476585DCE3A87455B01" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AEA4274-2DCC-49C9-A29F-5F08C5414584}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2346" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2416" uniqueCount="277">
   <si>
     <t>Producto</t>
   </si>
@@ -827,6 +827,30 @@
   </si>
   <si>
     <t>87%</t>
+  </si>
+  <si>
+    <t>194%</t>
+  </si>
+  <si>
+    <t>Lider Dayana Lopez Llorente</t>
+  </si>
+  <si>
+    <t>SEGOVIA</t>
+  </si>
+  <si>
+    <t>105%</t>
+  </si>
+  <si>
+    <t>129%</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Miranda Rodriguez</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>54%</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L326"/>
+  <dimension ref="A1:L336"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -4573,22 +4597,22 @@
         <v>12</v>
       </c>
       <c r="B97">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C97">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="E97" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="F97" t="s">
         <v>14</v>
       </c>
       <c r="G97" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -4600,7 +4624,7 @@
         <v>100</v>
       </c>
       <c r="L97">
-        <v>117.4</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.25">
@@ -4608,34 +4632,34 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E98" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="F98" t="s">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
       </c>
       <c r="I98" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K98">
         <v>100</v>
       </c>
       <c r="L98">
-        <v>117.4</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
@@ -4643,34 +4667,34 @@
         <v>20</v>
       </c>
       <c r="B99">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="C99">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="D99" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="E99" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="F99" t="s">
         <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
       </c>
       <c r="I99" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K99">
         <v>100</v>
       </c>
       <c r="L99">
-        <v>117.4</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.25">
@@ -4678,34 +4702,34 @@
         <v>21</v>
       </c>
       <c r="B100">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="C100">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D100" t="s">
         <v>22</v>
       </c>
       <c r="E100" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
       </c>
       <c r="I100" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K100">
         <v>100</v>
       </c>
       <c r="L100">
-        <v>117.4</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.25">
@@ -4713,22 +4737,22 @@
         <v>23</v>
       </c>
       <c r="B101">
-        <v>750</v>
+        <v>480</v>
       </c>
       <c r="C101">
-        <v>800</v>
+        <v>488</v>
       </c>
       <c r="D101" t="s">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="E101" t="s">
-        <v>253</v>
+        <v>167</v>
       </c>
       <c r="F101" t="s">
         <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -4740,7 +4764,7 @@
         <v>100</v>
       </c>
       <c r="L101">
-        <v>117.4</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.25">
@@ -4748,34 +4772,34 @@
         <v>12</v>
       </c>
       <c r="B102">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="D102" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="E102" t="s">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="F102" t="s">
         <v>25</v>
       </c>
       <c r="G102" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
       </c>
       <c r="I102" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K102">
         <v>100</v>
       </c>
       <c r="L102">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.25">
@@ -4783,34 +4807,34 @@
         <v>18</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D103" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E103" t="s">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="F103" t="s">
         <v>25</v>
       </c>
       <c r="G103" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
       </c>
       <c r="I103" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K103">
         <v>100</v>
       </c>
       <c r="L103">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.25">
@@ -4818,22 +4842,22 @@
         <v>20</v>
       </c>
       <c r="B104">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C104">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D104" t="s">
-        <v>256</v>
+        <v>79</v>
       </c>
       <c r="E104" t="s">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="F104" t="s">
         <v>25</v>
       </c>
       <c r="G104" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -4845,7 +4869,7 @@
         <v>100</v>
       </c>
       <c r="L104">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.25">
@@ -4853,22 +4877,22 @@
         <v>21</v>
       </c>
       <c r="B105">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C105">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D105" t="s">
         <v>22</v>
       </c>
       <c r="E105" t="s">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="F105" t="s">
         <v>25</v>
       </c>
       <c r="G105" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H105" t="s">
         <v>16</v>
@@ -4880,7 +4904,7 @@
         <v>100</v>
       </c>
       <c r="L105">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.25">
@@ -4888,34 +4912,34 @@
         <v>23</v>
       </c>
       <c r="B106">
-        <v>750</v>
+        <v>720</v>
       </c>
       <c r="C106">
-        <v>469</v>
+        <v>733</v>
       </c>
       <c r="D106" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="E106" t="s">
-        <v>255</v>
+        <v>170</v>
       </c>
       <c r="F106" t="s">
         <v>25</v>
       </c>
       <c r="G106" t="s">
-        <v>254</v>
+        <v>168</v>
       </c>
       <c r="H106" t="s">
         <v>16</v>
       </c>
       <c r="I106" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K106">
         <v>100</v>
       </c>
       <c r="L106">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.25">
@@ -4923,34 +4947,37 @@
         <v>12</v>
       </c>
       <c r="B107">
-        <v>930</v>
+        <v>21</v>
       </c>
       <c r="C107">
-        <v>1107</v>
+        <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="E107" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="F107" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G107" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="H107" t="s">
         <v>16</v>
       </c>
       <c r="I107" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J107" t="s">
+        <v>171</v>
       </c>
       <c r="K107">
         <v>100</v>
       </c>
       <c r="L107">
-        <v>86.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.25">
@@ -4958,34 +4985,37 @@
         <v>18</v>
       </c>
       <c r="B108">
-        <v>153</v>
+        <v>5</v>
       </c>
       <c r="C108">
-        <v>131</v>
+        <v>1</v>
       </c>
       <c r="D108" t="s">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="E108" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="F108" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G108" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
       </c>
       <c r="I108" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J108" t="s">
+        <v>172</v>
       </c>
       <c r="K108">
         <v>100</v>
       </c>
       <c r="L108">
-        <v>86.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.25">
@@ -4993,22 +5023,22 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>1712</v>
+        <v>30</v>
       </c>
       <c r="C109">
-        <v>1454</v>
+        <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="E109" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="F109" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G109" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="H109" t="s">
         <v>16</v>
@@ -5016,11 +5046,14 @@
       <c r="I109" t="s">
         <v>17</v>
       </c>
+      <c r="J109" t="s">
+        <v>173</v>
+      </c>
       <c r="K109">
         <v>100</v>
       </c>
       <c r="L109">
-        <v>86.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.25">
@@ -5028,34 +5061,37 @@
         <v>21</v>
       </c>
       <c r="B110">
-        <v>3255</v>
+        <v>78</v>
       </c>
       <c r="C110">
-        <v>3866</v>
+        <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="E110" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="F110" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G110" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="H110" t="s">
         <v>16</v>
       </c>
       <c r="I110" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J110" t="s">
+        <v>174</v>
       </c>
       <c r="K110">
         <v>100</v>
       </c>
       <c r="L110">
-        <v>86.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.25">
@@ -5063,7 +5099,7 @@
         <v>23</v>
       </c>
       <c r="B111">
-        <v>27700</v>
+        <v>720</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -5072,25 +5108,25 @@
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>257</v>
+        <v>133</v>
       </c>
       <c r="F111" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G111" t="s">
-        <v>258</v>
+        <v>168</v>
       </c>
       <c r="H111" t="s">
         <v>16</v>
       </c>
       <c r="I111" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K111">
         <v>100</v>
       </c>
       <c r="L111">
-        <v>86.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.25">
@@ -5098,22 +5134,22 @@
         <v>12</v>
       </c>
       <c r="B112">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C112">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D112" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="E112" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="F112" t="s">
         <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H112" t="s">
         <v>16</v>
@@ -5125,7 +5161,7 @@
         <v>100</v>
       </c>
       <c r="L112">
-        <v>83.2</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
@@ -5133,34 +5169,34 @@
         <v>18</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C113">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="E113" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="F113" t="s">
         <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H113" t="s">
         <v>16</v>
       </c>
       <c r="I113" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K113">
         <v>100</v>
       </c>
       <c r="L113">
-        <v>83.2</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
@@ -5168,34 +5204,34 @@
         <v>20</v>
       </c>
       <c r="B114">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C114">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D114" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="E114" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H114" t="s">
         <v>16</v>
       </c>
       <c r="I114" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K114">
         <v>100</v>
       </c>
       <c r="L114">
-        <v>83.2</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
@@ -5203,34 +5239,34 @@
         <v>21</v>
       </c>
       <c r="B115">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C115">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="D115" t="s">
         <v>22</v>
       </c>
       <c r="E115" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="F115" t="s">
         <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H115" t="s">
         <v>16</v>
       </c>
       <c r="I115" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K115">
         <v>100</v>
       </c>
       <c r="L115">
-        <v>83.2</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
@@ -5238,22 +5274,22 @@
         <v>23</v>
       </c>
       <c r="B116">
-        <v>480</v>
+        <v>546</v>
       </c>
       <c r="C116">
-        <v>488</v>
+        <v>546</v>
       </c>
       <c r="D116" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E116" t="s">
-        <v>167</v>
+        <v>108</v>
       </c>
       <c r="F116" t="s">
         <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H116" t="s">
         <v>16</v>
@@ -5265,7 +5301,7 @@
         <v>100</v>
       </c>
       <c r="L116">
-        <v>83.2</v>
+        <v>109.2</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
@@ -5273,22 +5309,22 @@
         <v>12</v>
       </c>
       <c r="B117">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C117">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E117" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F117" t="s">
         <v>25</v>
       </c>
       <c r="G117" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
@@ -5296,11 +5332,14 @@
       <c r="I117" t="s">
         <v>229</v>
       </c>
+      <c r="J117" t="s">
+        <v>112</v>
+      </c>
       <c r="K117">
         <v>100</v>
       </c>
       <c r="L117">
-        <v>98</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
@@ -5308,34 +5347,34 @@
         <v>18</v>
       </c>
       <c r="B118">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E118" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F118" t="s">
         <v>25</v>
       </c>
       <c r="G118" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H118" t="s">
         <v>16</v>
       </c>
       <c r="I118" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K118">
         <v>100</v>
       </c>
       <c r="L118">
-        <v>98</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
@@ -5343,34 +5382,34 @@
         <v>20</v>
       </c>
       <c r="B119">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C119">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D119" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="E119" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F119" t="s">
         <v>25</v>
       </c>
       <c r="G119" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H119" t="s">
         <v>16</v>
       </c>
       <c r="I119" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K119">
         <v>100</v>
       </c>
       <c r="L119">
-        <v>98</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
@@ -5378,34 +5417,34 @@
         <v>21</v>
       </c>
       <c r="B120">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="C120">
-        <v>91</v>
+        <v>49</v>
       </c>
       <c r="D120" t="s">
         <v>22</v>
       </c>
       <c r="E120" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F120" t="s">
         <v>25</v>
       </c>
       <c r="G120" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H120" t="s">
         <v>16</v>
       </c>
       <c r="I120" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K120">
         <v>100</v>
       </c>
       <c r="L120">
-        <v>98</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
@@ -5413,22 +5452,22 @@
         <v>23</v>
       </c>
       <c r="B121">
-        <v>720</v>
+        <v>351</v>
       </c>
       <c r="C121">
-        <v>733</v>
+        <v>416</v>
       </c>
       <c r="D121" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="E121" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F121" t="s">
         <v>25</v>
       </c>
       <c r="G121" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
@@ -5440,7 +5479,7 @@
         <v>100</v>
       </c>
       <c r="L121">
-        <v>98</v>
+        <v>112.7</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
@@ -5448,22 +5487,22 @@
         <v>12</v>
       </c>
       <c r="B122">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="E122" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F122" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G122" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H122" t="s">
         <v>16</v>
@@ -5472,13 +5511,13 @@
         <v>17</v>
       </c>
       <c r="J122" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="K122">
         <v>100</v>
       </c>
       <c r="L122">
-        <v>4.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
@@ -5489,34 +5528,31 @@
         <v>5</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D123" t="s">
-        <v>105</v>
+        <v>37</v>
       </c>
       <c r="E123" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F123" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G123" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H123" t="s">
         <v>16</v>
       </c>
       <c r="I123" t="s">
-        <v>229</v>
-      </c>
-      <c r="J123" t="s">
-        <v>172</v>
+        <v>17</v>
       </c>
       <c r="K123">
         <v>100</v>
       </c>
       <c r="L123">
-        <v>4.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
@@ -5527,19 +5563,19 @@
         <v>30</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>259</v>
+        <v>47</v>
       </c>
       <c r="E124" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F124" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G124" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H124" t="s">
         <v>16</v>
@@ -5547,14 +5583,11 @@
       <c r="I124" t="s">
         <v>17</v>
       </c>
-      <c r="J124" t="s">
-        <v>173</v>
-      </c>
       <c r="K124">
         <v>100</v>
       </c>
       <c r="L124">
-        <v>4.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
@@ -5562,22 +5595,22 @@
         <v>21</v>
       </c>
       <c r="B125">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="D125" t="s">
         <v>22</v>
       </c>
       <c r="E125" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F125" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G125" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H125" t="s">
         <v>16</v>
@@ -5585,14 +5618,11 @@
       <c r="I125" t="s">
         <v>17</v>
       </c>
-      <c r="J125" t="s">
-        <v>174</v>
-      </c>
       <c r="K125">
         <v>100</v>
       </c>
       <c r="L125">
-        <v>4.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
@@ -5600,34 +5630,34 @@
         <v>23</v>
       </c>
       <c r="B126">
-        <v>720</v>
+        <v>603</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="D126" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E126" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F126" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G126" t="s">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="H126" t="s">
         <v>16</v>
       </c>
       <c r="I126" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K126">
         <v>100</v>
       </c>
       <c r="L126">
-        <v>4.7</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
@@ -5635,19 +5665,19 @@
         <v>12</v>
       </c>
       <c r="B127">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C127">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E127" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F127" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G127" t="s">
         <v>109</v>
@@ -5656,13 +5686,16 @@
         <v>16</v>
       </c>
       <c r="I127" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J127" t="s">
+        <v>118</v>
       </c>
       <c r="K127">
         <v>100</v>
       </c>
       <c r="L127">
-        <v>109.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
@@ -5670,19 +5703,19 @@
         <v>18</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C128">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F128" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G128" t="s">
         <v>109</v>
@@ -5691,13 +5724,13 @@
         <v>16</v>
       </c>
       <c r="I128" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K128">
         <v>100</v>
       </c>
       <c r="L128">
-        <v>109.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.25">
@@ -5705,19 +5738,19 @@
         <v>20</v>
       </c>
       <c r="B129">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C129">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D129" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E129" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F129" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G129" t="s">
         <v>109</v>
@@ -5726,13 +5759,13 @@
         <v>16</v>
       </c>
       <c r="I129" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K129">
         <v>100</v>
       </c>
       <c r="L129">
-        <v>109.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.25">
@@ -5740,19 +5773,19 @@
         <v>21</v>
       </c>
       <c r="B130">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C130">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="D130" t="s">
         <v>22</v>
       </c>
       <c r="E130" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F130" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G130" t="s">
         <v>109</v>
@@ -5767,7 +5800,7 @@
         <v>100</v>
       </c>
       <c r="L130">
-        <v>109.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.25">
@@ -5775,19 +5808,19 @@
         <v>23</v>
       </c>
       <c r="B131">
-        <v>546</v>
+        <v>563</v>
       </c>
       <c r="C131">
-        <v>546</v>
+        <v>0</v>
       </c>
       <c r="D131" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E131" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F131" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G131" t="s">
         <v>109</v>
@@ -5796,13 +5829,13 @@
         <v>16</v>
       </c>
       <c r="I131" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K131">
         <v>100</v>
       </c>
       <c r="L131">
-        <v>109.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.25">
@@ -5810,22 +5843,22 @@
         <v>12</v>
       </c>
       <c r="B132">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C132">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D132" t="s">
-        <v>110</v>
+        <v>139</v>
       </c>
       <c r="E132" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F132" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G132" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H132" t="s">
         <v>16</v>
@@ -5833,14 +5866,11 @@
       <c r="I132" t="s">
         <v>229</v>
       </c>
-      <c r="J132" t="s">
-        <v>112</v>
-      </c>
       <c r="K132">
         <v>100</v>
       </c>
       <c r="L132">
-        <v>112.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.25">
@@ -5851,19 +5881,19 @@
         <v>3</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E133" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F133" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G133" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H133" t="s">
         <v>16</v>
@@ -5875,7 +5905,7 @@
         <v>100</v>
       </c>
       <c r="L133">
-        <v>112.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.25">
@@ -5883,34 +5913,34 @@
         <v>20</v>
       </c>
       <c r="B134">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C134">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D134" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="E134" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F134" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G134" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H134" t="s">
         <v>16</v>
       </c>
       <c r="I134" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K134">
         <v>100</v>
       </c>
       <c r="L134">
-        <v>112.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.25">
@@ -5918,34 +5948,34 @@
         <v>21</v>
       </c>
       <c r="B135">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="C135">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="D135" t="s">
-        <v>22</v>
+        <v>143</v>
       </c>
       <c r="E135" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F135" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G135" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H135" t="s">
         <v>16</v>
       </c>
       <c r="I135" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K135">
         <v>100</v>
       </c>
       <c r="L135">
-        <v>112.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.25">
@@ -5953,22 +5983,22 @@
         <v>23</v>
       </c>
       <c r="B136">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="C136">
-        <v>416</v>
+        <v>319</v>
       </c>
       <c r="D136" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E136" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="F136" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G136" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H136" t="s">
         <v>16</v>
@@ -5980,7 +6010,7 @@
         <v>100</v>
       </c>
       <c r="L136">
-        <v>112.7</v>
+        <v>108.4</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.25">
@@ -5988,37 +6018,34 @@
         <v>12</v>
       </c>
       <c r="B137">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C137">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D137" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="E137" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="F137" t="s">
         <v>25</v>
       </c>
       <c r="G137" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H137" t="s">
         <v>16</v>
       </c>
       <c r="I137" t="s">
-        <v>17</v>
-      </c>
-      <c r="J137" t="s">
-        <v>117</v>
+        <v>229</v>
       </c>
       <c r="K137">
         <v>100</v>
       </c>
       <c r="L137">
-        <v>62.5</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.25">
@@ -6026,34 +6053,34 @@
         <v>18</v>
       </c>
       <c r="B138">
+        <v>4</v>
+      </c>
+      <c r="C138">
         <v>5</v>
       </c>
-      <c r="C138">
-        <v>4</v>
-      </c>
       <c r="D138" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E138" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="F138" t="s">
         <v>25</v>
       </c>
       <c r="G138" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H138" t="s">
         <v>16</v>
       </c>
       <c r="I138" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K138">
         <v>100</v>
       </c>
       <c r="L138">
-        <v>62.5</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.25">
@@ -6061,34 +6088,34 @@
         <v>20</v>
       </c>
       <c r="B139">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="C139">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="D139" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E139" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="F139" t="s">
         <v>25</v>
       </c>
       <c r="G139" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H139" t="s">
         <v>16</v>
       </c>
       <c r="I139" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K139">
         <v>100</v>
       </c>
       <c r="L139">
-        <v>62.5</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.25">
@@ -6096,34 +6123,34 @@
         <v>21</v>
       </c>
       <c r="B140">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C140">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="D140" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="E140" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="F140" t="s">
         <v>25</v>
       </c>
       <c r="G140" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H140" t="s">
         <v>16</v>
       </c>
       <c r="I140" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K140">
         <v>100</v>
       </c>
       <c r="L140">
-        <v>62.5</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.25">
@@ -6131,22 +6158,22 @@
         <v>23</v>
       </c>
       <c r="B141">
-        <v>603</v>
+        <v>399</v>
       </c>
       <c r="C141">
-        <v>603</v>
+        <v>421</v>
       </c>
       <c r="D141" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E141" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="F141" t="s">
         <v>25</v>
       </c>
       <c r="G141" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H141" t="s">
         <v>16</v>
@@ -6158,7 +6185,7 @@
         <v>100</v>
       </c>
       <c r="L141">
-        <v>62.5</v>
+        <v>101.2</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.25">
@@ -6166,37 +6193,34 @@
         <v>12</v>
       </c>
       <c r="B142">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="D142" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E142" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="F142" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G142" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H142" t="s">
         <v>16</v>
       </c>
       <c r="I142" t="s">
-        <v>17</v>
-      </c>
-      <c r="J142" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="K142">
         <v>100</v>
       </c>
       <c r="L142">
-        <v>0.3</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.25">
@@ -6204,34 +6228,34 @@
         <v>18</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D143" t="s">
-        <v>19</v>
+        <v>148</v>
       </c>
       <c r="E143" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="F143" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G143" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H143" t="s">
         <v>16</v>
       </c>
       <c r="I143" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K143">
         <v>100</v>
       </c>
       <c r="L143">
-        <v>0.3</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.25">
@@ -6239,34 +6263,34 @@
         <v>20</v>
       </c>
       <c r="B144">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="D144" t="s">
-        <v>19</v>
+        <v>149</v>
       </c>
       <c r="E144" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="F144" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G144" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H144" t="s">
         <v>16</v>
       </c>
       <c r="I144" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K144">
         <v>100</v>
       </c>
       <c r="L144">
-        <v>0.3</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.25">
@@ -6274,34 +6298,34 @@
         <v>21</v>
       </c>
       <c r="B145">
-        <v>68</v>
+        <v>120</v>
       </c>
       <c r="C145">
-        <v>2</v>
+        <v>148</v>
       </c>
       <c r="D145" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="E145" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="F145" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G145" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H145" t="s">
         <v>16</v>
       </c>
       <c r="I145" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K145">
         <v>100</v>
       </c>
       <c r="L145">
-        <v>0.3</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.25">
@@ -6309,34 +6333,34 @@
         <v>23</v>
       </c>
       <c r="B146">
-        <v>563</v>
+        <v>399</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="D146" t="s">
-        <v>19</v>
+        <v>113</v>
       </c>
       <c r="E146" t="s">
-        <v>102</v>
+        <v>147</v>
       </c>
       <c r="F146" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G146" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="H146" t="s">
         <v>16</v>
       </c>
       <c r="I146" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K146">
         <v>100</v>
       </c>
       <c r="L146">
-        <v>0.3</v>
+        <v>120.4</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.25">
@@ -6344,19 +6368,19 @@
         <v>12</v>
       </c>
       <c r="B147">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C147">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D147" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E147" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F147" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G147" t="s">
         <v>141</v>
@@ -6365,13 +6389,16 @@
         <v>16</v>
       </c>
       <c r="I147" t="s">
-        <v>229</v>
+        <v>231</v>
+      </c>
+      <c r="J147" t="s">
+        <v>152</v>
       </c>
       <c r="K147">
         <v>100</v>
       </c>
       <c r="L147">
-        <v>108.4</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.25">
@@ -6379,19 +6406,19 @@
         <v>18</v>
       </c>
       <c r="B148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C148">
         <v>2</v>
       </c>
       <c r="D148" t="s">
-        <v>142</v>
+        <v>27</v>
       </c>
       <c r="E148" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F148" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G148" t="s">
         <v>141</v>
@@ -6402,11 +6429,14 @@
       <c r="I148" t="s">
         <v>17</v>
       </c>
+      <c r="J148" t="s">
+        <v>153</v>
+      </c>
       <c r="K148">
         <v>100</v>
       </c>
       <c r="L148">
-        <v>108.4</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.25">
@@ -6414,19 +6444,19 @@
         <v>20</v>
       </c>
       <c r="B149">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C149">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="D149" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="E149" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F149" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G149" t="s">
         <v>141</v>
@@ -6435,13 +6465,16 @@
         <v>16</v>
       </c>
       <c r="I149" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J149" t="s">
+        <v>155</v>
       </c>
       <c r="K149">
         <v>100</v>
       </c>
       <c r="L149">
-        <v>108.4</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.25">
@@ -6449,19 +6482,19 @@
         <v>21</v>
       </c>
       <c r="B150">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C150">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="D150" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="E150" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F150" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G150" t="s">
         <v>141</v>
@@ -6470,13 +6503,16 @@
         <v>16</v>
       </c>
       <c r="I150" t="s">
-        <v>229</v>
+        <v>231</v>
+      </c>
+      <c r="J150" t="s">
+        <v>157</v>
       </c>
       <c r="K150">
         <v>100</v>
       </c>
       <c r="L150">
-        <v>108.4</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.25">
@@ -6484,19 +6520,19 @@
         <v>23</v>
       </c>
       <c r="B151">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="C151">
-        <v>319</v>
+        <v>421</v>
       </c>
       <c r="D151" t="s">
         <v>113</v>
       </c>
       <c r="E151" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F151" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G151" t="s">
         <v>141</v>
@@ -6505,13 +6541,16 @@
         <v>16</v>
       </c>
       <c r="I151" t="s">
-        <v>229</v>
+        <v>231</v>
+      </c>
+      <c r="J151" t="s">
+        <v>158</v>
       </c>
       <c r="K151">
         <v>100</v>
       </c>
       <c r="L151">
-        <v>108.4</v>
+        <v>82.9</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.25">
@@ -6522,16 +6561,16 @@
         <v>37</v>
       </c>
       <c r="C152">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D152" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E152" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F152" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G152" t="s">
         <v>141</v>
@@ -6540,13 +6579,16 @@
         <v>16</v>
       </c>
       <c r="I152" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J152" t="s">
+        <v>160</v>
       </c>
       <c r="K152">
         <v>100</v>
       </c>
       <c r="L152">
-        <v>101.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.25">
@@ -6557,16 +6599,16 @@
         <v>4</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="E153" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F153" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G153" t="s">
         <v>141</v>
@@ -6575,13 +6617,13 @@
         <v>16</v>
       </c>
       <c r="I153" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K153">
         <v>100</v>
       </c>
       <c r="L153">
-        <v>101.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.25">
@@ -6592,16 +6634,16 @@
         <v>59</v>
       </c>
       <c r="C154">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E154" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F154" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G154" t="s">
         <v>141</v>
@@ -6610,13 +6652,13 @@
         <v>16</v>
       </c>
       <c r="I154" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K154">
         <v>100</v>
       </c>
       <c r="L154">
-        <v>101.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.25">
@@ -6627,16 +6669,16 @@
         <v>120</v>
       </c>
       <c r="C155">
-        <v>132</v>
+        <v>2</v>
       </c>
       <c r="D155" t="s">
-        <v>146</v>
+        <v>22</v>
       </c>
       <c r="E155" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F155" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G155" t="s">
         <v>141</v>
@@ -6645,13 +6687,13 @@
         <v>16</v>
       </c>
       <c r="I155" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K155">
         <v>100</v>
       </c>
       <c r="L155">
-        <v>101.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.25">
@@ -6662,16 +6704,16 @@
         <v>399</v>
       </c>
       <c r="C156">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="D156" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E156" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="F156" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G156" t="s">
         <v>141</v>
@@ -6680,13 +6722,13 @@
         <v>16</v>
       </c>
       <c r="I156" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K156">
         <v>100</v>
       </c>
       <c r="L156">
-        <v>101.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.25">
@@ -6697,16 +6739,16 @@
         <v>37</v>
       </c>
       <c r="C157">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="D157" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="E157" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F157" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G157" t="s">
         <v>141</v>
@@ -6717,11 +6759,14 @@
       <c r="I157" t="s">
         <v>229</v>
       </c>
+      <c r="J157" t="s">
+        <v>162</v>
+      </c>
       <c r="K157">
         <v>100</v>
       </c>
       <c r="L157">
-        <v>120.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.25">
@@ -6732,16 +6777,16 @@
         <v>4</v>
       </c>
       <c r="C158">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="E158" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F158" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G158" t="s">
         <v>141</v>
@@ -6750,13 +6795,16 @@
         <v>16</v>
       </c>
       <c r="I158" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J158" t="s">
+        <v>163</v>
       </c>
       <c r="K158">
         <v>100</v>
       </c>
       <c r="L158">
-        <v>120.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.25">
@@ -6767,16 +6815,16 @@
         <v>59</v>
       </c>
       <c r="C159">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E159" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F159" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G159" t="s">
         <v>141</v>
@@ -6787,11 +6835,14 @@
       <c r="I159" t="s">
         <v>229</v>
       </c>
+      <c r="J159" t="s">
+        <v>165</v>
+      </c>
       <c r="K159">
         <v>100</v>
       </c>
       <c r="L159">
-        <v>120.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.25">
@@ -6802,16 +6853,16 @@
         <v>120</v>
       </c>
       <c r="C160">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="D160" t="s">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="E160" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F160" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G160" t="s">
         <v>141</v>
@@ -6820,13 +6871,16 @@
         <v>16</v>
       </c>
       <c r="I160" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J160" t="s">
+        <v>166</v>
       </c>
       <c r="K160">
         <v>100</v>
       </c>
       <c r="L160">
-        <v>120.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.25">
@@ -6837,16 +6891,16 @@
         <v>399</v>
       </c>
       <c r="C161">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E161" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="F161" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G161" t="s">
         <v>141</v>
@@ -6855,13 +6909,13 @@
         <v>16</v>
       </c>
       <c r="I161" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K161">
         <v>100</v>
       </c>
       <c r="L161">
-        <v>120.4</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.25">
@@ -6869,37 +6923,34 @@
         <v>12</v>
       </c>
       <c r="B162">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C162">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D162" t="s">
-        <v>149</v>
+        <v>260</v>
       </c>
       <c r="E162" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="F162" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H162" t="s">
         <v>16</v>
       </c>
       <c r="I162" t="s">
-        <v>231</v>
-      </c>
-      <c r="J162" t="s">
-        <v>152</v>
+        <v>229</v>
       </c>
       <c r="K162">
         <v>100</v>
       </c>
       <c r="L162">
-        <v>82.9</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.25">
@@ -6907,37 +6958,34 @@
         <v>18</v>
       </c>
       <c r="B163">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D163" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E163" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="F163" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H163" t="s">
         <v>16</v>
       </c>
       <c r="I163" t="s">
-        <v>17</v>
-      </c>
-      <c r="J163" t="s">
-        <v>153</v>
+        <v>229</v>
       </c>
       <c r="K163">
         <v>100</v>
       </c>
       <c r="L163">
-        <v>82.9</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.25">
@@ -6945,37 +6993,34 @@
         <v>20</v>
       </c>
       <c r="B164">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C164">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D164" t="s">
-        <v>154</v>
+        <v>41</v>
       </c>
       <c r="E164" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="F164" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H164" t="s">
         <v>16</v>
       </c>
       <c r="I164" t="s">
-        <v>17</v>
-      </c>
-      <c r="J164" t="s">
-        <v>155</v>
+        <v>229</v>
       </c>
       <c r="K164">
         <v>100</v>
       </c>
       <c r="L164">
-        <v>82.9</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.25">
@@ -6983,37 +7028,34 @@
         <v>21</v>
       </c>
       <c r="B165">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C165">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="D165" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="E165" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="F165" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G165" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
       </c>
       <c r="I165" t="s">
-        <v>231</v>
-      </c>
-      <c r="J165" t="s">
-        <v>157</v>
+        <v>229</v>
       </c>
       <c r="K165">
         <v>100</v>
       </c>
       <c r="L165">
-        <v>82.9</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.25">
@@ -7021,37 +7063,34 @@
         <v>23</v>
       </c>
       <c r="B166">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="C166">
-        <v>421</v>
+        <v>1205</v>
       </c>
       <c r="D166" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="E166" t="s">
-        <v>151</v>
+        <v>261</v>
       </c>
       <c r="F166" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G166" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H166" t="s">
         <v>16</v>
       </c>
       <c r="I166" t="s">
-        <v>231</v>
-      </c>
-      <c r="J166" t="s">
-        <v>158</v>
+        <v>229</v>
       </c>
       <c r="K166">
         <v>100</v>
       </c>
       <c r="L166">
-        <v>82.9</v>
+        <v>98.6</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.25">
@@ -7059,7 +7098,7 @@
         <v>12</v>
       </c>
       <c r="B167">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -7074,7 +7113,7 @@
         <v>103</v>
       </c>
       <c r="G167" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H167" t="s">
         <v>16</v>
@@ -7082,14 +7121,11 @@
       <c r="I167" t="s">
         <v>17</v>
       </c>
-      <c r="J167" t="s">
-        <v>160</v>
-      </c>
       <c r="K167">
         <v>100</v>
       </c>
       <c r="L167">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.25">
@@ -7097,7 +7133,7 @@
         <v>18</v>
       </c>
       <c r="B168">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -7112,7 +7148,7 @@
         <v>103</v>
       </c>
       <c r="G168" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H168" t="s">
         <v>16</v>
@@ -7124,7 +7160,7 @@
         <v>100</v>
       </c>
       <c r="L168">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.25">
@@ -7132,13 +7168,13 @@
         <v>20</v>
       </c>
       <c r="B169">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>19</v>
+        <v>259</v>
       </c>
       <c r="E169" t="s">
         <v>159</v>
@@ -7147,7 +7183,7 @@
         <v>103</v>
       </c>
       <c r="G169" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H169" t="s">
         <v>16</v>
@@ -7159,7 +7195,7 @@
         <v>100</v>
       </c>
       <c r="L169">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.25">
@@ -7167,10 +7203,10 @@
         <v>21</v>
       </c>
       <c r="B170">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="C170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D170" t="s">
         <v>22</v>
@@ -7182,7 +7218,7 @@
         <v>103</v>
       </c>
       <c r="G170" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H170" t="s">
         <v>16</v>
@@ -7194,7 +7230,7 @@
         <v>100</v>
       </c>
       <c r="L170">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.25">
@@ -7202,7 +7238,7 @@
         <v>23</v>
       </c>
       <c r="B171">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -7217,7 +7253,7 @@
         <v>103</v>
       </c>
       <c r="G171" t="s">
-        <v>141</v>
+        <v>262</v>
       </c>
       <c r="H171" t="s">
         <v>16</v>
@@ -7229,7 +7265,7 @@
         <v>100</v>
       </c>
       <c r="L171">
-        <v>0.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.25">
@@ -7237,22 +7273,22 @@
         <v>12</v>
       </c>
       <c r="B172">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C172">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D172" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="E172" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="F172" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G172" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H172" t="s">
         <v>16</v>
@@ -7260,14 +7296,11 @@
       <c r="I172" t="s">
         <v>229</v>
       </c>
-      <c r="J172" t="s">
-        <v>162</v>
-      </c>
       <c r="K172">
         <v>100</v>
       </c>
       <c r="L172">
-        <v>7.1</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.25">
@@ -7275,7 +7308,7 @@
         <v>18</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -7284,13 +7317,13 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="F173" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G173" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H173" t="s">
         <v>16</v>
@@ -7298,14 +7331,11 @@
       <c r="I173" t="s">
         <v>17</v>
       </c>
-      <c r="J173" t="s">
-        <v>163</v>
-      </c>
       <c r="K173">
         <v>100</v>
       </c>
       <c r="L173">
-        <v>7.1</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.25">
@@ -7313,22 +7343,22 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="C174">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D174" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E174" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="F174" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G174" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H174" t="s">
         <v>16</v>
@@ -7336,14 +7366,11 @@
       <c r="I174" t="s">
         <v>229</v>
       </c>
-      <c r="J174" t="s">
-        <v>165</v>
-      </c>
       <c r="K174">
         <v>100</v>
       </c>
       <c r="L174">
-        <v>7.1</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="175" spans="1:12" x14ac:dyDescent="0.25">
@@ -7351,37 +7378,34 @@
         <v>21</v>
       </c>
       <c r="B175">
-        <v>120</v>
+        <v>28</v>
       </c>
       <c r="C175">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D175" t="s">
         <v>22</v>
       </c>
       <c r="E175" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="F175" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G175" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H175" t="s">
         <v>16</v>
       </c>
       <c r="I175" t="s">
-        <v>17</v>
-      </c>
-      <c r="J175" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
       <c r="K175">
         <v>100</v>
       </c>
       <c r="L175">
-        <v>7.1</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.25">
@@ -7389,34 +7413,34 @@
         <v>23</v>
       </c>
       <c r="B176">
-        <v>399</v>
+        <v>320</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D176" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="E176" t="s">
-        <v>133</v>
+        <v>263</v>
       </c>
       <c r="F176" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s">
-        <v>141</v>
+        <v>264</v>
       </c>
       <c r="H176" t="s">
         <v>16</v>
       </c>
       <c r="I176" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K176">
         <v>100</v>
       </c>
       <c r="L176">
-        <v>7.1</v>
+        <v>94.8</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.25">
@@ -7424,22 +7448,22 @@
         <v>12</v>
       </c>
       <c r="B177">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C177">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D177" t="s">
-        <v>260</v>
+        <v>183</v>
       </c>
       <c r="E177" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F177" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G177" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H177" t="s">
         <v>16</v>
@@ -7451,7 +7475,7 @@
         <v>100</v>
       </c>
       <c r="L177">
-        <v>98.6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.25">
@@ -7459,22 +7483,22 @@
         <v>18</v>
       </c>
       <c r="B178">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C178">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D178" t="s">
         <v>41</v>
       </c>
       <c r="E178" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F178" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G178" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H178" t="s">
         <v>16</v>
@@ -7486,7 +7510,7 @@
         <v>100</v>
       </c>
       <c r="L178">
-        <v>98.6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.25">
@@ -7494,34 +7518,34 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C179">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D179" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="E179" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F179" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G179" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H179" t="s">
         <v>16</v>
       </c>
       <c r="I179" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K179">
         <v>100</v>
       </c>
       <c r="L179">
-        <v>98.6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.25">
@@ -7529,34 +7553,34 @@
         <v>21</v>
       </c>
       <c r="B180">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C180">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D180" t="s">
-        <v>113</v>
+        <v>22</v>
       </c>
       <c r="E180" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F180" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G180" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H180" t="s">
         <v>16</v>
       </c>
       <c r="I180" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K180">
         <v>100</v>
       </c>
       <c r="L180">
-        <v>98.6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.25">
@@ -7564,22 +7588,22 @@
         <v>23</v>
       </c>
       <c r="B181">
-        <v>1200</v>
+        <v>480</v>
       </c>
       <c r="C181">
-        <v>1205</v>
+        <v>509</v>
       </c>
       <c r="D181" t="s">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="E181" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F181" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G181" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H181" t="s">
         <v>16</v>
@@ -7591,7 +7615,7 @@
         <v>100</v>
       </c>
       <c r="L181">
-        <v>98.6</v>
+        <v>90</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.25">
@@ -7599,7 +7623,7 @@
         <v>12</v>
       </c>
       <c r="B182">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C182">
         <v>0</v>
@@ -7611,10 +7635,10 @@
         <v>159</v>
       </c>
       <c r="F182" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G182" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H182" t="s">
         <v>16</v>
@@ -7626,7 +7650,7 @@
         <v>100</v>
       </c>
       <c r="L182">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.25">
@@ -7634,7 +7658,7 @@
         <v>18</v>
       </c>
       <c r="B183">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -7646,10 +7670,10 @@
         <v>159</v>
       </c>
       <c r="F183" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G183" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H183" t="s">
         <v>16</v>
@@ -7661,7 +7685,7 @@
         <v>100</v>
       </c>
       <c r="L183">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.25">
@@ -7669,22 +7693,22 @@
         <v>20</v>
       </c>
       <c r="B184">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
       <c r="E184" t="s">
         <v>159</v>
       </c>
       <c r="F184" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G184" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H184" t="s">
         <v>16</v>
@@ -7696,7 +7720,7 @@
         <v>100</v>
       </c>
       <c r="L184">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.25">
@@ -7704,10 +7728,10 @@
         <v>21</v>
       </c>
       <c r="B185">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="C185">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D185" t="s">
         <v>22</v>
@@ -7716,10 +7740,10 @@
         <v>159</v>
       </c>
       <c r="F185" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G185" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H185" t="s">
         <v>16</v>
@@ -7731,7 +7755,7 @@
         <v>100</v>
       </c>
       <c r="L185">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.25">
@@ -7739,7 +7763,7 @@
         <v>23</v>
       </c>
       <c r="B186">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7751,10 +7775,10 @@
         <v>159</v>
       </c>
       <c r="F186" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G186" t="s">
-        <v>262</v>
+        <v>214</v>
       </c>
       <c r="H186" t="s">
         <v>16</v>
@@ -7766,7 +7790,7 @@
         <v>100</v>
       </c>
       <c r="L186">
-        <v>1.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.25">
@@ -7774,34 +7798,37 @@
         <v>12</v>
       </c>
       <c r="B187">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C187">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
       <c r="E187" t="s">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="F187" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G187" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H187" t="s">
         <v>16</v>
       </c>
       <c r="I187" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J187" t="s">
+        <v>216</v>
       </c>
       <c r="K187">
         <v>100</v>
       </c>
       <c r="L187">
-        <v>94.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.25">
@@ -7809,22 +7836,22 @@
         <v>18</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E188" t="s">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="F188" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G188" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H188" t="s">
         <v>16</v>
@@ -7832,11 +7859,14 @@
       <c r="I188" t="s">
         <v>17</v>
       </c>
+      <c r="J188" t="s">
+        <v>217</v>
+      </c>
       <c r="K188">
         <v>100</v>
       </c>
       <c r="L188">
-        <v>94.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.25">
@@ -7844,34 +7874,37 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C189">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D189" t="s">
-        <v>149</v>
+        <v>27</v>
       </c>
       <c r="E189" t="s">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="F189" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G189" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H189" t="s">
         <v>16</v>
       </c>
       <c r="I189" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J189" t="s">
+        <v>218</v>
       </c>
       <c r="K189">
         <v>100</v>
       </c>
       <c r="L189">
-        <v>94.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.25">
@@ -7879,34 +7912,37 @@
         <v>21</v>
       </c>
       <c r="B190">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C190">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D190" t="s">
         <v>22</v>
       </c>
       <c r="E190" t="s">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="F190" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G190" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H190" t="s">
         <v>16</v>
       </c>
       <c r="I190" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J190" t="s">
+        <v>219</v>
       </c>
       <c r="K190">
         <v>100</v>
       </c>
       <c r="L190">
-        <v>94.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.25">
@@ -7914,34 +7950,34 @@
         <v>23</v>
       </c>
       <c r="B191">
-        <v>320</v>
+        <v>600</v>
       </c>
       <c r="C191">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D191" t="s">
-        <v>107</v>
+        <v>19</v>
       </c>
       <c r="E191" t="s">
-        <v>263</v>
+        <v>102</v>
       </c>
       <c r="F191" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G191" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H191" t="s">
         <v>16</v>
       </c>
       <c r="I191" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K191">
         <v>100</v>
       </c>
       <c r="L191">
-        <v>94.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.25">
@@ -7949,22 +7985,22 @@
         <v>12</v>
       </c>
       <c r="B192">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C192">
         <v>12</v>
       </c>
       <c r="D192" t="s">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="E192" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F192" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G192" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H192" t="s">
         <v>16</v>
@@ -7972,11 +8008,14 @@
       <c r="I192" t="s">
         <v>229</v>
       </c>
+      <c r="J192" t="s">
+        <v>221</v>
+      </c>
       <c r="K192">
         <v>100</v>
       </c>
       <c r="L192">
-        <v>90</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.25">
@@ -7984,34 +8023,37 @@
         <v>18</v>
       </c>
       <c r="B193">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E193" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F193" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G193" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H193" t="s">
         <v>16</v>
       </c>
       <c r="I193" t="s">
-        <v>229</v>
+        <v>17</v>
+      </c>
+      <c r="J193" t="s">
+        <v>222</v>
       </c>
       <c r="K193">
         <v>100</v>
       </c>
       <c r="L193">
-        <v>90</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.25">
@@ -8019,34 +8061,37 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C194">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D194" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="E194" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F194" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G194" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H194" t="s">
         <v>16</v>
       </c>
       <c r="I194" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="J194" t="s">
+        <v>224</v>
       </c>
       <c r="K194">
         <v>100</v>
       </c>
       <c r="L194">
-        <v>90</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.25">
@@ -8054,34 +8099,37 @@
         <v>21</v>
       </c>
       <c r="B195">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C195">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D195" t="s">
         <v>22</v>
       </c>
       <c r="E195" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F195" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G195" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H195" t="s">
         <v>16</v>
       </c>
       <c r="I195" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J195" t="s">
+        <v>225</v>
       </c>
       <c r="K195">
         <v>100</v>
       </c>
       <c r="L195">
-        <v>90</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.25">
@@ -8089,34 +8137,34 @@
         <v>23</v>
       </c>
       <c r="B196">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="C196">
-        <v>509</v>
+        <v>0</v>
       </c>
       <c r="D196" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="E196" t="s">
-        <v>265</v>
+        <v>133</v>
       </c>
       <c r="F196" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G196" t="s">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="H196" t="s">
         <v>16</v>
       </c>
       <c r="I196" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K196">
         <v>100</v>
       </c>
       <c r="L196">
-        <v>90</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.25">
@@ -8124,34 +8172,34 @@
         <v>12</v>
       </c>
       <c r="B197">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D197" t="s">
-        <v>19</v>
+        <v>75</v>
       </c>
       <c r="E197" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F197" t="s">
         <v>14</v>
       </c>
       <c r="G197" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H197" t="s">
         <v>16</v>
       </c>
       <c r="I197" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K197">
         <v>100</v>
       </c>
       <c r="L197">
-        <v>0.1</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.25">
@@ -8159,34 +8207,34 @@
         <v>18</v>
       </c>
       <c r="B198">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D198" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E198" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F198" t="s">
         <v>14</v>
       </c>
       <c r="G198" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H198" t="s">
         <v>16</v>
       </c>
       <c r="I198" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K198">
         <v>100</v>
       </c>
       <c r="L198">
-        <v>0.1</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.25">
@@ -8194,22 +8242,22 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C199">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D199" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="E199" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F199" t="s">
         <v>14</v>
       </c>
       <c r="G199" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H199" t="s">
         <v>16</v>
@@ -8221,7 +8269,7 @@
         <v>100</v>
       </c>
       <c r="L199">
-        <v>0.1</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.25">
@@ -8229,34 +8277,34 @@
         <v>21</v>
       </c>
       <c r="B200">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C200">
-        <v>4</v>
+        <v>105</v>
       </c>
       <c r="D200" t="s">
-        <v>22</v>
+        <v>178</v>
       </c>
       <c r="E200" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F200" t="s">
         <v>14</v>
       </c>
       <c r="G200" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H200" t="s">
         <v>16</v>
       </c>
       <c r="I200" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K200">
         <v>100</v>
       </c>
       <c r="L200">
-        <v>0.1</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.25">
@@ -8264,34 +8312,34 @@
         <v>23</v>
       </c>
       <c r="B201">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>1201</v>
       </c>
       <c r="D201" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E201" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="F201" t="s">
         <v>14</v>
       </c>
       <c r="G201" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H201" t="s">
         <v>16</v>
       </c>
       <c r="I201" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K201">
         <v>100</v>
       </c>
       <c r="L201">
-        <v>0.1</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.25">
@@ -8299,22 +8347,22 @@
         <v>12</v>
       </c>
       <c r="B202">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D202" t="s">
-        <v>215</v>
+        <v>19</v>
       </c>
       <c r="E202" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F202" t="s">
         <v>103</v>
       </c>
       <c r="G202" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H202" t="s">
         <v>16</v>
@@ -8323,13 +8371,13 @@
         <v>17</v>
       </c>
       <c r="J202" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="K202">
         <v>100</v>
       </c>
       <c r="L202">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.25">
@@ -8337,22 +8385,22 @@
         <v>18</v>
       </c>
       <c r="B203">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F203" t="s">
         <v>103</v>
       </c>
       <c r="G203" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H203" t="s">
         <v>16</v>
@@ -8360,14 +8408,11 @@
       <c r="I203" t="s">
         <v>17</v>
       </c>
-      <c r="J203" t="s">
-        <v>217</v>
-      </c>
       <c r="K203">
         <v>100</v>
       </c>
       <c r="L203">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.25">
@@ -8375,22 +8420,22 @@
         <v>20</v>
       </c>
       <c r="B204">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C204">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D204" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E204" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F204" t="s">
         <v>103</v>
       </c>
       <c r="G204" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H204" t="s">
         <v>16</v>
@@ -8398,14 +8443,11 @@
       <c r="I204" t="s">
         <v>17</v>
       </c>
-      <c r="J204" t="s">
-        <v>218</v>
-      </c>
       <c r="K204">
         <v>100</v>
       </c>
       <c r="L204">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.25">
@@ -8413,22 +8455,22 @@
         <v>21</v>
       </c>
       <c r="B205">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C205">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D205" t="s">
         <v>22</v>
       </c>
       <c r="E205" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F205" t="s">
         <v>103</v>
       </c>
       <c r="G205" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H205" t="s">
         <v>16</v>
@@ -8436,14 +8478,11 @@
       <c r="I205" t="s">
         <v>17</v>
       </c>
-      <c r="J205" t="s">
-        <v>219</v>
-      </c>
       <c r="K205">
         <v>100</v>
       </c>
       <c r="L205">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.25">
@@ -8451,7 +8490,7 @@
         <v>23</v>
       </c>
       <c r="B206">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -8460,13 +8499,13 @@
         <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F206" t="s">
         <v>103</v>
       </c>
       <c r="G206" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="H206" t="s">
         <v>16</v>
@@ -8478,7 +8517,7 @@
         <v>100</v>
       </c>
       <c r="L206">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.25">
@@ -8486,37 +8525,37 @@
         <v>12</v>
       </c>
       <c r="B207">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C207">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D207" t="s">
-        <v>220</v>
+        <v>87</v>
       </c>
       <c r="E207" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F207" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G207" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H207" t="s">
         <v>16</v>
       </c>
       <c r="I207" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="J207" t="s">
-        <v>221</v>
+        <v>90</v>
       </c>
       <c r="K207">
         <v>100</v>
       </c>
       <c r="L207">
-        <v>1.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.25">
@@ -8524,22 +8563,22 @@
         <v>18</v>
       </c>
       <c r="B208">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C208">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D208" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E208" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F208" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G208" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H208" t="s">
         <v>16</v>
@@ -8547,14 +8586,11 @@
       <c r="I208" t="s">
         <v>17</v>
       </c>
-      <c r="J208" t="s">
-        <v>222</v>
-      </c>
       <c r="K208">
         <v>100</v>
       </c>
       <c r="L208">
-        <v>1.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="209" spans="1:12" x14ac:dyDescent="0.25">
@@ -8562,37 +8598,34 @@
         <v>20</v>
       </c>
       <c r="B209">
+        <v>19</v>
+      </c>
+      <c r="C209">
         <v>10</v>
       </c>
-      <c r="C209">
-        <v>28</v>
-      </c>
       <c r="D209" t="s">
-        <v>223</v>
+        <v>47</v>
       </c>
       <c r="E209" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F209" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G209" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H209" t="s">
         <v>16</v>
       </c>
       <c r="I209" t="s">
-        <v>229</v>
-      </c>
-      <c r="J209" t="s">
-        <v>224</v>
+        <v>17</v>
       </c>
       <c r="K209">
         <v>100</v>
       </c>
       <c r="L209">
-        <v>1.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.25">
@@ -8600,22 +8633,22 @@
         <v>21</v>
       </c>
       <c r="B210">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="C210">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="D210" t="s">
         <v>22</v>
       </c>
       <c r="E210" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F210" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G210" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H210" t="s">
         <v>16</v>
@@ -8623,14 +8656,11 @@
       <c r="I210" t="s">
         <v>17</v>
       </c>
-      <c r="J210" t="s">
-        <v>225</v>
-      </c>
       <c r="K210">
         <v>100</v>
       </c>
       <c r="L210">
-        <v>1.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="211" spans="1:12" x14ac:dyDescent="0.25">
@@ -8638,22 +8668,22 @@
         <v>23</v>
       </c>
       <c r="B211">
-        <v>600</v>
+        <v>465</v>
       </c>
       <c r="C211">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="D211" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="E211" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="F211" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G211" t="s">
-        <v>214</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s">
         <v>16</v>
@@ -8665,7 +8695,7 @@
         <v>100</v>
       </c>
       <c r="L211">
-        <v>1.3</v>
+        <v>65</v>
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.25">
@@ -8673,34 +8703,34 @@
         <v>12</v>
       </c>
       <c r="B212">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C212">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D212" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="E212" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="F212" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G212" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H212" t="s">
         <v>16</v>
       </c>
       <c r="I212" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K212">
         <v>100</v>
       </c>
       <c r="L212">
-        <v>87.8</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="213" spans="1:12" x14ac:dyDescent="0.25">
@@ -8708,34 +8738,34 @@
         <v>18</v>
       </c>
       <c r="B213">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C213">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
       <c r="E213" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="F213" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G213" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H213" t="s">
         <v>16</v>
       </c>
       <c r="I213" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K213">
         <v>100</v>
       </c>
       <c r="L213">
-        <v>87.8</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.25">
@@ -8743,34 +8773,34 @@
         <v>20</v>
       </c>
       <c r="B214">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C214">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D214" t="s">
-        <v>177</v>
+        <v>95</v>
       </c>
       <c r="E214" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="F214" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G214" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H214" t="s">
         <v>16</v>
       </c>
       <c r="I214" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K214">
         <v>100</v>
       </c>
       <c r="L214">
-        <v>87.8</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.25">
@@ -8778,34 +8808,34 @@
         <v>21</v>
       </c>
       <c r="B215">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C215">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D215" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="E215" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="F215" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G215" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H215" t="s">
         <v>16</v>
       </c>
       <c r="I215" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K215">
         <v>100</v>
       </c>
       <c r="L215">
-        <v>87.8</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.25">
@@ -8813,34 +8843,34 @@
         <v>23</v>
       </c>
       <c r="B216">
-        <v>1200</v>
+        <v>698</v>
       </c>
       <c r="C216">
-        <v>1201</v>
+        <v>482</v>
       </c>
       <c r="D216" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="E216" t="s">
-        <v>175</v>
+        <v>93</v>
       </c>
       <c r="F216" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G216" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H216" t="s">
         <v>16</v>
       </c>
       <c r="I216" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K216">
         <v>100</v>
       </c>
       <c r="L216">
-        <v>87.8</v>
+        <v>116.6</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.25">
@@ -8848,22 +8878,22 @@
         <v>12</v>
       </c>
       <c r="B217">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D217" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="E217" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F217" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G217" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H217" t="s">
         <v>16</v>
@@ -8872,13 +8902,13 @@
         <v>17</v>
       </c>
       <c r="J217" t="s">
-        <v>179</v>
+        <v>99</v>
       </c>
       <c r="K217">
         <v>100</v>
       </c>
       <c r="L217">
-        <v>0.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.25">
@@ -8886,7 +8916,7 @@
         <v>18</v>
       </c>
       <c r="B218">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -8895,13 +8925,13 @@
         <v>19</v>
       </c>
       <c r="E218" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F218" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G218" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H218" t="s">
         <v>16</v>
@@ -8913,7 +8943,7 @@
         <v>100</v>
       </c>
       <c r="L218">
-        <v>0.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="219" spans="1:12" x14ac:dyDescent="0.25">
@@ -8921,22 +8951,22 @@
         <v>20</v>
       </c>
       <c r="B219">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C219">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D219" t="s">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="E219" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F219" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G219" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H219" t="s">
         <v>16</v>
@@ -8948,7 +8978,7 @@
         <v>100</v>
       </c>
       <c r="L219">
-        <v>0.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.25">
@@ -8956,22 +8986,22 @@
         <v>21</v>
       </c>
       <c r="B220">
-        <v>70</v>
+        <v>47</v>
       </c>
       <c r="C220">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D220" t="s">
         <v>22</v>
       </c>
       <c r="E220" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F220" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G220" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H220" t="s">
         <v>16</v>
@@ -8983,7 +9013,7 @@
         <v>100</v>
       </c>
       <c r="L220">
-        <v>0.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="221" spans="1:12" x14ac:dyDescent="0.25">
@@ -8991,22 +9021,22 @@
         <v>23</v>
       </c>
       <c r="B221">
-        <v>1200</v>
+        <v>338</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="D221" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="E221" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F221" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G221" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="H221" t="s">
         <v>16</v>
@@ -9018,7 +9048,7 @@
         <v>100</v>
       </c>
       <c r="L221">
-        <v>0.1</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.25">
@@ -9026,19 +9056,19 @@
         <v>12</v>
       </c>
       <c r="B222">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C222">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E222" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F222" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G222" t="s">
         <v>89</v>
@@ -9050,13 +9080,13 @@
         <v>17</v>
       </c>
       <c r="J222" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="K222">
         <v>100</v>
       </c>
       <c r="L222">
-        <v>65</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="223" spans="1:12" x14ac:dyDescent="0.25">
@@ -9064,19 +9094,19 @@
         <v>18</v>
       </c>
       <c r="B223">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C223">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="E223" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F223" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G223" t="s">
         <v>89</v>
@@ -9091,7 +9121,7 @@
         <v>100</v>
       </c>
       <c r="L223">
-        <v>65</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.25">
@@ -9099,19 +9129,19 @@
         <v>20</v>
       </c>
       <c r="B224">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C224">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D224" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="E224" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F224" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G224" t="s">
         <v>89</v>
@@ -9126,7 +9156,7 @@
         <v>100</v>
       </c>
       <c r="L224">
-        <v>65</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.25">
@@ -9134,19 +9164,19 @@
         <v>21</v>
       </c>
       <c r="B225">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="C225">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="D225" t="s">
         <v>22</v>
       </c>
       <c r="E225" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F225" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G225" t="s">
         <v>89</v>
@@ -9161,7 +9191,7 @@
         <v>100</v>
       </c>
       <c r="L225">
-        <v>65</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.25">
@@ -9169,19 +9199,19 @@
         <v>23</v>
       </c>
       <c r="B226">
-        <v>465</v>
+        <v>563</v>
       </c>
       <c r="C226">
-        <v>645</v>
+        <v>0</v>
       </c>
       <c r="D226" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="F226" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G226" t="s">
         <v>89</v>
@@ -9196,7 +9226,7 @@
         <v>100</v>
       </c>
       <c r="L226">
-        <v>65</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.25">
@@ -9204,34 +9234,34 @@
         <v>12</v>
       </c>
       <c r="B227">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C227">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D227" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="E227" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="F227" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G227" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="H227" t="s">
         <v>16</v>
       </c>
       <c r="I227" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K227">
         <v>100</v>
       </c>
       <c r="L227">
-        <v>116.6</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.25">
@@ -9239,34 +9269,34 @@
         <v>18</v>
       </c>
       <c r="B228">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C228">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D228" t="s">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="E228" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="F228" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G228" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="H228" t="s">
         <v>16</v>
       </c>
       <c r="I228" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K228">
         <v>100</v>
       </c>
       <c r="L228">
-        <v>116.6</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.25">
@@ -9274,34 +9304,34 @@
         <v>20</v>
       </c>
       <c r="B229">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C229">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D229" t="s">
-        <v>95</v>
+        <v>268</v>
       </c>
       <c r="E229" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="F229" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G229" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="H229" t="s">
         <v>16</v>
       </c>
       <c r="I229" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K229">
         <v>100</v>
       </c>
       <c r="L229">
-        <v>116.6</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.25">
@@ -9309,34 +9339,34 @@
         <v>21</v>
       </c>
       <c r="B230">
-        <v>98</v>
+        <v>70</v>
       </c>
       <c r="C230">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D230" t="s">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="E230" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="F230" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G230" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="H230" t="s">
         <v>16</v>
       </c>
       <c r="I230" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K230">
         <v>100</v>
       </c>
       <c r="L230">
-        <v>116.6</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.25">
@@ -9344,22 +9374,22 @@
         <v>23</v>
       </c>
       <c r="B231">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>482</v>
+        <v>0</v>
       </c>
       <c r="D231" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>93</v>
+        <v>266</v>
       </c>
       <c r="F231" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G231" t="s">
-        <v>89</v>
+        <v>267</v>
       </c>
       <c r="H231" t="s">
         <v>16</v>
@@ -9371,7 +9401,7 @@
         <v>100</v>
       </c>
       <c r="L231">
-        <v>116.6</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.25">
@@ -9382,19 +9412,19 @@
         <v>14</v>
       </c>
       <c r="C232">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D232" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="E232" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F232" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G232" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H232" t="s">
         <v>16</v>
@@ -9403,13 +9433,13 @@
         <v>17</v>
       </c>
       <c r="J232" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="K232">
         <v>100</v>
       </c>
       <c r="L232">
-        <v>47.3</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.25">
@@ -9417,22 +9447,22 @@
         <v>18</v>
       </c>
       <c r="B233">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D233" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="E233" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F233" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G233" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H233" t="s">
         <v>16</v>
@@ -9440,11 +9470,14 @@
       <c r="I233" t="s">
         <v>17</v>
       </c>
+      <c r="J233" t="s">
+        <v>122</v>
+      </c>
       <c r="K233">
         <v>100</v>
       </c>
       <c r="L233">
-        <v>47.3</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.25">
@@ -9452,22 +9485,22 @@
         <v>20</v>
       </c>
       <c r="B234">
+        <v>28</v>
+      </c>
+      <c r="C234">
+        <v>26</v>
+      </c>
+      <c r="D234" t="s">
+        <v>123</v>
+      </c>
+      <c r="E234" t="s">
+        <v>119</v>
+      </c>
+      <c r="F234" t="s">
         <v>14</v>
       </c>
-      <c r="C234">
-        <v>8</v>
-      </c>
-      <c r="D234" t="s">
-        <v>73</v>
-      </c>
-      <c r="E234" t="s">
-        <v>98</v>
-      </c>
-      <c r="F234" t="s">
-        <v>25</v>
-      </c>
       <c r="G234" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H234" t="s">
         <v>16</v>
@@ -9475,11 +9508,14 @@
       <c r="I234" t="s">
         <v>17</v>
       </c>
+      <c r="J234" t="s">
+        <v>124</v>
+      </c>
       <c r="K234">
         <v>100</v>
       </c>
       <c r="L234">
-        <v>47.3</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="235" spans="1:12" x14ac:dyDescent="0.25">
@@ -9487,22 +9523,22 @@
         <v>21</v>
       </c>
       <c r="B235">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C235">
-        <v>35</v>
+        <v>83</v>
       </c>
       <c r="D235" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="E235" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F235" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G235" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H235" t="s">
         <v>16</v>
@@ -9510,11 +9546,14 @@
       <c r="I235" t="s">
         <v>17</v>
       </c>
+      <c r="J235" t="s">
+        <v>126</v>
+      </c>
       <c r="K235">
         <v>100</v>
       </c>
       <c r="L235">
-        <v>47.3</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.25">
@@ -9522,22 +9561,22 @@
         <v>23</v>
       </c>
       <c r="B236">
-        <v>338</v>
+        <v>600</v>
       </c>
       <c r="C236">
-        <v>126</v>
+        <v>314</v>
       </c>
       <c r="D236" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="E236" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="F236" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G236" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H236" t="s">
         <v>16</v>
@@ -9545,11 +9584,14 @@
       <c r="I236" t="s">
         <v>17</v>
       </c>
+      <c r="J236" t="s">
+        <v>128</v>
+      </c>
       <c r="K236">
         <v>100</v>
       </c>
       <c r="L236">
-        <v>47.3</v>
+        <v>71.599999999999994</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.25">
@@ -9557,22 +9599,22 @@
         <v>12</v>
       </c>
       <c r="B237">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D237" t="s">
-        <v>101</v>
+        <v>57</v>
       </c>
       <c r="E237" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F237" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G237" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H237" t="s">
         <v>16</v>
@@ -9580,14 +9622,11 @@
       <c r="I237" t="s">
         <v>17</v>
       </c>
-      <c r="J237" t="s">
-        <v>104</v>
-      </c>
       <c r="K237">
         <v>100</v>
       </c>
       <c r="L237">
-        <v>11.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.25">
@@ -9595,22 +9634,22 @@
         <v>18</v>
       </c>
       <c r="B238">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D238" t="s">
-        <v>105</v>
+        <v>19</v>
       </c>
       <c r="E238" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F238" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G238" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H238" t="s">
         <v>16</v>
@@ -9622,7 +9661,7 @@
         <v>100</v>
       </c>
       <c r="L238">
-        <v>11.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="239" spans="1:12" x14ac:dyDescent="0.25">
@@ -9630,22 +9669,22 @@
         <v>20</v>
       </c>
       <c r="B239">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C239">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="D239" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="E239" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F239" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G239" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H239" t="s">
         <v>16</v>
@@ -9657,7 +9696,7 @@
         <v>100</v>
       </c>
       <c r="L239">
-        <v>11.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.25">
@@ -9665,22 +9704,22 @@
         <v>21</v>
       </c>
       <c r="B240">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C240">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="D240" t="s">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="E240" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F240" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G240" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H240" t="s">
         <v>16</v>
@@ -9692,7 +9731,7 @@
         <v>100</v>
       </c>
       <c r="L240">
-        <v>11.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="241" spans="1:12" x14ac:dyDescent="0.25">
@@ -9700,22 +9739,22 @@
         <v>23</v>
       </c>
       <c r="B241">
-        <v>563</v>
+        <v>900</v>
       </c>
       <c r="C241">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D241" t="s">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="E241" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="F241" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G241" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="H241" t="s">
         <v>16</v>
@@ -9727,7 +9766,7 @@
         <v>100</v>
       </c>
       <c r="L241">
-        <v>11.7</v>
+        <v>64.8</v>
       </c>
     </row>
     <row r="242" spans="1:12" x14ac:dyDescent="0.25">
@@ -9735,34 +9774,37 @@
         <v>12</v>
       </c>
       <c r="B242">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C242">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="D242" t="s">
-        <v>205</v>
+        <v>31</v>
       </c>
       <c r="E242" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="F242" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G242" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="H242" t="s">
         <v>16</v>
       </c>
       <c r="I242" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="J242" t="s">
+        <v>134</v>
       </c>
       <c r="K242">
         <v>100</v>
       </c>
       <c r="L242">
-        <v>89.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="243" spans="1:12" x14ac:dyDescent="0.25">
@@ -9770,34 +9812,37 @@
         <v>18</v>
       </c>
       <c r="B243">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D243" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E243" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="F243" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G243" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="H243" t="s">
         <v>16</v>
       </c>
       <c r="I243" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J243" t="s">
+        <v>135</v>
       </c>
       <c r="K243">
         <v>100</v>
       </c>
       <c r="L243">
-        <v>89.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="244" spans="1:12" x14ac:dyDescent="0.25">
@@ -9805,34 +9850,37 @@
         <v>20</v>
       </c>
       <c r="B244">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="C244">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D244" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="E244" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="F244" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G244" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="H244" t="s">
         <v>16</v>
       </c>
       <c r="I244" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="J244" t="s">
+        <v>137</v>
       </c>
       <c r="K244">
         <v>100</v>
       </c>
       <c r="L244">
-        <v>89.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="245" spans="1:12" x14ac:dyDescent="0.25">
@@ -9840,34 +9888,37 @@
         <v>21</v>
       </c>
       <c r="B245">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C245">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="D245" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E245" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="F245" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G245" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="H245" t="s">
         <v>16</v>
       </c>
       <c r="I245" t="s">
-        <v>231</v>
+        <v>17</v>
+      </c>
+      <c r="J245" t="s">
+        <v>138</v>
       </c>
       <c r="K245">
         <v>100</v>
       </c>
       <c r="L245">
-        <v>89.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="246" spans="1:12" x14ac:dyDescent="0.25">
@@ -9875,7 +9926,7 @@
         <v>23</v>
       </c>
       <c r="B246">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9884,13 +9935,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>266</v>
+        <v>133</v>
       </c>
       <c r="F246" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G246" t="s">
-        <v>267</v>
+        <v>120</v>
       </c>
       <c r="H246" t="s">
         <v>16</v>
@@ -9902,7 +9953,7 @@
         <v>100</v>
       </c>
       <c r="L246">
-        <v>89.7</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="247" spans="1:12" x14ac:dyDescent="0.25">
@@ -9910,22 +9961,22 @@
         <v>12</v>
       </c>
       <c r="B247">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C247">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D247" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E247" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F247" t="s">
         <v>14</v>
       </c>
       <c r="G247" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H247" t="s">
         <v>16</v>
@@ -9933,14 +9984,11 @@
       <c r="I247" t="s">
         <v>17</v>
       </c>
-      <c r="J247" t="s">
-        <v>121</v>
-      </c>
       <c r="K247">
         <v>100</v>
       </c>
       <c r="L247">
-        <v>71.599999999999994</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="248" spans="1:12" x14ac:dyDescent="0.25">
@@ -9948,22 +9996,22 @@
         <v>18</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C248">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D248" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="E248" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F248" t="s">
         <v>14</v>
       </c>
       <c r="G248" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H248" t="s">
         <v>16</v>
@@ -9971,14 +10019,11 @@
       <c r="I248" t="s">
         <v>17</v>
       </c>
-      <c r="J248" t="s">
-        <v>122</v>
-      </c>
       <c r="K248">
         <v>100</v>
       </c>
       <c r="L248">
-        <v>71.599999999999994</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="249" spans="1:12" x14ac:dyDescent="0.25">
@@ -9986,22 +10031,22 @@
         <v>20</v>
       </c>
       <c r="B249">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C249">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D249" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="E249" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F249" t="s">
         <v>14</v>
       </c>
       <c r="G249" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H249" t="s">
         <v>16</v>
@@ -10009,14 +10054,11 @@
       <c r="I249" t="s">
         <v>17</v>
       </c>
-      <c r="J249" t="s">
-        <v>124</v>
-      </c>
       <c r="K249">
         <v>100</v>
       </c>
       <c r="L249">
-        <v>71.599999999999994</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="250" spans="1:12" x14ac:dyDescent="0.25">
@@ -10024,22 +10066,22 @@
         <v>21</v>
       </c>
       <c r="B250">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="C250">
-        <v>83</v>
+        <v>139</v>
       </c>
       <c r="D250" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="E250" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F250" t="s">
         <v>14</v>
       </c>
       <c r="G250" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H250" t="s">
         <v>16</v>
@@ -10047,14 +10089,11 @@
       <c r="I250" t="s">
         <v>17</v>
       </c>
-      <c r="J250" t="s">
-        <v>126</v>
-      </c>
       <c r="K250">
         <v>100</v>
       </c>
       <c r="L250">
-        <v>71.599999999999994</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="251" spans="1:12" x14ac:dyDescent="0.25">
@@ -10062,22 +10101,22 @@
         <v>23</v>
       </c>
       <c r="B251">
-        <v>600</v>
+        <v>768</v>
       </c>
       <c r="C251">
-        <v>314</v>
+        <v>256</v>
       </c>
       <c r="D251" t="s">
-        <v>127</v>
+        <v>40</v>
       </c>
       <c r="E251" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="F251" t="s">
         <v>14</v>
       </c>
       <c r="G251" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H251" t="s">
         <v>16</v>
@@ -10085,14 +10124,11 @@
       <c r="I251" t="s">
         <v>17</v>
       </c>
-      <c r="J251" t="s">
-        <v>128</v>
-      </c>
       <c r="K251">
         <v>100</v>
       </c>
       <c r="L251">
-        <v>71.599999999999994</v>
+        <v>65.900000000000006</v>
       </c>
     </row>
     <row r="252" spans="1:12" x14ac:dyDescent="0.25">
@@ -10100,22 +10136,22 @@
         <v>12</v>
       </c>
       <c r="B252">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C252">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D252" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="E252" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="F252" t="s">
         <v>25</v>
       </c>
       <c r="G252" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H252" t="s">
         <v>16</v>
@@ -10123,11 +10159,14 @@
       <c r="I252" t="s">
         <v>17</v>
       </c>
+      <c r="J252" t="s">
+        <v>43</v>
+      </c>
       <c r="K252">
         <v>100</v>
       </c>
       <c r="L252">
-        <v>64.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="253" spans="1:12" x14ac:dyDescent="0.25">
@@ -10135,7 +10174,7 @@
         <v>18</v>
       </c>
       <c r="B253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -10144,13 +10183,13 @@
         <v>19</v>
       </c>
       <c r="E253" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="F253" t="s">
         <v>25</v>
       </c>
       <c r="G253" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H253" t="s">
         <v>16</v>
@@ -10162,7 +10201,7 @@
         <v>100</v>
       </c>
       <c r="L253">
-        <v>64.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="254" spans="1:12" x14ac:dyDescent="0.25">
@@ -10170,22 +10209,22 @@
         <v>20</v>
       </c>
       <c r="B254">
+        <v>20</v>
+      </c>
+      <c r="C254">
+        <v>11</v>
+      </c>
+      <c r="D254" t="s">
+        <v>44</v>
+      </c>
+      <c r="E254" t="s">
         <v>42</v>
       </c>
-      <c r="C254">
-        <v>34</v>
-      </c>
-      <c r="D254" t="s">
-        <v>130</v>
-      </c>
-      <c r="E254" t="s">
-        <v>129</v>
-      </c>
       <c r="F254" t="s">
         <v>25</v>
       </c>
       <c r="G254" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H254" t="s">
         <v>16</v>
@@ -10197,7 +10236,7 @@
         <v>100</v>
       </c>
       <c r="L254">
-        <v>64.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="255" spans="1:12" x14ac:dyDescent="0.25">
@@ -10205,22 +10244,22 @@
         <v>21</v>
       </c>
       <c r="B255">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="C255">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="D255" t="s">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="E255" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="F255" t="s">
         <v>25</v>
       </c>
       <c r="G255" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H255" t="s">
         <v>16</v>
@@ -10232,7 +10271,7 @@
         <v>100</v>
       </c>
       <c r="L255">
-        <v>64.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="256" spans="1:12" x14ac:dyDescent="0.25">
@@ -10240,22 +10279,22 @@
         <v>23</v>
       </c>
       <c r="B256">
-        <v>900</v>
+        <v>432</v>
       </c>
       <c r="C256">
+        <v>171</v>
+      </c>
+      <c r="D256" t="s">
         <v>46</v>
       </c>
-      <c r="D256" t="s">
-        <v>132</v>
-      </c>
       <c r="E256" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="F256" t="s">
         <v>25</v>
       </c>
       <c r="G256" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="H256" t="s">
         <v>16</v>
@@ -10267,7 +10306,7 @@
         <v>100</v>
       </c>
       <c r="L256">
-        <v>64.8</v>
+        <v>58.5</v>
       </c>
     </row>
     <row r="257" spans="1:12" x14ac:dyDescent="0.25">
@@ -10275,37 +10314,37 @@
         <v>12</v>
       </c>
       <c r="B257">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C257">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D257" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E257" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F257" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G257" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H257" t="s">
         <v>16</v>
       </c>
       <c r="I257" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J257" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="K257">
         <v>100</v>
       </c>
       <c r="L257">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="258" spans="1:12" x14ac:dyDescent="0.25">
@@ -10313,37 +10352,37 @@
         <v>18</v>
       </c>
       <c r="B258">
+        <v>3</v>
+      </c>
+      <c r="C258">
         <v>2</v>
       </c>
-      <c r="C258">
-        <v>0</v>
-      </c>
       <c r="D258" t="s">
-        <v>19</v>
+        <v>142</v>
       </c>
       <c r="E258" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F258" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G258" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H258" t="s">
         <v>16</v>
       </c>
       <c r="I258" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="J258" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="K258">
         <v>100</v>
       </c>
       <c r="L258">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="259" spans="1:12" x14ac:dyDescent="0.25">
@@ -10351,37 +10390,37 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C259">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D259" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="E259" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F259" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G259" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H259" t="s">
         <v>16</v>
       </c>
       <c r="I259" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J259" t="s">
-        <v>137</v>
+        <v>198</v>
       </c>
       <c r="K259">
         <v>100</v>
       </c>
       <c r="L259">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="260" spans="1:12" x14ac:dyDescent="0.25">
@@ -10389,22 +10428,22 @@
         <v>21</v>
       </c>
       <c r="B260">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C260">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D260" t="s">
-        <v>22</v>
+        <v>96</v>
       </c>
       <c r="E260" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F260" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G260" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H260" t="s">
         <v>16</v>
@@ -10413,13 +10452,13 @@
         <v>17</v>
       </c>
       <c r="J260" t="s">
-        <v>138</v>
+        <v>199</v>
       </c>
       <c r="K260">
         <v>100</v>
       </c>
       <c r="L260">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="261" spans="1:12" x14ac:dyDescent="0.25">
@@ -10427,22 +10466,22 @@
         <v>23</v>
       </c>
       <c r="B261">
-        <v>900</v>
+        <v>510</v>
       </c>
       <c r="C261">
-        <v>0</v>
+        <v>547</v>
       </c>
       <c r="D261" t="s">
-        <v>19</v>
+        <v>200</v>
       </c>
       <c r="E261" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c r="F261" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G261" t="s">
-        <v>120</v>
+        <v>195</v>
       </c>
       <c r="H261" t="s">
         <v>16</v>
@@ -10450,11 +10489,14 @@
       <c r="I261" t="s">
         <v>17</v>
       </c>
+      <c r="J261" t="s">
+        <v>201</v>
+      </c>
       <c r="K261">
         <v>100</v>
       </c>
       <c r="L261">
-        <v>22.8</v>
+        <v>73.099999999999994</v>
       </c>
     </row>
     <row r="262" spans="1:12" x14ac:dyDescent="0.25">
@@ -10462,34 +10504,34 @@
         <v>12</v>
       </c>
       <c r="B262">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C262">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D262" t="s">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="E262" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F262" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G262" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H262" t="s">
         <v>16</v>
       </c>
       <c r="I262" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K262">
         <v>100</v>
       </c>
       <c r="L262">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="263" spans="1:12" x14ac:dyDescent="0.25">
@@ -10500,19 +10542,19 @@
         <v>5</v>
       </c>
       <c r="C263">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D263" t="s">
-        <v>37</v>
+        <v>169</v>
       </c>
       <c r="E263" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F263" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G263" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H263" t="s">
         <v>16</v>
@@ -10524,7 +10566,7 @@
         <v>100</v>
       </c>
       <c r="L263">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="264" spans="1:12" x14ac:dyDescent="0.25">
@@ -10532,22 +10574,22 @@
         <v>20</v>
       </c>
       <c r="B264">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C264">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D264" t="s">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="E264" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F264" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G264" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H264" t="s">
         <v>16</v>
@@ -10559,7 +10601,7 @@
         <v>100</v>
       </c>
       <c r="L264">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="265" spans="1:12" x14ac:dyDescent="0.25">
@@ -10567,34 +10609,34 @@
         <v>21</v>
       </c>
       <c r="B265">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="C265">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="D265" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="E265" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F265" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G265" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H265" t="s">
         <v>16</v>
       </c>
       <c r="I265" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K265">
         <v>100</v>
       </c>
       <c r="L265">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="266" spans="1:12" x14ac:dyDescent="0.25">
@@ -10602,34 +10644,34 @@
         <v>23</v>
       </c>
       <c r="B266">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="C266">
-        <v>256</v>
+        <v>733</v>
       </c>
       <c r="D266" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="E266" t="s">
-        <v>35</v>
+        <v>203</v>
       </c>
       <c r="F266" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G266" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H266" t="s">
         <v>16</v>
       </c>
       <c r="I266" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K266">
         <v>100</v>
       </c>
       <c r="L266">
-        <v>65.900000000000006</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="267" spans="1:12" x14ac:dyDescent="0.25">
@@ -10637,37 +10679,37 @@
         <v>12</v>
       </c>
       <c r="B267">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C267">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D267" t="s">
-        <v>41</v>
+        <v>205</v>
       </c>
       <c r="E267" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F267" t="s">
         <v>25</v>
       </c>
       <c r="G267" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H267" t="s">
         <v>16</v>
       </c>
       <c r="I267" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="J267" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="K267">
         <v>100</v>
       </c>
       <c r="L267">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="268" spans="1:12" x14ac:dyDescent="0.25">
@@ -10675,22 +10717,22 @@
         <v>18</v>
       </c>
       <c r="B268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E268" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F268" t="s">
         <v>25</v>
       </c>
       <c r="G268" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H268" t="s">
         <v>16</v>
@@ -10702,7 +10744,7 @@
         <v>100</v>
       </c>
       <c r="L268">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="269" spans="1:12" x14ac:dyDescent="0.25">
@@ -10710,34 +10752,34 @@
         <v>20</v>
       </c>
       <c r="B269">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C269">
         <v>11</v>
       </c>
       <c r="D269" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E269" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F269" t="s">
         <v>25</v>
       </c>
       <c r="G269" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H269" t="s">
         <v>16</v>
       </c>
       <c r="I269" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K269">
         <v>100</v>
       </c>
       <c r="L269">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="270" spans="1:12" x14ac:dyDescent="0.25">
@@ -10745,22 +10787,22 @@
         <v>21</v>
       </c>
       <c r="B270">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="C270">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="D270" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E270" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F270" t="s">
         <v>25</v>
       </c>
       <c r="G270" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H270" t="s">
         <v>16</v>
@@ -10772,7 +10814,7 @@
         <v>100</v>
       </c>
       <c r="L270">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="271" spans="1:12" x14ac:dyDescent="0.25">
@@ -10780,34 +10822,34 @@
         <v>23</v>
       </c>
       <c r="B271">
-        <v>432</v>
+        <v>225</v>
       </c>
       <c r="C271">
-        <v>171</v>
+        <v>306</v>
       </c>
       <c r="D271" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E271" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F271" t="s">
         <v>25</v>
       </c>
       <c r="G271" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="H271" t="s">
         <v>16</v>
       </c>
       <c r="I271" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K271">
         <v>100</v>
       </c>
       <c r="L271">
-        <v>58.5</v>
+        <v>126.6</v>
       </c>
     </row>
     <row r="272" spans="1:12" x14ac:dyDescent="0.25">
@@ -10815,37 +10857,37 @@
         <v>12</v>
       </c>
       <c r="B272">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D272" t="s">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="E272" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F272" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G272" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H272" t="s">
         <v>16</v>
       </c>
       <c r="I272" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="J272" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="K272">
         <v>100</v>
       </c>
       <c r="L272">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="273" spans="1:12" x14ac:dyDescent="0.25">
@@ -10853,7 +10895,7 @@
         <v>18</v>
       </c>
       <c r="B273">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -10862,13 +10904,13 @@
         <v>19</v>
       </c>
       <c r="E273" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F273" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G273" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H273" t="s">
         <v>16</v>
@@ -10876,11 +10918,14 @@
       <c r="I273" t="s">
         <v>17</v>
       </c>
+      <c r="J273" t="s">
+        <v>210</v>
+      </c>
       <c r="K273">
         <v>100</v>
       </c>
       <c r="L273">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="274" spans="1:12" x14ac:dyDescent="0.25">
@@ -10888,34 +10933,37 @@
         <v>20</v>
       </c>
       <c r="B274">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="C274">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D274" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="E274" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F274" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G274" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H274" t="s">
         <v>16</v>
       </c>
       <c r="I274" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J274" t="s">
+        <v>212</v>
       </c>
       <c r="K274">
         <v>100</v>
       </c>
       <c r="L274">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="275" spans="1:12" x14ac:dyDescent="0.25">
@@ -10923,34 +10971,37 @@
         <v>21</v>
       </c>
       <c r="B275">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C275">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D275" t="s">
         <v>22</v>
       </c>
       <c r="E275" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F275" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G275" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H275" t="s">
         <v>16</v>
       </c>
       <c r="I275" t="s">
-        <v>17</v>
+        <v>229</v>
+      </c>
+      <c r="J275" t="s">
+        <v>213</v>
       </c>
       <c r="K275">
         <v>100</v>
       </c>
       <c r="L275">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="276" spans="1:12" x14ac:dyDescent="0.25">
@@ -10958,22 +11009,22 @@
         <v>23</v>
       </c>
       <c r="B276">
-        <v>211</v>
+        <v>563</v>
       </c>
       <c r="C276">
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="D276" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="E276" t="s">
-        <v>66</v>
+        <v>133</v>
       </c>
       <c r="F276" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="G276" t="s">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="H276" t="s">
         <v>16</v>
@@ -10985,7 +11036,7 @@
         <v>100</v>
       </c>
       <c r="L276">
-        <v>94.2</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="277" spans="1:12" x14ac:dyDescent="0.25">
@@ -10993,34 +11044,34 @@
         <v>12</v>
       </c>
       <c r="B277">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C277">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D277" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="E277" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F277" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G277" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H277" t="s">
         <v>16</v>
       </c>
       <c r="I277" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K277">
         <v>100</v>
       </c>
       <c r="L277">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="278" spans="1:12" x14ac:dyDescent="0.25">
@@ -11028,34 +11079,34 @@
         <v>18</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C278">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D278" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E278" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F278" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G278" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H278" t="s">
         <v>16</v>
       </c>
       <c r="I278" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K278">
         <v>100</v>
       </c>
       <c r="L278">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="279" spans="1:12" x14ac:dyDescent="0.25">
@@ -11063,22 +11114,22 @@
         <v>20</v>
       </c>
       <c r="B279">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C279">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D279" t="s">
-        <v>73</v>
+        <v>182</v>
       </c>
       <c r="E279" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F279" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G279" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H279" t="s">
         <v>16</v>
@@ -11090,7 +11141,7 @@
         <v>100</v>
       </c>
       <c r="L279">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="280" spans="1:12" x14ac:dyDescent="0.25">
@@ -11098,34 +11149,34 @@
         <v>21</v>
       </c>
       <c r="B280">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C280">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D280" t="s">
-        <v>22</v>
+        <v>183</v>
       </c>
       <c r="E280" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F280" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G280" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H280" t="s">
         <v>16</v>
       </c>
       <c r="I280" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K280">
         <v>100</v>
       </c>
       <c r="L280">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="281" spans="1:12" x14ac:dyDescent="0.25">
@@ -11133,34 +11184,34 @@
         <v>23</v>
       </c>
       <c r="B281">
-        <v>989</v>
+        <v>402</v>
       </c>
       <c r="C281">
-        <v>653</v>
+        <v>402</v>
       </c>
       <c r="D281" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="E281" t="s">
-        <v>72</v>
+        <v>180</v>
       </c>
       <c r="F281" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G281" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="H281" t="s">
         <v>16</v>
       </c>
       <c r="I281" t="s">
-        <v>17</v>
+        <v>231</v>
       </c>
       <c r="K281">
         <v>100</v>
       </c>
       <c r="L281">
-        <v>62.2</v>
+        <v>83.6</v>
       </c>
     </row>
     <row r="282" spans="1:12" x14ac:dyDescent="0.25">
@@ -11168,22 +11219,22 @@
         <v>12</v>
       </c>
       <c r="B282">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C282">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D282" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E282" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F282" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G282" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H282" t="s">
         <v>16</v>
@@ -11191,14 +11242,11 @@
       <c r="I282" t="s">
         <v>231</v>
       </c>
-      <c r="J282" t="s">
-        <v>196</v>
-      </c>
       <c r="K282">
         <v>100</v>
       </c>
       <c r="L282">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="283" spans="1:12" x14ac:dyDescent="0.25">
@@ -11206,37 +11254,34 @@
         <v>18</v>
       </c>
       <c r="B283">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C283">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D283" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="E283" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F283" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G283" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H283" t="s">
         <v>16</v>
       </c>
       <c r="I283" t="s">
-        <v>229</v>
-      </c>
-      <c r="J283" t="s">
-        <v>197</v>
+        <v>17</v>
       </c>
       <c r="K283">
         <v>100</v>
       </c>
       <c r="L283">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="284" spans="1:12" x14ac:dyDescent="0.25">
@@ -11244,37 +11289,34 @@
         <v>20</v>
       </c>
       <c r="B284">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C284">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D284" t="s">
-        <v>51</v>
+        <v>185</v>
       </c>
       <c r="E284" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F284" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G284" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H284" t="s">
         <v>16</v>
       </c>
       <c r="I284" t="s">
-        <v>231</v>
-      </c>
-      <c r="J284" t="s">
-        <v>198</v>
+        <v>17</v>
       </c>
       <c r="K284">
         <v>100</v>
       </c>
       <c r="L284">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="285" spans="1:12" x14ac:dyDescent="0.25">
@@ -11282,37 +11324,34 @@
         <v>21</v>
       </c>
       <c r="B285">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="C285">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="D285" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E285" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F285" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G285" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H285" t="s">
         <v>16</v>
       </c>
       <c r="I285" t="s">
-        <v>17</v>
-      </c>
-      <c r="J285" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="K285">
         <v>100</v>
       </c>
       <c r="L285">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="286" spans="1:12" x14ac:dyDescent="0.25">
@@ -11320,37 +11359,34 @@
         <v>23</v>
       </c>
       <c r="B286">
-        <v>510</v>
+        <v>603</v>
       </c>
       <c r="C286">
-        <v>547</v>
+        <v>603</v>
       </c>
       <c r="D286" t="s">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="E286" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F286" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G286" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H286" t="s">
         <v>16</v>
       </c>
       <c r="I286" t="s">
-        <v>17</v>
-      </c>
-      <c r="J286" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="K286">
         <v>100</v>
       </c>
       <c r="L286">
-        <v>73.099999999999994</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="287" spans="1:12" x14ac:dyDescent="0.25">
@@ -11358,34 +11394,37 @@
         <v>12</v>
       </c>
       <c r="B287">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C287">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D287" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="E287" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F287" t="s">
         <v>25</v>
       </c>
       <c r="G287" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H287" t="s">
         <v>16</v>
       </c>
       <c r="I287" t="s">
-        <v>231</v>
+        <v>229</v>
+      </c>
+      <c r="J287" t="s">
+        <v>188</v>
       </c>
       <c r="K287">
         <v>100</v>
       </c>
       <c r="L287">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="288" spans="1:12" x14ac:dyDescent="0.25">
@@ -11393,34 +11432,34 @@
         <v>18</v>
       </c>
       <c r="B288">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C288">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D288" t="s">
-        <v>169</v>
+        <v>57</v>
       </c>
       <c r="E288" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F288" t="s">
         <v>25</v>
       </c>
       <c r="G288" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H288" t="s">
         <v>16</v>
       </c>
       <c r="I288" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K288">
         <v>100</v>
       </c>
       <c r="L288">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="289" spans="1:12" x14ac:dyDescent="0.25">
@@ -11428,22 +11467,22 @@
         <v>20</v>
       </c>
       <c r="B289">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C289">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D289" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E289" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F289" t="s">
         <v>25</v>
       </c>
       <c r="G289" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H289" t="s">
         <v>16</v>
@@ -11455,7 +11494,7 @@
         <v>100</v>
       </c>
       <c r="L289">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="290" spans="1:12" x14ac:dyDescent="0.25">
@@ -11463,34 +11502,34 @@
         <v>21</v>
       </c>
       <c r="B290">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C290">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D290" t="s">
-        <v>204</v>
+        <v>53</v>
       </c>
       <c r="E290" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F290" t="s">
         <v>25</v>
       </c>
       <c r="G290" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H290" t="s">
         <v>16</v>
       </c>
       <c r="I290" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K290">
         <v>100</v>
       </c>
       <c r="L290">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="291" spans="1:12" x14ac:dyDescent="0.25">
@@ -11498,34 +11537,34 @@
         <v>23</v>
       </c>
       <c r="B291">
-        <v>765</v>
+        <v>495</v>
       </c>
       <c r="C291">
-        <v>733</v>
+        <v>507</v>
       </c>
       <c r="D291" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E291" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F291" t="s">
         <v>25</v>
       </c>
       <c r="G291" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H291" t="s">
         <v>16</v>
       </c>
       <c r="I291" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K291">
         <v>100</v>
       </c>
       <c r="L291">
-        <v>83.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="292" spans="1:12" x14ac:dyDescent="0.25">
@@ -11533,37 +11572,34 @@
         <v>12</v>
       </c>
       <c r="B292">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C292">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D292" t="s">
-        <v>205</v>
+        <v>19</v>
       </c>
       <c r="E292" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F292" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G292" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H292" t="s">
         <v>16</v>
       </c>
       <c r="I292" t="s">
-        <v>229</v>
-      </c>
-      <c r="J292" t="s">
-        <v>207</v>
+        <v>17</v>
       </c>
       <c r="K292">
         <v>100</v>
       </c>
       <c r="L292">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="293" spans="1:12" x14ac:dyDescent="0.25">
@@ -11571,22 +11607,22 @@
         <v>18</v>
       </c>
       <c r="B293">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C293">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D293" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E293" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F293" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G293" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H293" t="s">
         <v>16</v>
@@ -11598,7 +11634,7 @@
         <v>100</v>
       </c>
       <c r="L293">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="294" spans="1:12" x14ac:dyDescent="0.25">
@@ -11606,34 +11642,34 @@
         <v>20</v>
       </c>
       <c r="B294">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C294">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D294" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E294" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F294" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G294" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H294" t="s">
         <v>16</v>
       </c>
       <c r="I294" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K294">
         <v>100</v>
       </c>
       <c r="L294">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="295" spans="1:12" x14ac:dyDescent="0.25">
@@ -11641,22 +11677,22 @@
         <v>21</v>
       </c>
       <c r="B295">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="C295">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D295" t="s">
         <v>22</v>
       </c>
       <c r="E295" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F295" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G295" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H295" t="s">
         <v>16</v>
@@ -11668,7 +11704,7 @@
         <v>100</v>
       </c>
       <c r="L295">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="296" spans="1:12" x14ac:dyDescent="0.25">
@@ -11676,34 +11712,34 @@
         <v>23</v>
       </c>
       <c r="B296">
-        <v>225</v>
+        <v>563</v>
       </c>
       <c r="C296">
-        <v>306</v>
+        <v>0</v>
       </c>
       <c r="D296" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E296" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="F296" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="G296" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H296" t="s">
         <v>16</v>
       </c>
       <c r="I296" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K296">
         <v>100</v>
       </c>
       <c r="L296">
-        <v>126.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="297" spans="1:12" x14ac:dyDescent="0.25">
@@ -11711,13 +11747,13 @@
         <v>12</v>
       </c>
       <c r="B297">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C297">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D297" t="s">
-        <v>208</v>
+        <v>19</v>
       </c>
       <c r="E297" t="s">
         <v>133</v>
@@ -11726,22 +11762,22 @@
         <v>103</v>
       </c>
       <c r="G297" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H297" t="s">
         <v>16</v>
       </c>
       <c r="I297" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="J297" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="K297">
         <v>100</v>
       </c>
       <c r="L297">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="298" spans="1:12" x14ac:dyDescent="0.25">
@@ -11749,7 +11785,7 @@
         <v>18</v>
       </c>
       <c r="B298">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C298">
         <v>0</v>
@@ -11764,7 +11800,7 @@
         <v>103</v>
       </c>
       <c r="G298" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H298" t="s">
         <v>16</v>
@@ -11773,13 +11809,13 @@
         <v>17</v>
       </c>
       <c r="J298" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="K298">
         <v>100</v>
       </c>
       <c r="L298">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="299" spans="1:12" x14ac:dyDescent="0.25">
@@ -11787,13 +11823,13 @@
         <v>20</v>
       </c>
       <c r="B299">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C299">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D299" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="E299" t="s">
         <v>133</v>
@@ -11802,22 +11838,22 @@
         <v>103</v>
       </c>
       <c r="G299" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H299" t="s">
         <v>16</v>
       </c>
       <c r="I299" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="J299" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="K299">
         <v>100</v>
       </c>
       <c r="L299">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="300" spans="1:12" x14ac:dyDescent="0.25">
@@ -11825,10 +11861,10 @@
         <v>21</v>
       </c>
       <c r="B300">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C300">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D300" t="s">
         <v>22</v>
@@ -11840,22 +11876,22 @@
         <v>103</v>
       </c>
       <c r="G300" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H300" t="s">
         <v>16</v>
       </c>
       <c r="I300" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="J300" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="K300">
         <v>100</v>
       </c>
       <c r="L300">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="301" spans="1:12" x14ac:dyDescent="0.25">
@@ -11878,7 +11914,7 @@
         <v>103</v>
       </c>
       <c r="G301" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="H301" t="s">
         <v>16</v>
@@ -11890,7 +11926,7 @@
         <v>100</v>
       </c>
       <c r="L301">
-        <v>13.9</v>
+        <v>2.2000000000000002</v>
       </c>
     </row>
     <row r="302" spans="1:12" x14ac:dyDescent="0.25">
@@ -11898,34 +11934,34 @@
         <v>12</v>
       </c>
       <c r="B302">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C302">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D302" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="E302" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F302" t="s">
         <v>14</v>
       </c>
       <c r="G302" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H302" t="s">
         <v>16</v>
       </c>
       <c r="I302" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K302">
         <v>100</v>
       </c>
       <c r="L302">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="303" spans="1:12" x14ac:dyDescent="0.25">
@@ -11933,34 +11969,34 @@
         <v>18</v>
       </c>
       <c r="B303">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C303">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D303" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E303" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F303" t="s">
         <v>14</v>
       </c>
       <c r="G303" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H303" t="s">
         <v>16</v>
       </c>
       <c r="I303" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K303">
         <v>100</v>
       </c>
       <c r="L303">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="304" spans="1:12" x14ac:dyDescent="0.25">
@@ -11968,34 +12004,34 @@
         <v>20</v>
       </c>
       <c r="B304">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C304">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="D304" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="E304" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F304" t="s">
         <v>14</v>
       </c>
       <c r="G304" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H304" t="s">
         <v>16</v>
       </c>
       <c r="I304" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K304">
         <v>100</v>
       </c>
       <c r="L304">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="305" spans="1:12" x14ac:dyDescent="0.25">
@@ -12003,34 +12039,34 @@
         <v>21</v>
       </c>
       <c r="B305">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C305">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D305" t="s">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="E305" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F305" t="s">
         <v>14</v>
       </c>
       <c r="G305" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H305" t="s">
         <v>16</v>
       </c>
       <c r="I305" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K305">
         <v>100</v>
       </c>
       <c r="L305">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="306" spans="1:12" x14ac:dyDescent="0.25">
@@ -12038,34 +12074,34 @@
         <v>23</v>
       </c>
       <c r="B306">
-        <v>402</v>
+        <v>750</v>
       </c>
       <c r="C306">
-        <v>402</v>
+        <v>800</v>
       </c>
       <c r="D306" t="s">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="E306" t="s">
-        <v>180</v>
+        <v>253</v>
       </c>
       <c r="F306" t="s">
         <v>14</v>
       </c>
       <c r="G306" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H306" t="s">
         <v>16</v>
       </c>
       <c r="I306" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="K306">
         <v>100</v>
       </c>
       <c r="L306">
-        <v>83.6</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="307" spans="1:12" x14ac:dyDescent="0.25">
@@ -12073,34 +12109,34 @@
         <v>12</v>
       </c>
       <c r="B307">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C307">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="D307" t="s">
-        <v>80</v>
+        <v>142</v>
       </c>
       <c r="E307" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F307" t="s">
         <v>25</v>
       </c>
       <c r="G307" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H307" t="s">
         <v>16</v>
       </c>
       <c r="I307" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K307">
         <v>100</v>
       </c>
       <c r="L307">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="308" spans="1:12" x14ac:dyDescent="0.25">
@@ -12108,22 +12144,22 @@
         <v>18</v>
       </c>
       <c r="B308">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C308">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D308" t="s">
-        <v>182</v>
+        <v>19</v>
       </c>
       <c r="E308" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F308" t="s">
         <v>25</v>
       </c>
       <c r="G308" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H308" t="s">
         <v>16</v>
@@ -12135,7 +12171,7 @@
         <v>100</v>
       </c>
       <c r="L308">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="309" spans="1:12" x14ac:dyDescent="0.25">
@@ -12143,22 +12179,22 @@
         <v>20</v>
       </c>
       <c r="B309">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C309">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D309" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="E309" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F309" t="s">
         <v>25</v>
       </c>
       <c r="G309" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H309" t="s">
         <v>16</v>
@@ -12170,7 +12206,7 @@
         <v>100</v>
       </c>
       <c r="L309">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="310" spans="1:12" x14ac:dyDescent="0.25">
@@ -12178,34 +12214,34 @@
         <v>21</v>
       </c>
       <c r="B310">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C310">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="D310" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="E310" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F310" t="s">
         <v>25</v>
       </c>
       <c r="G310" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H310" t="s">
         <v>16</v>
       </c>
       <c r="I310" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K310">
         <v>100</v>
       </c>
       <c r="L310">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="311" spans="1:12" x14ac:dyDescent="0.25">
@@ -12213,34 +12249,34 @@
         <v>23</v>
       </c>
       <c r="B311">
-        <v>603</v>
+        <v>750</v>
       </c>
       <c r="C311">
-        <v>603</v>
+        <v>469</v>
       </c>
       <c r="D311" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E311" t="s">
-        <v>184</v>
+        <v>255</v>
       </c>
       <c r="F311" t="s">
         <v>25</v>
       </c>
       <c r="G311" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="H311" t="s">
         <v>16</v>
       </c>
       <c r="I311" t="s">
-        <v>231</v>
+        <v>17</v>
       </c>
       <c r="K311">
         <v>100</v>
       </c>
       <c r="L311">
-        <v>87.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="312" spans="1:12" x14ac:dyDescent="0.25">
@@ -12248,22 +12284,22 @@
         <v>12</v>
       </c>
       <c r="B312">
-        <v>26</v>
+        <v>930</v>
       </c>
       <c r="C312">
-        <v>34</v>
+        <v>1107</v>
       </c>
       <c r="D312" t="s">
-        <v>186</v>
+        <v>114</v>
       </c>
       <c r="E312" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F312" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G312" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H312" t="s">
         <v>16</v>
@@ -12271,14 +12307,11 @@
       <c r="I312" t="s">
         <v>229</v>
       </c>
-      <c r="J312" t="s">
-        <v>188</v>
-      </c>
       <c r="K312">
         <v>100</v>
       </c>
       <c r="L312">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="313" spans="1:12" x14ac:dyDescent="0.25">
@@ -12286,34 +12319,34 @@
         <v>18</v>
       </c>
       <c r="B313">
-        <v>7</v>
+        <v>153</v>
       </c>
       <c r="C313">
-        <v>8</v>
+        <v>131</v>
       </c>
       <c r="D313" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
       <c r="E313" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F313" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G313" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H313" t="s">
         <v>16</v>
       </c>
       <c r="I313" t="s">
-        <v>229</v>
+        <v>17</v>
       </c>
       <c r="K313">
         <v>100</v>
       </c>
       <c r="L313">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="314" spans="1:12" x14ac:dyDescent="0.25">
@@ -12321,22 +12354,22 @@
         <v>20</v>
       </c>
       <c r="B314">
-        <v>30</v>
+        <v>1712</v>
       </c>
       <c r="C314">
-        <v>20</v>
+        <v>1454</v>
       </c>
       <c r="D314" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="E314" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F314" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G314" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H314" t="s">
         <v>16</v>
@@ -12348,7 +12381,7 @@
         <v>100</v>
       </c>
       <c r="L314">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="315" spans="1:12" x14ac:dyDescent="0.25">
@@ -12356,22 +12389,22 @@
         <v>21</v>
       </c>
       <c r="B315">
-        <v>63</v>
+        <v>3255</v>
       </c>
       <c r="C315">
-        <v>87</v>
+        <v>3866</v>
       </c>
       <c r="D315" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="E315" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F315" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G315" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H315" t="s">
         <v>16</v>
@@ -12383,7 +12416,7 @@
         <v>100</v>
       </c>
       <c r="L315">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="316" spans="1:12" x14ac:dyDescent="0.25">
@@ -12391,34 +12424,34 @@
         <v>23</v>
       </c>
       <c r="B316">
-        <v>495</v>
+        <v>27700</v>
       </c>
       <c r="C316">
-        <v>507</v>
+        <v>0</v>
       </c>
       <c r="D316" t="s">
-        <v>64</v>
+        <v>19</v>
       </c>
       <c r="E316" t="s">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="F316" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G316" t="s">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="H316" t="s">
         <v>16</v>
       </c>
       <c r="I316" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K316">
         <v>100</v>
       </c>
       <c r="L316">
-        <v>92.7</v>
+        <v>86.1</v>
       </c>
     </row>
     <row r="317" spans="1:12" x14ac:dyDescent="0.25">
@@ -12426,34 +12459,34 @@
         <v>12</v>
       </c>
       <c r="B317">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C317">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D317" t="s">
-        <v>19</v>
+        <v>269</v>
       </c>
       <c r="E317" t="s">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F317" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G317" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H317" t="s">
         <v>16</v>
       </c>
       <c r="I317" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K317">
         <v>100</v>
       </c>
       <c r="L317">
-        <v>0.3</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="318" spans="1:12" x14ac:dyDescent="0.25">
@@ -12461,7 +12494,7 @@
         <v>18</v>
       </c>
       <c r="B318">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -12470,13 +12503,13 @@
         <v>19</v>
       </c>
       <c r="E318" t="s">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F318" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G318" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H318" t="s">
         <v>16</v>
@@ -12488,7 +12521,7 @@
         <v>100</v>
       </c>
       <c r="L318">
-        <v>0.3</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="319" spans="1:12" x14ac:dyDescent="0.25">
@@ -12496,34 +12529,34 @@
         <v>20</v>
       </c>
       <c r="B319">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C319">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D319" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="E319" t="s">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F319" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G319" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H319" t="s">
         <v>16</v>
       </c>
       <c r="I319" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K319">
         <v>100</v>
       </c>
       <c r="L319">
-        <v>0.3</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="320" spans="1:12" x14ac:dyDescent="0.25">
@@ -12531,34 +12564,34 @@
         <v>21</v>
       </c>
       <c r="B320">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="D320" t="s">
-        <v>22</v>
+        <v>272</v>
       </c>
       <c r="E320" t="s">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F320" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G320" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H320" t="s">
         <v>16</v>
       </c>
       <c r="I320" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K320">
         <v>100</v>
       </c>
       <c r="L320">
-        <v>0.3</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="321" spans="1:12" x14ac:dyDescent="0.25">
@@ -12566,34 +12599,34 @@
         <v>23</v>
       </c>
       <c r="B321">
-        <v>563</v>
+        <v>480</v>
       </c>
       <c r="C321">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="D321" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E321" t="s">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="F321" t="s">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="G321" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H321" t="s">
         <v>16</v>
       </c>
       <c r="I321" t="s">
-        <v>17</v>
+        <v>229</v>
       </c>
       <c r="K321">
         <v>100</v>
       </c>
       <c r="L321">
-        <v>0.3</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="322" spans="1:12" x14ac:dyDescent="0.25">
@@ -12601,22 +12634,22 @@
         <v>12</v>
       </c>
       <c r="B322">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C322">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D322" t="s">
-        <v>19</v>
+        <v>273</v>
       </c>
       <c r="E322" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="F322" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G322" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H322" t="s">
         <v>16</v>
@@ -12624,14 +12657,11 @@
       <c r="I322" t="s">
         <v>17</v>
       </c>
-      <c r="J322" t="s">
-        <v>189</v>
-      </c>
       <c r="K322">
         <v>100</v>
       </c>
       <c r="L322">
-        <v>2.2000000000000002</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="323" spans="1:12" x14ac:dyDescent="0.25">
@@ -12639,7 +12669,7 @@
         <v>18</v>
       </c>
       <c r="B323">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -12648,13 +12678,13 @@
         <v>19</v>
       </c>
       <c r="E323" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="F323" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G323" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H323" t="s">
         <v>16</v>
@@ -12662,14 +12692,11 @@
       <c r="I323" t="s">
         <v>17</v>
       </c>
-      <c r="J323" t="s">
-        <v>190</v>
-      </c>
       <c r="K323">
         <v>100</v>
       </c>
       <c r="L323">
-        <v>2.2000000000000002</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="324" spans="1:12" x14ac:dyDescent="0.25">
@@ -12677,22 +12704,22 @@
         <v>20</v>
       </c>
       <c r="B324">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C324">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D324" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="E324" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="F324" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G324" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H324" t="s">
         <v>16</v>
@@ -12700,14 +12727,11 @@
       <c r="I324" t="s">
         <v>17</v>
       </c>
-      <c r="J324" t="s">
-        <v>192</v>
-      </c>
       <c r="K324">
         <v>100</v>
       </c>
       <c r="L324">
-        <v>2.2000000000000002</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="325" spans="1:12" x14ac:dyDescent="0.25">
@@ -12715,22 +12739,22 @@
         <v>21</v>
       </c>
       <c r="B325">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="C325">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="D325" t="s">
-        <v>22</v>
+        <v>275</v>
       </c>
       <c r="E325" t="s">
-        <v>133</v>
+        <v>274</v>
       </c>
       <c r="F325" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="G325" t="s">
-        <v>181</v>
+        <v>271</v>
       </c>
       <c r="H325" t="s">
         <v>16</v>
@@ -12738,14 +12762,11 @@
       <c r="I325" t="s">
         <v>17</v>
       </c>
-      <c r="J325" t="s">
-        <v>193</v>
-      </c>
       <c r="K325">
         <v>100</v>
       </c>
       <c r="L325">
-        <v>2.2000000000000002</v>
+        <v>72.099999999999994</v>
       </c>
     </row>
     <row r="326" spans="1:12" x14ac:dyDescent="0.25">
@@ -12753,34 +12774,387 @@
         <v>23</v>
       </c>
       <c r="B326">
-        <v>563</v>
+        <v>720</v>
       </c>
       <c r="C326">
+        <v>387</v>
+      </c>
+      <c r="D326" t="s">
+        <v>276</v>
+      </c>
+      <c r="E326" t="s">
+        <v>274</v>
+      </c>
+      <c r="F326" t="s">
+        <v>25</v>
+      </c>
+      <c r="G326" t="s">
+        <v>271</v>
+      </c>
+      <c r="H326" t="s">
+        <v>16</v>
+      </c>
+      <c r="I326" t="s">
+        <v>17</v>
+      </c>
+      <c r="K326">
+        <v>100</v>
+      </c>
+      <c r="L326">
+        <v>72.099999999999994</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>12</v>
+      </c>
+      <c r="B327">
+        <v>4</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+      <c r="D327" t="s">
+        <v>65</v>
+      </c>
+      <c r="E327" t="s">
+        <v>66</v>
+      </c>
+      <c r="F327" t="s">
+        <v>14</v>
+      </c>
+      <c r="G327" t="s">
+        <v>67</v>
+      </c>
+      <c r="H327" t="s">
+        <v>16</v>
+      </c>
+      <c r="I327" t="s">
+        <v>17</v>
+      </c>
+      <c r="J327" t="s">
+        <v>68</v>
+      </c>
+      <c r="K327">
+        <v>100</v>
+      </c>
+      <c r="L327">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>18</v>
+      </c>
+      <c r="B328">
         <v>0</v>
       </c>
-      <c r="D326" t="s">
+      <c r="C328">
+        <v>0</v>
+      </c>
+      <c r="D328" t="s">
         <v>19</v>
       </c>
-      <c r="E326" t="s">
-        <v>133</v>
-      </c>
-      <c r="F326" t="s">
-        <v>103</v>
-      </c>
-      <c r="G326" t="s">
-        <v>181</v>
-      </c>
-      <c r="H326" t="s">
-        <v>16</v>
-      </c>
-      <c r="I326" t="s">
-        <v>17</v>
-      </c>
-      <c r="K326">
-        <v>100</v>
-      </c>
-      <c r="L326">
-        <v>2.2000000000000002</v>
+      <c r="E328" t="s">
+        <v>66</v>
+      </c>
+      <c r="F328" t="s">
+        <v>14</v>
+      </c>
+      <c r="G328" t="s">
+        <v>67</v>
+      </c>
+      <c r="H328" t="s">
+        <v>16</v>
+      </c>
+      <c r="I328" t="s">
+        <v>17</v>
+      </c>
+      <c r="K328">
+        <v>100</v>
+      </c>
+      <c r="L328">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>20</v>
+      </c>
+      <c r="B329">
+        <v>12</v>
+      </c>
+      <c r="C329">
+        <v>14</v>
+      </c>
+      <c r="D329" t="s">
+        <v>69</v>
+      </c>
+      <c r="E329" t="s">
+        <v>66</v>
+      </c>
+      <c r="F329" t="s">
+        <v>14</v>
+      </c>
+      <c r="G329" t="s">
+        <v>67</v>
+      </c>
+      <c r="H329" t="s">
+        <v>16</v>
+      </c>
+      <c r="I329" t="s">
+        <v>17</v>
+      </c>
+      <c r="K329">
+        <v>100</v>
+      </c>
+      <c r="L329">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>21</v>
+      </c>
+      <c r="B330">
+        <v>16</v>
+      </c>
+      <c r="C330">
+        <v>18</v>
+      </c>
+      <c r="D330" t="s">
+        <v>22</v>
+      </c>
+      <c r="E330" t="s">
+        <v>66</v>
+      </c>
+      <c r="F330" t="s">
+        <v>14</v>
+      </c>
+      <c r="G330" t="s">
+        <v>67</v>
+      </c>
+      <c r="H330" t="s">
+        <v>16</v>
+      </c>
+      <c r="I330" t="s">
+        <v>17</v>
+      </c>
+      <c r="K330">
+        <v>100</v>
+      </c>
+      <c r="L330">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>23</v>
+      </c>
+      <c r="B331">
+        <v>211</v>
+      </c>
+      <c r="C331">
+        <v>480</v>
+      </c>
+      <c r="D331" t="s">
+        <v>70</v>
+      </c>
+      <c r="E331" t="s">
+        <v>66</v>
+      </c>
+      <c r="F331" t="s">
+        <v>14</v>
+      </c>
+      <c r="G331" t="s">
+        <v>67</v>
+      </c>
+      <c r="H331" t="s">
+        <v>16</v>
+      </c>
+      <c r="I331" t="s">
+        <v>17</v>
+      </c>
+      <c r="K331">
+        <v>100</v>
+      </c>
+      <c r="L331">
+        <v>94.2</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>12</v>
+      </c>
+      <c r="B332">
+        <v>20</v>
+      </c>
+      <c r="C332">
+        <v>25</v>
+      </c>
+      <c r="D332" t="s">
+        <v>71</v>
+      </c>
+      <c r="E332" t="s">
+        <v>72</v>
+      </c>
+      <c r="F332" t="s">
+        <v>25</v>
+      </c>
+      <c r="G332" t="s">
+        <v>67</v>
+      </c>
+      <c r="H332" t="s">
+        <v>16</v>
+      </c>
+      <c r="I332" t="s">
+        <v>229</v>
+      </c>
+      <c r="K332">
+        <v>100</v>
+      </c>
+      <c r="L332">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>18</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333">
+        <v>0</v>
+      </c>
+      <c r="D333" t="s">
+        <v>19</v>
+      </c>
+      <c r="E333" t="s">
+        <v>72</v>
+      </c>
+      <c r="F333" t="s">
+        <v>25</v>
+      </c>
+      <c r="G333" t="s">
+        <v>67</v>
+      </c>
+      <c r="H333" t="s">
+        <v>16</v>
+      </c>
+      <c r="I333" t="s">
+        <v>17</v>
+      </c>
+      <c r="K333">
+        <v>100</v>
+      </c>
+      <c r="L333">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>20</v>
+      </c>
+      <c r="B334">
+        <v>58</v>
+      </c>
+      <c r="C334">
+        <v>33</v>
+      </c>
+      <c r="D334" t="s">
+        <v>73</v>
+      </c>
+      <c r="E334" t="s">
+        <v>72</v>
+      </c>
+      <c r="F334" t="s">
+        <v>25</v>
+      </c>
+      <c r="G334" t="s">
+        <v>67</v>
+      </c>
+      <c r="H334" t="s">
+        <v>16</v>
+      </c>
+      <c r="I334" t="s">
+        <v>17</v>
+      </c>
+      <c r="K334">
+        <v>100</v>
+      </c>
+      <c r="L334">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335">
+        <v>74</v>
+      </c>
+      <c r="C335">
+        <v>78</v>
+      </c>
+      <c r="D335" t="s">
+        <v>22</v>
+      </c>
+      <c r="E335" t="s">
+        <v>72</v>
+      </c>
+      <c r="F335" t="s">
+        <v>25</v>
+      </c>
+      <c r="G335" t="s">
+        <v>67</v>
+      </c>
+      <c r="H335" t="s">
+        <v>16</v>
+      </c>
+      <c r="I335" t="s">
+        <v>229</v>
+      </c>
+      <c r="K335">
+        <v>100</v>
+      </c>
+      <c r="L335">
+        <v>62.2</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>23</v>
+      </c>
+      <c r="B336">
+        <v>989</v>
+      </c>
+      <c r="C336">
+        <v>653</v>
+      </c>
+      <c r="D336" t="s">
+        <v>74</v>
+      </c>
+      <c r="E336" t="s">
+        <v>72</v>
+      </c>
+      <c r="F336" t="s">
+        <v>25</v>
+      </c>
+      <c r="G336" t="s">
+        <v>67</v>
+      </c>
+      <c r="H336" t="s">
+        <v>16</v>
+      </c>
+      <c r="I336" t="s">
+        <v>17</v>
+      </c>
+      <c r="K336">
+        <v>100</v>
+      </c>
+      <c r="L336">
+        <v>62.2</v>
       </c>
     </row>
   </sheetData>
